--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -12,9 +12,9 @@
     <sheet name="初診外来" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,21 +469,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,15 +535,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>治療区分</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>治療レジメン</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>サイクル数</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -550,9 +556,9 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -561,12 +567,13 @@
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -575,12 +582,13 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -589,12 +597,13 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -603,12 +612,13 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -617,12 +627,13 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
@@ -631,12 +642,13 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
@@ -645,12 +657,13 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
@@ -659,12 +672,13 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -673,12 +687,13 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -687,12 +702,13 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
@@ -701,12 +717,13 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -715,12 +732,13 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -729,12 +747,13 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
@@ -743,12 +762,13 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
@@ -757,12 +777,13 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
@@ -771,12 +792,13 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
@@ -785,12 +807,13 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
@@ -799,12 +822,13 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -813,12 +837,13 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
@@ -827,12 +852,13 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
@@ -841,12 +867,13 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
@@ -855,12 +882,13 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
@@ -869,12 +897,13 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
@@ -883,12 +912,13 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
@@ -897,12 +927,13 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
@@ -911,12 +942,13 @@
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -925,12 +957,13 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -939,12 +972,13 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -953,12 +987,13 @@
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -967,12 +1002,13 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -981,12 +1017,13 @@
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -995,12 +1032,13 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1009,12 +1047,13 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -1023,12 +1062,13 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
@@ -1037,12 +1077,13 @@
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
@@ -1051,12 +1092,13 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
@@ -1065,12 +1107,13 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
@@ -1079,12 +1122,13 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
@@ -1093,12 +1137,13 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
@@ -1107,12 +1152,13 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
@@ -1121,12 +1167,13 @@
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -1135,12 +1182,13 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="n"/>
       <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
@@ -1149,12 +1197,13 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
@@ -1163,12 +1212,13 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
@@ -1177,12 +1227,13 @@
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
@@ -1191,12 +1242,13 @@
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
@@ -1205,12 +1257,13 @@
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
@@ -1219,12 +1272,13 @@
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="n"/>
       <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
@@ -1233,12 +1287,13 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
@@ -1247,9 +1302,24 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
+  <dataValidations count="4">
+    <dataValidation sqref="D2:D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"M,F"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"0,1,2,3,4"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1264,18 +1334,18 @@
   <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1342,9 +1412,9 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -1356,9 +1426,9 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -1370,9 +1440,9 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -1384,9 +1454,9 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -1398,9 +1468,9 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -1412,9 +1482,9 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
@@ -1426,9 +1496,9 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
@@ -1440,9 +1510,9 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
@@ -1454,9 +1524,9 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -1468,9 +1538,9 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -1482,9 +1552,9 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
@@ -1496,9 +1566,9 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -1510,9 +1580,9 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -1524,9 +1594,9 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
@@ -1538,9 +1608,9 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
@@ -1552,9 +1622,9 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
@@ -1566,9 +1636,9 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
@@ -1580,9 +1650,9 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
@@ -1594,9 +1664,9 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -1608,9 +1678,9 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
@@ -1622,9 +1692,9 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
@@ -1636,9 +1706,9 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
@@ -1650,9 +1720,9 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
@@ -1664,9 +1734,9 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
@@ -1678,9 +1748,9 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
@@ -1692,9 +1762,9 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
@@ -1706,9 +1776,9 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -1720,9 +1790,9 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -1734,9 +1804,9 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -1748,9 +1818,9 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -1762,9 +1832,9 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -1776,9 +1846,9 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -1790,9 +1860,9 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -1804,9 +1874,9 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -1818,9 +1888,9 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
@@ -1832,9 +1902,9 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
@@ -1846,9 +1916,9 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
@@ -1860,9 +1930,9 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
@@ -1874,9 +1944,9 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
@@ -1888,9 +1958,9 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
@@ -1902,9 +1972,9 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
@@ -1916,9 +1986,9 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -1930,9 +2000,9 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
@@ -1944,9 +2014,9 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
@@ -1958,9 +2028,9 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
@@ -1972,9 +2042,9 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
@@ -1986,9 +2056,9 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
@@ -2000,9 +2070,9 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
@@ -2014,9 +2084,9 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
@@ -2028,9 +2098,9 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
@@ -2042,6 +2112,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
+  <dataValidations count="3">
+    <dataValidation sqref="D2:D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"M,F"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"要,不要,済"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2053,22 +2134,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2124,15 +2206,20 @@
       </c>
       <c r="K1" s="5" t="inlineStr">
         <is>
+          <t>治療区分</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
           <t>治療方針</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>次回予約日</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -2140,9 +2227,9 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
@@ -2152,12 +2239,13 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -2167,12 +2255,13 @@
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
@@ -2182,12 +2271,13 @@
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
@@ -2197,12 +2287,13 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
@@ -2212,12 +2303,13 @@
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
@@ -2227,12 +2319,13 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
@@ -2242,12 +2335,13 @@
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
@@ -2257,12 +2351,13 @@
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
@@ -2272,12 +2367,13 @@
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
@@ -2287,12 +2383,13 @@
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
@@ -2302,12 +2399,13 @@
       <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="n"/>
       <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
@@ -2317,12 +2415,13 @@
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n"/>
       <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
@@ -2332,12 +2431,13 @@
       <c r="K14" s="3" t="n"/>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
@@ -2347,12 +2447,13 @@
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
@@ -2362,12 +2463,13 @@
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
@@ -2377,12 +2479,13 @@
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
@@ -2392,12 +2495,13 @@
       <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n"/>
       <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
@@ -2407,12 +2511,13 @@
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
@@ -2422,12 +2527,13 @@
       <c r="K20" s="3" t="n"/>
       <c r="L20" s="3" t="n"/>
       <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
@@ -2437,12 +2543,13 @@
       <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n"/>
       <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
@@ -2452,12 +2559,13 @@
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
@@ -2467,12 +2575,13 @@
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n"/>
       <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
@@ -2482,12 +2591,13 @@
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
@@ -2497,12 +2607,13 @@
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
@@ -2512,12 +2623,13 @@
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
@@ -2527,12 +2639,13 @@
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="3" t="n"/>
       <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
@@ -2542,12 +2655,13 @@
       <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n"/>
       <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -2557,12 +2671,13 @@
       <c r="K29" s="3" t="n"/>
       <c r="L29" s="3" t="n"/>
       <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -2572,12 +2687,13 @@
       <c r="K30" s="3" t="n"/>
       <c r="L30" s="3" t="n"/>
       <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
@@ -2587,12 +2703,13 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n"/>
       <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
@@ -2602,12 +2719,13 @@
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
@@ -2617,12 +2735,13 @@
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
@@ -2632,12 +2751,13 @@
       <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n"/>
       <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
@@ -2647,12 +2767,13 @@
       <c r="K35" s="3" t="n"/>
       <c r="L35" s="3" t="n"/>
       <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
@@ -2662,12 +2783,13 @@
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
@@ -2677,12 +2799,13 @@
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
@@ -2692,12 +2815,13 @@
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
+      <c r="N38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
@@ -2707,12 +2831,13 @@
       <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n"/>
       <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
@@ -2722,12 +2847,13 @@
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
+      <c r="N40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
@@ -2737,12 +2863,13 @@
       <c r="K41" s="3" t="n"/>
       <c r="L41" s="3" t="n"/>
       <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
@@ -2752,12 +2879,13 @@
       <c r="K42" s="3" t="n"/>
       <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="n"/>
+      <c r="N42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
@@ -2767,12 +2895,13 @@
       <c r="K43" s="3" t="n"/>
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
@@ -2782,12 +2911,13 @@
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
+      <c r="N44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
@@ -2797,12 +2927,13 @@
       <c r="K45" s="3" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n"/>
+      <c r="N45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
@@ -2812,12 +2943,13 @@
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
@@ -2827,12 +2959,13 @@
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="3" t="n"/>
       <c r="M47" s="3" t="n"/>
+      <c r="N47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
@@ -2842,12 +2975,13 @@
       <c r="K48" s="3" t="n"/>
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
+      <c r="N48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
@@ -2857,12 +2991,13 @@
       <c r="K49" s="3" t="n"/>
       <c r="L49" s="3" t="n"/>
       <c r="M49" s="3" t="n"/>
+      <c r="N49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
@@ -2872,12 +3007,13 @@
       <c r="K50" s="3" t="n"/>
       <c r="L50" s="3" t="n"/>
       <c r="M50" s="3" t="n"/>
+      <c r="N50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
@@ -2887,9 +3023,24 @@
       <c r="K51" s="3" t="n"/>
       <c r="L51" s="3" t="n"/>
       <c r="M51" s="3" t="n"/>
+      <c r="N51" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:N1"/>
+  <dataValidations count="4">
+    <dataValidation sqref="D2:D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"M,F"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"0,1,2,3,4"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -10,10 +10,11 @@
     <sheet name="入院患者" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="他科コンサルト" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="初診外来" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="サマリー" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$2:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="00000000"/>
     <numFmt numFmtId="165" formatCode="YYYY/MM/DD"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +51,25 @@
       <name val="Meiryo"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="001A365D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="002B5797"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -148,8 +166,20 @@
         <bgColor rgb="00FDF5EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE4"/>
+        <bgColor rgb="00D6DCE4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -171,11 +201,44 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -237,11 +300,11 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -270,11 +333,31 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="13">
     <dxf>
       <font>
         <name val="Meiryo"/>
@@ -398,6 +481,59 @@
         <patternFill patternType="solid">
           <fgColor rgb="00E7E6E6"/>
           <bgColor rgb="00E7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <b val="1"/>
+        <color rgb="00C62828"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4EC"/>
+          <bgColor rgb="00FCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <color rgb="00767171"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E7E6E6"/>
+          <bgColor rgb="00E7E6E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <color rgb="0044546A"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D6DCE4"/>
+          <bgColor rgb="00D6DCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <color rgb="0044546A"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F7FB"/>
+          <bgColor rgb="00F2F7FB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -764,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -775,11 +911,13 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -799,19 +937,21 @@
       <c r="F1" s="4" t="n"/>
       <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>治療</t>
         </is>
       </c>
-      <c r="J1" s="6" t="n"/>
       <c r="K1" s="6" t="n"/>
       <c r="L1" s="6" t="n"/>
-      <c r="M1" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="M1" s="6" t="n"/>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -856,25 +996,35 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
+          <t>在院日数</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>治療区分</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>治療レジメン</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>サイクル数</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -889,11 +1039,16 @@
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="11" t="n"/>
       <c r="H3" s="11" t="n"/>
-      <c r="I3" s="10" t="n"/>
+      <c r="I3" s="9">
+        <f>IF(AND(G3&lt;&gt;"",H3&lt;&gt;""),H3-G3,"")</f>
+        <v/>
+      </c>
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
       <c r="L3" s="10" t="n"/>
       <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -904,11 +1059,16 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="15" t="n"/>
       <c r="H4" s="15" t="n"/>
-      <c r="I4" s="14" t="n"/>
+      <c r="I4" s="13">
+        <f>IF(AND(G4&lt;&gt;"",H4&lt;&gt;""),H4-G4,"")</f>
+        <v/>
+      </c>
       <c r="J4" s="14" t="n"/>
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -919,11 +1079,16 @@
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n"/>
-      <c r="I5" s="10" t="n"/>
+      <c r="I5" s="9">
+        <f>IF(AND(G5&lt;&gt;"",H5&lt;&gt;""),H5-G5,"")</f>
+        <v/>
+      </c>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="n"/>
       <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -934,11 +1099,16 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="14" t="n"/>
+      <c r="I6" s="13">
+        <f>IF(AND(G6&lt;&gt;"",H6&lt;&gt;""),H6-G6,"")</f>
+        <v/>
+      </c>
       <c r="J6" s="14" t="n"/>
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -949,11 +1119,16 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n"/>
-      <c r="I7" s="10" t="n"/>
+      <c r="I7" s="9">
+        <f>IF(AND(G7&lt;&gt;"",H7&lt;&gt;""),H7-G7,"")</f>
+        <v/>
+      </c>
       <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -964,11 +1139,16 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="I8" s="13">
+        <f>IF(AND(G8&lt;&gt;"",H8&lt;&gt;""),H8-G8,"")</f>
+        <v/>
+      </c>
       <c r="J8" s="14" t="n"/>
       <c r="K8" s="14" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -979,11 +1159,16 @@
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n"/>
-      <c r="I9" s="10" t="n"/>
+      <c r="I9" s="9">
+        <f>IF(AND(G9&lt;&gt;"",H9&lt;&gt;""),H9-G9,"")</f>
+        <v/>
+      </c>
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -994,11 +1179,16 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="14" t="n"/>
+      <c r="I10" s="13">
+        <f>IF(AND(G10&lt;&gt;"",H10&lt;&gt;""),H10-G10,"")</f>
+        <v/>
+      </c>
       <c r="J10" s="14" t="n"/>
       <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1009,11 +1199,16 @@
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="I11" s="9">
+        <f>IF(AND(G11&lt;&gt;"",H11&lt;&gt;""),H11-G11,"")</f>
+        <v/>
+      </c>
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="n"/>
       <c r="L11" s="10" t="n"/>
       <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -1024,11 +1219,16 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="14" t="n"/>
+      <c r="I12" s="13">
+        <f>IF(AND(G12&lt;&gt;"",H12&lt;&gt;""),H12-G12,"")</f>
+        <v/>
+      </c>
       <c r="J12" s="14" t="n"/>
       <c r="K12" s="14" t="n"/>
       <c r="L12" s="14" t="n"/>
       <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1039,11 +1239,16 @@
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="10" t="n"/>
+      <c r="I13" s="9">
+        <f>IF(AND(G13&lt;&gt;"",H13&lt;&gt;""),H13-G13,"")</f>
+        <v/>
+      </c>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="n"/>
       <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -1054,11 +1259,16 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="14" t="n"/>
+      <c r="I14" s="13">
+        <f>IF(AND(G14&lt;&gt;"",H14&lt;&gt;""),H14-G14,"")</f>
+        <v/>
+      </c>
       <c r="J14" s="14" t="n"/>
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1069,11 +1279,16 @@
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
-      <c r="I15" s="10" t="n"/>
+      <c r="I15" s="9">
+        <f>IF(AND(G15&lt;&gt;"",H15&lt;&gt;""),H15-G15,"")</f>
+        <v/>
+      </c>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1084,11 +1299,16 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="14" t="n"/>
+      <c r="I16" s="13">
+        <f>IF(AND(G16&lt;&gt;"",H16&lt;&gt;""),H16-G16,"")</f>
+        <v/>
+      </c>
       <c r="J16" s="14" t="n"/>
       <c r="K16" s="14" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1099,11 +1319,16 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
-      <c r="I17" s="10" t="n"/>
+      <c r="I17" s="9">
+        <f>IF(AND(G17&lt;&gt;"",H17&lt;&gt;""),H17-G17,"")</f>
+        <v/>
+      </c>
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -1114,11 +1339,16 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="14" t="n"/>
+      <c r="I18" s="13">
+        <f>IF(AND(G18&lt;&gt;"",H18&lt;&gt;""),H18-G18,"")</f>
+        <v/>
+      </c>
       <c r="J18" s="14" t="n"/>
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1129,11 +1359,16 @@
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="n"/>
-      <c r="I19" s="10" t="n"/>
+      <c r="I19" s="9">
+        <f>IF(AND(G19&lt;&gt;"",H19&lt;&gt;""),H19-G19,"")</f>
+        <v/>
+      </c>
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1144,11 +1379,16 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="15" t="n"/>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="14" t="n"/>
+      <c r="I20" s="13">
+        <f>IF(AND(G20&lt;&gt;"",H20&lt;&gt;""),H20-G20,"")</f>
+        <v/>
+      </c>
       <c r="J20" s="14" t="n"/>
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1159,11 +1399,16 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="10" t="n"/>
+      <c r="I21" s="9">
+        <f>IF(AND(G21&lt;&gt;"",H21&lt;&gt;""),H21-G21,"")</f>
+        <v/>
+      </c>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1174,11 +1419,16 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="14" t="n"/>
+      <c r="I22" s="13">
+        <f>IF(AND(G22&lt;&gt;"",H22&lt;&gt;""),H22-G22,"")</f>
+        <v/>
+      </c>
       <c r="J22" s="14" t="n"/>
       <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1189,11 +1439,16 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
-      <c r="I23" s="10" t="n"/>
+      <c r="I23" s="9">
+        <f>IF(AND(G23&lt;&gt;"",H23&lt;&gt;""),H23-G23,"")</f>
+        <v/>
+      </c>
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1204,11 +1459,16 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="15" t="n"/>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="14" t="n"/>
+      <c r="I24" s="13">
+        <f>IF(AND(G24&lt;&gt;"",H24&lt;&gt;""),H24-G24,"")</f>
+        <v/>
+      </c>
       <c r="J24" s="14" t="n"/>
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1219,11 +1479,16 @@
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="n"/>
-      <c r="I25" s="10" t="n"/>
+      <c r="I25" s="9">
+        <f>IF(AND(G25&lt;&gt;"",H25&lt;&gt;""),H25-G25,"")</f>
+        <v/>
+      </c>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="10" t="n"/>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1234,11 +1499,16 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="15" t="n"/>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="14" t="n"/>
+      <c r="I26" s="13">
+        <f>IF(AND(G26&lt;&gt;"",H26&lt;&gt;""),H26-G26,"")</f>
+        <v/>
+      </c>
       <c r="J26" s="14" t="n"/>
       <c r="K26" s="14" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
+      <c r="O26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1249,11 +1519,16 @@
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="11" t="n"/>
       <c r="H27" s="11" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="I27" s="9">
+        <f>IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),H27-G27,"")</f>
+        <v/>
+      </c>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1264,11 +1539,16 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="15" t="n"/>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="14" t="n"/>
+      <c r="I28" s="13">
+        <f>IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),H28-G28,"")</f>
+        <v/>
+      </c>
       <c r="J28" s="14" t="n"/>
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -1279,11 +1559,16 @@
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="n"/>
-      <c r="I29" s="10" t="n"/>
+      <c r="I29" s="9">
+        <f>IF(AND(G29&lt;&gt;"",H29&lt;&gt;""),H29-G29,"")</f>
+        <v/>
+      </c>
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="10" t="n"/>
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="10" t="n"/>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1294,11 +1579,16 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="15" t="n"/>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="14" t="n"/>
+      <c r="I30" s="13">
+        <f>IF(AND(G30&lt;&gt;"",H30&lt;&gt;""),H30-G30,"")</f>
+        <v/>
+      </c>
       <c r="J30" s="14" t="n"/>
       <c r="K30" s="14" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
+      <c r="O30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1309,11 +1599,16 @@
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="n"/>
-      <c r="I31" s="10" t="n"/>
+      <c r="I31" s="9">
+        <f>IF(AND(G31&lt;&gt;"",H31&lt;&gt;""),H31-G31,"")</f>
+        <v/>
+      </c>
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="10" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1324,11 +1619,16 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="15" t="n"/>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="14" t="n"/>
+      <c r="I32" s="13">
+        <f>IF(AND(G32&lt;&gt;"",H32&lt;&gt;""),H32-G32,"")</f>
+        <v/>
+      </c>
       <c r="J32" s="14" t="n"/>
       <c r="K32" s="14" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
+      <c r="O32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -1339,11 +1639,16 @@
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="11" t="n"/>
       <c r="H33" s="11" t="n"/>
-      <c r="I33" s="10" t="n"/>
+      <c r="I33" s="9">
+        <f>IF(AND(G33&lt;&gt;"",H33&lt;&gt;""),H33-G33,"")</f>
+        <v/>
+      </c>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="10" t="n"/>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1354,11 +1659,16 @@
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="15" t="n"/>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="14" t="n"/>
+      <c r="I34" s="13">
+        <f>IF(AND(G34&lt;&gt;"",H34&lt;&gt;""),H34-G34,"")</f>
+        <v/>
+      </c>
       <c r="J34" s="14" t="n"/>
       <c r="K34" s="14" t="n"/>
       <c r="L34" s="14" t="n"/>
       <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
+      <c r="O34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -1369,11 +1679,16 @@
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="11" t="n"/>
       <c r="H35" s="11" t="n"/>
-      <c r="I35" s="10" t="n"/>
+      <c r="I35" s="9">
+        <f>IF(AND(G35&lt;&gt;"",H35&lt;&gt;""),H35-G35,"")</f>
+        <v/>
+      </c>
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="10" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1384,11 +1699,16 @@
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="15" t="n"/>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="14" t="n"/>
+      <c r="I36" s="13">
+        <f>IF(AND(G36&lt;&gt;"",H36&lt;&gt;""),H36-G36,"")</f>
+        <v/>
+      </c>
       <c r="J36" s="14" t="n"/>
       <c r="K36" s="14" t="n"/>
       <c r="L36" s="14" t="n"/>
       <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14" t="n"/>
+      <c r="O36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -1399,11 +1719,16 @@
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="11" t="n"/>
       <c r="H37" s="11" t="n"/>
-      <c r="I37" s="10" t="n"/>
+      <c r="I37" s="9">
+        <f>IF(AND(G37&lt;&gt;"",H37&lt;&gt;""),H37-G37,"")</f>
+        <v/>
+      </c>
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1414,11 +1739,16 @@
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="15" t="n"/>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="14" t="n"/>
+      <c r="I38" s="13">
+        <f>IF(AND(G38&lt;&gt;"",H38&lt;&gt;""),H38-G38,"")</f>
+        <v/>
+      </c>
       <c r="J38" s="14" t="n"/>
       <c r="K38" s="14" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
+      <c r="O38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -1429,11 +1759,16 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="11" t="n"/>
       <c r="H39" s="11" t="n"/>
-      <c r="I39" s="10" t="n"/>
+      <c r="I39" s="9">
+        <f>IF(AND(G39&lt;&gt;"",H39&lt;&gt;""),H39-G39,"")</f>
+        <v/>
+      </c>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -1444,11 +1779,16 @@
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="15" t="n"/>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="14" t="n"/>
+      <c r="I40" s="13">
+        <f>IF(AND(G40&lt;&gt;"",H40&lt;&gt;""),H40-G40,"")</f>
+        <v/>
+      </c>
       <c r="J40" s="14" t="n"/>
       <c r="K40" s="14" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14" t="n"/>
+      <c r="O40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -1459,11 +1799,16 @@
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="11" t="n"/>
       <c r="H41" s="11" t="n"/>
-      <c r="I41" s="10" t="n"/>
+      <c r="I41" s="9">
+        <f>IF(AND(G41&lt;&gt;"",H41&lt;&gt;""),H41-G41,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="10" t="n"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -1474,11 +1819,16 @@
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="15" t="n"/>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="14" t="n"/>
+      <c r="I42" s="13">
+        <f>IF(AND(G42&lt;&gt;"",H42&lt;&gt;""),H42-G42,"")</f>
+        <v/>
+      </c>
       <c r="J42" s="14" t="n"/>
       <c r="K42" s="14" t="n"/>
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14" t="n"/>
+      <c r="O42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -1489,11 +1839,16 @@
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="11" t="n"/>
       <c r="H43" s="11" t="n"/>
-      <c r="I43" s="10" t="n"/>
+      <c r="I43" s="9">
+        <f>IF(AND(G43&lt;&gt;"",H43&lt;&gt;""),H43-G43,"")</f>
+        <v/>
+      </c>
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
       <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -1504,11 +1859,16 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="15" t="n"/>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="14" t="n"/>
+      <c r="I44" s="13">
+        <f>IF(AND(G44&lt;&gt;"",H44&lt;&gt;""),H44-G44,"")</f>
+        <v/>
+      </c>
       <c r="J44" s="14" t="n"/>
       <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14" t="n"/>
+      <c r="O44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -1519,11 +1879,16 @@
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="11" t="n"/>
       <c r="H45" s="11" t="n"/>
-      <c r="I45" s="10" t="n"/>
+      <c r="I45" s="9">
+        <f>IF(AND(G45&lt;&gt;"",H45&lt;&gt;""),H45-G45,"")</f>
+        <v/>
+      </c>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
       <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -1534,11 +1899,16 @@
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="15" t="n"/>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="14" t="n"/>
+      <c r="I46" s="13">
+        <f>IF(AND(G46&lt;&gt;"",H46&lt;&gt;""),H46-G46,"")</f>
+        <v/>
+      </c>
       <c r="J46" s="14" t="n"/>
       <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14" t="n"/>
+      <c r="O46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -1549,11 +1919,16 @@
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="11" t="n"/>
       <c r="H47" s="11" t="n"/>
-      <c r="I47" s="10" t="n"/>
+      <c r="I47" s="9">
+        <f>IF(AND(G47&lt;&gt;"",H47&lt;&gt;""),H47-G47,"")</f>
+        <v/>
+      </c>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="n"/>
       <c r="M47" s="10" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -1564,11 +1939,16 @@
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="15" t="n"/>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="14" t="n"/>
+      <c r="I48" s="13">
+        <f>IF(AND(G48&lt;&gt;"",H48&lt;&gt;""),H48-G48,"")</f>
+        <v/>
+      </c>
       <c r="J48" s="14" t="n"/>
       <c r="K48" s="14" t="n"/>
       <c r="L48" s="14" t="n"/>
       <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n"/>
+      <c r="O48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -1579,11 +1959,16 @@
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="11" t="n"/>
       <c r="H49" s="11" t="n"/>
-      <c r="I49" s="10" t="n"/>
+      <c r="I49" s="9">
+        <f>IF(AND(G49&lt;&gt;"",H49&lt;&gt;""),H49-G49,"")</f>
+        <v/>
+      </c>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -1594,11 +1979,16 @@
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="15" t="n"/>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="14" t="n"/>
+      <c r="I50" s="13">
+        <f>IF(AND(G50&lt;&gt;"",H50&lt;&gt;""),H50-G50,"")</f>
+        <v/>
+      </c>
       <c r="J50" s="14" t="n"/>
       <c r="K50" s="14" t="n"/>
       <c r="L50" s="14" t="n"/>
       <c r="M50" s="14" t="n"/>
+      <c r="N50" s="14" t="n"/>
+      <c r="O50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -1609,11 +1999,16 @@
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="11" t="n"/>
       <c r="H51" s="11" t="n"/>
-      <c r="I51" s="10" t="n"/>
+      <c r="I51" s="9">
+        <f>IF(AND(G51&lt;&gt;"",H51&lt;&gt;""),H51-G51,"")</f>
+        <v/>
+      </c>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
       <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -1624,11 +2019,16 @@
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="15" t="n"/>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="14" t="n"/>
+      <c r="I52" s="13">
+        <f>IF(AND(G52&lt;&gt;"",H52&lt;&gt;""),H52-G52,"")</f>
+        <v/>
+      </c>
       <c r="J52" s="14" t="n"/>
       <c r="K52" s="14" t="n"/>
       <c r="L52" s="14" t="n"/>
       <c r="M52" s="14" t="n"/>
+      <c r="N52" s="14" t="n"/>
+      <c r="O52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -1639,11 +2039,16 @@
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="11" t="n"/>
       <c r="H53" s="11" t="n"/>
-      <c r="I53" s="10" t="n"/>
+      <c r="I53" s="9">
+        <f>IF(AND(G53&lt;&gt;"",H53&lt;&gt;""),H53-G53,"")</f>
+        <v/>
+      </c>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="10" t="n"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -1654,11 +2059,16 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="15" t="n"/>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="14" t="n"/>
+      <c r="I54" s="13">
+        <f>IF(AND(G54&lt;&gt;"",H54&lt;&gt;""),H54-G54,"")</f>
+        <v/>
+      </c>
       <c r="J54" s="14" t="n"/>
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="14" t="n"/>
       <c r="M54" s="14" t="n"/>
+      <c r="N54" s="14" t="n"/>
+      <c r="O54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -1669,11 +2079,16 @@
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="11" t="n"/>
       <c r="H55" s="11" t="n"/>
-      <c r="I55" s="10" t="n"/>
+      <c r="I55" s="9">
+        <f>IF(AND(G55&lt;&gt;"",H55&lt;&gt;""),H55-G55,"")</f>
+        <v/>
+      </c>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -1684,11 +2099,16 @@
       <c r="F56" s="14" t="n"/>
       <c r="G56" s="15" t="n"/>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="14" t="n"/>
+      <c r="I56" s="13">
+        <f>IF(AND(G56&lt;&gt;"",H56&lt;&gt;""),H56-G56,"")</f>
+        <v/>
+      </c>
       <c r="J56" s="14" t="n"/>
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="14" t="n"/>
       <c r="M56" s="14" t="n"/>
+      <c r="N56" s="14" t="n"/>
+      <c r="O56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -1699,11 +2119,16 @@
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="11" t="n"/>
       <c r="H57" s="11" t="n"/>
-      <c r="I57" s="10" t="n"/>
+      <c r="I57" s="9">
+        <f>IF(AND(G57&lt;&gt;"",H57&lt;&gt;""),H57-G57,"")</f>
+        <v/>
+      </c>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -1714,11 +2139,16 @@
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="15" t="n"/>
       <c r="H58" s="15" t="n"/>
-      <c r="I58" s="14" t="n"/>
+      <c r="I58" s="13">
+        <f>IF(AND(G58&lt;&gt;"",H58&lt;&gt;""),H58-G58,"")</f>
+        <v/>
+      </c>
       <c r="J58" s="14" t="n"/>
       <c r="K58" s="14" t="n"/>
       <c r="L58" s="14" t="n"/>
       <c r="M58" s="14" t="n"/>
+      <c r="N58" s="14" t="n"/>
+      <c r="O58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -1729,11 +2159,16 @@
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="11" t="n"/>
       <c r="H59" s="11" t="n"/>
-      <c r="I59" s="10" t="n"/>
+      <c r="I59" s="9">
+        <f>IF(AND(G59&lt;&gt;"",H59&lt;&gt;""),H59-G59,"")</f>
+        <v/>
+      </c>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -1744,11 +2179,16 @@
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="15" t="n"/>
       <c r="H60" s="15" t="n"/>
-      <c r="I60" s="14" t="n"/>
+      <c r="I60" s="13">
+        <f>IF(AND(G60&lt;&gt;"",H60&lt;&gt;""),H60-G60,"")</f>
+        <v/>
+      </c>
       <c r="J60" s="14" t="n"/>
       <c r="K60" s="14" t="n"/>
       <c r="L60" s="14" t="n"/>
       <c r="M60" s="14" t="n"/>
+      <c r="N60" s="14" t="n"/>
+      <c r="O60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -1759,11 +2199,16 @@
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="11" t="n"/>
       <c r="H61" s="11" t="n"/>
-      <c r="I61" s="10" t="n"/>
+      <c r="I61" s="9">
+        <f>IF(AND(G61&lt;&gt;"",H61&lt;&gt;""),H61-G61,"")</f>
+        <v/>
+      </c>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
       <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -1774,11 +2219,16 @@
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="15" t="n"/>
       <c r="H62" s="15" t="n"/>
-      <c r="I62" s="14" t="n"/>
+      <c r="I62" s="13">
+        <f>IF(AND(G62&lt;&gt;"",H62&lt;&gt;""),H62-G62,"")</f>
+        <v/>
+      </c>
       <c r="J62" s="14" t="n"/>
       <c r="K62" s="14" t="n"/>
       <c r="L62" s="14" t="n"/>
       <c r="M62" s="14" t="n"/>
+      <c r="N62" s="14" t="n"/>
+      <c r="O62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -1789,11 +2239,16 @@
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="11" t="n"/>
       <c r="H63" s="11" t="n"/>
-      <c r="I63" s="10" t="n"/>
+      <c r="I63" s="9">
+        <f>IF(AND(G63&lt;&gt;"",H63&lt;&gt;""),H63-G63,"")</f>
+        <v/>
+      </c>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
       <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -1804,11 +2259,16 @@
       <c r="F64" s="14" t="n"/>
       <c r="G64" s="15" t="n"/>
       <c r="H64" s="15" t="n"/>
-      <c r="I64" s="14" t="n"/>
+      <c r="I64" s="13">
+        <f>IF(AND(G64&lt;&gt;"",H64&lt;&gt;""),H64-G64,"")</f>
+        <v/>
+      </c>
       <c r="J64" s="14" t="n"/>
       <c r="K64" s="14" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="14" t="n"/>
+      <c r="N64" s="14" t="n"/>
+      <c r="O64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -1819,11 +2279,16 @@
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="11" t="n"/>
       <c r="H65" s="11" t="n"/>
-      <c r="I65" s="10" t="n"/>
+      <c r="I65" s="9">
+        <f>IF(AND(G65&lt;&gt;"",H65&lt;&gt;""),H65-G65,"")</f>
+        <v/>
+      </c>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
       <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -1834,11 +2299,16 @@
       <c r="F66" s="14" t="n"/>
       <c r="G66" s="15" t="n"/>
       <c r="H66" s="15" t="n"/>
-      <c r="I66" s="14" t="n"/>
+      <c r="I66" s="13">
+        <f>IF(AND(G66&lt;&gt;"",H66&lt;&gt;""),H66-G66,"")</f>
+        <v/>
+      </c>
       <c r="J66" s="14" t="n"/>
       <c r="K66" s="14" t="n"/>
       <c r="L66" s="14" t="n"/>
       <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14" t="n"/>
+      <c r="O66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -1849,11 +2319,16 @@
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="11" t="n"/>
       <c r="H67" s="11" t="n"/>
-      <c r="I67" s="10" t="n"/>
+      <c r="I67" s="9">
+        <f>IF(AND(G67&lt;&gt;"",H67&lt;&gt;""),H67-G67,"")</f>
+        <v/>
+      </c>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="10" t="n"/>
       <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -1864,11 +2339,16 @@
       <c r="F68" s="14" t="n"/>
       <c r="G68" s="15" t="n"/>
       <c r="H68" s="15" t="n"/>
-      <c r="I68" s="14" t="n"/>
+      <c r="I68" s="13">
+        <f>IF(AND(G68&lt;&gt;"",H68&lt;&gt;""),H68-G68,"")</f>
+        <v/>
+      </c>
       <c r="J68" s="14" t="n"/>
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n"/>
       <c r="M68" s="14" t="n"/>
+      <c r="N68" s="14" t="n"/>
+      <c r="O68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -1879,11 +2359,16 @@
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="11" t="n"/>
       <c r="H69" s="11" t="n"/>
-      <c r="I69" s="10" t="n"/>
+      <c r="I69" s="9">
+        <f>IF(AND(G69&lt;&gt;"",H69&lt;&gt;""),H69-G69,"")</f>
+        <v/>
+      </c>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="10" t="n"/>
       <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -1894,11 +2379,16 @@
       <c r="F70" s="14" t="n"/>
       <c r="G70" s="15" t="n"/>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="14" t="n"/>
+      <c r="I70" s="13">
+        <f>IF(AND(G70&lt;&gt;"",H70&lt;&gt;""),H70-G70,"")</f>
+        <v/>
+      </c>
       <c r="J70" s="14" t="n"/>
       <c r="K70" s="14" t="n"/>
       <c r="L70" s="14" t="n"/>
       <c r="M70" s="14" t="n"/>
+      <c r="N70" s="14" t="n"/>
+      <c r="O70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -1909,11 +2399,16 @@
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="11" t="n"/>
       <c r="H71" s="11" t="n"/>
-      <c r="I71" s="10" t="n"/>
+      <c r="I71" s="9">
+        <f>IF(AND(G71&lt;&gt;"",H71&lt;&gt;""),H71-G71,"")</f>
+        <v/>
+      </c>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
       <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -1924,11 +2419,16 @@
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="15" t="n"/>
       <c r="H72" s="15" t="n"/>
-      <c r="I72" s="14" t="n"/>
+      <c r="I72" s="13">
+        <f>IF(AND(G72&lt;&gt;"",H72&lt;&gt;""),H72-G72,"")</f>
+        <v/>
+      </c>
       <c r="J72" s="14" t="n"/>
       <c r="K72" s="14" t="n"/>
       <c r="L72" s="14" t="n"/>
       <c r="M72" s="14" t="n"/>
+      <c r="N72" s="14" t="n"/>
+      <c r="O72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -1939,11 +2439,16 @@
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="11" t="n"/>
       <c r="H73" s="11" t="n"/>
-      <c r="I73" s="10" t="n"/>
+      <c r="I73" s="9">
+        <f>IF(AND(G73&lt;&gt;"",H73&lt;&gt;""),H73-G73,"")</f>
+        <v/>
+      </c>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
       <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -1954,11 +2459,16 @@
       <c r="F74" s="14" t="n"/>
       <c r="G74" s="15" t="n"/>
       <c r="H74" s="15" t="n"/>
-      <c r="I74" s="14" t="n"/>
+      <c r="I74" s="13">
+        <f>IF(AND(G74&lt;&gt;"",H74&lt;&gt;""),H74-G74,"")</f>
+        <v/>
+      </c>
       <c r="J74" s="14" t="n"/>
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="14" t="n"/>
       <c r="M74" s="14" t="n"/>
+      <c r="N74" s="14" t="n"/>
+      <c r="O74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -1969,11 +2479,16 @@
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="11" t="n"/>
       <c r="H75" s="11" t="n"/>
-      <c r="I75" s="10" t="n"/>
+      <c r="I75" s="9">
+        <f>IF(AND(G75&lt;&gt;"",H75&lt;&gt;""),H75-G75,"")</f>
+        <v/>
+      </c>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
       <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -1984,11 +2499,16 @@
       <c r="F76" s="14" t="n"/>
       <c r="G76" s="15" t="n"/>
       <c r="H76" s="15" t="n"/>
-      <c r="I76" s="14" t="n"/>
+      <c r="I76" s="13">
+        <f>IF(AND(G76&lt;&gt;"",H76&lt;&gt;""),H76-G76,"")</f>
+        <v/>
+      </c>
       <c r="J76" s="14" t="n"/>
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="14" t="n"/>
       <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n"/>
+      <c r="O76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -1999,11 +2519,16 @@
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="11" t="n"/>
       <c r="H77" s="11" t="n"/>
-      <c r="I77" s="10" t="n"/>
+      <c r="I77" s="9">
+        <f>IF(AND(G77&lt;&gt;"",H77&lt;&gt;""),H77-G77,"")</f>
+        <v/>
+      </c>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
       <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -2014,11 +2539,16 @@
       <c r="F78" s="14" t="n"/>
       <c r="G78" s="15" t="n"/>
       <c r="H78" s="15" t="n"/>
-      <c r="I78" s="14" t="n"/>
+      <c r="I78" s="13">
+        <f>IF(AND(G78&lt;&gt;"",H78&lt;&gt;""),H78-G78,"")</f>
+        <v/>
+      </c>
       <c r="J78" s="14" t="n"/>
       <c r="K78" s="14" t="n"/>
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
+      <c r="O78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -2029,11 +2559,16 @@
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="11" t="n"/>
       <c r="H79" s="11" t="n"/>
-      <c r="I79" s="10" t="n"/>
+      <c r="I79" s="9">
+        <f>IF(AND(G79&lt;&gt;"",H79&lt;&gt;""),H79-G79,"")</f>
+        <v/>
+      </c>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
       <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2044,11 +2579,16 @@
       <c r="F80" s="14" t="n"/>
       <c r="G80" s="15" t="n"/>
       <c r="H80" s="15" t="n"/>
-      <c r="I80" s="14" t="n"/>
+      <c r="I80" s="13">
+        <f>IF(AND(G80&lt;&gt;"",H80&lt;&gt;""),H80-G80,"")</f>
+        <v/>
+      </c>
       <c r="J80" s="14" t="n"/>
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
       <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="n"/>
+      <c r="O80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -2059,11 +2599,16 @@
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="11" t="n"/>
       <c r="H81" s="11" t="n"/>
-      <c r="I81" s="10" t="n"/>
+      <c r="I81" s="9">
+        <f>IF(AND(G81&lt;&gt;"",H81&lt;&gt;""),H81-G81,"")</f>
+        <v/>
+      </c>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
       <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -2074,11 +2619,16 @@
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="15" t="n"/>
       <c r="H82" s="15" t="n"/>
-      <c r="I82" s="14" t="n"/>
+      <c r="I82" s="13">
+        <f>IF(AND(G82&lt;&gt;"",H82&lt;&gt;""),H82-G82,"")</f>
+        <v/>
+      </c>
       <c r="J82" s="14" t="n"/>
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
       <c r="M82" s="14" t="n"/>
+      <c r="N82" s="14" t="n"/>
+      <c r="O82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -2089,11 +2639,16 @@
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="11" t="n"/>
       <c r="H83" s="11" t="n"/>
-      <c r="I83" s="10" t="n"/>
+      <c r="I83" s="9">
+        <f>IF(AND(G83&lt;&gt;"",H83&lt;&gt;""),H83-G83,"")</f>
+        <v/>
+      </c>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
       <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -2104,11 +2659,16 @@
       <c r="F84" s="14" t="n"/>
       <c r="G84" s="15" t="n"/>
       <c r="H84" s="15" t="n"/>
-      <c r="I84" s="14" t="n"/>
+      <c r="I84" s="13">
+        <f>IF(AND(G84&lt;&gt;"",H84&lt;&gt;""),H84-G84,"")</f>
+        <v/>
+      </c>
       <c r="J84" s="14" t="n"/>
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14" t="n"/>
+      <c r="O84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -2119,11 +2679,16 @@
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="11" t="n"/>
       <c r="H85" s="11" t="n"/>
-      <c r="I85" s="10" t="n"/>
+      <c r="I85" s="9">
+        <f>IF(AND(G85&lt;&gt;"",H85&lt;&gt;""),H85-G85,"")</f>
+        <v/>
+      </c>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
       <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -2134,11 +2699,16 @@
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="15" t="n"/>
       <c r="H86" s="15" t="n"/>
-      <c r="I86" s="14" t="n"/>
+      <c r="I86" s="13">
+        <f>IF(AND(G86&lt;&gt;"",H86&lt;&gt;""),H86-G86,"")</f>
+        <v/>
+      </c>
       <c r="J86" s="14" t="n"/>
       <c r="K86" s="14" t="n"/>
       <c r="L86" s="14" t="n"/>
       <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14" t="n"/>
+      <c r="O86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -2149,11 +2719,16 @@
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="11" t="n"/>
       <c r="H87" s="11" t="n"/>
-      <c r="I87" s="10" t="n"/>
+      <c r="I87" s="9">
+        <f>IF(AND(G87&lt;&gt;"",H87&lt;&gt;""),H87-G87,"")</f>
+        <v/>
+      </c>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="10" t="n"/>
       <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -2164,11 +2739,16 @@
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="15" t="n"/>
       <c r="H88" s="15" t="n"/>
-      <c r="I88" s="14" t="n"/>
+      <c r="I88" s="13">
+        <f>IF(AND(G88&lt;&gt;"",H88&lt;&gt;""),H88-G88,"")</f>
+        <v/>
+      </c>
       <c r="J88" s="14" t="n"/>
       <c r="K88" s="14" t="n"/>
       <c r="L88" s="14" t="n"/>
       <c r="M88" s="14" t="n"/>
+      <c r="N88" s="14" t="n"/>
+      <c r="O88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -2179,11 +2759,16 @@
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="11" t="n"/>
       <c r="H89" s="11" t="n"/>
-      <c r="I89" s="10" t="n"/>
+      <c r="I89" s="9">
+        <f>IF(AND(G89&lt;&gt;"",H89&lt;&gt;""),H89-G89,"")</f>
+        <v/>
+      </c>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="10" t="n"/>
       <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -2194,11 +2779,16 @@
       <c r="F90" s="14" t="n"/>
       <c r="G90" s="15" t="n"/>
       <c r="H90" s="15" t="n"/>
-      <c r="I90" s="14" t="n"/>
+      <c r="I90" s="13">
+        <f>IF(AND(G90&lt;&gt;"",H90&lt;&gt;""),H90-G90,"")</f>
+        <v/>
+      </c>
       <c r="J90" s="14" t="n"/>
       <c r="K90" s="14" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="14" t="n"/>
+      <c r="N90" s="14" t="n"/>
+      <c r="O90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -2209,11 +2799,16 @@
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="11" t="n"/>
       <c r="H91" s="11" t="n"/>
-      <c r="I91" s="10" t="n"/>
+      <c r="I91" s="9">
+        <f>IF(AND(G91&lt;&gt;"",H91&lt;&gt;""),H91-G91,"")</f>
+        <v/>
+      </c>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="10" t="n"/>
       <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -2224,11 +2819,16 @@
       <c r="F92" s="14" t="n"/>
       <c r="G92" s="15" t="n"/>
       <c r="H92" s="15" t="n"/>
-      <c r="I92" s="14" t="n"/>
+      <c r="I92" s="13">
+        <f>IF(AND(G92&lt;&gt;"",H92&lt;&gt;""),H92-G92,"")</f>
+        <v/>
+      </c>
       <c r="J92" s="14" t="n"/>
       <c r="K92" s="14" t="n"/>
       <c r="L92" s="14" t="n"/>
       <c r="M92" s="14" t="n"/>
+      <c r="N92" s="14" t="n"/>
+      <c r="O92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -2239,11 +2839,16 @@
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="11" t="n"/>
       <c r="H93" s="11" t="n"/>
-      <c r="I93" s="10" t="n"/>
+      <c r="I93" s="9">
+        <f>IF(AND(G93&lt;&gt;"",H93&lt;&gt;""),H93-G93,"")</f>
+        <v/>
+      </c>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="10" t="n"/>
       <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -2254,11 +2859,16 @@
       <c r="F94" s="14" t="n"/>
       <c r="G94" s="15" t="n"/>
       <c r="H94" s="15" t="n"/>
-      <c r="I94" s="14" t="n"/>
+      <c r="I94" s="13">
+        <f>IF(AND(G94&lt;&gt;"",H94&lt;&gt;""),H94-G94,"")</f>
+        <v/>
+      </c>
       <c r="J94" s="14" t="n"/>
       <c r="K94" s="14" t="n"/>
       <c r="L94" s="14" t="n"/>
       <c r="M94" s="14" t="n"/>
+      <c r="N94" s="14" t="n"/>
+      <c r="O94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -2269,11 +2879,16 @@
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="11" t="n"/>
       <c r="H95" s="11" t="n"/>
-      <c r="I95" s="10" t="n"/>
+      <c r="I95" s="9">
+        <f>IF(AND(G95&lt;&gt;"",H95&lt;&gt;""),H95-G95,"")</f>
+        <v/>
+      </c>
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
       <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -2284,11 +2899,16 @@
       <c r="F96" s="14" t="n"/>
       <c r="G96" s="15" t="n"/>
       <c r="H96" s="15" t="n"/>
-      <c r="I96" s="14" t="n"/>
+      <c r="I96" s="13">
+        <f>IF(AND(G96&lt;&gt;"",H96&lt;&gt;""),H96-G96,"")</f>
+        <v/>
+      </c>
       <c r="J96" s="14" t="n"/>
       <c r="K96" s="14" t="n"/>
       <c r="L96" s="14" t="n"/>
       <c r="M96" s="14" t="n"/>
+      <c r="N96" s="14" t="n"/>
+      <c r="O96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -2299,11 +2919,16 @@
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="11" t="n"/>
       <c r="H97" s="11" t="n"/>
-      <c r="I97" s="10" t="n"/>
+      <c r="I97" s="9">
+        <f>IF(AND(G97&lt;&gt;"",H97&lt;&gt;""),H97-G97,"")</f>
+        <v/>
+      </c>
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="n"/>
       <c r="L97" s="10" t="n"/>
       <c r="M97" s="10" t="n"/>
+      <c r="N97" s="10" t="n"/>
+      <c r="O97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -2314,11 +2939,16 @@
       <c r="F98" s="14" t="n"/>
       <c r="G98" s="15" t="n"/>
       <c r="H98" s="15" t="n"/>
-      <c r="I98" s="14" t="n"/>
+      <c r="I98" s="13">
+        <f>IF(AND(G98&lt;&gt;"",H98&lt;&gt;""),H98-G98,"")</f>
+        <v/>
+      </c>
       <c r="J98" s="14" t="n"/>
       <c r="K98" s="14" t="n"/>
       <c r="L98" s="14" t="n"/>
       <c r="M98" s="14" t="n"/>
+      <c r="N98" s="14" t="n"/>
+      <c r="O98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -2329,11 +2959,16 @@
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="11" t="n"/>
       <c r="H99" s="11" t="n"/>
-      <c r="I99" s="10" t="n"/>
+      <c r="I99" s="9">
+        <f>IF(AND(G99&lt;&gt;"",H99&lt;&gt;""),H99-G99,"")</f>
+        <v/>
+      </c>
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
       <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -2344,11 +2979,16 @@
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="15" t="n"/>
       <c r="H100" s="15" t="n"/>
-      <c r="I100" s="14" t="n"/>
+      <c r="I100" s="13">
+        <f>IF(AND(G100&lt;&gt;"",H100&lt;&gt;""),H100-G100,"")</f>
+        <v/>
+      </c>
       <c r="J100" s="14" t="n"/>
       <c r="K100" s="14" t="n"/>
       <c r="L100" s="14" t="n"/>
       <c r="M100" s="14" t="n"/>
+      <c r="N100" s="14" t="n"/>
+      <c r="O100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -2359,11 +2999,16 @@
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="11" t="n"/>
       <c r="H101" s="11" t="n"/>
-      <c r="I101" s="10" t="n"/>
+      <c r="I101" s="9">
+        <f>IF(AND(G101&lt;&gt;"",H101&lt;&gt;""),H101-G101,"")</f>
+        <v/>
+      </c>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="n"/>
       <c r="L101" s="10" t="n"/>
       <c r="M101" s="10" t="n"/>
+      <c r="N101" s="10" t="n"/>
+      <c r="O101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -2374,20 +3019,26 @@
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="15" t="n"/>
       <c r="H102" s="15" t="n"/>
-      <c r="I102" s="14" t="n"/>
+      <c r="I102" s="13">
+        <f>IF(AND(G102&lt;&gt;"",H102&lt;&gt;""),H102-G102,"")</f>
+        <v/>
+      </c>
       <c r="J102" s="14" t="n"/>
       <c r="K102" s="14" t="n"/>
       <c r="L102" s="14" t="n"/>
       <c r="M102" s="14" t="n"/>
+      <c r="N102" s="14" t="n"/>
+      <c r="O102" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M2"/>
-  <mergeCells count="3">
-    <mergeCell ref="I1:L1"/>
+  <autoFilter ref="A2:O2"/>
+  <mergeCells count="4">
+    <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="J1:M1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3:J102">
+  <conditionalFormatting sqref="K3:K102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"自家移植"</formula>
     </cfRule>
@@ -2416,7 +3067,26 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <conditionalFormatting sqref="N3:N102">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
+      <formula>"入院中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="8">
+      <formula>"退院済"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+      <formula>"外来移行"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J102">
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="9">
+      <formula>"3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="9">
+      <formula>"4"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
@@ -2426,11 +3096,14 @@
     <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"I,II,III,IV,Limited,Extensive,ISS-I,ISS-II,ISS-III,R-ISS-I,R-ISS-II,R-ISS-III,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"0,1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"入院中,退院済,外来移行"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2444,21 +3117,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2479,15 +3153,16 @@
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="20" t="inlineStr">
+      <c r="J1" s="19" t="n"/>
+      <c r="K1" s="20" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="K1" s="21" t="n"/>
-      <c r="L1" s="20" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="L1" s="21" t="n"/>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>その他</t>
         </is>
       </c>
     </row>
@@ -2514,40 +3189,45 @@
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
+          <t>緊急度</t>
+        </is>
+      </c>
+      <c r="F2" s="22" t="inlineStr">
+        <is>
           <t>コンサルト日</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>依頼科</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>依頼医</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>コンサルト理由</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>疾患(疑い含む)</t>
         </is>
       </c>
-      <c r="J2" s="22" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>対応内容</t>
         </is>
       </c>
-      <c r="K2" s="22" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>フォロー要否</t>
         </is>
       </c>
-      <c r="L2" s="22" t="inlineStr">
+      <c r="M2" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -2558,14 +3238,15 @@
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
       <c r="I3" s="10" t="n"/>
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
       <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="23" t="n"/>
@@ -2574,26 +3255,28 @@
       <c r="D4" s="24" t="n"/>
       <c r="E4" s="25" t="n"/>
       <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
-      <c r="H4" s="26" t="n"/>
-      <c r="I4" s="26" t="n"/>
-      <c r="J4" s="26" t="n"/>
-      <c r="K4" s="26" t="n"/>
-      <c r="L4" s="26" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="11" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n"/>
@@ -2602,26 +3285,28 @@
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="26" t="n"/>
-      <c r="J6" s="26" t="n"/>
-      <c r="K6" s="26" t="n"/>
-      <c r="L6" s="26" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="25" t="n"/>
+      <c r="M6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="11" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n"/>
@@ -2630,26 +3315,28 @@
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="26" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
+      <c r="M8" s="25" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="11" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n"/>
@@ -2658,26 +3345,28 @@
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="26" t="n"/>
-      <c r="L10" s="26" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
+      <c r="M10" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="11" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="n"/>
       <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n"/>
@@ -2686,26 +3375,28 @@
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="25" t="n"/>
       <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="25" t="n"/>
+      <c r="M12" s="25" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="n"/>
@@ -2714,26 +3405,28 @@
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="25" t="n"/>
       <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
+      <c r="M14" s="25" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n"/>
@@ -2742,26 +3435,28 @@
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="25" t="n"/>
       <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
+      <c r="M16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="11" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="n"/>
@@ -2770,26 +3465,28 @@
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="26" t="n"/>
-      <c r="K18" s="26" t="n"/>
-      <c r="L18" s="26" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
+      <c r="M18" s="25" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="11" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n"/>
@@ -2798,26 +3495,28 @@
       <c r="D20" s="24" t="n"/>
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="26" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="26" t="n"/>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="26" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
+      <c r="M20" s="25" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="11" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n"/>
@@ -2826,26 +3525,28 @@
       <c r="D22" s="24" t="n"/>
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="26" t="n"/>
-      <c r="I22" s="26" t="n"/>
-      <c r="J22" s="26" t="n"/>
-      <c r="K22" s="26" t="n"/>
-      <c r="L22" s="26" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
+      <c r="M22" s="25" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="11" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
+      <c r="M23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n"/>
@@ -2854,26 +3555,28 @@
       <c r="D24" s="24" t="n"/>
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="26" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
+      <c r="M24" s="25" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="11" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="n"/>
+      <c r="M25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="n"/>
@@ -2882,26 +3585,28 @@
       <c r="D26" s="24" t="n"/>
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="26" t="n"/>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="26" t="n"/>
-      <c r="L26" s="26" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
+      <c r="M26" s="25" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="11" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
+      <c r="M27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23" t="n"/>
@@ -2910,26 +3615,28 @@
       <c r="D28" s="24" t="n"/>
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="26" t="n"/>
-      <c r="L28" s="26" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="25" t="n"/>
+      <c r="M28" s="25" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="11" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="10" t="n"/>
       <c r="L29" s="10" t="n"/>
+      <c r="M29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n"/>
@@ -2938,26 +3645,28 @@
       <c r="D30" s="24" t="n"/>
       <c r="E30" s="25" t="n"/>
       <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="26" t="n"/>
-      <c r="I30" s="26" t="n"/>
-      <c r="J30" s="26" t="n"/>
-      <c r="K30" s="26" t="n"/>
-      <c r="L30" s="26" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="25" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="n"/>
@@ -2966,26 +3675,28 @@
       <c r="D32" s="24" t="n"/>
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
+      <c r="M32" s="25" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
+      <c r="M33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n"/>
@@ -2994,26 +3705,28 @@
       <c r="D34" s="24" t="n"/>
       <c r="E34" s="25" t="n"/>
       <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="26" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="25" t="n"/>
+      <c r="M34" s="25" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="11" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n"/>
@@ -3022,26 +3735,28 @@
       <c r="D36" s="24" t="n"/>
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="26" t="n"/>
-      <c r="L36" s="26" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
+      <c r="M36" s="25" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
+      <c r="M37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="23" t="n"/>
@@ -3050,26 +3765,28 @@
       <c r="D38" s="24" t="n"/>
       <c r="E38" s="25" t="n"/>
       <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="n"/>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="26" t="n"/>
-      <c r="K38" s="26" t="n"/>
-      <c r="L38" s="26" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="23" t="n"/>
@@ -3078,26 +3795,28 @@
       <c r="D40" s="24" t="n"/>
       <c r="E40" s="25" t="n"/>
       <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="K40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
+      <c r="M40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="11" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n"/>
@@ -3106,26 +3825,28 @@
       <c r="D42" s="24" t="n"/>
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="n"/>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
+      <c r="M42" s="25" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="11" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n"/>
@@ -3134,26 +3855,28 @@
       <c r="D44" s="24" t="n"/>
       <c r="E44" s="25" t="n"/>
       <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="n"/>
-      <c r="H44" s="26" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="n"/>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
+      <c r="M44" s="25" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="11" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n"/>
@@ -3162,26 +3885,28 @@
       <c r="D46" s="24" t="n"/>
       <c r="E46" s="25" t="n"/>
       <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="n"/>
-      <c r="I46" s="26" t="n"/>
-      <c r="J46" s="26" t="n"/>
-      <c r="K46" s="26" t="n"/>
-      <c r="L46" s="26" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="25" t="n"/>
+      <c r="L46" s="25" t="n"/>
+      <c r="M46" s="25" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="11" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23" t="n"/>
@@ -3190,26 +3915,28 @@
       <c r="D48" s="24" t="n"/>
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
-      <c r="G48" s="26" t="n"/>
-      <c r="H48" s="26" t="n"/>
-      <c r="I48" s="26" t="n"/>
-      <c r="J48" s="26" t="n"/>
-      <c r="K48" s="26" t="n"/>
-      <c r="L48" s="26" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
+      <c r="M48" s="25" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="9" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="11" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n"/>
@@ -3218,26 +3945,28 @@
       <c r="D50" s="24" t="n"/>
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
-      <c r="G50" s="26" t="n"/>
-      <c r="H50" s="26" t="n"/>
-      <c r="I50" s="26" t="n"/>
-      <c r="J50" s="26" t="n"/>
-      <c r="K50" s="26" t="n"/>
-      <c r="L50" s="26" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
+      <c r="M50" s="25" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="11" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="23" t="n"/>
@@ -3246,26 +3975,28 @@
       <c r="D52" s="24" t="n"/>
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="26" t="n"/>
-      <c r="G52" s="26" t="n"/>
-      <c r="H52" s="26" t="n"/>
-      <c r="I52" s="26" t="n"/>
-      <c r="J52" s="26" t="n"/>
-      <c r="K52" s="26" t="n"/>
-      <c r="L52" s="26" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="25" t="n"/>
+      <c r="M52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="11" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23" t="n"/>
@@ -3274,26 +4005,28 @@
       <c r="D54" s="24" t="n"/>
       <c r="E54" s="25" t="n"/>
       <c r="F54" s="26" t="n"/>
-      <c r="G54" s="26" t="n"/>
-      <c r="H54" s="26" t="n"/>
-      <c r="I54" s="26" t="n"/>
-      <c r="J54" s="26" t="n"/>
-      <c r="K54" s="26" t="n"/>
-      <c r="L54" s="26" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="9" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="11" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
       <c r="I55" s="10" t="n"/>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="23" t="n"/>
@@ -3302,26 +4035,28 @@
       <c r="D56" s="24" t="n"/>
       <c r="E56" s="25" t="n"/>
       <c r="F56" s="26" t="n"/>
-      <c r="G56" s="26" t="n"/>
-      <c r="H56" s="26" t="n"/>
-      <c r="I56" s="26" t="n"/>
-      <c r="J56" s="26" t="n"/>
-      <c r="K56" s="26" t="n"/>
-      <c r="L56" s="26" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="25" t="n"/>
+      <c r="I56" s="25" t="n"/>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="25" t="n"/>
+      <c r="M56" s="25" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="9" t="n"/>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="11" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
       <c r="I57" s="10" t="n"/>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="23" t="n"/>
@@ -3330,26 +4065,28 @@
       <c r="D58" s="24" t="n"/>
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
-      <c r="G58" s="26" t="n"/>
-      <c r="H58" s="26" t="n"/>
-      <c r="I58" s="26" t="n"/>
-      <c r="J58" s="26" t="n"/>
-      <c r="K58" s="26" t="n"/>
-      <c r="L58" s="26" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="25" t="n"/>
+      <c r="M58" s="25" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="9" t="n"/>
       <c r="D59" s="9" t="n"/>
-      <c r="E59" s="11" t="n"/>
-      <c r="F59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="11" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
       <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="23" t="n"/>
@@ -3358,26 +4095,28 @@
       <c r="D60" s="24" t="n"/>
       <c r="E60" s="25" t="n"/>
       <c r="F60" s="26" t="n"/>
-      <c r="G60" s="26" t="n"/>
-      <c r="H60" s="26" t="n"/>
-      <c r="I60" s="26" t="n"/>
-      <c r="J60" s="26" t="n"/>
-      <c r="K60" s="26" t="n"/>
-      <c r="L60" s="26" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="25" t="n"/>
+      <c r="M60" s="25" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
       <c r="D61" s="9" t="n"/>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="11" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="23" t="n"/>
@@ -3386,26 +4125,28 @@
       <c r="D62" s="24" t="n"/>
       <c r="E62" s="25" t="n"/>
       <c r="F62" s="26" t="n"/>
-      <c r="G62" s="26" t="n"/>
-      <c r="H62" s="26" t="n"/>
-      <c r="I62" s="26" t="n"/>
-      <c r="J62" s="26" t="n"/>
-      <c r="K62" s="26" t="n"/>
-      <c r="L62" s="26" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="25" t="n"/>
+      <c r="J62" s="25" t="n"/>
+      <c r="K62" s="25" t="n"/>
+      <c r="L62" s="25" t="n"/>
+      <c r="M62" s="25" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="9" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="11" t="n"/>
-      <c r="F63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="11" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n"/>
@@ -3414,26 +4155,28 @@
       <c r="D64" s="24" t="n"/>
       <c r="E64" s="25" t="n"/>
       <c r="F64" s="26" t="n"/>
-      <c r="G64" s="26" t="n"/>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26" t="n"/>
-      <c r="J64" s="26" t="n"/>
-      <c r="K64" s="26" t="n"/>
-      <c r="L64" s="26" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
+      <c r="I64" s="25" t="n"/>
+      <c r="J64" s="25" t="n"/>
+      <c r="K64" s="25" t="n"/>
+      <c r="L64" s="25" t="n"/>
+      <c r="M64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n"/>
-      <c r="E65" s="11" t="n"/>
-      <c r="F65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="11" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="n"/>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="23" t="n"/>
@@ -3442,26 +4185,28 @@
       <c r="D66" s="24" t="n"/>
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="26" t="n"/>
-      <c r="G66" s="26" t="n"/>
-      <c r="H66" s="26" t="n"/>
-      <c r="I66" s="26" t="n"/>
-      <c r="J66" s="26" t="n"/>
-      <c r="K66" s="26" t="n"/>
-      <c r="L66" s="26" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="25" t="n"/>
+      <c r="K66" s="25" t="n"/>
+      <c r="L66" s="25" t="n"/>
+      <c r="M66" s="25" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="9" t="n"/>
       <c r="D67" s="9" t="n"/>
-      <c r="E67" s="11" t="n"/>
-      <c r="F67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="11" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="n"/>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="23" t="n"/>
@@ -3470,26 +4215,28 @@
       <c r="D68" s="24" t="n"/>
       <c r="E68" s="25" t="n"/>
       <c r="F68" s="26" t="n"/>
-      <c r="G68" s="26" t="n"/>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26" t="n"/>
-      <c r="J68" s="26" t="n"/>
-      <c r="K68" s="26" t="n"/>
-      <c r="L68" s="26" t="n"/>
+      <c r="G68" s="25" t="n"/>
+      <c r="H68" s="25" t="n"/>
+      <c r="I68" s="25" t="n"/>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="25" t="n"/>
+      <c r="L68" s="25" t="n"/>
+      <c r="M68" s="25" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="9" t="n"/>
       <c r="D69" s="9" t="n"/>
-      <c r="E69" s="11" t="n"/>
-      <c r="F69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="11" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="23" t="n"/>
@@ -3498,26 +4245,28 @@
       <c r="D70" s="24" t="n"/>
       <c r="E70" s="25" t="n"/>
       <c r="F70" s="26" t="n"/>
-      <c r="G70" s="26" t="n"/>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26" t="n"/>
-      <c r="J70" s="26" t="n"/>
-      <c r="K70" s="26" t="n"/>
-      <c r="L70" s="26" t="n"/>
+      <c r="G70" s="25" t="n"/>
+      <c r="H70" s="25" t="n"/>
+      <c r="I70" s="25" t="n"/>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="25" t="n"/>
+      <c r="L70" s="25" t="n"/>
+      <c r="M70" s="25" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="9" t="n"/>
       <c r="D71" s="9" t="n"/>
-      <c r="E71" s="11" t="n"/>
-      <c r="F71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="11" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="23" t="n"/>
@@ -3526,26 +4275,28 @@
       <c r="D72" s="24" t="n"/>
       <c r="E72" s="25" t="n"/>
       <c r="F72" s="26" t="n"/>
-      <c r="G72" s="26" t="n"/>
-      <c r="H72" s="26" t="n"/>
-      <c r="I72" s="26" t="n"/>
-      <c r="J72" s="26" t="n"/>
-      <c r="K72" s="26" t="n"/>
-      <c r="L72" s="26" t="n"/>
+      <c r="G72" s="25" t="n"/>
+      <c r="H72" s="25" t="n"/>
+      <c r="I72" s="25" t="n"/>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="25" t="n"/>
+      <c r="L72" s="25" t="n"/>
+      <c r="M72" s="25" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
       <c r="D73" s="9" t="n"/>
-      <c r="E73" s="11" t="n"/>
-      <c r="F73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="11" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="23" t="n"/>
@@ -3554,26 +4305,28 @@
       <c r="D74" s="24" t="n"/>
       <c r="E74" s="25" t="n"/>
       <c r="F74" s="26" t="n"/>
-      <c r="G74" s="26" t="n"/>
-      <c r="H74" s="26" t="n"/>
-      <c r="I74" s="26" t="n"/>
-      <c r="J74" s="26" t="n"/>
-      <c r="K74" s="26" t="n"/>
-      <c r="L74" s="26" t="n"/>
+      <c r="G74" s="25" t="n"/>
+      <c r="H74" s="25" t="n"/>
+      <c r="I74" s="25" t="n"/>
+      <c r="J74" s="25" t="n"/>
+      <c r="K74" s="25" t="n"/>
+      <c r="L74" s="25" t="n"/>
+      <c r="M74" s="25" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="9" t="n"/>
       <c r="D75" s="9" t="n"/>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="11" t="n"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="23" t="n"/>
@@ -3582,26 +4335,28 @@
       <c r="D76" s="24" t="n"/>
       <c r="E76" s="25" t="n"/>
       <c r="F76" s="26" t="n"/>
-      <c r="G76" s="26" t="n"/>
-      <c r="H76" s="26" t="n"/>
-      <c r="I76" s="26" t="n"/>
-      <c r="J76" s="26" t="n"/>
-      <c r="K76" s="26" t="n"/>
-      <c r="L76" s="26" t="n"/>
+      <c r="G76" s="25" t="n"/>
+      <c r="H76" s="25" t="n"/>
+      <c r="I76" s="25" t="n"/>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="25" t="n"/>
+      <c r="L76" s="25" t="n"/>
+      <c r="M76" s="25" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
       <c r="D77" s="9" t="n"/>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="11" t="n"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="23" t="n"/>
@@ -3610,26 +4365,28 @@
       <c r="D78" s="24" t="n"/>
       <c r="E78" s="25" t="n"/>
       <c r="F78" s="26" t="n"/>
-      <c r="G78" s="26" t="n"/>
-      <c r="H78" s="26" t="n"/>
-      <c r="I78" s="26" t="n"/>
-      <c r="J78" s="26" t="n"/>
-      <c r="K78" s="26" t="n"/>
-      <c r="L78" s="26" t="n"/>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="25" t="n"/>
+      <c r="I78" s="25" t="n"/>
+      <c r="J78" s="25" t="n"/>
+      <c r="K78" s="25" t="n"/>
+      <c r="L78" s="25" t="n"/>
+      <c r="M78" s="25" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="9" t="n"/>
       <c r="D79" s="9" t="n"/>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="11" t="n"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="23" t="n"/>
@@ -3638,26 +4395,28 @@
       <c r="D80" s="24" t="n"/>
       <c r="E80" s="25" t="n"/>
       <c r="F80" s="26" t="n"/>
-      <c r="G80" s="26" t="n"/>
-      <c r="H80" s="26" t="n"/>
-      <c r="I80" s="26" t="n"/>
-      <c r="J80" s="26" t="n"/>
-      <c r="K80" s="26" t="n"/>
-      <c r="L80" s="26" t="n"/>
+      <c r="G80" s="25" t="n"/>
+      <c r="H80" s="25" t="n"/>
+      <c r="I80" s="25" t="n"/>
+      <c r="J80" s="25" t="n"/>
+      <c r="K80" s="25" t="n"/>
+      <c r="L80" s="25" t="n"/>
+      <c r="M80" s="25" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="9" t="n"/>
       <c r="D81" s="9" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="11" t="n"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n"/>
@@ -3666,26 +4425,28 @@
       <c r="D82" s="24" t="n"/>
       <c r="E82" s="25" t="n"/>
       <c r="F82" s="26" t="n"/>
-      <c r="G82" s="26" t="n"/>
-      <c r="H82" s="26" t="n"/>
-      <c r="I82" s="26" t="n"/>
-      <c r="J82" s="26" t="n"/>
-      <c r="K82" s="26" t="n"/>
-      <c r="L82" s="26" t="n"/>
+      <c r="G82" s="25" t="n"/>
+      <c r="H82" s="25" t="n"/>
+      <c r="I82" s="25" t="n"/>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="25" t="n"/>
+      <c r="L82" s="25" t="n"/>
+      <c r="M82" s="25" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="9" t="n"/>
       <c r="D83" s="9" t="n"/>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="11" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="23" t="n"/>
@@ -3694,26 +4455,28 @@
       <c r="D84" s="24" t="n"/>
       <c r="E84" s="25" t="n"/>
       <c r="F84" s="26" t="n"/>
-      <c r="G84" s="26" t="n"/>
-      <c r="H84" s="26" t="n"/>
-      <c r="I84" s="26" t="n"/>
-      <c r="J84" s="26" t="n"/>
-      <c r="K84" s="26" t="n"/>
-      <c r="L84" s="26" t="n"/>
+      <c r="G84" s="25" t="n"/>
+      <c r="H84" s="25" t="n"/>
+      <c r="I84" s="25" t="n"/>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="25" t="n"/>
+      <c r="L84" s="25" t="n"/>
+      <c r="M84" s="25" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="9" t="n"/>
-      <c r="E85" s="11" t="n"/>
-      <c r="F85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="11" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="23" t="n"/>
@@ -3722,26 +4485,28 @@
       <c r="D86" s="24" t="n"/>
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
-      <c r="G86" s="26" t="n"/>
-      <c r="H86" s="26" t="n"/>
-      <c r="I86" s="26" t="n"/>
-      <c r="J86" s="26" t="n"/>
-      <c r="K86" s="26" t="n"/>
-      <c r="L86" s="26" t="n"/>
+      <c r="G86" s="25" t="n"/>
+      <c r="H86" s="25" t="n"/>
+      <c r="I86" s="25" t="n"/>
+      <c r="J86" s="25" t="n"/>
+      <c r="K86" s="25" t="n"/>
+      <c r="L86" s="25" t="n"/>
+      <c r="M86" s="25" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="11" t="n"/>
-      <c r="F87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="11" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="23" t="n"/>
@@ -3750,26 +4515,28 @@
       <c r="D88" s="24" t="n"/>
       <c r="E88" s="25" t="n"/>
       <c r="F88" s="26" t="n"/>
-      <c r="G88" s="26" t="n"/>
-      <c r="H88" s="26" t="n"/>
-      <c r="I88" s="26" t="n"/>
-      <c r="J88" s="26" t="n"/>
-      <c r="K88" s="26" t="n"/>
-      <c r="L88" s="26" t="n"/>
+      <c r="G88" s="25" t="n"/>
+      <c r="H88" s="25" t="n"/>
+      <c r="I88" s="25" t="n"/>
+      <c r="J88" s="25" t="n"/>
+      <c r="K88" s="25" t="n"/>
+      <c r="L88" s="25" t="n"/>
+      <c r="M88" s="25" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="9" t="n"/>
       <c r="D89" s="9" t="n"/>
-      <c r="E89" s="11" t="n"/>
-      <c r="F89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="11" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n"/>
@@ -3778,26 +4545,28 @@
       <c r="D90" s="24" t="n"/>
       <c r="E90" s="25" t="n"/>
       <c r="F90" s="26" t="n"/>
-      <c r="G90" s="26" t="n"/>
-      <c r="H90" s="26" t="n"/>
-      <c r="I90" s="26" t="n"/>
-      <c r="J90" s="26" t="n"/>
-      <c r="K90" s="26" t="n"/>
-      <c r="L90" s="26" t="n"/>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="25" t="n"/>
+      <c r="I90" s="25" t="n"/>
+      <c r="J90" s="25" t="n"/>
+      <c r="K90" s="25" t="n"/>
+      <c r="L90" s="25" t="n"/>
+      <c r="M90" s="25" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="9" t="n"/>
       <c r="D91" s="9" t="n"/>
-      <c r="E91" s="11" t="n"/>
-      <c r="F91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="11" t="n"/>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n"/>
@@ -3806,26 +4575,28 @@
       <c r="D92" s="24" t="n"/>
       <c r="E92" s="25" t="n"/>
       <c r="F92" s="26" t="n"/>
-      <c r="G92" s="26" t="n"/>
-      <c r="H92" s="26" t="n"/>
-      <c r="I92" s="26" t="n"/>
-      <c r="J92" s="26" t="n"/>
-      <c r="K92" s="26" t="n"/>
-      <c r="L92" s="26" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="25" t="n"/>
+      <c r="I92" s="25" t="n"/>
+      <c r="J92" s="25" t="n"/>
+      <c r="K92" s="25" t="n"/>
+      <c r="L92" s="25" t="n"/>
+      <c r="M92" s="25" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
       <c r="D93" s="9" t="n"/>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="11" t="n"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="23" t="n"/>
@@ -3834,26 +4605,28 @@
       <c r="D94" s="24" t="n"/>
       <c r="E94" s="25" t="n"/>
       <c r="F94" s="26" t="n"/>
-      <c r="G94" s="26" t="n"/>
-      <c r="H94" s="26" t="n"/>
-      <c r="I94" s="26" t="n"/>
-      <c r="J94" s="26" t="n"/>
-      <c r="K94" s="26" t="n"/>
-      <c r="L94" s="26" t="n"/>
+      <c r="G94" s="25" t="n"/>
+      <c r="H94" s="25" t="n"/>
+      <c r="I94" s="25" t="n"/>
+      <c r="J94" s="25" t="n"/>
+      <c r="K94" s="25" t="n"/>
+      <c r="L94" s="25" t="n"/>
+      <c r="M94" s="25" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
       <c r="D95" s="9" t="n"/>
-      <c r="E95" s="11" t="n"/>
-      <c r="F95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="11" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="23" t="n"/>
@@ -3862,26 +4635,28 @@
       <c r="D96" s="24" t="n"/>
       <c r="E96" s="25" t="n"/>
       <c r="F96" s="26" t="n"/>
-      <c r="G96" s="26" t="n"/>
-      <c r="H96" s="26" t="n"/>
-      <c r="I96" s="26" t="n"/>
-      <c r="J96" s="26" t="n"/>
-      <c r="K96" s="26" t="n"/>
-      <c r="L96" s="26" t="n"/>
+      <c r="G96" s="25" t="n"/>
+      <c r="H96" s="25" t="n"/>
+      <c r="I96" s="25" t="n"/>
+      <c r="J96" s="25" t="n"/>
+      <c r="K96" s="25" t="n"/>
+      <c r="L96" s="25" t="n"/>
+      <c r="M96" s="25" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
       <c r="D97" s="9" t="n"/>
-      <c r="E97" s="11" t="n"/>
-      <c r="F97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="11" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="n"/>
       <c r="L97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="23" t="n"/>
@@ -3890,26 +4665,28 @@
       <c r="D98" s="24" t="n"/>
       <c r="E98" s="25" t="n"/>
       <c r="F98" s="26" t="n"/>
-      <c r="G98" s="26" t="n"/>
-      <c r="H98" s="26" t="n"/>
-      <c r="I98" s="26" t="n"/>
-      <c r="J98" s="26" t="n"/>
-      <c r="K98" s="26" t="n"/>
-      <c r="L98" s="26" t="n"/>
+      <c r="G98" s="25" t="n"/>
+      <c r="H98" s="25" t="n"/>
+      <c r="I98" s="25" t="n"/>
+      <c r="J98" s="25" t="n"/>
+      <c r="K98" s="25" t="n"/>
+      <c r="L98" s="25" t="n"/>
+      <c r="M98" s="25" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
       <c r="D99" s="9" t="n"/>
-      <c r="E99" s="11" t="n"/>
-      <c r="F99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="11" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="23" t="n"/>
@@ -3918,26 +4695,28 @@
       <c r="D100" s="24" t="n"/>
       <c r="E100" s="25" t="n"/>
       <c r="F100" s="26" t="n"/>
-      <c r="G100" s="26" t="n"/>
-      <c r="H100" s="26" t="n"/>
-      <c r="I100" s="26" t="n"/>
-      <c r="J100" s="26" t="n"/>
-      <c r="K100" s="26" t="n"/>
-      <c r="L100" s="26" t="n"/>
+      <c r="G100" s="25" t="n"/>
+      <c r="H100" s="25" t="n"/>
+      <c r="I100" s="25" t="n"/>
+      <c r="J100" s="25" t="n"/>
+      <c r="K100" s="25" t="n"/>
+      <c r="L100" s="25" t="n"/>
+      <c r="M100" s="25" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
       <c r="D101" s="9" t="n"/>
-      <c r="E101" s="11" t="n"/>
-      <c r="F101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="11" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="n"/>
       <c r="L101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="23" t="n"/>
@@ -3946,28 +4725,54 @@
       <c r="D102" s="24" t="n"/>
       <c r="E102" s="25" t="n"/>
       <c r="F102" s="26" t="n"/>
-      <c r="G102" s="26" t="n"/>
-      <c r="H102" s="26" t="n"/>
-      <c r="I102" s="26" t="n"/>
-      <c r="J102" s="26" t="n"/>
-      <c r="K102" s="26" t="n"/>
-      <c r="L102" s="26" t="n"/>
+      <c r="G102" s="25" t="n"/>
+      <c r="H102" s="25" t="n"/>
+      <c r="I102" s="25" t="n"/>
+      <c r="J102" s="25" t="n"/>
+      <c r="K102" s="25" t="n"/>
+      <c r="L102" s="25" t="n"/>
+      <c r="M102" s="25" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L2"/>
+  <autoFilter ref="A2:M2"/>
   <mergeCells count="3">
-    <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <conditionalFormatting sqref="L3:L102">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="9">
+      <formula>"要"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="10">
+      <formula>"不要"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="11">
+      <formula>"済"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E102">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="9">
+      <formula>"緊急"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="12">
+      <formula>"通常"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="5">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"緊急,通常"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"消化器内科,循環器内科,呼吸器内科,腎臓内科,内分泌内科,神経内科,膠原病内科,一般外科,心臓外科,脳神経外科,整形外科,泌尿器科,産婦人科,皮膚科,耳鼻咽喉科,眼科,精神科,小児科,救急科,麻酔科,放射線科,病理,その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"要,不要,済"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4033,7 +4838,7 @@
       <c r="M1" s="32" t="n"/>
       <c r="N1" s="31" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>その他</t>
         </is>
       </c>
     </row>
@@ -5746,6 +6551,14 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J102">
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
+      <formula>"3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="9">
+      <formula>"4"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
@@ -5765,4 +6578,1201 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001A365D"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>症例管理サマリー</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>入院患者 - 疾患別</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="n"/>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>入院患者 - 治療区分別</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="n"/>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>入院患者 - ステータス別</t>
+        </is>
+      </c>
+      <c r="I4" s="40" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="I5" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="C6" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"AML")</f>
+        <v/>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>化学療法</t>
+        </is>
+      </c>
+      <c r="F6" s="42">
+        <f>COUNTIF('入院患者'!K3:K102,"化学療法")</f>
+        <v/>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>入院中</t>
+        </is>
+      </c>
+      <c r="I6" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"入院中")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C7" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"ALL")</f>
+        <v/>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>自家移植</t>
+        </is>
+      </c>
+      <c r="F7" s="43">
+        <f>COUNTIF('入院患者'!K3:K102,"自家移植")</f>
+        <v/>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>退院済</t>
+        </is>
+      </c>
+      <c r="I7" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"退院済")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="C8" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"CML")</f>
+        <v/>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>同種移植</t>
+        </is>
+      </c>
+      <c r="F8" s="42">
+        <f>COUNTIF('入院患者'!K3:K102,"同種移植")</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>外来移行</t>
+        </is>
+      </c>
+      <c r="I8" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"外来移行")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>CLL</t>
+        </is>
+      </c>
+      <c r="C9" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"CLL")</f>
+        <v/>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>CAR-T</t>
+        </is>
+      </c>
+      <c r="F9" s="43">
+        <f>COUNTIF('入院患者'!K3:K102,"CAR-T")</f>
+        <v/>
+      </c>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="I9" s="45">
+        <f>COUNTA('入院患者'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="C10" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"MDS")</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>分子標的薬</t>
+        </is>
+      </c>
+      <c r="F10" s="42">
+        <f>COUNTIF('入院患者'!K3:K102,"分子標的薬")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="C11" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"MPN")</f>
+        <v/>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>免疫療法</t>
+        </is>
+      </c>
+      <c r="F11" s="43">
+        <f>COUNTIF('入院患者'!K3:K102,"免疫療法")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>CMML</t>
+        </is>
+      </c>
+      <c r="C12" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"CMML")</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>放射線</t>
+        </is>
+      </c>
+      <c r="F12" s="42">
+        <f>COUNTIF('入院患者'!K3:K102,"放射線")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>DLBCL</t>
+        </is>
+      </c>
+      <c r="C13" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"DLBCL")</f>
+        <v/>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>BSC</t>
+        </is>
+      </c>
+      <c r="F13" s="43">
+        <f>COUNTIF('入院患者'!K3:K102,"BSC")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="C14" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"FL")</f>
+        <v/>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>経過観察</t>
+        </is>
+      </c>
+      <c r="F14" s="42">
+        <f>COUNTIF('入院患者'!K3:K102,"経過観察")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="C15" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"MCL")</f>
+        <v/>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F15" s="45">
+        <f>COUNTA('入院患者'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="C16" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"BL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
+      <c r="C17" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"MALT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>ATLL</t>
+        </is>
+      </c>
+      <c r="C18" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"ATLL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>PTCL</t>
+        </is>
+      </c>
+      <c r="C19" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"PTCL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AITL</t>
+        </is>
+      </c>
+      <c r="C20" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"AITL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>NK/T</t>
+        </is>
+      </c>
+      <c r="C21" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"NK/T")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="C22" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"HL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C23" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"MM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="C24" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"WM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>AL amyloidosis</t>
+        </is>
+      </c>
+      <c r="C25" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"AL amyloidosis")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C26" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"AA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>PNH</t>
+        </is>
+      </c>
+      <c r="C27" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"PNH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="C28" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"ITP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>TTP</t>
+        </is>
+      </c>
+      <c r="C29" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"TTP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="C30" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"HUS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="C31" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"DIC")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>HLH</t>
+        </is>
+      </c>
+      <c r="C32" s="42">
+        <f>COUNTIF('入院患者'!E3:E102,"HLH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C33" s="43">
+        <f>COUNTIF('入院患者'!E3:E102,"その他")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C34" s="45">
+        <f>COUNTA('入院患者'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="39" t="inlineStr">
+        <is>
+          <t>他科コンサルト - 疾患別</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="n"/>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>他科コンサルト - 緊急度別</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="n"/>
+      <c r="H36" s="39" t="inlineStr">
+        <is>
+          <t>初診外来 - 疾患別</t>
+        </is>
+      </c>
+      <c r="I36" s="40" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="F37" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="I37" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="C38" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AML")</f>
+        <v/>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>緊急</t>
+        </is>
+      </c>
+      <c r="F38" s="42">
+        <f>COUNTIF('他科コンサルト'!E3:E102,"緊急")</f>
+        <v/>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="I38" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"AML")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C39" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"ALL")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="F39" s="43">
+        <f>COUNTIF('他科コンサルト'!E3:E102,"通常")</f>
+        <v/>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="I39" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"ALL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="C40" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"CML")</f>
+        <v/>
+      </c>
+      <c r="E40" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F40" s="45">
+        <f>COUNTA('他科コンサルト'!A3:A102)</f>
+        <v/>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="I40" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"CML")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>CLL</t>
+        </is>
+      </c>
+      <c r="C41" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"CLL")</f>
+        <v/>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>CLL</t>
+        </is>
+      </c>
+      <c r="I41" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"CLL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="C42" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MDS")</f>
+        <v/>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="I42" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"MDS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="C43" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MPN")</f>
+        <v/>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="I43" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MPN")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>CMML</t>
+        </is>
+      </c>
+      <c r="C44" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"CMML")</f>
+        <v/>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>CMML</t>
+        </is>
+      </c>
+      <c r="I44" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"CMML")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>DLBCL</t>
+        </is>
+      </c>
+      <c r="C45" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"DLBCL")</f>
+        <v/>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>DLBCL</t>
+        </is>
+      </c>
+      <c r="I45" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"DLBCL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="C46" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"FL")</f>
+        <v/>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="I46" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"FL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="C47" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MCL")</f>
+        <v/>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="I47" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MCL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="C48" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"BL")</f>
+        <v/>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="I48" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"BL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
+      <c r="C49" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MALT")</f>
+        <v/>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
+      <c r="I49" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MALT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>ATLL</t>
+        </is>
+      </c>
+      <c r="C50" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"ATLL")</f>
+        <v/>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>ATLL</t>
+        </is>
+      </c>
+      <c r="I50" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"ATLL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>PTCL</t>
+        </is>
+      </c>
+      <c r="C51" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"PTCL")</f>
+        <v/>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>PTCL</t>
+        </is>
+      </c>
+      <c r="I51" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"PTCL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>AITL</t>
+        </is>
+      </c>
+      <c r="C52" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AITL")</f>
+        <v/>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>AITL</t>
+        </is>
+      </c>
+      <c r="I52" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"AITL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>NK/T</t>
+        </is>
+      </c>
+      <c r="C53" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"NK/T")</f>
+        <v/>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>NK/T</t>
+        </is>
+      </c>
+      <c r="I53" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"NK/T")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="C54" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HL")</f>
+        <v/>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="I54" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"HL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="C55" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MM")</f>
+        <v/>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="I55" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="C56" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"WM")</f>
+        <v/>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="I56" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"WM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>AL amyloidosis</t>
+        </is>
+      </c>
+      <c r="C57" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AL amyloidosis")</f>
+        <v/>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>AL amyloidosis</t>
+        </is>
+      </c>
+      <c r="I57" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"AL amyloidosis")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="C58" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AA")</f>
+        <v/>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="I58" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"AA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>PNH</t>
+        </is>
+      </c>
+      <c r="C59" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"PNH")</f>
+        <v/>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>PNH</t>
+        </is>
+      </c>
+      <c r="I59" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"PNH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="C60" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"ITP")</f>
+        <v/>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="I60" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"ITP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>TTP</t>
+        </is>
+      </c>
+      <c r="C61" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"TTP")</f>
+        <v/>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>TTP</t>
+        </is>
+      </c>
+      <c r="I61" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"TTP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="C62" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HUS")</f>
+        <v/>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="I62" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"HUS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="C63" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"DIC")</f>
+        <v/>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="I63" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"DIC")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>HLH</t>
+        </is>
+      </c>
+      <c r="C64" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HLH")</f>
+        <v/>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>HLH</t>
+        </is>
+      </c>
+      <c r="I64" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"HLH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C65" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"その他")</f>
+        <v/>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="I65" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"その他")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C66" s="45">
+        <f>COUNTA('他科コンサルト'!A3:A102)</f>
+        <v/>
+      </c>
+      <c r="H66" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="I66" s="45">
+        <f>COUNTA('初診外来'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -13,9 +13,9 @@
     <sheet name="サマリー" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$O$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +357,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
     <dxf>
       <font>
         <name val="Meiryo"/>
@@ -495,6 +495,34 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FCE4EC"/>
           <bgColor rgb="00FCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Meiryo"/>
+        <b val="1"/>
+        <color rgb="004E8A2D"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2EFDA"/>
+          <bgColor rgb="00E2EFDA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -900,7 +928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -916,8 +944,9 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -946,12 +975,13 @@
       <c r="K1" s="6" t="n"/>
       <c r="L1" s="6" t="n"/>
       <c r="M1" s="6" t="n"/>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="6" t="n"/>
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="O1" s="6" t="n"/>
+      <c r="P1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1021,10 +1051,15 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
+          <t>転帰</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1049,6 +1084,7 @@
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -1069,6 +1105,7 @@
       <c r="M4" s="14" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -1089,6 +1126,7 @@
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -1109,6 +1147,7 @@
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -1129,6 +1168,7 @@
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -1149,6 +1189,7 @@
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -1169,6 +1210,7 @@
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -1189,6 +1231,7 @@
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
+      <c r="P10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1209,6 +1252,7 @@
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -1229,6 +1273,7 @@
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
+      <c r="P12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1249,6 +1294,7 @@
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -1269,6 +1315,7 @@
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
+      <c r="P14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1289,6 +1336,7 @@
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1309,6 +1357,7 @@
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1329,6 +1378,7 @@
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -1349,6 +1399,7 @@
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1369,6 +1420,7 @@
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1389,6 +1441,7 @@
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1409,6 +1462,7 @@
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1429,6 +1483,7 @@
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1449,6 +1504,7 @@
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
+      <c r="P23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1469,6 +1525,7 @@
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1489,6 +1546,7 @@
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
+      <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1509,6 +1567,7 @@
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
       <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1529,6 +1588,7 @@
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
+      <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1549,6 +1609,7 @@
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
+      <c r="P28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -1569,6 +1630,7 @@
       <c r="M29" s="10" t="n"/>
       <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
+      <c r="P29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1589,6 +1651,7 @@
       <c r="M30" s="14" t="n"/>
       <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
+      <c r="P30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1609,6 +1672,7 @@
       <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1629,6 +1693,7 @@
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
+      <c r="P32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -1649,6 +1714,7 @@
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
+      <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1669,6 +1735,7 @@
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -1689,6 +1756,7 @@
       <c r="M35" s="10" t="n"/>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1709,6 +1777,7 @@
       <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
+      <c r="P36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -1729,6 +1798,7 @@
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1749,6 +1819,7 @@
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -1769,6 +1840,7 @@
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -1789,6 +1861,7 @@
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
+      <c r="P40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -1809,6 +1882,7 @@
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -1829,6 +1903,7 @@
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
+      <c r="P42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -1849,6 +1924,7 @@
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
+      <c r="P43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -1869,6 +1945,7 @@
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="14" t="n"/>
       <c r="O44" s="14" t="n"/>
+      <c r="P44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -1889,6 +1966,7 @@
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -1909,6 +1987,7 @@
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
+      <c r="P46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -1929,6 +2008,7 @@
       <c r="M47" s="10" t="n"/>
       <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -1949,6 +2029,7 @@
       <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
+      <c r="P48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -1969,6 +2050,7 @@
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -1989,6 +2071,7 @@
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
+      <c r="P50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -2009,6 +2092,7 @@
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -2029,6 +2113,7 @@
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
+      <c r="P52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -2049,6 +2134,7 @@
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -2069,6 +2155,7 @@
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="14" t="n"/>
       <c r="O54" s="14" t="n"/>
+      <c r="P54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -2089,6 +2176,7 @@
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -2109,6 +2197,7 @@
       <c r="M56" s="14" t="n"/>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
+      <c r="P56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -2129,6 +2218,7 @@
       <c r="M57" s="10" t="n"/>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -2149,6 +2239,7 @@
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
+      <c r="P58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -2169,6 +2260,7 @@
       <c r="M59" s="10" t="n"/>
       <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -2189,6 +2281,7 @@
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
+      <c r="P60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -2209,6 +2302,7 @@
       <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -2229,6 +2323,7 @@
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
+      <c r="P62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -2249,6 +2344,7 @@
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -2269,6 +2365,7 @@
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
       <c r="O64" s="14" t="n"/>
+      <c r="P64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -2289,6 +2386,7 @@
       <c r="M65" s="10" t="n"/>
       <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -2309,6 +2407,7 @@
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
+      <c r="P66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -2329,6 +2428,7 @@
       <c r="M67" s="10" t="n"/>
       <c r="N67" s="10" t="n"/>
       <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -2349,6 +2449,7 @@
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
+      <c r="P68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -2369,6 +2470,7 @@
       <c r="M69" s="10" t="n"/>
       <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -2389,6 +2491,7 @@
       <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
+      <c r="P70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -2409,6 +2512,7 @@
       <c r="M71" s="10" t="n"/>
       <c r="N71" s="10" t="n"/>
       <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -2429,6 +2533,7 @@
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
       <c r="O72" s="14" t="n"/>
+      <c r="P72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -2449,6 +2554,7 @@
       <c r="M73" s="10" t="n"/>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -2469,6 +2575,7 @@
       <c r="M74" s="14" t="n"/>
       <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
+      <c r="P74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -2489,6 +2596,7 @@
       <c r="M75" s="10" t="n"/>
       <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -2509,6 +2617,7 @@
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -2529,6 +2638,7 @@
       <c r="M77" s="10" t="n"/>
       <c r="N77" s="10" t="n"/>
       <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -2549,6 +2659,7 @@
       <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -2569,6 +2680,7 @@
       <c r="M79" s="10" t="n"/>
       <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2589,6 +2701,7 @@
       <c r="M80" s="14" t="n"/>
       <c r="N80" s="14" t="n"/>
       <c r="O80" s="14" t="n"/>
+      <c r="P80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -2609,6 +2722,7 @@
       <c r="M81" s="10" t="n"/>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -2629,6 +2743,7 @@
       <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="n"/>
       <c r="O82" s="14" t="n"/>
+      <c r="P82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -2649,6 +2764,7 @@
       <c r="M83" s="10" t="n"/>
       <c r="N83" s="10" t="n"/>
       <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -2669,6 +2785,7 @@
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
+      <c r="P84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -2689,6 +2806,7 @@
       <c r="M85" s="10" t="n"/>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -2709,6 +2827,7 @@
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
       <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -2729,6 +2848,7 @@
       <c r="M87" s="10" t="n"/>
       <c r="N87" s="10" t="n"/>
       <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -2749,6 +2869,7 @@
       <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
       <c r="O88" s="14" t="n"/>
+      <c r="P88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -2769,6 +2890,7 @@
       <c r="M89" s="10" t="n"/>
       <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -2789,6 +2911,7 @@
       <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n"/>
+      <c r="P90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -2809,6 +2932,7 @@
       <c r="M91" s="10" t="n"/>
       <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -2829,6 +2953,7 @@
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
       <c r="O92" s="14" t="n"/>
+      <c r="P92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -2849,6 +2974,7 @@
       <c r="M93" s="10" t="n"/>
       <c r="N93" s="10" t="n"/>
       <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -2869,6 +2995,7 @@
       <c r="M94" s="14" t="n"/>
       <c r="N94" s="14" t="n"/>
       <c r="O94" s="14" t="n"/>
+      <c r="P94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -2889,6 +3016,7 @@
       <c r="M95" s="10" t="n"/>
       <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -2909,6 +3037,7 @@
       <c r="M96" s="14" t="n"/>
       <c r="N96" s="14" t="n"/>
       <c r="O96" s="14" t="n"/>
+      <c r="P96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -2929,6 +3058,7 @@
       <c r="M97" s="10" t="n"/>
       <c r="N97" s="10" t="n"/>
       <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -2949,6 +3079,7 @@
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
       <c r="O98" s="14" t="n"/>
+      <c r="P98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -2969,6 +3100,7 @@
       <c r="M99" s="10" t="n"/>
       <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -2989,6 +3121,7 @@
       <c r="M100" s="14" t="n"/>
       <c r="N100" s="14" t="n"/>
       <c r="O100" s="14" t="n"/>
+      <c r="P100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -3009,6 +3142,7 @@
       <c r="M101" s="10" t="n"/>
       <c r="N101" s="10" t="n"/>
       <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -3029,14 +3163,15 @@
       <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
       <c r="O102" s="14" t="n"/>
+      <c r="P102" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O2"/>
+  <autoFilter ref="A2:P2"/>
   <mergeCells count="4">
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="J1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="K3:K102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -3067,7 +3202,7 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N102">
+  <conditionalFormatting sqref="O3:O102">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"入院中"</formula>
     </cfRule>
@@ -3086,7 +3221,42 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <conditionalFormatting sqref="N3:N102">
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="1">
+      <formula>"CR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="1">
+      <formula>"CRi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="10">
+      <formula>"sCR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="11">
+      <formula>"VGPR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
+      <formula>"PR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="5">
+      <formula>"SD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="2">
+      <formula>"PD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="2">
+      <formula>"再発"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="9">
+      <formula>"死亡"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="12">
+      <formula>"評価前"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="12">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
@@ -3102,7 +3272,13 @@
     <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
     </dataValidation>
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
+    </dataValidation>
     <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"入院中,退院済,外来移行"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4744,10 +4920,10 @@
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="9">
       <formula>"要"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="10">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="12">
       <formula>"不要"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="11">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="13">
       <formula>"済"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4755,7 +4931,7 @@
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="9">
       <formula>"緊急"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="12">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="14">
       <formula>"通常"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4787,7 +4963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4801,9 +4977,10 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4836,7 +5013,8 @@
       </c>
       <c r="L1" s="32" t="n"/>
       <c r="M1" s="32" t="n"/>
-      <c r="N1" s="31" t="inlineStr">
+      <c r="N1" s="32" t="n"/>
+      <c r="O1" s="31" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
@@ -4900,15 +5078,20 @@
       </c>
       <c r="L2" s="33" t="inlineStr">
         <is>
-          <t>治療方針</t>
+          <t>治療レジメン</t>
         </is>
       </c>
       <c r="M2" s="33" t="inlineStr">
         <is>
+          <t>転帰</t>
+        </is>
+      </c>
+      <c r="N2" s="33" t="inlineStr">
+        <is>
           <t>次回予約日</t>
         </is>
       </c>
-      <c r="N2" s="33" t="inlineStr">
+      <c r="O2" s="33" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -4927,8 +5110,9 @@
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
       <c r="L3" s="10" t="n"/>
-      <c r="M3" s="11" t="n"/>
-      <c r="N3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="34" t="n"/>
@@ -4943,8 +5127,9 @@
       <c r="J4" s="37" t="n"/>
       <c r="K4" s="37" t="n"/>
       <c r="L4" s="37" t="n"/>
-      <c r="M4" s="36" t="n"/>
-      <c r="N4" s="37" t="n"/>
+      <c r="M4" s="37" t="n"/>
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="37" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -4959,8 +5144,9 @@
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="n"/>
-      <c r="M5" s="11" t="n"/>
-      <c r="N5" s="10" t="n"/>
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="34" t="n"/>
@@ -4975,8 +5161,9 @@
       <c r="J6" s="37" t="n"/>
       <c r="K6" s="37" t="n"/>
       <c r="L6" s="37" t="n"/>
-      <c r="M6" s="36" t="n"/>
-      <c r="N6" s="37" t="n"/>
+      <c r="M6" s="37" t="n"/>
+      <c r="N6" s="36" t="n"/>
+      <c r="O6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -4991,8 +5178,9 @@
       <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
-      <c r="M7" s="11" t="n"/>
-      <c r="N7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="34" t="n"/>
@@ -5007,8 +5195,9 @@
       <c r="J8" s="37" t="n"/>
       <c r="K8" s="37" t="n"/>
       <c r="L8" s="37" t="n"/>
-      <c r="M8" s="36" t="n"/>
-      <c r="N8" s="37" t="n"/>
+      <c r="M8" s="37" t="n"/>
+      <c r="N8" s="36" t="n"/>
+      <c r="O8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -5023,8 +5212,9 @@
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
-      <c r="M9" s="11" t="n"/>
-      <c r="N9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n"/>
@@ -5039,8 +5229,9 @@
       <c r="J10" s="37" t="n"/>
       <c r="K10" s="37" t="n"/>
       <c r="L10" s="37" t="n"/>
-      <c r="M10" s="36" t="n"/>
-      <c r="N10" s="37" t="n"/>
+      <c r="M10" s="37" t="n"/>
+      <c r="N10" s="36" t="n"/>
+      <c r="O10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -5055,8 +5246,9 @@
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="n"/>
       <c r="L11" s="10" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n"/>
@@ -5071,8 +5263,9 @@
       <c r="J12" s="37" t="n"/>
       <c r="K12" s="37" t="n"/>
       <c r="L12" s="37" t="n"/>
-      <c r="M12" s="36" t="n"/>
-      <c r="N12" s="37" t="n"/>
+      <c r="M12" s="37" t="n"/>
+      <c r="N12" s="36" t="n"/>
+      <c r="O12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -5087,8 +5280,9 @@
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n"/>
@@ -5103,8 +5297,9 @@
       <c r="J14" s="37" t="n"/>
       <c r="K14" s="37" t="n"/>
       <c r="L14" s="37" t="n"/>
-      <c r="M14" s="36" t="n"/>
-      <c r="N14" s="37" t="n"/>
+      <c r="M14" s="37" t="n"/>
+      <c r="N14" s="36" t="n"/>
+      <c r="O14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -5119,8 +5314,9 @@
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="34" t="n"/>
@@ -5135,8 +5331,9 @@
       <c r="J16" s="37" t="n"/>
       <c r="K16" s="37" t="n"/>
       <c r="L16" s="37" t="n"/>
-      <c r="M16" s="36" t="n"/>
-      <c r="N16" s="37" t="n"/>
+      <c r="M16" s="37" t="n"/>
+      <c r="N16" s="36" t="n"/>
+      <c r="O16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -5151,8 +5348,9 @@
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
-      <c r="M17" s="11" t="n"/>
-      <c r="N17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="34" t="n"/>
@@ -5167,8 +5365,9 @@
       <c r="J18" s="37" t="n"/>
       <c r="K18" s="37" t="n"/>
       <c r="L18" s="37" t="n"/>
-      <c r="M18" s="36" t="n"/>
-      <c r="N18" s="37" t="n"/>
+      <c r="M18" s="37" t="n"/>
+      <c r="N18" s="36" t="n"/>
+      <c r="O18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -5183,8 +5382,9 @@
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
-      <c r="M19" s="11" t="n"/>
-      <c r="N19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="34" t="n"/>
@@ -5199,8 +5399,9 @@
       <c r="J20" s="37" t="n"/>
       <c r="K20" s="37" t="n"/>
       <c r="L20" s="37" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="37" t="n"/>
+      <c r="M20" s="37" t="n"/>
+      <c r="N20" s="36" t="n"/>
+      <c r="O20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -5215,8 +5416,9 @@
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
-      <c r="M21" s="11" t="n"/>
-      <c r="N21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="34" t="n"/>
@@ -5231,8 +5433,9 @@
       <c r="J22" s="37" t="n"/>
       <c r="K22" s="37" t="n"/>
       <c r="L22" s="37" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="37" t="n"/>
+      <c r="M22" s="37" t="n"/>
+      <c r="N22" s="36" t="n"/>
+      <c r="O22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -5247,8 +5450,9 @@
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="10" t="n"/>
+      <c r="M23" s="10" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="34" t="n"/>
@@ -5263,8 +5467,9 @@
       <c r="J24" s="37" t="n"/>
       <c r="K24" s="37" t="n"/>
       <c r="L24" s="37" t="n"/>
-      <c r="M24" s="36" t="n"/>
-      <c r="N24" s="37" t="n"/>
+      <c r="M24" s="37" t="n"/>
+      <c r="N24" s="36" t="n"/>
+      <c r="O24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -5279,8 +5484,9 @@
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="n"/>
-      <c r="M25" s="11" t="n"/>
-      <c r="N25" s="10" t="n"/>
+      <c r="M25" s="10" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="34" t="n"/>
@@ -5295,8 +5501,9 @@
       <c r="J26" s="37" t="n"/>
       <c r="K26" s="37" t="n"/>
       <c r="L26" s="37" t="n"/>
-      <c r="M26" s="36" t="n"/>
-      <c r="N26" s="37" t="n"/>
+      <c r="M26" s="37" t="n"/>
+      <c r="N26" s="36" t="n"/>
+      <c r="O26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -5311,8 +5518,9 @@
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
-      <c r="M27" s="11" t="n"/>
-      <c r="N27" s="10" t="n"/>
+      <c r="M27" s="10" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="34" t="n"/>
@@ -5327,8 +5535,9 @@
       <c r="J28" s="37" t="n"/>
       <c r="K28" s="37" t="n"/>
       <c r="L28" s="37" t="n"/>
-      <c r="M28" s="36" t="n"/>
-      <c r="N28" s="37" t="n"/>
+      <c r="M28" s="37" t="n"/>
+      <c r="N28" s="36" t="n"/>
+      <c r="O28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -5343,8 +5552,9 @@
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="10" t="n"/>
       <c r="L29" s="10" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="10" t="n"/>
+      <c r="M29" s="10" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="34" t="n"/>
@@ -5359,8 +5569,9 @@
       <c r="J30" s="37" t="n"/>
       <c r="K30" s="37" t="n"/>
       <c r="L30" s="37" t="n"/>
-      <c r="M30" s="36" t="n"/>
-      <c r="N30" s="37" t="n"/>
+      <c r="M30" s="37" t="n"/>
+      <c r="N30" s="36" t="n"/>
+      <c r="O30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -5375,8 +5586,9 @@
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="10" t="n"/>
+      <c r="M31" s="10" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="34" t="n"/>
@@ -5391,8 +5603,9 @@
       <c r="J32" s="37" t="n"/>
       <c r="K32" s="37" t="n"/>
       <c r="L32" s="37" t="n"/>
-      <c r="M32" s="36" t="n"/>
-      <c r="N32" s="37" t="n"/>
+      <c r="M32" s="37" t="n"/>
+      <c r="N32" s="36" t="n"/>
+      <c r="O32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -5407,8 +5620,9 @@
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="10" t="n"/>
+      <c r="M33" s="10" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="34" t="n"/>
@@ -5423,8 +5637,9 @@
       <c r="J34" s="37" t="n"/>
       <c r="K34" s="37" t="n"/>
       <c r="L34" s="37" t="n"/>
-      <c r="M34" s="36" t="n"/>
-      <c r="N34" s="37" t="n"/>
+      <c r="M34" s="37" t="n"/>
+      <c r="N34" s="36" t="n"/>
+      <c r="O34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -5439,8 +5654,9 @@
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="10" t="n"/>
+      <c r="M35" s="10" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="34" t="n"/>
@@ -5455,8 +5671,9 @@
       <c r="J36" s="37" t="n"/>
       <c r="K36" s="37" t="n"/>
       <c r="L36" s="37" t="n"/>
-      <c r="M36" s="36" t="n"/>
-      <c r="N36" s="37" t="n"/>
+      <c r="M36" s="37" t="n"/>
+      <c r="N36" s="36" t="n"/>
+      <c r="O36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -5471,8 +5688,9 @@
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
-      <c r="M37" s="11" t="n"/>
-      <c r="N37" s="10" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="34" t="n"/>
@@ -5487,8 +5705,9 @@
       <c r="J38" s="37" t="n"/>
       <c r="K38" s="37" t="n"/>
       <c r="L38" s="37" t="n"/>
-      <c r="M38" s="36" t="n"/>
-      <c r="N38" s="37" t="n"/>
+      <c r="M38" s="37" t="n"/>
+      <c r="N38" s="36" t="n"/>
+      <c r="O38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -5503,8 +5722,9 @@
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
-      <c r="M39" s="11" t="n"/>
-      <c r="N39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="34" t="n"/>
@@ -5519,8 +5739,9 @@
       <c r="J40" s="37" t="n"/>
       <c r="K40" s="37" t="n"/>
       <c r="L40" s="37" t="n"/>
-      <c r="M40" s="36" t="n"/>
-      <c r="N40" s="37" t="n"/>
+      <c r="M40" s="37" t="n"/>
+      <c r="N40" s="36" t="n"/>
+      <c r="O40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -5535,8 +5756,9 @@
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
-      <c r="M41" s="11" t="n"/>
-      <c r="N41" s="10" t="n"/>
+      <c r="M41" s="10" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="O41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="34" t="n"/>
@@ -5551,8 +5773,9 @@
       <c r="J42" s="37" t="n"/>
       <c r="K42" s="37" t="n"/>
       <c r="L42" s="37" t="n"/>
-      <c r="M42" s="36" t="n"/>
-      <c r="N42" s="37" t="n"/>
+      <c r="M42" s="37" t="n"/>
+      <c r="N42" s="36" t="n"/>
+      <c r="O42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -5567,8 +5790,9 @@
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
-      <c r="M43" s="11" t="n"/>
-      <c r="N43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="11" t="n"/>
+      <c r="O43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="34" t="n"/>
@@ -5583,8 +5807,9 @@
       <c r="J44" s="37" t="n"/>
       <c r="K44" s="37" t="n"/>
       <c r="L44" s="37" t="n"/>
-      <c r="M44" s="36" t="n"/>
-      <c r="N44" s="37" t="n"/>
+      <c r="M44" s="37" t="n"/>
+      <c r="N44" s="36" t="n"/>
+      <c r="O44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -5599,8 +5824,9 @@
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="34" t="n"/>
@@ -5615,8 +5841,9 @@
       <c r="J46" s="37" t="n"/>
       <c r="K46" s="37" t="n"/>
       <c r="L46" s="37" t="n"/>
-      <c r="M46" s="36" t="n"/>
-      <c r="N46" s="37" t="n"/>
+      <c r="M46" s="37" t="n"/>
+      <c r="N46" s="36" t="n"/>
+      <c r="O46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -5631,8 +5858,9 @@
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="10" t="n"/>
+      <c r="M47" s="10" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="O47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="34" t="n"/>
@@ -5647,8 +5875,9 @@
       <c r="J48" s="37" t="n"/>
       <c r="K48" s="37" t="n"/>
       <c r="L48" s="37" t="n"/>
-      <c r="M48" s="36" t="n"/>
-      <c r="N48" s="37" t="n"/>
+      <c r="M48" s="37" t="n"/>
+      <c r="N48" s="36" t="n"/>
+      <c r="O48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -5663,8 +5892,9 @@
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
-      <c r="M49" s="11" t="n"/>
-      <c r="N49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="11" t="n"/>
+      <c r="O49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="34" t="n"/>
@@ -5679,8 +5909,9 @@
       <c r="J50" s="37" t="n"/>
       <c r="K50" s="37" t="n"/>
       <c r="L50" s="37" t="n"/>
-      <c r="M50" s="36" t="n"/>
-      <c r="N50" s="37" t="n"/>
+      <c r="M50" s="37" t="n"/>
+      <c r="N50" s="36" t="n"/>
+      <c r="O50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -5695,8 +5926,9 @@
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
-      <c r="M51" s="11" t="n"/>
-      <c r="N51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="34" t="n"/>
@@ -5711,8 +5943,9 @@
       <c r="J52" s="37" t="n"/>
       <c r="K52" s="37" t="n"/>
       <c r="L52" s="37" t="n"/>
-      <c r="M52" s="36" t="n"/>
-      <c r="N52" s="37" t="n"/>
+      <c r="M52" s="37" t="n"/>
+      <c r="N52" s="36" t="n"/>
+      <c r="O52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -5727,8 +5960,9 @@
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
-      <c r="M53" s="11" t="n"/>
-      <c r="N53" s="10" t="n"/>
+      <c r="M53" s="10" t="n"/>
+      <c r="N53" s="11" t="n"/>
+      <c r="O53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="34" t="n"/>
@@ -5743,8 +5977,9 @@
       <c r="J54" s="37" t="n"/>
       <c r="K54" s="37" t="n"/>
       <c r="L54" s="37" t="n"/>
-      <c r="M54" s="36" t="n"/>
-      <c r="N54" s="37" t="n"/>
+      <c r="M54" s="37" t="n"/>
+      <c r="N54" s="36" t="n"/>
+      <c r="O54" s="37" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -5759,8 +5994,9 @@
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
-      <c r="M55" s="11" t="n"/>
-      <c r="N55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="34" t="n"/>
@@ -5775,8 +6011,9 @@
       <c r="J56" s="37" t="n"/>
       <c r="K56" s="37" t="n"/>
       <c r="L56" s="37" t="n"/>
-      <c r="M56" s="36" t="n"/>
-      <c r="N56" s="37" t="n"/>
+      <c r="M56" s="37" t="n"/>
+      <c r="N56" s="36" t="n"/>
+      <c r="O56" s="37" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -5791,8 +6028,9 @@
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
-      <c r="M57" s="11" t="n"/>
-      <c r="N57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="11" t="n"/>
+      <c r="O57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="34" t="n"/>
@@ -5807,8 +6045,9 @@
       <c r="J58" s="37" t="n"/>
       <c r="K58" s="37" t="n"/>
       <c r="L58" s="37" t="n"/>
-      <c r="M58" s="36" t="n"/>
-      <c r="N58" s="37" t="n"/>
+      <c r="M58" s="37" t="n"/>
+      <c r="N58" s="36" t="n"/>
+      <c r="O58" s="37" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -5823,8 +6062,9 @@
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
-      <c r="M59" s="11" t="n"/>
-      <c r="N59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="11" t="n"/>
+      <c r="O59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="34" t="n"/>
@@ -5839,8 +6079,9 @@
       <c r="J60" s="37" t="n"/>
       <c r="K60" s="37" t="n"/>
       <c r="L60" s="37" t="n"/>
-      <c r="M60" s="36" t="n"/>
-      <c r="N60" s="37" t="n"/>
+      <c r="M60" s="37" t="n"/>
+      <c r="N60" s="36" t="n"/>
+      <c r="O60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -5855,8 +6096,9 @@
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="O61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="34" t="n"/>
@@ -5871,8 +6113,9 @@
       <c r="J62" s="37" t="n"/>
       <c r="K62" s="37" t="n"/>
       <c r="L62" s="37" t="n"/>
-      <c r="M62" s="36" t="n"/>
-      <c r="N62" s="37" t="n"/>
+      <c r="M62" s="37" t="n"/>
+      <c r="N62" s="36" t="n"/>
+      <c r="O62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -5887,8 +6130,9 @@
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="11" t="n"/>
+      <c r="O63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="34" t="n"/>
@@ -5903,8 +6147,9 @@
       <c r="J64" s="37" t="n"/>
       <c r="K64" s="37" t="n"/>
       <c r="L64" s="37" t="n"/>
-      <c r="M64" s="36" t="n"/>
-      <c r="N64" s="37" t="n"/>
+      <c r="M64" s="37" t="n"/>
+      <c r="N64" s="36" t="n"/>
+      <c r="O64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -5919,8 +6164,9 @@
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="O65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="34" t="n"/>
@@ -5935,8 +6181,9 @@
       <c r="J66" s="37" t="n"/>
       <c r="K66" s="37" t="n"/>
       <c r="L66" s="37" t="n"/>
-      <c r="M66" s="36" t="n"/>
-      <c r="N66" s="37" t="n"/>
+      <c r="M66" s="37" t="n"/>
+      <c r="N66" s="36" t="n"/>
+      <c r="O66" s="37" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -5951,8 +6198,9 @@
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="10" t="n"/>
-      <c r="M67" s="11" t="n"/>
-      <c r="N67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="11" t="n"/>
+      <c r="O67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="34" t="n"/>
@@ -5967,8 +6215,9 @@
       <c r="J68" s="37" t="n"/>
       <c r="K68" s="37" t="n"/>
       <c r="L68" s="37" t="n"/>
-      <c r="M68" s="36" t="n"/>
-      <c r="N68" s="37" t="n"/>
+      <c r="M68" s="37" t="n"/>
+      <c r="N68" s="36" t="n"/>
+      <c r="O68" s="37" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -5983,8 +6232,9 @@
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="10" t="n"/>
-      <c r="M69" s="11" t="n"/>
-      <c r="N69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="11" t="n"/>
+      <c r="O69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="34" t="n"/>
@@ -5999,8 +6249,9 @@
       <c r="J70" s="37" t="n"/>
       <c r="K70" s="37" t="n"/>
       <c r="L70" s="37" t="n"/>
-      <c r="M70" s="36" t="n"/>
-      <c r="N70" s="37" t="n"/>
+      <c r="M70" s="37" t="n"/>
+      <c r="N70" s="36" t="n"/>
+      <c r="O70" s="37" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -6015,8 +6266,9 @@
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
-      <c r="M71" s="11" t="n"/>
-      <c r="N71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="11" t="n"/>
+      <c r="O71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="34" t="n"/>
@@ -6031,8 +6283,9 @@
       <c r="J72" s="37" t="n"/>
       <c r="K72" s="37" t="n"/>
       <c r="L72" s="37" t="n"/>
-      <c r="M72" s="36" t="n"/>
-      <c r="N72" s="37" t="n"/>
+      <c r="M72" s="37" t="n"/>
+      <c r="N72" s="36" t="n"/>
+      <c r="O72" s="37" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -6047,8 +6300,9 @@
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
-      <c r="M73" s="11" t="n"/>
-      <c r="N73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="11" t="n"/>
+      <c r="O73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="34" t="n"/>
@@ -6063,8 +6317,9 @@
       <c r="J74" s="37" t="n"/>
       <c r="K74" s="37" t="n"/>
       <c r="L74" s="37" t="n"/>
-      <c r="M74" s="36" t="n"/>
-      <c r="N74" s="37" t="n"/>
+      <c r="M74" s="37" t="n"/>
+      <c r="N74" s="36" t="n"/>
+      <c r="O74" s="37" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -6079,8 +6334,9 @@
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
-      <c r="M75" s="11" t="n"/>
-      <c r="N75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="34" t="n"/>
@@ -6095,8 +6351,9 @@
       <c r="J76" s="37" t="n"/>
       <c r="K76" s="37" t="n"/>
       <c r="L76" s="37" t="n"/>
-      <c r="M76" s="36" t="n"/>
-      <c r="N76" s="37" t="n"/>
+      <c r="M76" s="37" t="n"/>
+      <c r="N76" s="36" t="n"/>
+      <c r="O76" s="37" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -6111,8 +6368,9 @@
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="O77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="34" t="n"/>
@@ -6127,8 +6385,9 @@
       <c r="J78" s="37" t="n"/>
       <c r="K78" s="37" t="n"/>
       <c r="L78" s="37" t="n"/>
-      <c r="M78" s="36" t="n"/>
-      <c r="N78" s="37" t="n"/>
+      <c r="M78" s="37" t="n"/>
+      <c r="N78" s="36" t="n"/>
+      <c r="O78" s="37" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -6143,8 +6402,9 @@
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="11" t="n"/>
+      <c r="O79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="34" t="n"/>
@@ -6159,8 +6419,9 @@
       <c r="J80" s="37" t="n"/>
       <c r="K80" s="37" t="n"/>
       <c r="L80" s="37" t="n"/>
-      <c r="M80" s="36" t="n"/>
-      <c r="N80" s="37" t="n"/>
+      <c r="M80" s="37" t="n"/>
+      <c r="N80" s="36" t="n"/>
+      <c r="O80" s="37" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -6175,8 +6436,9 @@
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="11" t="n"/>
+      <c r="O81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="34" t="n"/>
@@ -6191,8 +6453,9 @@
       <c r="J82" s="37" t="n"/>
       <c r="K82" s="37" t="n"/>
       <c r="L82" s="37" t="n"/>
-      <c r="M82" s="36" t="n"/>
-      <c r="N82" s="37" t="n"/>
+      <c r="M82" s="37" t="n"/>
+      <c r="N82" s="36" t="n"/>
+      <c r="O82" s="37" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -6207,8 +6470,9 @@
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="11" t="n"/>
+      <c r="O83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="34" t="n"/>
@@ -6223,8 +6487,9 @@
       <c r="J84" s="37" t="n"/>
       <c r="K84" s="37" t="n"/>
       <c r="L84" s="37" t="n"/>
-      <c r="M84" s="36" t="n"/>
-      <c r="N84" s="37" t="n"/>
+      <c r="M84" s="37" t="n"/>
+      <c r="N84" s="36" t="n"/>
+      <c r="O84" s="37" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -6239,8 +6504,9 @@
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
-      <c r="M85" s="11" t="n"/>
-      <c r="N85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="11" t="n"/>
+      <c r="O85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="34" t="n"/>
@@ -6255,8 +6521,9 @@
       <c r="J86" s="37" t="n"/>
       <c r="K86" s="37" t="n"/>
       <c r="L86" s="37" t="n"/>
-      <c r="M86" s="36" t="n"/>
-      <c r="N86" s="37" t="n"/>
+      <c r="M86" s="37" t="n"/>
+      <c r="N86" s="36" t="n"/>
+      <c r="O86" s="37" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -6271,8 +6538,9 @@
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="10" t="n"/>
-      <c r="M87" s="11" t="n"/>
-      <c r="N87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="11" t="n"/>
+      <c r="O87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="34" t="n"/>
@@ -6287,8 +6555,9 @@
       <c r="J88" s="37" t="n"/>
       <c r="K88" s="37" t="n"/>
       <c r="L88" s="37" t="n"/>
-      <c r="M88" s="36" t="n"/>
-      <c r="N88" s="37" t="n"/>
+      <c r="M88" s="37" t="n"/>
+      <c r="N88" s="36" t="n"/>
+      <c r="O88" s="37" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -6303,8 +6572,9 @@
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="10" t="n"/>
-      <c r="M89" s="11" t="n"/>
-      <c r="N89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="11" t="n"/>
+      <c r="O89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="34" t="n"/>
@@ -6319,8 +6589,9 @@
       <c r="J90" s="37" t="n"/>
       <c r="K90" s="37" t="n"/>
       <c r="L90" s="37" t="n"/>
-      <c r="M90" s="36" t="n"/>
-      <c r="N90" s="37" t="n"/>
+      <c r="M90" s="37" t="n"/>
+      <c r="N90" s="36" t="n"/>
+      <c r="O90" s="37" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -6335,8 +6606,9 @@
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="10" t="n"/>
-      <c r="M91" s="11" t="n"/>
-      <c r="N91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="O91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="34" t="n"/>
@@ -6351,8 +6623,9 @@
       <c r="J92" s="37" t="n"/>
       <c r="K92" s="37" t="n"/>
       <c r="L92" s="37" t="n"/>
-      <c r="M92" s="36" t="n"/>
-      <c r="N92" s="37" t="n"/>
+      <c r="M92" s="37" t="n"/>
+      <c r="N92" s="36" t="n"/>
+      <c r="O92" s="37" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -6367,8 +6640,9 @@
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="10" t="n"/>
-      <c r="M93" s="11" t="n"/>
-      <c r="N93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="11" t="n"/>
+      <c r="O93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="34" t="n"/>
@@ -6383,8 +6657,9 @@
       <c r="J94" s="37" t="n"/>
       <c r="K94" s="37" t="n"/>
       <c r="L94" s="37" t="n"/>
-      <c r="M94" s="36" t="n"/>
-      <c r="N94" s="37" t="n"/>
+      <c r="M94" s="37" t="n"/>
+      <c r="N94" s="36" t="n"/>
+      <c r="O94" s="37" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -6399,8 +6674,9 @@
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
-      <c r="M95" s="11" t="n"/>
-      <c r="N95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="11" t="n"/>
+      <c r="O95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="34" t="n"/>
@@ -6415,8 +6691,9 @@
       <c r="J96" s="37" t="n"/>
       <c r="K96" s="37" t="n"/>
       <c r="L96" s="37" t="n"/>
-      <c r="M96" s="36" t="n"/>
-      <c r="N96" s="37" t="n"/>
+      <c r="M96" s="37" t="n"/>
+      <c r="N96" s="36" t="n"/>
+      <c r="O96" s="37" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -6431,8 +6708,9 @@
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="n"/>
       <c r="L97" s="10" t="n"/>
-      <c r="M97" s="11" t="n"/>
-      <c r="N97" s="10" t="n"/>
+      <c r="M97" s="10" t="n"/>
+      <c r="N97" s="11" t="n"/>
+      <c r="O97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="34" t="n"/>
@@ -6447,8 +6725,9 @@
       <c r="J98" s="37" t="n"/>
       <c r="K98" s="37" t="n"/>
       <c r="L98" s="37" t="n"/>
-      <c r="M98" s="36" t="n"/>
-      <c r="N98" s="37" t="n"/>
+      <c r="M98" s="37" t="n"/>
+      <c r="N98" s="36" t="n"/>
+      <c r="O98" s="37" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -6463,8 +6742,9 @@
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
-      <c r="M99" s="11" t="n"/>
-      <c r="N99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="11" t="n"/>
+      <c r="O99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="34" t="n"/>
@@ -6479,8 +6759,9 @@
       <c r="J100" s="37" t="n"/>
       <c r="K100" s="37" t="n"/>
       <c r="L100" s="37" t="n"/>
-      <c r="M100" s="36" t="n"/>
-      <c r="N100" s="37" t="n"/>
+      <c r="M100" s="37" t="n"/>
+      <c r="N100" s="36" t="n"/>
+      <c r="O100" s="37" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -6495,8 +6776,9 @@
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="n"/>
       <c r="L101" s="10" t="n"/>
-      <c r="M101" s="11" t="n"/>
-      <c r="N101" s="10" t="n"/>
+      <c r="M101" s="10" t="n"/>
+      <c r="N101" s="11" t="n"/>
+      <c r="O101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="34" t="n"/>
@@ -6511,16 +6793,17 @@
       <c r="J102" s="37" t="n"/>
       <c r="K102" s="37" t="n"/>
       <c r="L102" s="37" t="n"/>
-      <c r="M102" s="36" t="n"/>
-      <c r="N102" s="37" t="n"/>
+      <c r="M102" s="37" t="n"/>
+      <c r="N102" s="36" t="n"/>
+      <c r="O102" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N2"/>
+  <autoFilter ref="A2:O2"/>
   <mergeCells count="4">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="K1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="K3:K102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -6559,7 +6842,42 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <conditionalFormatting sqref="M3:M102">
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+      <formula>"CR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="1">
+      <formula>"CRi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="10">
+      <formula>"sCR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="11">
+      <formula>"VGPR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+      <formula>"PR"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="5">
+      <formula>"SD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+      <formula>"PD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" dxfId="2">
+      <formula>"再発"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" dxfId="9">
+      <formula>"死亡"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="12">
+      <formula>"評価前"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="12">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
@@ -6575,6 +6893,12 @@
     <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
     </dataValidation>
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6587,7 +6911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I66"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6685,7 +7009,7 @@
         </is>
       </c>
       <c r="I6" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"入院中")</f>
+        <f>COUNTIF('入院患者'!O3:O102,"入院中")</f>
         <v/>
       </c>
     </row>
@@ -6714,7 +7038,7 @@
         </is>
       </c>
       <c r="I7" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"退院済")</f>
+        <f>COUNTIF('入院患者'!O3:O102,"退院済")</f>
         <v/>
       </c>
     </row>
@@ -6743,7 +7067,7 @@
         </is>
       </c>
       <c r="I8" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"外来移行")</f>
+        <f>COUNTIF('入院患者'!O3:O102,"外来移行")</f>
         <v/>
       </c>
     </row>
@@ -7108,19 +7432,19 @@
     <row r="36">
       <c r="B36" s="39" t="inlineStr">
         <is>
-          <t>他科コンサルト - 疾患別</t>
+          <t>入院患者 - 転帰別</t>
         </is>
       </c>
       <c r="C36" s="40" t="n"/>
       <c r="E36" s="39" t="inlineStr">
         <is>
-          <t>他科コンサルト - 緊急度別</t>
+          <t>他科コンサルト - 疾患別</t>
         </is>
       </c>
       <c r="F36" s="40" t="n"/>
       <c r="H36" s="39" t="inlineStr">
         <is>
-          <t>初診外来 - 疾患別</t>
+          <t>他科コンサルト - 緊急度別</t>
         </is>
       </c>
       <c r="I36" s="40" t="n"/>
@@ -7160,613 +7484,925 @@
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="C38" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"CR")</f>
+        <v/>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
           <t>AML</t>
         </is>
       </c>
-      <c r="C38" s="42">
+      <c r="F38" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"AML")</f>
         <v/>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>緊急</t>
         </is>
       </c>
-      <c r="F38" s="42">
+      <c r="I38" s="42">
         <f>COUNTIF('他科コンサルト'!E3:E102,"緊急")</f>
-        <v/>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>AML</t>
-        </is>
-      </c>
-      <c r="I38" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"AML")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="14" t="inlineStr">
         <is>
+          <t>CRi</t>
+        </is>
+      </c>
+      <c r="C39" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"CRi")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C39" s="43">
+      <c r="F39" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"ALL")</f>
         <v/>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="F39" s="43">
+      <c r="I39" s="43">
         <f>COUNTIF('他科コンサルト'!E3:E102,"通常")</f>
-        <v/>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="I39" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"ALL")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="10" t="inlineStr">
         <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C40" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"PR")</f>
+        <v/>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
           <t>CML</t>
         </is>
       </c>
-      <c r="C40" s="42">
+      <c r="F40" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CML")</f>
         <v/>
       </c>
-      <c r="E40" s="44" t="inlineStr">
+      <c r="H40" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="F40" s="45">
+      <c r="I40" s="45">
         <f>COUNTA('他科コンサルト'!A3:A102)</f>
-        <v/>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>CML</t>
-        </is>
-      </c>
-      <c r="I40" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"CML")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="14" t="inlineStr">
         <is>
+          <t>VGPR</t>
+        </is>
+      </c>
+      <c r="C41" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"VGPR")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
           <t>CLL</t>
         </is>
       </c>
-      <c r="C41" s="43">
+      <c r="F41" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CLL")</f>
-        <v/>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>CLL</t>
-        </is>
-      </c>
-      <c r="I41" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"CLL")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="10" t="inlineStr">
         <is>
+          <t>sCR</t>
+        </is>
+      </c>
+      <c r="C42" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"sCR")</f>
+        <v/>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
           <t>MDS</t>
         </is>
       </c>
-      <c r="C42" s="42">
+      <c r="F42" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MDS")</f>
-        <v/>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>MDS</t>
-        </is>
-      </c>
-      <c r="I42" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"MDS")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="14" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="C43" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"SD")</f>
+        <v/>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
           <t>MPN</t>
         </is>
       </c>
-      <c r="C43" s="43">
+      <c r="F43" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MPN")</f>
-        <v/>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>MPN</t>
-        </is>
-      </c>
-      <c r="I43" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MPN")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="10" t="inlineStr">
         <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="C44" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"PD")</f>
+        <v/>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
           <t>CMML</t>
         </is>
       </c>
-      <c r="C44" s="42">
+      <c r="F44" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CMML")</f>
-        <v/>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>CMML</t>
-        </is>
-      </c>
-      <c r="I44" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"CMML")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="14" t="inlineStr">
         <is>
+          <t>再発</t>
+        </is>
+      </c>
+      <c r="C45" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"再発")</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
           <t>DLBCL</t>
         </is>
       </c>
-      <c r="C45" s="43">
+      <c r="F45" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"DLBCL")</f>
-        <v/>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>DLBCL</t>
-        </is>
-      </c>
-      <c r="I45" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"DLBCL")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="10" t="inlineStr">
         <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="C46" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"死亡")</f>
+        <v/>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="C46" s="42">
+      <c r="F46" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"FL")</f>
-        <v/>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="I46" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"FL")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="14" t="inlineStr">
         <is>
+          <t>評価前</t>
+        </is>
+      </c>
+      <c r="C47" s="43">
+        <f>COUNTIF('入院患者'!N3:N102,"評価前")</f>
+        <v/>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
           <t>MCL</t>
         </is>
       </c>
-      <c r="C47" s="43">
+      <c r="F47" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MCL")</f>
-        <v/>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>MCL</t>
-        </is>
-      </c>
-      <c r="I47" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MCL")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="42">
+        <f>COUNTIF('入院患者'!N3:N102,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="C48" s="42">
+      <c r="F48" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"BL")</f>
         <v/>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="B49" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C49" s="45">
+        <f>COUNTA('入院患者'!A3:A102)</f>
+        <v/>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
+      <c r="F49" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MALT")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>ATLL</t>
+        </is>
+      </c>
+      <c r="F50" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"ATLL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>PTCL</t>
+        </is>
+      </c>
+      <c r="F51" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"PTCL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>AITL</t>
+        </is>
+      </c>
+      <c r="F52" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AITL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>NK/T</t>
+        </is>
+      </c>
+      <c r="F53" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"NK/T")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="F54" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="F55" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"MM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="F56" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"WM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>AL amyloidosis</t>
+        </is>
+      </c>
+      <c r="F57" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AL amyloidosis")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F58" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"AA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>PNH</t>
+        </is>
+      </c>
+      <c r="F59" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"PNH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="F60" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"ITP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>TTP</t>
+        </is>
+      </c>
+      <c r="F61" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"TTP")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="F62" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HUS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="F63" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"DIC")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>HLH</t>
+        </is>
+      </c>
+      <c r="F64" s="42">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"HLH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="F65" s="43">
+        <f>COUNTIF('他科コンサルト'!J3:J102,"その他")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F66" s="45">
+        <f>COUNTA('他科コンサルト'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="39" t="inlineStr">
+        <is>
+          <t>初診外来 - 疾患別</t>
+        </is>
+      </c>
+      <c r="C68" s="40" t="n"/>
+      <c r="E68" s="39" t="inlineStr">
+        <is>
+          <t>初診外来 - 転帰別</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E69" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="F69" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="C70" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"AML")</f>
+        <v/>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="F70" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"CR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C71" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"ALL")</f>
+        <v/>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>CRi</t>
+        </is>
+      </c>
+      <c r="F71" s="43">
+        <f>COUNTIF('初診外来'!M3:M102,"CRi")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="C72" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"CML")</f>
+        <v/>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F72" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"PR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>CLL</t>
+        </is>
+      </c>
+      <c r="C73" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"CLL")</f>
+        <v/>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>VGPR</t>
+        </is>
+      </c>
+      <c r="F73" s="43">
+        <f>COUNTIF('初診外来'!M3:M102,"VGPR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="C74" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"MDS")</f>
+        <v/>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>sCR</t>
+        </is>
+      </c>
+      <c r="F74" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"sCR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="C75" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MPN")</f>
+        <v/>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="F75" s="43">
+        <f>COUNTIF('初診外来'!M3:M102,"SD")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>CMML</t>
+        </is>
+      </c>
+      <c r="C76" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"CMML")</f>
+        <v/>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="F76" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"PD")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>DLBCL</t>
+        </is>
+      </c>
+      <c r="C77" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"DLBCL")</f>
+        <v/>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>再発</t>
+        </is>
+      </c>
+      <c r="F77" s="43">
+        <f>COUNTIF('初診外来'!M3:M102,"再発")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="C78" s="42">
+        <f>COUNTIF('初診外来'!H3:H102,"FL")</f>
+        <v/>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="F78" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"死亡")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="C79" s="43">
+        <f>COUNTIF('初診外来'!H3:H102,"MCL")</f>
+        <v/>
+      </c>
+      <c r="E79" s="14" t="inlineStr">
+        <is>
+          <t>評価前</t>
+        </is>
+      </c>
+      <c r="F79" s="43">
+        <f>COUNTIF('初診外来'!M3:M102,"評価前")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="I48" s="42">
+      <c r="C80" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"BL")</f>
         <v/>
       </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="14" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F80" s="42">
+        <f>COUNTIF('初診外来'!M3:M102,"N/A")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>MALT</t>
         </is>
       </c>
-      <c r="C49" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MALT")</f>
-        <v/>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>MALT</t>
-        </is>
-      </c>
-      <c r="I49" s="43">
+      <c r="C81" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MALT")</f>
         <v/>
       </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="10" t="inlineStr">
+      <c r="E81" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F81" s="45">
+        <f>COUNTA('初診外来'!A3:A102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>ATLL</t>
         </is>
       </c>
-      <c r="C50" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"ATLL")</f>
-        <v/>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>ATLL</t>
-        </is>
-      </c>
-      <c r="I50" s="42">
+      <c r="C82" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"ATLL")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="14" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>PTCL</t>
         </is>
       </c>
-      <c r="C51" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"PTCL")</f>
-        <v/>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>PTCL</t>
-        </is>
-      </c>
-      <c r="I51" s="43">
+      <c r="C83" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"PTCL")</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="10" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>AITL</t>
         </is>
       </c>
-      <c r="C52" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AITL")</f>
-        <v/>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>AITL</t>
-        </is>
-      </c>
-      <c r="I52" s="42">
+      <c r="C84" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"AITL")</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="14" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>NK/T</t>
         </is>
       </c>
-      <c r="C53" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"NK/T")</f>
-        <v/>
-      </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>NK/T</t>
-        </is>
-      </c>
-      <c r="I53" s="43">
+      <c r="C85" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"NK/T")</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="10" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>HL</t>
         </is>
       </c>
-      <c r="C54" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HL")</f>
-        <v/>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="I54" s="42">
+      <c r="C86" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HL")</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="14" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="C55" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MM")</f>
-        <v/>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>MM</t>
-        </is>
-      </c>
-      <c r="I55" s="43">
+      <c r="C87" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MM")</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="10" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>WM</t>
         </is>
       </c>
-      <c r="C56" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"WM")</f>
-        <v/>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>WM</t>
-        </is>
-      </c>
-      <c r="I56" s="42">
+      <c r="C88" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"WM")</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="14" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>AL amyloidosis</t>
         </is>
       </c>
-      <c r="C57" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AL amyloidosis")</f>
-        <v/>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>AL amyloidosis</t>
-        </is>
-      </c>
-      <c r="I57" s="43">
+      <c r="C89" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="10" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="C58" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AA")</f>
-        <v/>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="I58" s="42">
+      <c r="C90" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"AA")</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="14" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>PNH</t>
         </is>
       </c>
-      <c r="C59" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"PNH")</f>
-        <v/>
-      </c>
-      <c r="H59" s="14" t="inlineStr">
-        <is>
-          <t>PNH</t>
-        </is>
-      </c>
-      <c r="I59" s="43">
+      <c r="C91" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"PNH")</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="10" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>ITP</t>
         </is>
       </c>
-      <c r="C60" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"ITP")</f>
-        <v/>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>ITP</t>
-        </is>
-      </c>
-      <c r="I60" s="42">
+      <c r="C92" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"ITP")</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="14" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>TTP</t>
         </is>
       </c>
-      <c r="C61" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"TTP")</f>
-        <v/>
-      </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>TTP</t>
-        </is>
-      </c>
-      <c r="I61" s="43">
+      <c r="C93" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"TTP")</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="10" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>HUS</t>
         </is>
       </c>
-      <c r="C62" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HUS")</f>
-        <v/>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>HUS</t>
-        </is>
-      </c>
-      <c r="I62" s="42">
+      <c r="C94" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HUS")</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="14" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="C63" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"DIC")</f>
-        <v/>
-      </c>
-      <c r="H63" s="14" t="inlineStr">
-        <is>
-          <t>DIC</t>
-        </is>
-      </c>
-      <c r="I63" s="43">
+      <c r="C95" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"DIC")</f>
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="10" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>HLH</t>
         </is>
       </c>
-      <c r="C64" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HLH")</f>
-        <v/>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>HLH</t>
-        </is>
-      </c>
-      <c r="I64" s="42">
+      <c r="C96" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HLH")</f>
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="14" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="C65" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"その他")</f>
-        <v/>
-      </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="I65" s="43">
+      <c r="C97" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"その他")</f>
         <v/>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="44" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C66" s="45">
-        <f>COUNTA('他科コンサルト'!A3:A102)</f>
-        <v/>
-      </c>
-      <c r="H66" s="44" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="I66" s="45">
+      <c r="C98" s="45">
         <f>COUNTA('初診外来'!A3:A102)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="E36:F36"/>
     <mergeCell ref="H4:I4"/>

--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -13,9 +13,12 @@
     <sheet name="サマリー" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$S$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'入院患者'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$O$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'他科コンサルト'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$R$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'初診外来'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -926,9 +929,9 @@
   <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:S102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -937,16 +940,19 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -967,21 +973,24 @@
       <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
       <c r="I1" s="4" t="n"/>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>治療</t>
         </is>
       </c>
-      <c r="K1" s="6" t="n"/>
-      <c r="L1" s="6" t="n"/>
-      <c r="M1" s="6" t="n"/>
       <c r="N1" s="6" t="n"/>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="6" t="n"/>
+      <c r="P1" s="6" t="n"/>
+      <c r="Q1" s="6" t="n"/>
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="P1" s="6" t="n"/>
+      <c r="S1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1016,50 +1025,65 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
+          <t>染色体</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>遺伝子</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>リスク分類</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
           <t>入院日</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>退院日</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>在院日数</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>治療区分</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>治療レジメン</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>サイクル数</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>転帰</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="R2" s="7" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1072,19 +1096,22 @@
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="9">
-        <f>IF(AND(G3&lt;&gt;"",H3&lt;&gt;""),H3-G3,"")</f>
-        <v/>
-      </c>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="9">
+        <f>IF(AND(J3&lt;&gt;"",K3&lt;&gt;""),K3-J3,"")</f>
+        <v/>
+      </c>
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
       <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -1093,19 +1120,22 @@
       <c r="D4" s="13" t="n"/>
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="14" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="13">
-        <f>IF(AND(G4&lt;&gt;"",H4&lt;&gt;""),H4-G4,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="13">
+        <f>IF(AND(J4&lt;&gt;"",K4&lt;&gt;""),K4-J4,"")</f>
+        <v/>
+      </c>
       <c r="M4" s="14" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
       <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -1114,19 +1144,22 @@
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="9">
-        <f>IF(AND(G5&lt;&gt;"",H5&lt;&gt;""),H5-G5,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="9">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;""),K5-J5,"")</f>
+        <v/>
+      </c>
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -1135,19 +1168,22 @@
       <c r="D6" s="13" t="n"/>
       <c r="E6" s="14" t="n"/>
       <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13">
-        <f>IF(AND(G6&lt;&gt;"",H6&lt;&gt;""),H6-G6,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="13">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;""),K6-J6,"")</f>
+        <v/>
+      </c>
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
       <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -1156,19 +1192,22 @@
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="9">
-        <f>IF(AND(G7&lt;&gt;"",H7&lt;&gt;""),H7-G7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="9">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;""),K7-J7,"")</f>
+        <v/>
+      </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -1177,19 +1216,22 @@
       <c r="D8" s="13" t="n"/>
       <c r="E8" s="14" t="n"/>
       <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="13">
-        <f>IF(AND(G8&lt;&gt;"",H8&lt;&gt;""),H8-G8,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="13">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;""),K8-J8,"")</f>
+        <v/>
+      </c>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
       <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
+      <c r="R8" s="14" t="n"/>
+      <c r="S8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -1198,19 +1240,22 @@
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="9">
-        <f>IF(AND(G9&lt;&gt;"",H9&lt;&gt;""),H9-G9,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="9">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;""),K9-J9,"")</f>
+        <v/>
+      </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -1219,19 +1264,22 @@
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="13">
-        <f>IF(AND(G10&lt;&gt;"",H10&lt;&gt;""),H10-G10,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="13">
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;""),K10-J10,"")</f>
+        <v/>
+      </c>
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
       <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14" t="n"/>
+      <c r="R10" s="14" t="n"/>
+      <c r="S10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1240,19 +1288,22 @@
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="9">
-        <f>IF(AND(G11&lt;&gt;"",H11&lt;&gt;""),H11-G11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="9">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;""),K11-J11,"")</f>
+        <v/>
+      </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
       <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -1261,19 +1312,22 @@
       <c r="D12" s="13" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="13">
-        <f>IF(AND(G12&lt;&gt;"",H12&lt;&gt;""),H12-G12,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="13">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;""),K12-J12,"")</f>
+        <v/>
+      </c>
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
       <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="14" t="n"/>
+      <c r="S12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1282,19 +1336,22 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="9">
-        <f>IF(AND(G13&lt;&gt;"",H13&lt;&gt;""),H13-G13,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="9">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;""),K13-J13,"")</f>
+        <v/>
+      </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -1303,19 +1360,22 @@
       <c r="D14" s="13" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13">
-        <f>IF(AND(G14&lt;&gt;"",H14&lt;&gt;""),H14-G14,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="13">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;""),K14-J14,"")</f>
+        <v/>
+      </c>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
       <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1324,19 +1384,22 @@
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="9">
-        <f>IF(AND(G15&lt;&gt;"",H15&lt;&gt;""),H15-G15,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="9">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;""),K15-J15,"")</f>
+        <v/>
+      </c>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1345,19 +1408,22 @@
       <c r="D16" s="13" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="13">
-        <f>IF(AND(G16&lt;&gt;"",H16&lt;&gt;""),H16-G16,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="13">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;""),K16-J16,"")</f>
+        <v/>
+      </c>
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
       <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1366,19 +1432,22 @@
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n"/>
-      <c r="I17" s="9">
-        <f>IF(AND(G17&lt;&gt;"",H17&lt;&gt;""),H17-G17,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="9">
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;""),K17-J17,"")</f>
+        <v/>
+      </c>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
       <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -1387,19 +1456,22 @@
       <c r="D18" s="13" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="13">
-        <f>IF(AND(G18&lt;&gt;"",H18&lt;&gt;""),H18-G18,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="13">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;""),K18-J18,"")</f>
+        <v/>
+      </c>
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
       <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1408,19 +1480,22 @@
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="9">
-        <f>IF(AND(G19&lt;&gt;"",H19&lt;&gt;""),H19-G19,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="9">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;""),K19-J19,"")</f>
+        <v/>
+      </c>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1429,19 +1504,22 @@
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13">
-        <f>IF(AND(G20&lt;&gt;"",H20&lt;&gt;""),H20-G20,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="14" t="n"/>
-      <c r="L20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="13">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;""),K20-J20,"")</f>
+        <v/>
+      </c>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
       <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1450,19 +1528,22 @@
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="9">
-        <f>IF(AND(G21&lt;&gt;"",H21&lt;&gt;""),H21-G21,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="9">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;""),K21-J21,"")</f>
+        <v/>
+      </c>
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1471,19 +1552,22 @@
       <c r="D22" s="13" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="13">
-        <f>IF(AND(G22&lt;&gt;"",H22&lt;&gt;""),H22-G22,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="14" t="n"/>
-      <c r="L22" s="14" t="n"/>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="13">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;""),K22-J22,"")</f>
+        <v/>
+      </c>
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
       <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1492,19 +1576,22 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="9">
-        <f>IF(AND(G23&lt;&gt;"",H23&lt;&gt;""),H23-G23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="9">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;""),K23-J23,"")</f>
+        <v/>
+      </c>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1513,19 +1600,22 @@
       <c r="D24" s="13" t="n"/>
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13">
-        <f>IF(AND(G24&lt;&gt;"",H24&lt;&gt;""),H24-G24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14" t="n"/>
-      <c r="L24" s="14" t="n"/>
+      <c r="G24" s="14" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="13">
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;""),K24-J24,"")</f>
+        <v/>
+      </c>
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
       <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="14" t="n"/>
+      <c r="S24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1534,19 +1624,22 @@
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="9">
-        <f>IF(AND(G25&lt;&gt;"",H25&lt;&gt;""),H25-G25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="9">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;""),K25-J25,"")</f>
+        <v/>
+      </c>
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1555,19 +1648,22 @@
       <c r="D26" s="13" t="n"/>
       <c r="E26" s="14" t="n"/>
       <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="13">
-        <f>IF(AND(G26&lt;&gt;"",H26&lt;&gt;""),H26-G26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="14" t="n"/>
-      <c r="K26" s="14" t="n"/>
-      <c r="L26" s="14" t="n"/>
+      <c r="G26" s="14" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="15" t="n"/>
+      <c r="L26" s="13">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;""),K26-J26,"")</f>
+        <v/>
+      </c>
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
       <c r="O26" s="14" t="n"/>
       <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="14" t="n"/>
+      <c r="S26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1576,19 +1672,22 @@
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="9">
-        <f>IF(AND(G27&lt;&gt;"",H27&lt;&gt;""),H27-G27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="9">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;""),K27-J27,"")</f>
+        <v/>
+      </c>
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1597,19 +1696,22 @@
       <c r="D28" s="13" t="n"/>
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13">
-        <f>IF(AND(G28&lt;&gt;"",H28&lt;&gt;""),H28-G28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="15" t="n"/>
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="13">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;""),K28-J28,"")</f>
+        <v/>
+      </c>
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
       <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="14" t="n"/>
+      <c r="S28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -1618,19 +1720,22 @@
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="9">
-        <f>IF(AND(G29&lt;&gt;"",H29&lt;&gt;""),H29-G29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="9">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;""),K29-J29,"")</f>
+        <v/>
+      </c>
       <c r="M29" s="10" t="n"/>
       <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
       <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1639,19 +1744,22 @@
       <c r="D30" s="13" t="n"/>
       <c r="E30" s="14" t="n"/>
       <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13">
-        <f>IF(AND(G30&lt;&gt;"",H30&lt;&gt;""),H30-G30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
+      <c r="G30" s="14" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="13">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;""),K30-J30,"")</f>
+        <v/>
+      </c>
       <c r="M30" s="14" t="n"/>
       <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
       <c r="P30" s="14" t="n"/>
+      <c r="Q30" s="14" t="n"/>
+      <c r="R30" s="14" t="n"/>
+      <c r="S30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1660,19 +1768,22 @@
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="9">
-        <f>IF(AND(G31&lt;&gt;"",H31&lt;&gt;""),H31-G31,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="9">
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;""),K31-J31,"")</f>
+        <v/>
+      </c>
       <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1681,19 +1792,22 @@
       <c r="D32" s="13" t="n"/>
       <c r="E32" s="14" t="n"/>
       <c r="F32" s="14" t="n"/>
-      <c r="G32" s="15" t="n"/>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="13">
-        <f>IF(AND(G32&lt;&gt;"",H32&lt;&gt;""),H32-G32,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
+      <c r="G32" s="14" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="13">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;""),K32-J32,"")</f>
+        <v/>
+      </c>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
       <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="n"/>
+      <c r="R32" s="14" t="n"/>
+      <c r="S32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -1702,19 +1816,22 @@
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="9">
-        <f>IF(AND(G33&lt;&gt;"",H33&lt;&gt;""),H33-G33,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="9">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;""),K33-J33,"")</f>
+        <v/>
+      </c>
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1723,19 +1840,22 @@
       <c r="D34" s="13" t="n"/>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
-      <c r="G34" s="15" t="n"/>
-      <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13">
-        <f>IF(AND(G34&lt;&gt;"",H34&lt;&gt;""),H34-G34,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="13">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;""),K34-J34,"")</f>
+        <v/>
+      </c>
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
       <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14" t="n"/>
+      <c r="R34" s="14" t="n"/>
+      <c r="S34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -1744,19 +1864,22 @@
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="9">
-        <f>IF(AND(G35&lt;&gt;"",H35&lt;&gt;""),H35-G35,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="9">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;""),K35-J35,"")</f>
+        <v/>
+      </c>
       <c r="M35" s="10" t="n"/>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1765,19 +1888,22 @@
       <c r="D36" s="13" t="n"/>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="14" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
-      <c r="I36" s="13">
-        <f>IF(AND(G36&lt;&gt;"",H36&lt;&gt;""),H36-G36,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="n"/>
-      <c r="K36" s="14" t="n"/>
-      <c r="L36" s="14" t="n"/>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="13">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;""),K36-J36,"")</f>
+        <v/>
+      </c>
       <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
+      <c r="Q36" s="14" t="n"/>
+      <c r="R36" s="14" t="n"/>
+      <c r="S36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -1786,19 +1912,22 @@
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="9">
-        <f>IF(AND(G37&lt;&gt;"",H37&lt;&gt;""),H37-G37,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="9">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;""),K37-J37,"")</f>
+        <v/>
+      </c>
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
       <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1807,19 +1936,22 @@
       <c r="D38" s="13" t="n"/>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="14" t="n"/>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13">
-        <f>IF(AND(G38&lt;&gt;"",H38&lt;&gt;""),H38-G38,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="n"/>
-      <c r="K38" s="14" t="n"/>
-      <c r="L38" s="14" t="n"/>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="15" t="n"/>
+      <c r="K38" s="15" t="n"/>
+      <c r="L38" s="13">
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;""),K38-J38,"")</f>
+        <v/>
+      </c>
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
+      <c r="R38" s="14" t="n"/>
+      <c r="S38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -1828,19 +1960,22 @@
       <c r="D39" s="9" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="9">
-        <f>IF(AND(G39&lt;&gt;"",H39&lt;&gt;""),H39-G39,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="9">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;""),K39-J39,"")</f>
+        <v/>
+      </c>
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
       <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -1849,19 +1984,22 @@
       <c r="D40" s="13" t="n"/>
       <c r="E40" s="14" t="n"/>
       <c r="F40" s="14" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
-      <c r="I40" s="13">
-        <f>IF(AND(G40&lt;&gt;"",H40&lt;&gt;""),H40-G40,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="n"/>
-      <c r="K40" s="14" t="n"/>
-      <c r="L40" s="14" t="n"/>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="15" t="n"/>
+      <c r="K40" s="15" t="n"/>
+      <c r="L40" s="13">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;""),K40-J40,"")</f>
+        <v/>
+      </c>
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
       <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="14" t="n"/>
+      <c r="R40" s="14" t="n"/>
+      <c r="S40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -1870,19 +2008,22 @@
       <c r="D41" s="9" t="n"/>
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="9">
-        <f>IF(AND(G41&lt;&gt;"",H41&lt;&gt;""),H41-G41,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="9">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;""),K41-J41,"")</f>
+        <v/>
+      </c>
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
       <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -1891,19 +2032,22 @@
       <c r="D42" s="13" t="n"/>
       <c r="E42" s="14" t="n"/>
       <c r="F42" s="14" t="n"/>
-      <c r="G42" s="15" t="n"/>
-      <c r="H42" s="15" t="n"/>
-      <c r="I42" s="13">
-        <f>IF(AND(G42&lt;&gt;"",H42&lt;&gt;""),H42-G42,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="n"/>
-      <c r="K42" s="14" t="n"/>
-      <c r="L42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="15" t="n"/>
+      <c r="K42" s="15" t="n"/>
+      <c r="L42" s="13">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;""),K42-J42,"")</f>
+        <v/>
+      </c>
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="14" t="n"/>
+      <c r="R42" s="14" t="n"/>
+      <c r="S42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -1912,19 +2056,22 @@
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="9">
-        <f>IF(AND(G43&lt;&gt;"",H43&lt;&gt;""),H43-G43,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="9">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;""),K43-J43,"")</f>
+        <v/>
+      </c>
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
       <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -1933,19 +2080,22 @@
       <c r="D44" s="13" t="n"/>
       <c r="E44" s="14" t="n"/>
       <c r="F44" s="14" t="n"/>
-      <c r="G44" s="15" t="n"/>
-      <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13">
-        <f>IF(AND(G44&lt;&gt;"",H44&lt;&gt;""),H44-G44,"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="n"/>
-      <c r="K44" s="14" t="n"/>
-      <c r="L44" s="14" t="n"/>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="15" t="n"/>
+      <c r="K44" s="15" t="n"/>
+      <c r="L44" s="13">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;""),K44-J44,"")</f>
+        <v/>
+      </c>
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="14" t="n"/>
       <c r="O44" s="14" t="n"/>
       <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="14" t="n"/>
+      <c r="R44" s="14" t="n"/>
+      <c r="S44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -1954,19 +2104,22 @@
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="9">
-        <f>IF(AND(G45&lt;&gt;"",H45&lt;&gt;""),H45-G45,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="9">
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;""),K45-J45,"")</f>
+        <v/>
+      </c>
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
       <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -1975,19 +2128,22 @@
       <c r="D46" s="13" t="n"/>
       <c r="E46" s="14" t="n"/>
       <c r="F46" s="14" t="n"/>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13">
-        <f>IF(AND(G46&lt;&gt;"",H46&lt;&gt;""),H46-G46,"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="n"/>
-      <c r="K46" s="14" t="n"/>
-      <c r="L46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="14" t="n"/>
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="13">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;""),K46-J46,"")</f>
+        <v/>
+      </c>
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
       <c r="P46" s="14" t="n"/>
+      <c r="Q46" s="14" t="n"/>
+      <c r="R46" s="14" t="n"/>
+      <c r="S46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -1996,19 +2152,22 @@
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="10" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="9">
-        <f>IF(AND(G47&lt;&gt;"",H47&lt;&gt;""),H47-G47,"")</f>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="11" t="n"/>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="9">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;""),K47-J47,"")</f>
+        <v/>
+      </c>
       <c r="M47" s="10" t="n"/>
       <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
       <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -2017,19 +2176,22 @@
       <c r="D48" s="13" t="n"/>
       <c r="E48" s="14" t="n"/>
       <c r="F48" s="14" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13">
-        <f>IF(AND(G48&lt;&gt;"",H48&lt;&gt;""),H48-G48,"")</f>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="n"/>
-      <c r="K48" s="14" t="n"/>
-      <c r="L48" s="14" t="n"/>
+      <c r="G48" s="14" t="n"/>
+      <c r="H48" s="14" t="n"/>
+      <c r="I48" s="14" t="n"/>
+      <c r="J48" s="15" t="n"/>
+      <c r="K48" s="15" t="n"/>
+      <c r="L48" s="13">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;""),K48-J48,"")</f>
+        <v/>
+      </c>
       <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
+      <c r="Q48" s="14" t="n"/>
+      <c r="R48" s="14" t="n"/>
+      <c r="S48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -2038,19 +2200,22 @@
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="10" t="n"/>
       <c r="F49" s="10" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="11" t="n"/>
-      <c r="I49" s="9">
-        <f>IF(AND(G49&lt;&gt;"",H49&lt;&gt;""),H49-G49,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="11" t="n"/>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="9">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;""),K49-J49,"")</f>
+        <v/>
+      </c>
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
       <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -2059,19 +2224,22 @@
       <c r="D50" s="13" t="n"/>
       <c r="E50" s="14" t="n"/>
       <c r="F50" s="14" t="n"/>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13">
-        <f>IF(AND(G50&lt;&gt;"",H50&lt;&gt;""),H50-G50,"")</f>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="n"/>
-      <c r="K50" s="14" t="n"/>
-      <c r="L50" s="14" t="n"/>
+      <c r="G50" s="14" t="n"/>
+      <c r="H50" s="14" t="n"/>
+      <c r="I50" s="14" t="n"/>
+      <c r="J50" s="15" t="n"/>
+      <c r="K50" s="15" t="n"/>
+      <c r="L50" s="13">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;""),K50-J50,"")</f>
+        <v/>
+      </c>
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
       <c r="P50" s="14" t="n"/>
+      <c r="Q50" s="14" t="n"/>
+      <c r="R50" s="14" t="n"/>
+      <c r="S50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -2080,19 +2248,22 @@
       <c r="D51" s="9" t="n"/>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="9">
-        <f>IF(AND(G51&lt;&gt;"",H51&lt;&gt;""),H51-G51,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="11" t="n"/>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="9">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;""),K51-J51,"")</f>
+        <v/>
+      </c>
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
       <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -2101,19 +2272,22 @@
       <c r="D52" s="13" t="n"/>
       <c r="E52" s="14" t="n"/>
       <c r="F52" s="14" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13">
-        <f>IF(AND(G52&lt;&gt;"",H52&lt;&gt;""),H52-G52,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="n"/>
-      <c r="K52" s="14" t="n"/>
-      <c r="L52" s="14" t="n"/>
+      <c r="G52" s="14" t="n"/>
+      <c r="H52" s="14" t="n"/>
+      <c r="I52" s="14" t="n"/>
+      <c r="J52" s="15" t="n"/>
+      <c r="K52" s="15" t="n"/>
+      <c r="L52" s="13">
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;""),K52-J52,"")</f>
+        <v/>
+      </c>
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
       <c r="P52" s="14" t="n"/>
+      <c r="Q52" s="14" t="n"/>
+      <c r="R52" s="14" t="n"/>
+      <c r="S52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -2122,19 +2296,22 @@
       <c r="D53" s="9" t="n"/>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="n"/>
-      <c r="I53" s="9">
-        <f>IF(AND(G53&lt;&gt;"",H53&lt;&gt;""),H53-G53,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="9">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;""),K53-J53,"")</f>
+        <v/>
+      </c>
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
       <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -2143,19 +2320,22 @@
       <c r="D54" s="13" t="n"/>
       <c r="E54" s="14" t="n"/>
       <c r="F54" s="14" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="n"/>
-      <c r="I54" s="13">
-        <f>IF(AND(G54&lt;&gt;"",H54&lt;&gt;""),H54-G54,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="14" t="n"/>
-      <c r="K54" s="14" t="n"/>
-      <c r="L54" s="14" t="n"/>
+      <c r="G54" s="14" t="n"/>
+      <c r="H54" s="14" t="n"/>
+      <c r="I54" s="14" t="n"/>
+      <c r="J54" s="15" t="n"/>
+      <c r="K54" s="15" t="n"/>
+      <c r="L54" s="13">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;""),K54-J54,"")</f>
+        <v/>
+      </c>
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="14" t="n"/>
       <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14" t="n"/>
+      <c r="R54" s="14" t="n"/>
+      <c r="S54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -2164,19 +2344,22 @@
       <c r="D55" s="9" t="n"/>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
-      <c r="G55" s="11" t="n"/>
-      <c r="H55" s="11" t="n"/>
-      <c r="I55" s="9">
-        <f>IF(AND(G55&lt;&gt;"",H55&lt;&gt;""),H55-G55,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="11" t="n"/>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="9">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;""),K55-J55,"")</f>
+        <v/>
+      </c>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
       <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -2185,19 +2368,22 @@
       <c r="D56" s="13" t="n"/>
       <c r="E56" s="14" t="n"/>
       <c r="F56" s="14" t="n"/>
-      <c r="G56" s="15" t="n"/>
-      <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13">
-        <f>IF(AND(G56&lt;&gt;"",H56&lt;&gt;""),H56-G56,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n"/>
+      <c r="G56" s="14" t="n"/>
+      <c r="H56" s="14" t="n"/>
+      <c r="I56" s="14" t="n"/>
+      <c r="J56" s="15" t="n"/>
+      <c r="K56" s="15" t="n"/>
+      <c r="L56" s="13">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;""),K56-J56,"")</f>
+        <v/>
+      </c>
       <c r="M56" s="14" t="n"/>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
+      <c r="Q56" s="14" t="n"/>
+      <c r="R56" s="14" t="n"/>
+      <c r="S56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -2206,19 +2392,22 @@
       <c r="D57" s="9" t="n"/>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
-      <c r="G57" s="11" t="n"/>
-      <c r="H57" s="11" t="n"/>
-      <c r="I57" s="9">
-        <f>IF(AND(G57&lt;&gt;"",H57&lt;&gt;""),H57-G57,"")</f>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="11" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="9">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;""),K57-J57,"")</f>
+        <v/>
+      </c>
       <c r="M57" s="10" t="n"/>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
       <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -2227,19 +2416,22 @@
       <c r="D58" s="13" t="n"/>
       <c r="E58" s="14" t="n"/>
       <c r="F58" s="14" t="n"/>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="13">
-        <f>IF(AND(G58&lt;&gt;"",H58&lt;&gt;""),H58-G58,"")</f>
-        <v/>
-      </c>
-      <c r="J58" s="14" t="n"/>
-      <c r="K58" s="14" t="n"/>
-      <c r="L58" s="14" t="n"/>
+      <c r="G58" s="14" t="n"/>
+      <c r="H58" s="14" t="n"/>
+      <c r="I58" s="14" t="n"/>
+      <c r="J58" s="15" t="n"/>
+      <c r="K58" s="15" t="n"/>
+      <c r="L58" s="13">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;""),K58-J58,"")</f>
+        <v/>
+      </c>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
+      <c r="Q58" s="14" t="n"/>
+      <c r="R58" s="14" t="n"/>
+      <c r="S58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -2248,19 +2440,22 @@
       <c r="D59" s="9" t="n"/>
       <c r="E59" s="10" t="n"/>
       <c r="F59" s="10" t="n"/>
-      <c r="G59" s="11" t="n"/>
-      <c r="H59" s="11" t="n"/>
-      <c r="I59" s="9">
-        <f>IF(AND(G59&lt;&gt;"",H59&lt;&gt;""),H59-G59,"")</f>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="11" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="9">
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;""),K59-J59,"")</f>
+        <v/>
+      </c>
       <c r="M59" s="10" t="n"/>
       <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
       <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -2269,19 +2464,22 @@
       <c r="D60" s="13" t="n"/>
       <c r="E60" s="14" t="n"/>
       <c r="F60" s="14" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13">
-        <f>IF(AND(G60&lt;&gt;"",H60&lt;&gt;""),H60-G60,"")</f>
-        <v/>
-      </c>
-      <c r="J60" s="14" t="n"/>
-      <c r="K60" s="14" t="n"/>
-      <c r="L60" s="14" t="n"/>
+      <c r="G60" s="14" t="n"/>
+      <c r="H60" s="14" t="n"/>
+      <c r="I60" s="14" t="n"/>
+      <c r="J60" s="15" t="n"/>
+      <c r="K60" s="15" t="n"/>
+      <c r="L60" s="13">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;""),K60-J60,"")</f>
+        <v/>
+      </c>
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
+      <c r="Q60" s="14" t="n"/>
+      <c r="R60" s="14" t="n"/>
+      <c r="S60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -2290,19 +2488,22 @@
       <c r="D61" s="9" t="n"/>
       <c r="E61" s="10" t="n"/>
       <c r="F61" s="10" t="n"/>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="11" t="n"/>
-      <c r="I61" s="9">
-        <f>IF(AND(G61&lt;&gt;"",H61&lt;&gt;""),H61-G61,"")</f>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="9">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;""),K61-J61,"")</f>
+        <v/>
+      </c>
       <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
       <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -2311,19 +2512,22 @@
       <c r="D62" s="13" t="n"/>
       <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="n"/>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="15" t="n"/>
-      <c r="I62" s="13">
-        <f>IF(AND(G62&lt;&gt;"",H62&lt;&gt;""),H62-G62,"")</f>
-        <v/>
-      </c>
-      <c r="J62" s="14" t="n"/>
-      <c r="K62" s="14" t="n"/>
-      <c r="L62" s="14" t="n"/>
+      <c r="G62" s="14" t="n"/>
+      <c r="H62" s="14" t="n"/>
+      <c r="I62" s="14" t="n"/>
+      <c r="J62" s="15" t="n"/>
+      <c r="K62" s="15" t="n"/>
+      <c r="L62" s="13">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;""),K62-J62,"")</f>
+        <v/>
+      </c>
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
       <c r="P62" s="14" t="n"/>
+      <c r="Q62" s="14" t="n"/>
+      <c r="R62" s="14" t="n"/>
+      <c r="S62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -2332,19 +2536,22 @@
       <c r="D63" s="9" t="n"/>
       <c r="E63" s="10" t="n"/>
       <c r="F63" s="10" t="n"/>
-      <c r="G63" s="11" t="n"/>
-      <c r="H63" s="11" t="n"/>
-      <c r="I63" s="9">
-        <f>IF(AND(G63&lt;&gt;"",H63&lt;&gt;""),H63-G63,"")</f>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="9">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;""),K63-J63,"")</f>
+        <v/>
+      </c>
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
       <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -2353,19 +2560,22 @@
       <c r="D64" s="13" t="n"/>
       <c r="E64" s="14" t="n"/>
       <c r="F64" s="14" t="n"/>
-      <c r="G64" s="15" t="n"/>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13">
-        <f>IF(AND(G64&lt;&gt;"",H64&lt;&gt;""),H64-G64,"")</f>
-        <v/>
-      </c>
-      <c r="J64" s="14" t="n"/>
-      <c r="K64" s="14" t="n"/>
-      <c r="L64" s="14" t="n"/>
+      <c r="G64" s="14" t="n"/>
+      <c r="H64" s="14" t="n"/>
+      <c r="I64" s="14" t="n"/>
+      <c r="J64" s="15" t="n"/>
+      <c r="K64" s="15" t="n"/>
+      <c r="L64" s="13">
+        <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;""),K64-J64,"")</f>
+        <v/>
+      </c>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
       <c r="O64" s="14" t="n"/>
       <c r="P64" s="14" t="n"/>
+      <c r="Q64" s="14" t="n"/>
+      <c r="R64" s="14" t="n"/>
+      <c r="S64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -2374,19 +2584,22 @@
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="10" t="n"/>
       <c r="F65" s="10" t="n"/>
-      <c r="G65" s="11" t="n"/>
-      <c r="H65" s="11" t="n"/>
-      <c r="I65" s="9">
-        <f>IF(AND(G65&lt;&gt;"",H65&lt;&gt;""),H65-G65,"")</f>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="9">
+        <f>IF(AND(J65&lt;&gt;"",K65&lt;&gt;""),K65-J65,"")</f>
+        <v/>
+      </c>
       <c r="M65" s="10" t="n"/>
       <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
       <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -2395,19 +2608,22 @@
       <c r="D66" s="13" t="n"/>
       <c r="E66" s="14" t="n"/>
       <c r="F66" s="14" t="n"/>
-      <c r="G66" s="15" t="n"/>
-      <c r="H66" s="15" t="n"/>
-      <c r="I66" s="13">
-        <f>IF(AND(G66&lt;&gt;"",H66&lt;&gt;""),H66-G66,"")</f>
-        <v/>
-      </c>
-      <c r="J66" s="14" t="n"/>
-      <c r="K66" s="14" t="n"/>
-      <c r="L66" s="14" t="n"/>
+      <c r="G66" s="14" t="n"/>
+      <c r="H66" s="14" t="n"/>
+      <c r="I66" s="14" t="n"/>
+      <c r="J66" s="15" t="n"/>
+      <c r="K66" s="15" t="n"/>
+      <c r="L66" s="13">
+        <f>IF(AND(J66&lt;&gt;"",K66&lt;&gt;""),K66-J66,"")</f>
+        <v/>
+      </c>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
+      <c r="Q66" s="14" t="n"/>
+      <c r="R66" s="14" t="n"/>
+      <c r="S66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -2416,19 +2632,22 @@
       <c r="D67" s="9" t="n"/>
       <c r="E67" s="10" t="n"/>
       <c r="F67" s="10" t="n"/>
-      <c r="G67" s="11" t="n"/>
-      <c r="H67" s="11" t="n"/>
-      <c r="I67" s="9">
-        <f>IF(AND(G67&lt;&gt;"",H67&lt;&gt;""),H67-G67,"")</f>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="11" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="9">
+        <f>IF(AND(J67&lt;&gt;"",K67&lt;&gt;""),K67-J67,"")</f>
+        <v/>
+      </c>
       <c r="M67" s="10" t="n"/>
       <c r="N67" s="10" t="n"/>
       <c r="O67" s="10" t="n"/>
       <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -2437,19 +2656,22 @@
       <c r="D68" s="13" t="n"/>
       <c r="E68" s="14" t="n"/>
       <c r="F68" s="14" t="n"/>
-      <c r="G68" s="15" t="n"/>
-      <c r="H68" s="15" t="n"/>
-      <c r="I68" s="13">
-        <f>IF(AND(G68&lt;&gt;"",H68&lt;&gt;""),H68-G68,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="14" t="n"/>
-      <c r="K68" s="14" t="n"/>
-      <c r="L68" s="14" t="n"/>
+      <c r="G68" s="14" t="n"/>
+      <c r="H68" s="14" t="n"/>
+      <c r="I68" s="14" t="n"/>
+      <c r="J68" s="15" t="n"/>
+      <c r="K68" s="15" t="n"/>
+      <c r="L68" s="13">
+        <f>IF(AND(J68&lt;&gt;"",K68&lt;&gt;""),K68-J68,"")</f>
+        <v/>
+      </c>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
       <c r="P68" s="14" t="n"/>
+      <c r="Q68" s="14" t="n"/>
+      <c r="R68" s="14" t="n"/>
+      <c r="S68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -2458,19 +2680,22 @@
       <c r="D69" s="9" t="n"/>
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="10" t="n"/>
-      <c r="G69" s="11" t="n"/>
-      <c r="H69" s="11" t="n"/>
-      <c r="I69" s="9">
-        <f>IF(AND(G69&lt;&gt;"",H69&lt;&gt;""),H69-G69,"")</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="11" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="9">
+        <f>IF(AND(J69&lt;&gt;"",K69&lt;&gt;""),K69-J69,"")</f>
+        <v/>
+      </c>
       <c r="M69" s="10" t="n"/>
       <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
       <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -2479,19 +2704,22 @@
       <c r="D70" s="13" t="n"/>
       <c r="E70" s="14" t="n"/>
       <c r="F70" s="14" t="n"/>
-      <c r="G70" s="15" t="n"/>
-      <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13">
-        <f>IF(AND(G70&lt;&gt;"",H70&lt;&gt;""),H70-G70,"")</f>
-        <v/>
-      </c>
-      <c r="J70" s="14" t="n"/>
-      <c r="K70" s="14" t="n"/>
-      <c r="L70" s="14" t="n"/>
+      <c r="G70" s="14" t="n"/>
+      <c r="H70" s="14" t="n"/>
+      <c r="I70" s="14" t="n"/>
+      <c r="J70" s="15" t="n"/>
+      <c r="K70" s="15" t="n"/>
+      <c r="L70" s="13">
+        <f>IF(AND(J70&lt;&gt;"",K70&lt;&gt;""),K70-J70,"")</f>
+        <v/>
+      </c>
       <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
+      <c r="Q70" s="14" t="n"/>
+      <c r="R70" s="14" t="n"/>
+      <c r="S70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -2500,19 +2728,22 @@
       <c r="D71" s="9" t="n"/>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="10" t="n"/>
-      <c r="G71" s="11" t="n"/>
-      <c r="H71" s="11" t="n"/>
-      <c r="I71" s="9">
-        <f>IF(AND(G71&lt;&gt;"",H71&lt;&gt;""),H71-G71,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="11" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="9">
+        <f>IF(AND(J71&lt;&gt;"",K71&lt;&gt;""),K71-J71,"")</f>
+        <v/>
+      </c>
       <c r="M71" s="10" t="n"/>
       <c r="N71" s="10" t="n"/>
       <c r="O71" s="10" t="n"/>
       <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -2521,19 +2752,22 @@
       <c r="D72" s="13" t="n"/>
       <c r="E72" s="14" t="n"/>
       <c r="F72" s="14" t="n"/>
-      <c r="G72" s="15" t="n"/>
-      <c r="H72" s="15" t="n"/>
-      <c r="I72" s="13">
-        <f>IF(AND(G72&lt;&gt;"",H72&lt;&gt;""),H72-G72,"")</f>
-        <v/>
-      </c>
-      <c r="J72" s="14" t="n"/>
-      <c r="K72" s="14" t="n"/>
-      <c r="L72" s="14" t="n"/>
+      <c r="G72" s="14" t="n"/>
+      <c r="H72" s="14" t="n"/>
+      <c r="I72" s="14" t="n"/>
+      <c r="J72" s="15" t="n"/>
+      <c r="K72" s="15" t="n"/>
+      <c r="L72" s="13">
+        <f>IF(AND(J72&lt;&gt;"",K72&lt;&gt;""),K72-J72,"")</f>
+        <v/>
+      </c>
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
       <c r="O72" s="14" t="n"/>
       <c r="P72" s="14" t="n"/>
+      <c r="Q72" s="14" t="n"/>
+      <c r="R72" s="14" t="n"/>
+      <c r="S72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -2542,19 +2776,22 @@
       <c r="D73" s="9" t="n"/>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="10" t="n"/>
-      <c r="G73" s="11" t="n"/>
-      <c r="H73" s="11" t="n"/>
-      <c r="I73" s="9">
-        <f>IF(AND(G73&lt;&gt;"",H73&lt;&gt;""),H73-G73,"")</f>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="11" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="9">
+        <f>IF(AND(J73&lt;&gt;"",K73&lt;&gt;""),K73-J73,"")</f>
+        <v/>
+      </c>
       <c r="M73" s="10" t="n"/>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
       <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -2563,19 +2800,22 @@
       <c r="D74" s="13" t="n"/>
       <c r="E74" s="14" t="n"/>
       <c r="F74" s="14" t="n"/>
-      <c r="G74" s="15" t="n"/>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13">
-        <f>IF(AND(G74&lt;&gt;"",H74&lt;&gt;""),H74-G74,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="14" t="n"/>
-      <c r="K74" s="14" t="n"/>
-      <c r="L74" s="14" t="n"/>
+      <c r="G74" s="14" t="n"/>
+      <c r="H74" s="14" t="n"/>
+      <c r="I74" s="14" t="n"/>
+      <c r="J74" s="15" t="n"/>
+      <c r="K74" s="15" t="n"/>
+      <c r="L74" s="13">
+        <f>IF(AND(J74&lt;&gt;"",K74&lt;&gt;""),K74-J74,"")</f>
+        <v/>
+      </c>
       <c r="M74" s="14" t="n"/>
       <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
       <c r="P74" s="14" t="n"/>
+      <c r="Q74" s="14" t="n"/>
+      <c r="R74" s="14" t="n"/>
+      <c r="S74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -2584,19 +2824,22 @@
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="10" t="n"/>
       <c r="F75" s="10" t="n"/>
-      <c r="G75" s="11" t="n"/>
-      <c r="H75" s="11" t="n"/>
-      <c r="I75" s="9">
-        <f>IF(AND(G75&lt;&gt;"",H75&lt;&gt;""),H75-G75,"")</f>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="n"/>
-      <c r="K75" s="10" t="n"/>
-      <c r="L75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="9">
+        <f>IF(AND(J75&lt;&gt;"",K75&lt;&gt;""),K75-J75,"")</f>
+        <v/>
+      </c>
       <c r="M75" s="10" t="n"/>
       <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
       <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -2605,19 +2848,22 @@
       <c r="D76" s="13" t="n"/>
       <c r="E76" s="14" t="n"/>
       <c r="F76" s="14" t="n"/>
-      <c r="G76" s="15" t="n"/>
-      <c r="H76" s="15" t="n"/>
-      <c r="I76" s="13">
-        <f>IF(AND(G76&lt;&gt;"",H76&lt;&gt;""),H76-G76,"")</f>
-        <v/>
-      </c>
-      <c r="J76" s="14" t="n"/>
-      <c r="K76" s="14" t="n"/>
-      <c r="L76" s="14" t="n"/>
+      <c r="G76" s="14" t="n"/>
+      <c r="H76" s="14" t="n"/>
+      <c r="I76" s="14" t="n"/>
+      <c r="J76" s="15" t="n"/>
+      <c r="K76" s="15" t="n"/>
+      <c r="L76" s="13">
+        <f>IF(AND(J76&lt;&gt;"",K76&lt;&gt;""),K76-J76,"")</f>
+        <v/>
+      </c>
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n"/>
       <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n"/>
+      <c r="R76" s="14" t="n"/>
+      <c r="S76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -2626,19 +2872,22 @@
       <c r="D77" s="9" t="n"/>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="10" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="11" t="n"/>
-      <c r="I77" s="9">
-        <f>IF(AND(G77&lt;&gt;"",H77&lt;&gt;""),H77-G77,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="9">
+        <f>IF(AND(J77&lt;&gt;"",K77&lt;&gt;""),K77-J77,"")</f>
+        <v/>
+      </c>
       <c r="M77" s="10" t="n"/>
       <c r="N77" s="10" t="n"/>
       <c r="O77" s="10" t="n"/>
       <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -2647,19 +2896,22 @@
       <c r="D78" s="13" t="n"/>
       <c r="E78" s="14" t="n"/>
       <c r="F78" s="14" t="n"/>
-      <c r="G78" s="15" t="n"/>
-      <c r="H78" s="15" t="n"/>
-      <c r="I78" s="13">
-        <f>IF(AND(G78&lt;&gt;"",H78&lt;&gt;""),H78-G78,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="14" t="n"/>
-      <c r="K78" s="14" t="n"/>
-      <c r="L78" s="14" t="n"/>
+      <c r="G78" s="14" t="n"/>
+      <c r="H78" s="14" t="n"/>
+      <c r="I78" s="14" t="n"/>
+      <c r="J78" s="15" t="n"/>
+      <c r="K78" s="15" t="n"/>
+      <c r="L78" s="13">
+        <f>IF(AND(J78&lt;&gt;"",K78&lt;&gt;""),K78-J78,"")</f>
+        <v/>
+      </c>
       <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
       <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
+      <c r="R78" s="14" t="n"/>
+      <c r="S78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -2668,19 +2920,22 @@
       <c r="D79" s="9" t="n"/>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="10" t="n"/>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="11" t="n"/>
-      <c r="I79" s="9">
-        <f>IF(AND(G79&lt;&gt;"",H79&lt;&gt;""),H79-G79,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="9">
+        <f>IF(AND(J79&lt;&gt;"",K79&lt;&gt;""),K79-J79,"")</f>
+        <v/>
+      </c>
       <c r="M79" s="10" t="n"/>
       <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
       <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2689,19 +2944,22 @@
       <c r="D80" s="13" t="n"/>
       <c r="E80" s="14" t="n"/>
       <c r="F80" s="14" t="n"/>
-      <c r="G80" s="15" t="n"/>
-      <c r="H80" s="15" t="n"/>
-      <c r="I80" s="13">
-        <f>IF(AND(G80&lt;&gt;"",H80&lt;&gt;""),H80-G80,"")</f>
-        <v/>
-      </c>
-      <c r="J80" s="14" t="n"/>
-      <c r="K80" s="14" t="n"/>
-      <c r="L80" s="14" t="n"/>
+      <c r="G80" s="14" t="n"/>
+      <c r="H80" s="14" t="n"/>
+      <c r="I80" s="14" t="n"/>
+      <c r="J80" s="15" t="n"/>
+      <c r="K80" s="15" t="n"/>
+      <c r="L80" s="13">
+        <f>IF(AND(J80&lt;&gt;"",K80&lt;&gt;""),K80-J80,"")</f>
+        <v/>
+      </c>
       <c r="M80" s="14" t="n"/>
       <c r="N80" s="14" t="n"/>
       <c r="O80" s="14" t="n"/>
       <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14" t="n"/>
+      <c r="R80" s="14" t="n"/>
+      <c r="S80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -2710,19 +2968,22 @@
       <c r="D81" s="9" t="n"/>
       <c r="E81" s="10" t="n"/>
       <c r="F81" s="10" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="9">
-        <f>IF(AND(G81&lt;&gt;"",H81&lt;&gt;""),H81-G81,"")</f>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="9">
+        <f>IF(AND(J81&lt;&gt;"",K81&lt;&gt;""),K81-J81,"")</f>
+        <v/>
+      </c>
       <c r="M81" s="10" t="n"/>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
       <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -2731,19 +2992,22 @@
       <c r="D82" s="13" t="n"/>
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="14" t="n"/>
-      <c r="G82" s="15" t="n"/>
-      <c r="H82" s="15" t="n"/>
-      <c r="I82" s="13">
-        <f>IF(AND(G82&lt;&gt;"",H82&lt;&gt;""),H82-G82,"")</f>
-        <v/>
-      </c>
-      <c r="J82" s="14" t="n"/>
-      <c r="K82" s="14" t="n"/>
-      <c r="L82" s="14" t="n"/>
+      <c r="G82" s="14" t="n"/>
+      <c r="H82" s="14" t="n"/>
+      <c r="I82" s="14" t="n"/>
+      <c r="J82" s="15" t="n"/>
+      <c r="K82" s="15" t="n"/>
+      <c r="L82" s="13">
+        <f>IF(AND(J82&lt;&gt;"",K82&lt;&gt;""),K82-J82,"")</f>
+        <v/>
+      </c>
       <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="n"/>
       <c r="O82" s="14" t="n"/>
       <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14" t="n"/>
+      <c r="R82" s="14" t="n"/>
+      <c r="S82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -2752,19 +3016,22 @@
       <c r="D83" s="9" t="n"/>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="10" t="n"/>
-      <c r="G83" s="11" t="n"/>
-      <c r="H83" s="11" t="n"/>
-      <c r="I83" s="9">
-        <f>IF(AND(G83&lt;&gt;"",H83&lt;&gt;""),H83-G83,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="11" t="n"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="9">
+        <f>IF(AND(J83&lt;&gt;"",K83&lt;&gt;""),K83-J83,"")</f>
+        <v/>
+      </c>
       <c r="M83" s="10" t="n"/>
       <c r="N83" s="10" t="n"/>
       <c r="O83" s="10" t="n"/>
       <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -2773,19 +3040,22 @@
       <c r="D84" s="13" t="n"/>
       <c r="E84" s="14" t="n"/>
       <c r="F84" s="14" t="n"/>
-      <c r="G84" s="15" t="n"/>
-      <c r="H84" s="15" t="n"/>
-      <c r="I84" s="13">
-        <f>IF(AND(G84&lt;&gt;"",H84&lt;&gt;""),H84-G84,"")</f>
-        <v/>
-      </c>
-      <c r="J84" s="14" t="n"/>
-      <c r="K84" s="14" t="n"/>
-      <c r="L84" s="14" t="n"/>
+      <c r="G84" s="14" t="n"/>
+      <c r="H84" s="14" t="n"/>
+      <c r="I84" s="14" t="n"/>
+      <c r="J84" s="15" t="n"/>
+      <c r="K84" s="15" t="n"/>
+      <c r="L84" s="13">
+        <f>IF(AND(J84&lt;&gt;"",K84&lt;&gt;""),K84-J84,"")</f>
+        <v/>
+      </c>
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
       <c r="P84" s="14" t="n"/>
+      <c r="Q84" s="14" t="n"/>
+      <c r="R84" s="14" t="n"/>
+      <c r="S84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -2794,19 +3064,22 @@
       <c r="D85" s="9" t="n"/>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n"/>
-      <c r="G85" s="11" t="n"/>
-      <c r="H85" s="11" t="n"/>
-      <c r="I85" s="9">
-        <f>IF(AND(G85&lt;&gt;"",H85&lt;&gt;""),H85-G85,"")</f>
-        <v/>
-      </c>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="11" t="n"/>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="9">
+        <f>IF(AND(J85&lt;&gt;"",K85&lt;&gt;""),K85-J85,"")</f>
+        <v/>
+      </c>
       <c r="M85" s="10" t="n"/>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
       <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -2815,19 +3088,22 @@
       <c r="D86" s="13" t="n"/>
       <c r="E86" s="14" t="n"/>
       <c r="F86" s="14" t="n"/>
-      <c r="G86" s="15" t="n"/>
-      <c r="H86" s="15" t="n"/>
-      <c r="I86" s="13">
-        <f>IF(AND(G86&lt;&gt;"",H86&lt;&gt;""),H86-G86,"")</f>
-        <v/>
-      </c>
-      <c r="J86" s="14" t="n"/>
-      <c r="K86" s="14" t="n"/>
-      <c r="L86" s="14" t="n"/>
+      <c r="G86" s="14" t="n"/>
+      <c r="H86" s="14" t="n"/>
+      <c r="I86" s="14" t="n"/>
+      <c r="J86" s="15" t="n"/>
+      <c r="K86" s="15" t="n"/>
+      <c r="L86" s="13">
+        <f>IF(AND(J86&lt;&gt;"",K86&lt;&gt;""),K86-J86,"")</f>
+        <v/>
+      </c>
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
       <c r="O86" s="14" t="n"/>
       <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n"/>
+      <c r="R86" s="14" t="n"/>
+      <c r="S86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -2836,19 +3112,22 @@
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="10" t="n"/>
       <c r="F87" s="10" t="n"/>
-      <c r="G87" s="11" t="n"/>
-      <c r="H87" s="11" t="n"/>
-      <c r="I87" s="9">
-        <f>IF(AND(G87&lt;&gt;"",H87&lt;&gt;""),H87-G87,"")</f>
-        <v/>
-      </c>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="11" t="n"/>
+      <c r="K87" s="11" t="n"/>
+      <c r="L87" s="9">
+        <f>IF(AND(J87&lt;&gt;"",K87&lt;&gt;""),K87-J87,"")</f>
+        <v/>
+      </c>
       <c r="M87" s="10" t="n"/>
       <c r="N87" s="10" t="n"/>
       <c r="O87" s="10" t="n"/>
       <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -2857,19 +3136,22 @@
       <c r="D88" s="13" t="n"/>
       <c r="E88" s="14" t="n"/>
       <c r="F88" s="14" t="n"/>
-      <c r="G88" s="15" t="n"/>
-      <c r="H88" s="15" t="n"/>
-      <c r="I88" s="13">
-        <f>IF(AND(G88&lt;&gt;"",H88&lt;&gt;""),H88-G88,"")</f>
-        <v/>
-      </c>
-      <c r="J88" s="14" t="n"/>
-      <c r="K88" s="14" t="n"/>
-      <c r="L88" s="14" t="n"/>
+      <c r="G88" s="14" t="n"/>
+      <c r="H88" s="14" t="n"/>
+      <c r="I88" s="14" t="n"/>
+      <c r="J88" s="15" t="n"/>
+      <c r="K88" s="15" t="n"/>
+      <c r="L88" s="13">
+        <f>IF(AND(J88&lt;&gt;"",K88&lt;&gt;""),K88-J88,"")</f>
+        <v/>
+      </c>
       <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
       <c r="O88" s="14" t="n"/>
       <c r="P88" s="14" t="n"/>
+      <c r="Q88" s="14" t="n"/>
+      <c r="R88" s="14" t="n"/>
+      <c r="S88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -2878,19 +3160,22 @@
       <c r="D89" s="9" t="n"/>
       <c r="E89" s="10" t="n"/>
       <c r="F89" s="10" t="n"/>
-      <c r="G89" s="11" t="n"/>
-      <c r="H89" s="11" t="n"/>
-      <c r="I89" s="9">
-        <f>IF(AND(G89&lt;&gt;"",H89&lt;&gt;""),H89-G89,"")</f>
-        <v/>
-      </c>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="11" t="n"/>
+      <c r="K89" s="11" t="n"/>
+      <c r="L89" s="9">
+        <f>IF(AND(J89&lt;&gt;"",K89&lt;&gt;""),K89-J89,"")</f>
+        <v/>
+      </c>
       <c r="M89" s="10" t="n"/>
       <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
       <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -2899,19 +3184,22 @@
       <c r="D90" s="13" t="n"/>
       <c r="E90" s="14" t="n"/>
       <c r="F90" s="14" t="n"/>
-      <c r="G90" s="15" t="n"/>
-      <c r="H90" s="15" t="n"/>
-      <c r="I90" s="13">
-        <f>IF(AND(G90&lt;&gt;"",H90&lt;&gt;""),H90-G90,"")</f>
-        <v/>
-      </c>
-      <c r="J90" s="14" t="n"/>
-      <c r="K90" s="14" t="n"/>
-      <c r="L90" s="14" t="n"/>
+      <c r="G90" s="14" t="n"/>
+      <c r="H90" s="14" t="n"/>
+      <c r="I90" s="14" t="n"/>
+      <c r="J90" s="15" t="n"/>
+      <c r="K90" s="15" t="n"/>
+      <c r="L90" s="13">
+        <f>IF(AND(J90&lt;&gt;"",K90&lt;&gt;""),K90-J90,"")</f>
+        <v/>
+      </c>
       <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n"/>
       <c r="P90" s="14" t="n"/>
+      <c r="Q90" s="14" t="n"/>
+      <c r="R90" s="14" t="n"/>
+      <c r="S90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -2920,19 +3208,22 @@
       <c r="D91" s="9" t="n"/>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="10" t="n"/>
-      <c r="G91" s="11" t="n"/>
-      <c r="H91" s="11" t="n"/>
-      <c r="I91" s="9">
-        <f>IF(AND(G91&lt;&gt;"",H91&lt;&gt;""),H91-G91,"")</f>
-        <v/>
-      </c>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="9">
+        <f>IF(AND(J91&lt;&gt;"",K91&lt;&gt;""),K91-J91,"")</f>
+        <v/>
+      </c>
       <c r="M91" s="10" t="n"/>
       <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
       <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -2941,19 +3232,22 @@
       <c r="D92" s="13" t="n"/>
       <c r="E92" s="14" t="n"/>
       <c r="F92" s="14" t="n"/>
-      <c r="G92" s="15" t="n"/>
-      <c r="H92" s="15" t="n"/>
-      <c r="I92" s="13">
-        <f>IF(AND(G92&lt;&gt;"",H92&lt;&gt;""),H92-G92,"")</f>
-        <v/>
-      </c>
-      <c r="J92" s="14" t="n"/>
-      <c r="K92" s="14" t="n"/>
-      <c r="L92" s="14" t="n"/>
+      <c r="G92" s="14" t="n"/>
+      <c r="H92" s="14" t="n"/>
+      <c r="I92" s="14" t="n"/>
+      <c r="J92" s="15" t="n"/>
+      <c r="K92" s="15" t="n"/>
+      <c r="L92" s="13">
+        <f>IF(AND(J92&lt;&gt;"",K92&lt;&gt;""),K92-J92,"")</f>
+        <v/>
+      </c>
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
       <c r="O92" s="14" t="n"/>
       <c r="P92" s="14" t="n"/>
+      <c r="Q92" s="14" t="n"/>
+      <c r="R92" s="14" t="n"/>
+      <c r="S92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -2962,19 +3256,22 @@
       <c r="D93" s="9" t="n"/>
       <c r="E93" s="10" t="n"/>
       <c r="F93" s="10" t="n"/>
-      <c r="G93" s="11" t="n"/>
-      <c r="H93" s="11" t="n"/>
-      <c r="I93" s="9">
-        <f>IF(AND(G93&lt;&gt;"",H93&lt;&gt;""),H93-G93,"")</f>
-        <v/>
-      </c>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="9">
+        <f>IF(AND(J93&lt;&gt;"",K93&lt;&gt;""),K93-J93,"")</f>
+        <v/>
+      </c>
       <c r="M93" s="10" t="n"/>
       <c r="N93" s="10" t="n"/>
       <c r="O93" s="10" t="n"/>
       <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -2983,19 +3280,22 @@
       <c r="D94" s="13" t="n"/>
       <c r="E94" s="14" t="n"/>
       <c r="F94" s="14" t="n"/>
-      <c r="G94" s="15" t="n"/>
-      <c r="H94" s="15" t="n"/>
-      <c r="I94" s="13">
-        <f>IF(AND(G94&lt;&gt;"",H94&lt;&gt;""),H94-G94,"")</f>
-        <v/>
-      </c>
-      <c r="J94" s="14" t="n"/>
-      <c r="K94" s="14" t="n"/>
-      <c r="L94" s="14" t="n"/>
+      <c r="G94" s="14" t="n"/>
+      <c r="H94" s="14" t="n"/>
+      <c r="I94" s="14" t="n"/>
+      <c r="J94" s="15" t="n"/>
+      <c r="K94" s="15" t="n"/>
+      <c r="L94" s="13">
+        <f>IF(AND(J94&lt;&gt;"",K94&lt;&gt;""),K94-J94,"")</f>
+        <v/>
+      </c>
       <c r="M94" s="14" t="n"/>
       <c r="N94" s="14" t="n"/>
       <c r="O94" s="14" t="n"/>
       <c r="P94" s="14" t="n"/>
+      <c r="Q94" s="14" t="n"/>
+      <c r="R94" s="14" t="n"/>
+      <c r="S94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -3004,19 +3304,22 @@
       <c r="D95" s="9" t="n"/>
       <c r="E95" s="10" t="n"/>
       <c r="F95" s="10" t="n"/>
-      <c r="G95" s="11" t="n"/>
-      <c r="H95" s="11" t="n"/>
-      <c r="I95" s="9">
-        <f>IF(AND(G95&lt;&gt;"",H95&lt;&gt;""),H95-G95,"")</f>
-        <v/>
-      </c>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="9">
+        <f>IF(AND(J95&lt;&gt;"",K95&lt;&gt;""),K95-J95,"")</f>
+        <v/>
+      </c>
       <c r="M95" s="10" t="n"/>
       <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
       <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -3025,19 +3328,22 @@
       <c r="D96" s="13" t="n"/>
       <c r="E96" s="14" t="n"/>
       <c r="F96" s="14" t="n"/>
-      <c r="G96" s="15" t="n"/>
-      <c r="H96" s="15" t="n"/>
-      <c r="I96" s="13">
-        <f>IF(AND(G96&lt;&gt;"",H96&lt;&gt;""),H96-G96,"")</f>
-        <v/>
-      </c>
-      <c r="J96" s="14" t="n"/>
-      <c r="K96" s="14" t="n"/>
-      <c r="L96" s="14" t="n"/>
+      <c r="G96" s="14" t="n"/>
+      <c r="H96" s="14" t="n"/>
+      <c r="I96" s="14" t="n"/>
+      <c r="J96" s="15" t="n"/>
+      <c r="K96" s="15" t="n"/>
+      <c r="L96" s="13">
+        <f>IF(AND(J96&lt;&gt;"",K96&lt;&gt;""),K96-J96,"")</f>
+        <v/>
+      </c>
       <c r="M96" s="14" t="n"/>
       <c r="N96" s="14" t="n"/>
       <c r="O96" s="14" t="n"/>
       <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14" t="n"/>
+      <c r="R96" s="14" t="n"/>
+      <c r="S96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -3046,19 +3352,22 @@
       <c r="D97" s="9" t="n"/>
       <c r="E97" s="10" t="n"/>
       <c r="F97" s="10" t="n"/>
-      <c r="G97" s="11" t="n"/>
-      <c r="H97" s="11" t="n"/>
-      <c r="I97" s="9">
-        <f>IF(AND(G97&lt;&gt;"",H97&lt;&gt;""),H97-G97,"")</f>
-        <v/>
-      </c>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="9">
+        <f>IF(AND(J97&lt;&gt;"",K97&lt;&gt;""),K97-J97,"")</f>
+        <v/>
+      </c>
       <c r="M97" s="10" t="n"/>
       <c r="N97" s="10" t="n"/>
       <c r="O97" s="10" t="n"/>
       <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="10" t="n"/>
+      <c r="R97" s="10" t="n"/>
+      <c r="S97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -3067,19 +3376,22 @@
       <c r="D98" s="13" t="n"/>
       <c r="E98" s="14" t="n"/>
       <c r="F98" s="14" t="n"/>
-      <c r="G98" s="15" t="n"/>
-      <c r="H98" s="15" t="n"/>
-      <c r="I98" s="13">
-        <f>IF(AND(G98&lt;&gt;"",H98&lt;&gt;""),H98-G98,"")</f>
-        <v/>
-      </c>
-      <c r="J98" s="14" t="n"/>
-      <c r="K98" s="14" t="n"/>
-      <c r="L98" s="14" t="n"/>
+      <c r="G98" s="14" t="n"/>
+      <c r="H98" s="14" t="n"/>
+      <c r="I98" s="14" t="n"/>
+      <c r="J98" s="15" t="n"/>
+      <c r="K98" s="15" t="n"/>
+      <c r="L98" s="13">
+        <f>IF(AND(J98&lt;&gt;"",K98&lt;&gt;""),K98-J98,"")</f>
+        <v/>
+      </c>
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
       <c r="O98" s="14" t="n"/>
       <c r="P98" s="14" t="n"/>
+      <c r="Q98" s="14" t="n"/>
+      <c r="R98" s="14" t="n"/>
+      <c r="S98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -3088,19 +3400,22 @@
       <c r="D99" s="9" t="n"/>
       <c r="E99" s="10" t="n"/>
       <c r="F99" s="10" t="n"/>
-      <c r="G99" s="11" t="n"/>
-      <c r="H99" s="11" t="n"/>
-      <c r="I99" s="9">
-        <f>IF(AND(G99&lt;&gt;"",H99&lt;&gt;""),H99-G99,"")</f>
-        <v/>
-      </c>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="9">
+        <f>IF(AND(J99&lt;&gt;"",K99&lt;&gt;""),K99-J99,"")</f>
+        <v/>
+      </c>
       <c r="M99" s="10" t="n"/>
       <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
       <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -3109,19 +3424,22 @@
       <c r="D100" s="13" t="n"/>
       <c r="E100" s="14" t="n"/>
       <c r="F100" s="14" t="n"/>
-      <c r="G100" s="15" t="n"/>
-      <c r="H100" s="15" t="n"/>
-      <c r="I100" s="13">
-        <f>IF(AND(G100&lt;&gt;"",H100&lt;&gt;""),H100-G100,"")</f>
-        <v/>
-      </c>
-      <c r="J100" s="14" t="n"/>
-      <c r="K100" s="14" t="n"/>
-      <c r="L100" s="14" t="n"/>
+      <c r="G100" s="14" t="n"/>
+      <c r="H100" s="14" t="n"/>
+      <c r="I100" s="14" t="n"/>
+      <c r="J100" s="15" t="n"/>
+      <c r="K100" s="15" t="n"/>
+      <c r="L100" s="13">
+        <f>IF(AND(J100&lt;&gt;"",K100&lt;&gt;""),K100-J100,"")</f>
+        <v/>
+      </c>
       <c r="M100" s="14" t="n"/>
       <c r="N100" s="14" t="n"/>
       <c r="O100" s="14" t="n"/>
       <c r="P100" s="14" t="n"/>
+      <c r="Q100" s="14" t="n"/>
+      <c r="R100" s="14" t="n"/>
+      <c r="S100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -3130,19 +3448,22 @@
       <c r="D101" s="9" t="n"/>
       <c r="E101" s="10" t="n"/>
       <c r="F101" s="10" t="n"/>
-      <c r="G101" s="11" t="n"/>
-      <c r="H101" s="11" t="n"/>
-      <c r="I101" s="9">
-        <f>IF(AND(G101&lt;&gt;"",H101&lt;&gt;""),H101-G101,"")</f>
-        <v/>
-      </c>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="10" t="n"/>
+      <c r="J101" s="11" t="n"/>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="9">
+        <f>IF(AND(J101&lt;&gt;"",K101&lt;&gt;""),K101-J101,"")</f>
+        <v/>
+      </c>
       <c r="M101" s="10" t="n"/>
       <c r="N101" s="10" t="n"/>
       <c r="O101" s="10" t="n"/>
       <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="10" t="n"/>
+      <c r="S101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -3151,29 +3472,32 @@
       <c r="D102" s="13" t="n"/>
       <c r="E102" s="14" t="n"/>
       <c r="F102" s="14" t="n"/>
-      <c r="G102" s="15" t="n"/>
-      <c r="H102" s="15" t="n"/>
-      <c r="I102" s="13">
-        <f>IF(AND(G102&lt;&gt;"",H102&lt;&gt;""),H102-G102,"")</f>
-        <v/>
-      </c>
-      <c r="J102" s="14" t="n"/>
-      <c r="K102" s="14" t="n"/>
-      <c r="L102" s="14" t="n"/>
+      <c r="G102" s="14" t="n"/>
+      <c r="H102" s="14" t="n"/>
+      <c r="I102" s="14" t="n"/>
+      <c r="J102" s="15" t="n"/>
+      <c r="K102" s="15" t="n"/>
+      <c r="L102" s="13">
+        <f>IF(AND(J102&lt;&gt;"",K102&lt;&gt;""),K102-J102,"")</f>
+        <v/>
+      </c>
       <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
       <c r="O102" s="14" t="n"/>
       <c r="P102" s="14" t="n"/>
+      <c r="Q102" s="14" t="n"/>
+      <c r="R102" s="14" t="n"/>
+      <c r="S102" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P2"/>
+  <autoFilter ref="A2:S2"/>
   <mergeCells count="4">
-    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="R1:S1"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="E1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K3:K102">
+  <conditionalFormatting sqref="N3:N102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"自家移植"</formula>
     </cfRule>
@@ -3202,7 +3526,7 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O102">
+  <conditionalFormatting sqref="R3:R102">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"入院中"</formula>
     </cfRule>
@@ -3213,7 +3537,7 @@
       <formula>"外来移行"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J102">
+  <conditionalFormatting sqref="M3:M102">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="9">
       <formula>"3"</formula>
     </cfRule>
@@ -3221,7 +3545,7 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N102">
+  <conditionalFormatting sqref="Q3:Q102">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="1">
       <formula>"CR"</formula>
     </cfRule>
@@ -3256,7 +3580,33 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <conditionalFormatting sqref="I3:I102">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="10">
+      <formula>"Favorable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="10">
+      <formula>"Low"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="0">
+      <formula>"Standard"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="5">
+      <formula>"Intermediate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="2">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="9">
+      <formula>"Adverse"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="9">
+      <formula>"Very high"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="12">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="11">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
@@ -3266,23 +3616,41 @@
     <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"I,II,III,IV,Limited,Extensive,ISS-I,ISS-II,ISS-III,R-ISS-I,R-ISS-II,R-ISS-III,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"t(8;21),inv(16),t(15;17),t(9;11),t(6;9),inv(3),t(v;11q23),del(5q),-5,del(7q),-7,complex,normal karyotype,t(9;22)/BCR-ABL,t(4;11),t(1;19),hyper(&gt;50),hypo(&lt;44),t(4;14),t(14;16),t(11;14),del(17p),gain(1q),del(20q),del(5q) isolated,その他,検査中,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"FLT3-ITD,FLT3-TKD,NPM1,CEBPA(bi),RUNX1,ASXL1,TP53,IDH1,IDH2,DNMT3A,KIT,IKZF1,PAX5,Ph-like,SF3B1,SRSF2,U2AF1,ZRSR2,EZH2,del(17p)/TP53,MYC rearr.,BCL2 rearr.,BCL6 rearr.,Double-hit,Triple-hit,その他,検査中,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"Favorable,Intermediate,Adverse,Very high,High,Standard,Low,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"0,1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="Q3:Q102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="R3:R102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"入院中,退院済,外来移行"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;10 入院患者</oddHeader>
+    <oddFooter>&amp;C&amp;8 &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3291,7 +3659,7 @@
   <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4952,7 +5320,16 @@
       <formula1>"要,不要,済"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;10 他科コンサルト</oddHeader>
+    <oddFooter>&amp;C&amp;8 &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4961,9 +5338,9 @@
   <sheetPr>
     <tabColor rgb="00C55A11"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4975,12 +5352,15 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5006,15 +5386,18 @@
       </c>
       <c r="I1" s="32" t="n"/>
       <c r="J1" s="32" t="n"/>
-      <c r="K1" s="31" t="inlineStr">
-        <is>
-          <t>治療</t>
-        </is>
-      </c>
+      <c r="K1" s="32" t="n"/>
       <c r="L1" s="32" t="n"/>
       <c r="M1" s="32" t="n"/>
-      <c r="N1" s="32" t="n"/>
-      <c r="O1" s="31" t="inlineStr">
+      <c r="N1" s="31" t="inlineStr">
+        <is>
+          <t>治療</t>
+        </is>
+      </c>
+      <c r="O1" s="32" t="n"/>
+      <c r="P1" s="32" t="n"/>
+      <c r="Q1" s="32" t="n"/>
+      <c r="R1" s="31" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
@@ -5068,30 +5451,45 @@
       </c>
       <c r="J2" s="33" t="inlineStr">
         <is>
+          <t>染色体</t>
+        </is>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t>遺伝子</t>
+        </is>
+      </c>
+      <c r="L2" s="33" t="inlineStr">
+        <is>
+          <t>リスク分類</t>
+        </is>
+      </c>
+      <c r="M2" s="33" t="inlineStr">
+        <is>
           <t>PS</t>
         </is>
       </c>
-      <c r="K2" s="33" t="inlineStr">
+      <c r="N2" s="33" t="inlineStr">
         <is>
           <t>治療区分</t>
         </is>
       </c>
-      <c r="L2" s="33" t="inlineStr">
+      <c r="O2" s="33" t="inlineStr">
         <is>
           <t>治療レジメン</t>
         </is>
       </c>
-      <c r="M2" s="33" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t>転帰</t>
         </is>
       </c>
-      <c r="N2" s="33" t="inlineStr">
+      <c r="Q2" s="33" t="inlineStr">
         <is>
           <t>次回予約日</t>
         </is>
       </c>
-      <c r="O2" s="33" t="inlineStr">
+      <c r="R2" s="33" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -5111,8 +5509,11 @@
       <c r="K3" s="10" t="n"/>
       <c r="L3" s="10" t="n"/>
       <c r="M3" s="10" t="n"/>
-      <c r="N3" s="11" t="n"/>
+      <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="34" t="n"/>
@@ -5128,8 +5529,11 @@
       <c r="K4" s="37" t="n"/>
       <c r="L4" s="37" t="n"/>
       <c r="M4" s="37" t="n"/>
-      <c r="N4" s="36" t="n"/>
+      <c r="N4" s="37" t="n"/>
       <c r="O4" s="37" t="n"/>
+      <c r="P4" s="37" t="n"/>
+      <c r="Q4" s="36" t="n"/>
+      <c r="R4" s="37" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -5145,8 +5549,11 @@
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="n"/>
       <c r="M5" s="10" t="n"/>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="34" t="n"/>
@@ -5162,8 +5569,11 @@
       <c r="K6" s="37" t="n"/>
       <c r="L6" s="37" t="n"/>
       <c r="M6" s="37" t="n"/>
-      <c r="N6" s="36" t="n"/>
+      <c r="N6" s="37" t="n"/>
       <c r="O6" s="37" t="n"/>
+      <c r="P6" s="37" t="n"/>
+      <c r="Q6" s="36" t="n"/>
+      <c r="R6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -5179,8 +5589,11 @@
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="34" t="n"/>
@@ -5196,8 +5609,11 @@
       <c r="K8" s="37" t="n"/>
       <c r="L8" s="37" t="n"/>
       <c r="M8" s="37" t="n"/>
-      <c r="N8" s="36" t="n"/>
+      <c r="N8" s="37" t="n"/>
       <c r="O8" s="37" t="n"/>
+      <c r="P8" s="37" t="n"/>
+      <c r="Q8" s="36" t="n"/>
+      <c r="R8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -5213,8 +5629,11 @@
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
-      <c r="N9" s="11" t="n"/>
+      <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n"/>
@@ -5230,8 +5649,11 @@
       <c r="K10" s="37" t="n"/>
       <c r="L10" s="37" t="n"/>
       <c r="M10" s="37" t="n"/>
-      <c r="N10" s="36" t="n"/>
+      <c r="N10" s="37" t="n"/>
       <c r="O10" s="37" t="n"/>
+      <c r="P10" s="37" t="n"/>
+      <c r="Q10" s="36" t="n"/>
+      <c r="R10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -5247,8 +5669,11 @@
       <c r="K11" s="10" t="n"/>
       <c r="L11" s="10" t="n"/>
       <c r="M11" s="10" t="n"/>
-      <c r="N11" s="11" t="n"/>
+      <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n"/>
@@ -5264,8 +5689,11 @@
       <c r="K12" s="37" t="n"/>
       <c r="L12" s="37" t="n"/>
       <c r="M12" s="37" t="n"/>
-      <c r="N12" s="36" t="n"/>
+      <c r="N12" s="37" t="n"/>
       <c r="O12" s="37" t="n"/>
+      <c r="P12" s="37" t="n"/>
+      <c r="Q12" s="36" t="n"/>
+      <c r="R12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -5281,8 +5709,11 @@
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="n"/>
       <c r="M13" s="10" t="n"/>
-      <c r="N13" s="11" t="n"/>
+      <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n"/>
@@ -5298,8 +5729,11 @@
       <c r="K14" s="37" t="n"/>
       <c r="L14" s="37" t="n"/>
       <c r="M14" s="37" t="n"/>
-      <c r="N14" s="36" t="n"/>
+      <c r="N14" s="37" t="n"/>
       <c r="O14" s="37" t="n"/>
+      <c r="P14" s="37" t="n"/>
+      <c r="Q14" s="36" t="n"/>
+      <c r="R14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -5315,8 +5749,11 @@
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="10" t="n"/>
-      <c r="N15" s="11" t="n"/>
+      <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="34" t="n"/>
@@ -5332,8 +5769,11 @@
       <c r="K16" s="37" t="n"/>
       <c r="L16" s="37" t="n"/>
       <c r="M16" s="37" t="n"/>
-      <c r="N16" s="36" t="n"/>
+      <c r="N16" s="37" t="n"/>
       <c r="O16" s="37" t="n"/>
+      <c r="P16" s="37" t="n"/>
+      <c r="Q16" s="36" t="n"/>
+      <c r="R16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -5349,8 +5789,11 @@
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="10" t="n"/>
-      <c r="N17" s="11" t="n"/>
+      <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+      <c r="R17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="34" t="n"/>
@@ -5366,8 +5809,11 @@
       <c r="K18" s="37" t="n"/>
       <c r="L18" s="37" t="n"/>
       <c r="M18" s="37" t="n"/>
-      <c r="N18" s="36" t="n"/>
+      <c r="N18" s="37" t="n"/>
       <c r="O18" s="37" t="n"/>
+      <c r="P18" s="37" t="n"/>
+      <c r="Q18" s="36" t="n"/>
+      <c r="R18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -5383,8 +5829,11 @@
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
-      <c r="N19" s="11" t="n"/>
+      <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="34" t="n"/>
@@ -5400,8 +5849,11 @@
       <c r="K20" s="37" t="n"/>
       <c r="L20" s="37" t="n"/>
       <c r="M20" s="37" t="n"/>
-      <c r="N20" s="36" t="n"/>
+      <c r="N20" s="37" t="n"/>
       <c r="O20" s="37" t="n"/>
+      <c r="P20" s="37" t="n"/>
+      <c r="Q20" s="36" t="n"/>
+      <c r="R20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -5417,8 +5869,11 @@
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
-      <c r="N21" s="11" t="n"/>
+      <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="34" t="n"/>
@@ -5434,8 +5889,11 @@
       <c r="K22" s="37" t="n"/>
       <c r="L22" s="37" t="n"/>
       <c r="M22" s="37" t="n"/>
-      <c r="N22" s="36" t="n"/>
+      <c r="N22" s="37" t="n"/>
       <c r="O22" s="37" t="n"/>
+      <c r="P22" s="37" t="n"/>
+      <c r="Q22" s="36" t="n"/>
+      <c r="R22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -5451,8 +5909,11 @@
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
-      <c r="N23" s="11" t="n"/>
+      <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="11" t="n"/>
+      <c r="R23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="34" t="n"/>
@@ -5468,8 +5929,11 @@
       <c r="K24" s="37" t="n"/>
       <c r="L24" s="37" t="n"/>
       <c r="M24" s="37" t="n"/>
-      <c r="N24" s="36" t="n"/>
+      <c r="N24" s="37" t="n"/>
       <c r="O24" s="37" t="n"/>
+      <c r="P24" s="37" t="n"/>
+      <c r="Q24" s="36" t="n"/>
+      <c r="R24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -5485,8 +5949,11 @@
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="n"/>
       <c r="M25" s="10" t="n"/>
-      <c r="N25" s="11" t="n"/>
+      <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="34" t="n"/>
@@ -5502,8 +5969,11 @@
       <c r="K26" s="37" t="n"/>
       <c r="L26" s="37" t="n"/>
       <c r="M26" s="37" t="n"/>
-      <c r="N26" s="36" t="n"/>
+      <c r="N26" s="37" t="n"/>
       <c r="O26" s="37" t="n"/>
+      <c r="P26" s="37" t="n"/>
+      <c r="Q26" s="36" t="n"/>
+      <c r="R26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -5519,8 +5989,11 @@
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
-      <c r="N27" s="11" t="n"/>
+      <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="11" t="n"/>
+      <c r="R27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="34" t="n"/>
@@ -5536,8 +6009,11 @@
       <c r="K28" s="37" t="n"/>
       <c r="L28" s="37" t="n"/>
       <c r="M28" s="37" t="n"/>
-      <c r="N28" s="36" t="n"/>
+      <c r="N28" s="37" t="n"/>
       <c r="O28" s="37" t="n"/>
+      <c r="P28" s="37" t="n"/>
+      <c r="Q28" s="36" t="n"/>
+      <c r="R28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -5553,8 +6029,11 @@
       <c r="K29" s="10" t="n"/>
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="10" t="n"/>
-      <c r="N29" s="11" t="n"/>
+      <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="11" t="n"/>
+      <c r="R29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="34" t="n"/>
@@ -5570,8 +6049,11 @@
       <c r="K30" s="37" t="n"/>
       <c r="L30" s="37" t="n"/>
       <c r="M30" s="37" t="n"/>
-      <c r="N30" s="36" t="n"/>
+      <c r="N30" s="37" t="n"/>
       <c r="O30" s="37" t="n"/>
+      <c r="P30" s="37" t="n"/>
+      <c r="Q30" s="36" t="n"/>
+      <c r="R30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -5587,8 +6069,11 @@
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="n"/>
       <c r="M31" s="10" t="n"/>
-      <c r="N31" s="11" t="n"/>
+      <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="34" t="n"/>
@@ -5604,8 +6089,11 @@
       <c r="K32" s="37" t="n"/>
       <c r="L32" s="37" t="n"/>
       <c r="M32" s="37" t="n"/>
-      <c r="N32" s="36" t="n"/>
+      <c r="N32" s="37" t="n"/>
       <c r="O32" s="37" t="n"/>
+      <c r="P32" s="37" t="n"/>
+      <c r="Q32" s="36" t="n"/>
+      <c r="R32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -5621,8 +6109,11 @@
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
       <c r="M33" s="10" t="n"/>
-      <c r="N33" s="11" t="n"/>
+      <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="34" t="n"/>
@@ -5638,8 +6129,11 @@
       <c r="K34" s="37" t="n"/>
       <c r="L34" s="37" t="n"/>
       <c r="M34" s="37" t="n"/>
-      <c r="N34" s="36" t="n"/>
+      <c r="N34" s="37" t="n"/>
       <c r="O34" s="37" t="n"/>
+      <c r="P34" s="37" t="n"/>
+      <c r="Q34" s="36" t="n"/>
+      <c r="R34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -5655,8 +6149,11 @@
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
       <c r="M35" s="10" t="n"/>
-      <c r="N35" s="11" t="n"/>
+      <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="11" t="n"/>
+      <c r="R35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="34" t="n"/>
@@ -5672,8 +6169,11 @@
       <c r="K36" s="37" t="n"/>
       <c r="L36" s="37" t="n"/>
       <c r="M36" s="37" t="n"/>
-      <c r="N36" s="36" t="n"/>
+      <c r="N36" s="37" t="n"/>
       <c r="O36" s="37" t="n"/>
+      <c r="P36" s="37" t="n"/>
+      <c r="Q36" s="36" t="n"/>
+      <c r="R36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -5689,8 +6189,11 @@
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
-      <c r="N37" s="11" t="n"/>
+      <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="34" t="n"/>
@@ -5706,8 +6209,11 @@
       <c r="K38" s="37" t="n"/>
       <c r="L38" s="37" t="n"/>
       <c r="M38" s="37" t="n"/>
-      <c r="N38" s="36" t="n"/>
+      <c r="N38" s="37" t="n"/>
       <c r="O38" s="37" t="n"/>
+      <c r="P38" s="37" t="n"/>
+      <c r="Q38" s="36" t="n"/>
+      <c r="R38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -5723,8 +6229,11 @@
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
       <c r="M39" s="10" t="n"/>
-      <c r="N39" s="11" t="n"/>
+      <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="11" t="n"/>
+      <c r="R39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="34" t="n"/>
@@ -5740,8 +6249,11 @@
       <c r="K40" s="37" t="n"/>
       <c r="L40" s="37" t="n"/>
       <c r="M40" s="37" t="n"/>
-      <c r="N40" s="36" t="n"/>
+      <c r="N40" s="37" t="n"/>
       <c r="O40" s="37" t="n"/>
+      <c r="P40" s="37" t="n"/>
+      <c r="Q40" s="36" t="n"/>
+      <c r="R40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -5757,8 +6269,11 @@
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
       <c r="M41" s="10" t="n"/>
-      <c r="N41" s="11" t="n"/>
+      <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="11" t="n"/>
+      <c r="R41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="34" t="n"/>
@@ -5774,8 +6289,11 @@
       <c r="K42" s="37" t="n"/>
       <c r="L42" s="37" t="n"/>
       <c r="M42" s="37" t="n"/>
-      <c r="N42" s="36" t="n"/>
+      <c r="N42" s="37" t="n"/>
       <c r="O42" s="37" t="n"/>
+      <c r="P42" s="37" t="n"/>
+      <c r="Q42" s="36" t="n"/>
+      <c r="R42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -5791,8 +6309,11 @@
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
       <c r="M43" s="10" t="n"/>
-      <c r="N43" s="11" t="n"/>
+      <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="11" t="n"/>
+      <c r="R43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="34" t="n"/>
@@ -5808,8 +6329,11 @@
       <c r="K44" s="37" t="n"/>
       <c r="L44" s="37" t="n"/>
       <c r="M44" s="37" t="n"/>
-      <c r="N44" s="36" t="n"/>
+      <c r="N44" s="37" t="n"/>
       <c r="O44" s="37" t="n"/>
+      <c r="P44" s="37" t="n"/>
+      <c r="Q44" s="36" t="n"/>
+      <c r="R44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -5825,8 +6349,11 @@
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
       <c r="M45" s="10" t="n"/>
-      <c r="N45" s="11" t="n"/>
+      <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="11" t="n"/>
+      <c r="R45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="34" t="n"/>
@@ -5842,8 +6369,11 @@
       <c r="K46" s="37" t="n"/>
       <c r="L46" s="37" t="n"/>
       <c r="M46" s="37" t="n"/>
-      <c r="N46" s="36" t="n"/>
+      <c r="N46" s="37" t="n"/>
       <c r="O46" s="37" t="n"/>
+      <c r="P46" s="37" t="n"/>
+      <c r="Q46" s="36" t="n"/>
+      <c r="R46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -5859,8 +6389,11 @@
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="n"/>
       <c r="M47" s="10" t="n"/>
-      <c r="N47" s="11" t="n"/>
+      <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="11" t="n"/>
+      <c r="R47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="34" t="n"/>
@@ -5876,8 +6409,11 @@
       <c r="K48" s="37" t="n"/>
       <c r="L48" s="37" t="n"/>
       <c r="M48" s="37" t="n"/>
-      <c r="N48" s="36" t="n"/>
+      <c r="N48" s="37" t="n"/>
       <c r="O48" s="37" t="n"/>
+      <c r="P48" s="37" t="n"/>
+      <c r="Q48" s="36" t="n"/>
+      <c r="R48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -5893,8 +6429,11 @@
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
       <c r="M49" s="10" t="n"/>
-      <c r="N49" s="11" t="n"/>
+      <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="11" t="n"/>
+      <c r="R49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="34" t="n"/>
@@ -5910,8 +6449,11 @@
       <c r="K50" s="37" t="n"/>
       <c r="L50" s="37" t="n"/>
       <c r="M50" s="37" t="n"/>
-      <c r="N50" s="36" t="n"/>
+      <c r="N50" s="37" t="n"/>
       <c r="O50" s="37" t="n"/>
+      <c r="P50" s="37" t="n"/>
+      <c r="Q50" s="36" t="n"/>
+      <c r="R50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -5927,8 +6469,11 @@
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
       <c r="M51" s="10" t="n"/>
-      <c r="N51" s="11" t="n"/>
+      <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="11" t="n"/>
+      <c r="R51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="34" t="n"/>
@@ -5944,8 +6489,11 @@
       <c r="K52" s="37" t="n"/>
       <c r="L52" s="37" t="n"/>
       <c r="M52" s="37" t="n"/>
-      <c r="N52" s="36" t="n"/>
+      <c r="N52" s="37" t="n"/>
       <c r="O52" s="37" t="n"/>
+      <c r="P52" s="37" t="n"/>
+      <c r="Q52" s="36" t="n"/>
+      <c r="R52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -5961,8 +6509,11 @@
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="10" t="n"/>
-      <c r="N53" s="11" t="n"/>
+      <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="11" t="n"/>
+      <c r="R53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="34" t="n"/>
@@ -5978,8 +6529,11 @@
       <c r="K54" s="37" t="n"/>
       <c r="L54" s="37" t="n"/>
       <c r="M54" s="37" t="n"/>
-      <c r="N54" s="36" t="n"/>
+      <c r="N54" s="37" t="n"/>
       <c r="O54" s="37" t="n"/>
+      <c r="P54" s="37" t="n"/>
+      <c r="Q54" s="36" t="n"/>
+      <c r="R54" s="37" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -5995,8 +6549,11 @@
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
-      <c r="N55" s="11" t="n"/>
+      <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="11" t="n"/>
+      <c r="R55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="34" t="n"/>
@@ -6012,8 +6569,11 @@
       <c r="K56" s="37" t="n"/>
       <c r="L56" s="37" t="n"/>
       <c r="M56" s="37" t="n"/>
-      <c r="N56" s="36" t="n"/>
+      <c r="N56" s="37" t="n"/>
       <c r="O56" s="37" t="n"/>
+      <c r="P56" s="37" t="n"/>
+      <c r="Q56" s="36" t="n"/>
+      <c r="R56" s="37" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -6029,8 +6589,11 @@
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
       <c r="M57" s="10" t="n"/>
-      <c r="N57" s="11" t="n"/>
+      <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="11" t="n"/>
+      <c r="R57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="34" t="n"/>
@@ -6046,8 +6609,11 @@
       <c r="K58" s="37" t="n"/>
       <c r="L58" s="37" t="n"/>
       <c r="M58" s="37" t="n"/>
-      <c r="N58" s="36" t="n"/>
+      <c r="N58" s="37" t="n"/>
       <c r="O58" s="37" t="n"/>
+      <c r="P58" s="37" t="n"/>
+      <c r="Q58" s="36" t="n"/>
+      <c r="R58" s="37" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -6063,8 +6629,11 @@
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
       <c r="M59" s="10" t="n"/>
-      <c r="N59" s="11" t="n"/>
+      <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="11" t="n"/>
+      <c r="R59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="34" t="n"/>
@@ -6080,8 +6649,11 @@
       <c r="K60" s="37" t="n"/>
       <c r="L60" s="37" t="n"/>
       <c r="M60" s="37" t="n"/>
-      <c r="N60" s="36" t="n"/>
+      <c r="N60" s="37" t="n"/>
       <c r="O60" s="37" t="n"/>
+      <c r="P60" s="37" t="n"/>
+      <c r="Q60" s="36" t="n"/>
+      <c r="R60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -6097,8 +6669,11 @@
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
       <c r="M61" s="10" t="n"/>
-      <c r="N61" s="11" t="n"/>
+      <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="11" t="n"/>
+      <c r="R61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="34" t="n"/>
@@ -6114,8 +6689,11 @@
       <c r="K62" s="37" t="n"/>
       <c r="L62" s="37" t="n"/>
       <c r="M62" s="37" t="n"/>
-      <c r="N62" s="36" t="n"/>
+      <c r="N62" s="37" t="n"/>
       <c r="O62" s="37" t="n"/>
+      <c r="P62" s="37" t="n"/>
+      <c r="Q62" s="36" t="n"/>
+      <c r="R62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -6131,8 +6709,11 @@
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
       <c r="M63" s="10" t="n"/>
-      <c r="N63" s="11" t="n"/>
+      <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="11" t="n"/>
+      <c r="R63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="34" t="n"/>
@@ -6148,8 +6729,11 @@
       <c r="K64" s="37" t="n"/>
       <c r="L64" s="37" t="n"/>
       <c r="M64" s="37" t="n"/>
-      <c r="N64" s="36" t="n"/>
+      <c r="N64" s="37" t="n"/>
       <c r="O64" s="37" t="n"/>
+      <c r="P64" s="37" t="n"/>
+      <c r="Q64" s="36" t="n"/>
+      <c r="R64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -6165,8 +6749,11 @@
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
       <c r="M65" s="10" t="n"/>
-      <c r="N65" s="11" t="n"/>
+      <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="11" t="n"/>
+      <c r="R65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="34" t="n"/>
@@ -6182,8 +6769,11 @@
       <c r="K66" s="37" t="n"/>
       <c r="L66" s="37" t="n"/>
       <c r="M66" s="37" t="n"/>
-      <c r="N66" s="36" t="n"/>
+      <c r="N66" s="37" t="n"/>
       <c r="O66" s="37" t="n"/>
+      <c r="P66" s="37" t="n"/>
+      <c r="Q66" s="36" t="n"/>
+      <c r="R66" s="37" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -6199,8 +6789,11 @@
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="10" t="n"/>
       <c r="M67" s="10" t="n"/>
-      <c r="N67" s="11" t="n"/>
+      <c r="N67" s="10" t="n"/>
       <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="11" t="n"/>
+      <c r="R67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="34" t="n"/>
@@ -6216,8 +6809,11 @@
       <c r="K68" s="37" t="n"/>
       <c r="L68" s="37" t="n"/>
       <c r="M68" s="37" t="n"/>
-      <c r="N68" s="36" t="n"/>
+      <c r="N68" s="37" t="n"/>
       <c r="O68" s="37" t="n"/>
+      <c r="P68" s="37" t="n"/>
+      <c r="Q68" s="36" t="n"/>
+      <c r="R68" s="37" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -6233,8 +6829,11 @@
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="10" t="n"/>
       <c r="M69" s="10" t="n"/>
-      <c r="N69" s="11" t="n"/>
+      <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="11" t="n"/>
+      <c r="R69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="34" t="n"/>
@@ -6250,8 +6849,11 @@
       <c r="K70" s="37" t="n"/>
       <c r="L70" s="37" t="n"/>
       <c r="M70" s="37" t="n"/>
-      <c r="N70" s="36" t="n"/>
+      <c r="N70" s="37" t="n"/>
       <c r="O70" s="37" t="n"/>
+      <c r="P70" s="37" t="n"/>
+      <c r="Q70" s="36" t="n"/>
+      <c r="R70" s="37" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -6267,8 +6869,11 @@
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
       <c r="M71" s="10" t="n"/>
-      <c r="N71" s="11" t="n"/>
+      <c r="N71" s="10" t="n"/>
       <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="11" t="n"/>
+      <c r="R71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="34" t="n"/>
@@ -6284,8 +6889,11 @@
       <c r="K72" s="37" t="n"/>
       <c r="L72" s="37" t="n"/>
       <c r="M72" s="37" t="n"/>
-      <c r="N72" s="36" t="n"/>
+      <c r="N72" s="37" t="n"/>
       <c r="O72" s="37" t="n"/>
+      <c r="P72" s="37" t="n"/>
+      <c r="Q72" s="36" t="n"/>
+      <c r="R72" s="37" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -6301,8 +6909,11 @@
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
       <c r="M73" s="10" t="n"/>
-      <c r="N73" s="11" t="n"/>
+      <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="11" t="n"/>
+      <c r="R73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="34" t="n"/>
@@ -6318,8 +6929,11 @@
       <c r="K74" s="37" t="n"/>
       <c r="L74" s="37" t="n"/>
       <c r="M74" s="37" t="n"/>
-      <c r="N74" s="36" t="n"/>
+      <c r="N74" s="37" t="n"/>
       <c r="O74" s="37" t="n"/>
+      <c r="P74" s="37" t="n"/>
+      <c r="Q74" s="36" t="n"/>
+      <c r="R74" s="37" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -6335,8 +6949,11 @@
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
       <c r="M75" s="10" t="n"/>
-      <c r="N75" s="11" t="n"/>
+      <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="11" t="n"/>
+      <c r="R75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="34" t="n"/>
@@ -6352,8 +6969,11 @@
       <c r="K76" s="37" t="n"/>
       <c r="L76" s="37" t="n"/>
       <c r="M76" s="37" t="n"/>
-      <c r="N76" s="36" t="n"/>
+      <c r="N76" s="37" t="n"/>
       <c r="O76" s="37" t="n"/>
+      <c r="P76" s="37" t="n"/>
+      <c r="Q76" s="36" t="n"/>
+      <c r="R76" s="37" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -6369,8 +6989,11 @@
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
       <c r="M77" s="10" t="n"/>
-      <c r="N77" s="11" t="n"/>
+      <c r="N77" s="10" t="n"/>
       <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="11" t="n"/>
+      <c r="R77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="34" t="n"/>
@@ -6386,8 +7009,11 @@
       <c r="K78" s="37" t="n"/>
       <c r="L78" s="37" t="n"/>
       <c r="M78" s="37" t="n"/>
-      <c r="N78" s="36" t="n"/>
+      <c r="N78" s="37" t="n"/>
       <c r="O78" s="37" t="n"/>
+      <c r="P78" s="37" t="n"/>
+      <c r="Q78" s="36" t="n"/>
+      <c r="R78" s="37" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -6403,8 +7029,11 @@
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
       <c r="M79" s="10" t="n"/>
-      <c r="N79" s="11" t="n"/>
+      <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="11" t="n"/>
+      <c r="R79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="34" t="n"/>
@@ -6420,8 +7049,11 @@
       <c r="K80" s="37" t="n"/>
       <c r="L80" s="37" t="n"/>
       <c r="M80" s="37" t="n"/>
-      <c r="N80" s="36" t="n"/>
+      <c r="N80" s="37" t="n"/>
       <c r="O80" s="37" t="n"/>
+      <c r="P80" s="37" t="n"/>
+      <c r="Q80" s="36" t="n"/>
+      <c r="R80" s="37" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -6437,8 +7069,11 @@
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
       <c r="M81" s="10" t="n"/>
-      <c r="N81" s="11" t="n"/>
+      <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="11" t="n"/>
+      <c r="R81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="34" t="n"/>
@@ -6454,8 +7089,11 @@
       <c r="K82" s="37" t="n"/>
       <c r="L82" s="37" t="n"/>
       <c r="M82" s="37" t="n"/>
-      <c r="N82" s="36" t="n"/>
+      <c r="N82" s="37" t="n"/>
       <c r="O82" s="37" t="n"/>
+      <c r="P82" s="37" t="n"/>
+      <c r="Q82" s="36" t="n"/>
+      <c r="R82" s="37" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -6471,8 +7109,11 @@
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
       <c r="M83" s="10" t="n"/>
-      <c r="N83" s="11" t="n"/>
+      <c r="N83" s="10" t="n"/>
       <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="11" t="n"/>
+      <c r="R83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="34" t="n"/>
@@ -6488,8 +7129,11 @@
       <c r="K84" s="37" t="n"/>
       <c r="L84" s="37" t="n"/>
       <c r="M84" s="37" t="n"/>
-      <c r="N84" s="36" t="n"/>
+      <c r="N84" s="37" t="n"/>
       <c r="O84" s="37" t="n"/>
+      <c r="P84" s="37" t="n"/>
+      <c r="Q84" s="36" t="n"/>
+      <c r="R84" s="37" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -6505,8 +7149,11 @@
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
       <c r="M85" s="10" t="n"/>
-      <c r="N85" s="11" t="n"/>
+      <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="11" t="n"/>
+      <c r="R85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="34" t="n"/>
@@ -6522,8 +7169,11 @@
       <c r="K86" s="37" t="n"/>
       <c r="L86" s="37" t="n"/>
       <c r="M86" s="37" t="n"/>
-      <c r="N86" s="36" t="n"/>
+      <c r="N86" s="37" t="n"/>
       <c r="O86" s="37" t="n"/>
+      <c r="P86" s="37" t="n"/>
+      <c r="Q86" s="36" t="n"/>
+      <c r="R86" s="37" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -6539,8 +7189,11 @@
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="10" t="n"/>
       <c r="M87" s="10" t="n"/>
-      <c r="N87" s="11" t="n"/>
+      <c r="N87" s="10" t="n"/>
       <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="11" t="n"/>
+      <c r="R87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="34" t="n"/>
@@ -6556,8 +7209,11 @@
       <c r="K88" s="37" t="n"/>
       <c r="L88" s="37" t="n"/>
       <c r="M88" s="37" t="n"/>
-      <c r="N88" s="36" t="n"/>
+      <c r="N88" s="37" t="n"/>
       <c r="O88" s="37" t="n"/>
+      <c r="P88" s="37" t="n"/>
+      <c r="Q88" s="36" t="n"/>
+      <c r="R88" s="37" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -6573,8 +7229,11 @@
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="10" t="n"/>
       <c r="M89" s="10" t="n"/>
-      <c r="N89" s="11" t="n"/>
+      <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="11" t="n"/>
+      <c r="R89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="34" t="n"/>
@@ -6590,8 +7249,11 @@
       <c r="K90" s="37" t="n"/>
       <c r="L90" s="37" t="n"/>
       <c r="M90" s="37" t="n"/>
-      <c r="N90" s="36" t="n"/>
+      <c r="N90" s="37" t="n"/>
       <c r="O90" s="37" t="n"/>
+      <c r="P90" s="37" t="n"/>
+      <c r="Q90" s="36" t="n"/>
+      <c r="R90" s="37" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -6607,8 +7269,11 @@
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="10" t="n"/>
       <c r="M91" s="10" t="n"/>
-      <c r="N91" s="11" t="n"/>
+      <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="11" t="n"/>
+      <c r="R91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="34" t="n"/>
@@ -6624,8 +7289,11 @@
       <c r="K92" s="37" t="n"/>
       <c r="L92" s="37" t="n"/>
       <c r="M92" s="37" t="n"/>
-      <c r="N92" s="36" t="n"/>
+      <c r="N92" s="37" t="n"/>
       <c r="O92" s="37" t="n"/>
+      <c r="P92" s="37" t="n"/>
+      <c r="Q92" s="36" t="n"/>
+      <c r="R92" s="37" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -6641,8 +7309,11 @@
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="10" t="n"/>
       <c r="M93" s="10" t="n"/>
-      <c r="N93" s="11" t="n"/>
+      <c r="N93" s="10" t="n"/>
       <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="11" t="n"/>
+      <c r="R93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="34" t="n"/>
@@ -6658,8 +7329,11 @@
       <c r="K94" s="37" t="n"/>
       <c r="L94" s="37" t="n"/>
       <c r="M94" s="37" t="n"/>
-      <c r="N94" s="36" t="n"/>
+      <c r="N94" s="37" t="n"/>
       <c r="O94" s="37" t="n"/>
+      <c r="P94" s="37" t="n"/>
+      <c r="Q94" s="36" t="n"/>
+      <c r="R94" s="37" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -6675,8 +7349,11 @@
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
       <c r="M95" s="10" t="n"/>
-      <c r="N95" s="11" t="n"/>
+      <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="11" t="n"/>
+      <c r="R95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="34" t="n"/>
@@ -6692,8 +7369,11 @@
       <c r="K96" s="37" t="n"/>
       <c r="L96" s="37" t="n"/>
       <c r="M96" s="37" t="n"/>
-      <c r="N96" s="36" t="n"/>
+      <c r="N96" s="37" t="n"/>
       <c r="O96" s="37" t="n"/>
+      <c r="P96" s="37" t="n"/>
+      <c r="Q96" s="36" t="n"/>
+      <c r="R96" s="37" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -6709,8 +7389,11 @@
       <c r="K97" s="10" t="n"/>
       <c r="L97" s="10" t="n"/>
       <c r="M97" s="10" t="n"/>
-      <c r="N97" s="11" t="n"/>
+      <c r="N97" s="10" t="n"/>
       <c r="O97" s="10" t="n"/>
+      <c r="P97" s="10" t="n"/>
+      <c r="Q97" s="11" t="n"/>
+      <c r="R97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="34" t="n"/>
@@ -6726,8 +7409,11 @@
       <c r="K98" s="37" t="n"/>
       <c r="L98" s="37" t="n"/>
       <c r="M98" s="37" t="n"/>
-      <c r="N98" s="36" t="n"/>
+      <c r="N98" s="37" t="n"/>
       <c r="O98" s="37" t="n"/>
+      <c r="P98" s="37" t="n"/>
+      <c r="Q98" s="36" t="n"/>
+      <c r="R98" s="37" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -6743,8 +7429,11 @@
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
       <c r="M99" s="10" t="n"/>
-      <c r="N99" s="11" t="n"/>
+      <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="11" t="n"/>
+      <c r="R99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="34" t="n"/>
@@ -6760,8 +7449,11 @@
       <c r="K100" s="37" t="n"/>
       <c r="L100" s="37" t="n"/>
       <c r="M100" s="37" t="n"/>
-      <c r="N100" s="36" t="n"/>
+      <c r="N100" s="37" t="n"/>
       <c r="O100" s="37" t="n"/>
+      <c r="P100" s="37" t="n"/>
+      <c r="Q100" s="36" t="n"/>
+      <c r="R100" s="37" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -6777,8 +7469,11 @@
       <c r="K101" s="10" t="n"/>
       <c r="L101" s="10" t="n"/>
       <c r="M101" s="10" t="n"/>
-      <c r="N101" s="11" t="n"/>
+      <c r="N101" s="10" t="n"/>
       <c r="O101" s="10" t="n"/>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="11" t="n"/>
+      <c r="R101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="34" t="n"/>
@@ -6794,18 +7489,21 @@
       <c r="K102" s="37" t="n"/>
       <c r="L102" s="37" t="n"/>
       <c r="M102" s="37" t="n"/>
-      <c r="N102" s="36" t="n"/>
+      <c r="N102" s="37" t="n"/>
       <c r="O102" s="37" t="n"/>
+      <c r="P102" s="37" t="n"/>
+      <c r="Q102" s="36" t="n"/>
+      <c r="R102" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O2"/>
+  <autoFilter ref="A2:R2"/>
   <mergeCells count="4">
-    <mergeCell ref="H1:J1"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:Q1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="K3:K102">
+  <conditionalFormatting sqref="N3:N102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"自家移植"</formula>
     </cfRule>
@@ -6834,7 +7532,7 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J102">
+  <conditionalFormatting sqref="M3:M102">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"3"</formula>
     </cfRule>
@@ -6842,7 +7540,7 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M102">
+  <conditionalFormatting sqref="P3:P102">
     <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"CR"</formula>
     </cfRule>
@@ -6877,7 +7575,33 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
+  <conditionalFormatting sqref="L3:L102">
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="10">
+      <formula>"Favorable"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" dxfId="10">
+      <formula>"Low"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
+      <formula>"Standard"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="5">
+      <formula>"Intermediate"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="2">
+      <formula>"High"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="9">
+      <formula>"Adverse"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" dxfId="9">
+      <formula>"Very high"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="equal" dxfId="12">
+      <formula>"N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="10">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"M,F"</formula1>
     </dataValidation>
@@ -6888,19 +7612,37 @@
       <formula1>"I,II,III,IV,Limited,Extensive,ISS-I,ISS-II,ISS-III,R-ISS-I,R-ISS-II,R-ISS-III,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"t(8;21),inv(16),t(15;17),t(9;11),t(6;9),inv(3),t(v;11q23),del(5q),-5,del(7q),-7,complex,normal karyotype,t(9;22)/BCR-ABL,t(4;11),t(1;19),hyper(&gt;50),hypo(&lt;44),t(4;14),t(14;16),t(11;14),del(17p),gain(1q),del(20q),del(5q) isolated,その他,検査中,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"FLT3-ITD,FLT3-TKD,NPM1,CEBPA(bi),RUNX1,ASXL1,TP53,IDH1,IDH2,DNMT3A,KIT,IKZF1,PAX5,Ph-like,SF3B1,SRSF2,U2AF1,ZRSR2,EZH2,del(17p)/TP53,MYC rearr.,BCL2 rearr.,BCL6 rearr.,Double-hit,Triple-hit,その他,検査中,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+      <formula1>"Favorable,Intermediate,Adverse,Very high,High,Standard,Low,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"0,1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="P3:P102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;10 初診外来</oddHeader>
+    <oddFooter>&amp;C&amp;8 &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6909,7 +7651,7 @@
   <sheetPr>
     <tabColor rgb="001A365D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7000,7 +7742,7 @@
         </is>
       </c>
       <c r="F6" s="42">
-        <f>COUNTIF('入院患者'!K3:K102,"化学療法")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"化学療法")</f>
         <v/>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -7009,7 +7751,7 @@
         </is>
       </c>
       <c r="I6" s="42">
-        <f>COUNTIF('入院患者'!O3:O102,"入院中")</f>
+        <f>COUNTIF('入院患者'!R3:R102,"入院中")</f>
         <v/>
       </c>
     </row>
@@ -7029,7 +7771,7 @@
         </is>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIF('入院患者'!K3:K102,"自家移植")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"自家移植")</f>
         <v/>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -7038,7 +7780,7 @@
         </is>
       </c>
       <c r="I7" s="43">
-        <f>COUNTIF('入院患者'!O3:O102,"退院済")</f>
+        <f>COUNTIF('入院患者'!R3:R102,"退院済")</f>
         <v/>
       </c>
     </row>
@@ -7058,7 +7800,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>COUNTIF('入院患者'!K3:K102,"同種移植")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"同種移植")</f>
         <v/>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -7067,7 +7809,7 @@
         </is>
       </c>
       <c r="I8" s="42">
-        <f>COUNTIF('入院患者'!O3:O102,"外来移行")</f>
+        <f>COUNTIF('入院患者'!R3:R102,"外来移行")</f>
         <v/>
       </c>
     </row>
@@ -7087,7 +7829,7 @@
         </is>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIF('入院患者'!K3:K102,"CAR-T")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"CAR-T")</f>
         <v/>
       </c>
       <c r="H9" s="44" t="inlineStr">
@@ -7116,7 +7858,7 @@
         </is>
       </c>
       <c r="F10" s="42">
-        <f>COUNTIF('入院患者'!K3:K102,"分子標的薬")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"分子標的薬")</f>
         <v/>
       </c>
     </row>
@@ -7136,7 +7878,7 @@
         </is>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIF('入院患者'!K3:K102,"免疫療法")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"免疫療法")</f>
         <v/>
       </c>
     </row>
@@ -7156,7 +7898,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>COUNTIF('入院患者'!K3:K102,"放射線")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"放射線")</f>
         <v/>
       </c>
     </row>
@@ -7176,7 +7918,7 @@
         </is>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIF('入院患者'!K3:K102,"BSC")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"BSC")</f>
         <v/>
       </c>
     </row>
@@ -7196,7 +7938,7 @@
         </is>
       </c>
       <c r="F14" s="42">
-        <f>COUNTIF('入院患者'!K3:K102,"経過観察")</f>
+        <f>COUNTIF('入院患者'!N3:N102,"経過観察")</f>
         <v/>
       </c>
     </row>
@@ -7438,13 +8180,13 @@
       <c r="C36" s="40" t="n"/>
       <c r="E36" s="39" t="inlineStr">
         <is>
-          <t>他科コンサルト - 疾患別</t>
+          <t>入院患者 - リスク分類別</t>
         </is>
       </c>
       <c r="F36" s="40" t="n"/>
       <c r="H36" s="39" t="inlineStr">
         <is>
-          <t>他科コンサルト - 緊急度別</t>
+          <t>他科コンサルト - 疾患別</t>
         </is>
       </c>
       <c r="I36" s="40" t="n"/>
@@ -7488,25 +8230,25 @@
         </is>
       </c>
       <c r="C38" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"CR")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"CR")</f>
         <v/>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
+          <t>Favorable</t>
+        </is>
+      </c>
+      <c r="F38" s="42">
+        <f>COUNTIF('入院患者'!I3:I102,"Favorable")</f>
+        <v/>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
           <t>AML</t>
         </is>
       </c>
-      <c r="F38" s="42">
+      <c r="I38" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"AML")</f>
-        <v/>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>緊急</t>
-        </is>
-      </c>
-      <c r="I38" s="42">
-        <f>COUNTIF('他科コンサルト'!E3:E102,"緊急")</f>
         <v/>
       </c>
     </row>
@@ -7517,25 +8259,25 @@
         </is>
       </c>
       <c r="C39" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"CRi")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"CRi")</f>
         <v/>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="F39" s="43">
+        <f>COUNTIF('入院患者'!I3:I102,"Intermediate")</f>
+        <v/>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F39" s="43">
+      <c r="I39" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"ALL")</f>
-        <v/>
-      </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>通常</t>
-        </is>
-      </c>
-      <c r="I39" s="43">
-        <f>COUNTIF('他科コンサルト'!E3:E102,"通常")</f>
         <v/>
       </c>
     </row>
@@ -7546,25 +8288,25 @@
         </is>
       </c>
       <c r="C40" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"PR")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"PR")</f>
         <v/>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
+          <t>Adverse</t>
+        </is>
+      </c>
+      <c r="F40" s="42">
+        <f>COUNTIF('入院患者'!I3:I102,"Adverse")</f>
+        <v/>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
           <t>CML</t>
         </is>
       </c>
-      <c r="F40" s="42">
+      <c r="I40" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CML")</f>
-        <v/>
-      </c>
-      <c r="H40" s="44" t="inlineStr">
-        <is>
-          <t>合計</t>
-        </is>
-      </c>
-      <c r="I40" s="45">
-        <f>COUNTA('他科コンサルト'!A3:A102)</f>
         <v/>
       </c>
     </row>
@@ -7575,15 +8317,24 @@
         </is>
       </c>
       <c r="C41" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"VGPR")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"VGPR")</f>
         <v/>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
+          <t>Very high</t>
+        </is>
+      </c>
+      <c r="F41" s="43">
+        <f>COUNTIF('入院患者'!I3:I102,"Very high")</f>
+        <v/>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
           <t>CLL</t>
         </is>
       </c>
-      <c r="F41" s="43">
+      <c r="I41" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CLL")</f>
         <v/>
       </c>
@@ -7595,15 +8346,24 @@
         </is>
       </c>
       <c r="C42" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"sCR")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"sCR")</f>
         <v/>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" s="42">
+        <f>COUNTIF('入院患者'!I3:I102,"High")</f>
+        <v/>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
           <t>MDS</t>
         </is>
       </c>
-      <c r="F42" s="42">
+      <c r="I42" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MDS")</f>
         <v/>
       </c>
@@ -7615,15 +8375,24 @@
         </is>
       </c>
       <c r="C43" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"SD")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"SD")</f>
         <v/>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="F43" s="43">
+        <f>COUNTIF('入院患者'!I3:I102,"Standard")</f>
+        <v/>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
           <t>MPN</t>
         </is>
       </c>
-      <c r="F43" s="43">
+      <c r="I43" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MPN")</f>
         <v/>
       </c>
@@ -7635,15 +8404,24 @@
         </is>
       </c>
       <c r="C44" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"PD")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"PD")</f>
         <v/>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F44" s="42">
+        <f>COUNTIF('入院患者'!I3:I102,"Low")</f>
+        <v/>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
           <t>CMML</t>
         </is>
       </c>
-      <c r="F44" s="42">
+      <c r="I44" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"CMML")</f>
         <v/>
       </c>
@@ -7655,15 +8433,24 @@
         </is>
       </c>
       <c r="C45" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"再発")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"再発")</f>
         <v/>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="43">
+        <f>COUNTIF('入院患者'!I3:I102,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
           <t>DLBCL</t>
         </is>
       </c>
-      <c r="F45" s="43">
+      <c r="I45" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"DLBCL")</f>
         <v/>
       </c>
@@ -7675,15 +8462,24 @@
         </is>
       </c>
       <c r="C46" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"死亡")</f>
-        <v/>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
+        <f>COUNTIF('入院患者'!Q3:Q102,"死亡")</f>
+        <v/>
+      </c>
+      <c r="E46" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F46" s="45">
+        <f>COUNTA('入院患者'!A3:A102)</f>
+        <v/>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="F46" s="42">
+      <c r="I46" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"FL")</f>
         <v/>
       </c>
@@ -7695,15 +8491,15 @@
         </is>
       </c>
       <c r="C47" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"評価前")</f>
-        <v/>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
+        <f>COUNTIF('入院患者'!Q3:Q102,"評価前")</f>
+        <v/>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>MCL</t>
         </is>
       </c>
-      <c r="F47" s="43">
+      <c r="I47" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MCL")</f>
         <v/>
       </c>
@@ -7715,15 +8511,15 @@
         </is>
       </c>
       <c r="C48" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"N/A")</f>
-        <v/>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
+        <f>COUNTIF('入院患者'!Q3:Q102,"N/A")</f>
+        <v/>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="F48" s="42">
+      <c r="I48" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"BL")</f>
         <v/>
       </c>
@@ -7738,199 +8534,199 @@
         <f>COUNTA('入院患者'!A3:A102)</f>
         <v/>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>MALT</t>
         </is>
       </c>
-      <c r="F49" s="43">
+      <c r="I49" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MALT")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="E50" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>ATLL</t>
         </is>
       </c>
-      <c r="F50" s="42">
+      <c r="I50" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"ATLL")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="E51" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>PTCL</t>
         </is>
       </c>
-      <c r="F51" s="43">
+      <c r="I51" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"PTCL")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="E52" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>AITL</t>
         </is>
       </c>
-      <c r="F52" s="42">
+      <c r="I52" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"AITL")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="E53" s="14" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>NK/T</t>
         </is>
       </c>
-      <c r="F53" s="43">
+      <c r="I53" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"NK/T")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="E54" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>HL</t>
         </is>
       </c>
-      <c r="F54" s="42">
+      <c r="I54" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"HL")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="E55" s="14" t="inlineStr">
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="F55" s="43">
+      <c r="I55" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"MM")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="E56" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>WM</t>
         </is>
       </c>
-      <c r="F56" s="42">
+      <c r="I56" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"WM")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="E57" s="14" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>AL amyloidosis</t>
         </is>
       </c>
-      <c r="F57" s="43">
+      <c r="I57" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="E58" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F58" s="42">
+      <c r="I58" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"AA")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="E59" s="14" t="inlineStr">
+      <c r="H59" s="14" t="inlineStr">
         <is>
           <t>PNH</t>
         </is>
       </c>
-      <c r="F59" s="43">
+      <c r="I59" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"PNH")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="E60" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>ITP</t>
         </is>
       </c>
-      <c r="F60" s="42">
+      <c r="I60" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"ITP")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="E61" s="14" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>TTP</t>
         </is>
       </c>
-      <c r="F61" s="43">
+      <c r="I61" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"TTP")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="E62" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>HUS</t>
         </is>
       </c>
-      <c r="F62" s="42">
+      <c r="I62" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"HUS")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="E63" s="14" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="F63" s="43">
+      <c r="I63" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"DIC")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="E64" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>HLH</t>
         </is>
       </c>
-      <c r="F64" s="42">
+      <c r="I64" s="42">
         <f>COUNTIF('他科コンサルト'!J3:J102,"HLH")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="E65" s="14" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F65" s="43">
+      <c r="I65" s="43">
         <f>COUNTIF('他科コンサルト'!J3:J102,"その他")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="E66" s="44" t="inlineStr">
+      <c r="H66" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="F66" s="45">
+      <c r="I66" s="45">
         <f>COUNTA('他科コンサルト'!A3:A102)</f>
         <v/>
       </c>
@@ -7938,16 +8734,22 @@
     <row r="68">
       <c r="B68" s="39" t="inlineStr">
         <is>
-          <t>初診外来 - 疾患別</t>
+          <t>他科コンサルト - 緊急度別</t>
         </is>
       </c>
       <c r="C68" s="40" t="n"/>
       <c r="E68" s="39" t="inlineStr">
         <is>
+          <t>初診外来 - 疾患別</t>
+        </is>
+      </c>
+      <c r="F68" s="40" t="n"/>
+      <c r="H68" s="39" t="inlineStr">
+        <is>
           <t>初診外来 - 転帰別</t>
         </is>
       </c>
-      <c r="F68" s="40" t="n"/>
+      <c r="I68" s="40" t="n"/>
     </row>
     <row r="69">
       <c r="B69" s="41" t="inlineStr">
@@ -7970,436 +8772,474 @@
           <t>件数</t>
         </is>
       </c>
+      <c r="H69" s="41" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="I69" s="41" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="10" t="inlineStr">
         <is>
+          <t>緊急</t>
+        </is>
+      </c>
+      <c r="C70" s="42">
+        <f>COUNTIF('他科コンサルト'!E3:E102,"緊急")</f>
+        <v/>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
           <t>AML</t>
         </is>
       </c>
-      <c r="C70" s="42">
+      <c r="F70" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"AML")</f>
         <v/>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="F70" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"CR")</f>
+      <c r="I70" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"CR")</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="14" t="inlineStr">
         <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="C71" s="43">
+        <f>COUNTIF('他科コンサルト'!E3:E102,"通常")</f>
+        <v/>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="C71" s="43">
+      <c r="F71" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"ALL")</f>
         <v/>
       </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
         <is>
           <t>CRi</t>
         </is>
       </c>
-      <c r="F71" s="43">
-        <f>COUNTIF('初診外来'!M3:M102,"CRi")</f>
+      <c r="I71" s="43">
+        <f>COUNTIF('初診外来'!P3:P102,"CRi")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C72" s="45">
+        <f>COUNTA('他科コンサルト'!A3:A102)</f>
+        <v/>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>CML</t>
         </is>
       </c>
-      <c r="C72" s="42">
+      <c r="F72" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"CML")</f>
         <v/>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="F72" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"PR")</f>
+      <c r="I72" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"PR")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="14" t="inlineStr">
+      <c r="E73" s="14" t="inlineStr">
         <is>
           <t>CLL</t>
         </is>
       </c>
-      <c r="C73" s="43">
+      <c r="F73" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"CLL")</f>
         <v/>
       </c>
-      <c r="E73" s="14" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
         <is>
           <t>VGPR</t>
         </is>
       </c>
-      <c r="F73" s="43">
-        <f>COUNTIF('初診外来'!M3:M102,"VGPR")</f>
+      <c r="I73" s="43">
+        <f>COUNTIF('初診外来'!P3:P102,"VGPR")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="10" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>MDS</t>
         </is>
       </c>
-      <c r="C74" s="42">
+      <c r="F74" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"MDS")</f>
         <v/>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>sCR</t>
         </is>
       </c>
-      <c r="F74" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"sCR")</f>
+      <c r="I74" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"sCR")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="14" t="inlineStr">
+      <c r="E75" s="14" t="inlineStr">
         <is>
           <t>MPN</t>
         </is>
       </c>
-      <c r="C75" s="43">
+      <c r="F75" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MPN")</f>
         <v/>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="F75" s="43">
-        <f>COUNTIF('初診外来'!M3:M102,"SD")</f>
+      <c r="I75" s="43">
+        <f>COUNTIF('初診外来'!P3:P102,"SD")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="10" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>CMML</t>
         </is>
       </c>
-      <c r="C76" s="42">
+      <c r="F76" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"CMML")</f>
         <v/>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="F76" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"PD")</f>
+      <c r="I76" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"PD")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="14" t="inlineStr">
+      <c r="E77" s="14" t="inlineStr">
         <is>
           <t>DLBCL</t>
         </is>
       </c>
-      <c r="C77" s="43">
+      <c r="F77" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"DLBCL")</f>
         <v/>
       </c>
-      <c r="E77" s="14" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>再発</t>
         </is>
       </c>
-      <c r="F77" s="43">
-        <f>COUNTIF('初診外来'!M3:M102,"再発")</f>
+      <c r="I77" s="43">
+        <f>COUNTIF('初診外来'!P3:P102,"再発")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="10" t="inlineStr">
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="C78" s="42">
+      <c r="F78" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"FL")</f>
         <v/>
       </c>
-      <c r="E78" s="10" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>死亡</t>
         </is>
       </c>
-      <c r="F78" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"死亡")</f>
+      <c r="I78" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"死亡")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="14" t="inlineStr">
+      <c r="E79" s="14" t="inlineStr">
         <is>
           <t>MCL</t>
         </is>
       </c>
-      <c r="C79" s="43">
+      <c r="F79" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MCL")</f>
         <v/>
       </c>
-      <c r="E79" s="14" t="inlineStr">
+      <c r="H79" s="14" t="inlineStr">
         <is>
           <t>評価前</t>
         </is>
       </c>
-      <c r="F79" s="43">
-        <f>COUNTIF('初診外来'!M3:M102,"評価前")</f>
+      <c r="I79" s="43">
+        <f>COUNTIF('初診外来'!P3:P102,"評価前")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="10" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="C80" s="42">
+      <c r="F80" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"BL")</f>
         <v/>
       </c>
-      <c r="E80" s="10" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F80" s="42">
-        <f>COUNTIF('初診外来'!M3:M102,"N/A")</f>
+      <c r="I80" s="42">
+        <f>COUNTIF('初診外来'!P3:P102,"N/A")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="14" t="inlineStr">
+      <c r="E81" s="14" t="inlineStr">
         <is>
           <t>MALT</t>
         </is>
       </c>
-      <c r="C81" s="43">
+      <c r="F81" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MALT")</f>
         <v/>
       </c>
-      <c r="E81" s="44" t="inlineStr">
+      <c r="H81" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="F81" s="45">
+      <c r="I81" s="45">
         <f>COUNTA('初診外来'!A3:A102)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="10" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>ATLL</t>
         </is>
       </c>
-      <c r="C82" s="42">
+      <c r="F82" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"ATLL")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="14" t="inlineStr">
+      <c r="E83" s="14" t="inlineStr">
         <is>
           <t>PTCL</t>
         </is>
       </c>
-      <c r="C83" s="43">
+      <c r="F83" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"PTCL")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="10" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>AITL</t>
         </is>
       </c>
-      <c r="C84" s="42">
+      <c r="F84" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"AITL")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="14" t="inlineStr">
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>NK/T</t>
         </is>
       </c>
-      <c r="C85" s="43">
+      <c r="F85" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"NK/T")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="10" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>HL</t>
         </is>
       </c>
-      <c r="C86" s="42">
+      <c r="F86" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HL")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="14" t="inlineStr">
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="C87" s="43">
+      <c r="F87" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"MM")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="10" t="inlineStr">
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>WM</t>
         </is>
       </c>
-      <c r="C88" s="42">
+      <c r="F88" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"WM")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="14" t="inlineStr">
+      <c r="E89" s="14" t="inlineStr">
         <is>
           <t>AL amyloidosis</t>
         </is>
       </c>
-      <c r="C89" s="43">
+      <c r="F89" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="10" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="C90" s="42">
+      <c r="F90" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"AA")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="14" t="inlineStr">
+      <c r="E91" s="14" t="inlineStr">
         <is>
           <t>PNH</t>
         </is>
       </c>
-      <c r="C91" s="43">
+      <c r="F91" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"PNH")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="10" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>ITP</t>
         </is>
       </c>
-      <c r="C92" s="42">
+      <c r="F92" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"ITP")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="14" t="inlineStr">
+      <c r="E93" s="14" t="inlineStr">
         <is>
           <t>TTP</t>
         </is>
       </c>
-      <c r="C93" s="43">
+      <c r="F93" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"TTP")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="10" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>HUS</t>
         </is>
       </c>
-      <c r="C94" s="42">
+      <c r="F94" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HUS")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="14" t="inlineStr">
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>DIC</t>
         </is>
       </c>
-      <c r="C95" s="43">
+      <c r="F95" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"DIC")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="10" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>HLH</t>
         </is>
       </c>
-      <c r="C96" s="42">
+      <c r="F96" s="42">
         <f>COUNTIF('初診外来'!H3:H102,"HLH")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="14" t="inlineStr">
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="C97" s="43">
+      <c r="F97" s="43">
         <f>COUNTIF('初診外来'!H3:H102,"その他")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="44" t="inlineStr">
+      <c r="E98" s="44" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C98" s="45">
+      <c r="F98" s="45">
         <f>COUNTA('初診外来'!A3:A102)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="H68:I68"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="B68:C68"/>
     <mergeCell ref="E68:F68"/>
@@ -8409,6 +9249,7 @@
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -8,17 +8,32 @@
   </bookViews>
   <sheets>
     <sheet name="入院患者" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="他科コンサルト" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="初診外来" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="サマリー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="_Lists" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="他科コンサルト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="初診外来" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="サマリー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="sex">'_Lists'!$A$2:$A$3</definedName>
+    <definedName name="ps">'_Lists'!$B$2:$B$6</definedName>
+    <definedName name="disease">'_Lists'!$C$2:$C$29</definedName>
+    <definedName name="label">'_Lists'!$D$2:$D$10</definedName>
+    <definedName name="followup">'_Lists'!$E$2:$E$4</definedName>
+    <definedName name="stage">'_Lists'!$F$2:$F$14</definedName>
+    <definedName name="status">'_Lists'!$G$2:$G$4</definedName>
+    <definedName name="urgency">'_Lists'!$H$2:$H$3</definedName>
+    <definedName name="outcome">'_Lists'!$I$2:$I$12</definedName>
+    <definedName name="regimen">'_Lists'!$J$2:$J$46</definedName>
+    <definedName name="cytogenetics">'_Lists'!$K$2:$K$29</definedName>
+    <definedName name="gene">'_Lists'!$L$2:$L$29</definedName>
+    <definedName name="risk">'_Lists'!$M$2:$M$9</definedName>
+    <definedName name="dept">'_Lists'!$N$2:$N$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$S$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'入院患者'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'他科コンサルト'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'初診外来'!$A$2:$R$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'初診外来'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'他科コンサルト'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'初診外来'!$A$2:$R$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'初診外来'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3608,37 +3623,37 @@
   </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"M,F"</formula1>
+      <formula1>sex</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+      <formula1>disease</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"I,II,III,IV,Limited,Extensive,ISS-I,ISS-II,ISS-III,R-ISS-I,R-ISS-II,R-ISS-III,N/A"</formula1>
+      <formula1>stage</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"t(8;21),inv(16),t(15;17),t(9;11),t(6;9),inv(3),t(v;11q23),del(5q),-5,del(7q),-7,complex,normal karyotype,t(9;22)/BCR-ABL,t(4;11),t(1;19),hyper(&gt;50),hypo(&lt;44),t(4;14),t(14;16),t(11;14),del(17p),gain(1q),del(20q),del(5q) isolated,その他,検査中,N/A"</formula1>
+      <formula1>cytogenetics</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"FLT3-ITD,FLT3-TKD,NPM1,CEBPA(bi),RUNX1,ASXL1,TP53,IDH1,IDH2,DNMT3A,KIT,IKZF1,PAX5,Ph-like,SF3B1,SRSF2,U2AF1,ZRSR2,EZH2,del(17p)/TP53,MYC rearr.,BCL2 rearr.,BCL6 rearr.,Double-hit,Triple-hit,その他,検査中,N/A"</formula1>
+      <formula1>gene</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"Favorable,Intermediate,Adverse,Very high,High,Standard,Low,N/A"</formula1>
+      <formula1>risk</formula1>
     </dataValidation>
     <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>ps</formula1>
     </dataValidation>
     <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
+      <formula1>label</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
+      <formula1>regimen</formula1>
     </dataValidation>
     <dataValidation sqref="Q3:Q102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
+      <formula1>outcome</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"入院中,退院済,外来移行"</formula1>
+      <formula1>status</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -3655,6 +3670,1222 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ps</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>followup</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>urgency</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>regimen</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cytogenetics</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dept</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AML</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>化学療法</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>要</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>入院中</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>緊急</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>AZA+VEN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>t(8;21)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>FLT3-ITD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Favorable</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>消化器内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>自家移植</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>退院済</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CRi</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7+3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>inv(16)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>FLT3-TKD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Intermediate</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>循環器内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>同種移植</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>外来移行</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FLAG-IDA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>t(15;17)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NPM1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Adverse</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>呼吸器内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CAR-T</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>VGPR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AZA</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>t(9;11)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CEBPA(bi)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Very high</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>腎臓内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>分子標的薬</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Limited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>sCR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AZA+IVO</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>t(6;9)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>RUNX1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>内分泌内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>免疫療法</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Extensive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>LDAC</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>inv(3)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ASXL1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>神経内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CMML</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>放射線</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ISS-I</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>HyperCVAD</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>t(v;11q23)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>TP53</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>膠原病内科</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DLBCL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BSC</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ISS-II</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>再発</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ino+mP</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>del(5q)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>IDH1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>一般外科</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>経過観察</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ISS-III</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BLN+chemo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>IDH2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>心臓外科</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MCL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>R-ISS-I</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>評価前</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ph+ALL(DAS)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>del(7q)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DNMT3A</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>脳神経外科</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>R-ISS-II</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>R-CHOP</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>整形外科</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MALT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>R-ISS-III</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pola-R-CHP</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complex</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>IKZF1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>泌尿器科</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ATLL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>R-ICE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>normal karyotype</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PAX5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>産婦人科</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PTCL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>R-DHAP</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>t(9;22)/BCR-ABL</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ph-like</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>皮膚科</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AITL</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>R-GDP</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>t(4;11)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>SF3B1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>耳鼻咽喉科</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NK/T</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>R-MPV</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>t(1;19)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>SRSF2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>眼科</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>hyper(&gt;50)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>U2AF1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>精神科</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MM</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>R-CVP</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>hypo(&lt;44)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>ZRSR2</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>小児科</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>t(4;14)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>EZH2</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>救急科</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AL amyloidosis</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ob-CHOP</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>t(14;16)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>del(17p)/TP53</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>麻酔科</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ABVD</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>t(11;14)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MYC rearr.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>放射線科</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PNH</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>A-AVD</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>del(17p)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>BCL2 rearr.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>病理</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ITP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BV+AVD</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>gain(1q)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>BCL6 rearr.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TTP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VRd</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>del(20q)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Double-hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DRd</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>del(5q) isolated</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Triple-hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dara-VRd</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HLH</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>KRd</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>検査中</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>検査中</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>IRd</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dara-Kd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>VCd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Elo-Pd</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>IMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>PON</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Auto-PBSCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Allo-PBSCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Allo-BMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>CAR-T(tisa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CAR-T(axi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CAR-T(liso)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -5305,19 +6536,19 @@
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"M,F"</formula1>
+      <formula1>sex</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"緊急,通常"</formula1>
+      <formula1>urgency</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"消化器内科,循環器内科,呼吸器内科,腎臓内科,内分泌内科,神経内科,膠原病内科,一般外科,心臓外科,脳神経外科,整形外科,泌尿器科,産婦人科,皮膚科,耳鼻咽喉科,眼科,精神科,小児科,救急科,麻酔科,放射線科,病理,その他"</formula1>
+      <formula1>dept</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+      <formula1>disease</formula1>
     </dataValidation>
     <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"要,不要,済"</formula1>
+      <formula1>followup</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -5333,7 +6564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C55A11"/>
@@ -7603,34 +8834,34 @@
   </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"M,F"</formula1>
+      <formula1>sex</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"AML,ALL,CML,CLL,MDS,MPN,CMML,DLBCL,FL,MCL,BL,MALT,ATLL,PTCL,AITL,NK/T,HL,MM,WM,AL amyloidosis,AA,PNH,ITP,TTP,HUS,DIC,HLH,その他"</formula1>
+      <formula1>disease</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"I,II,III,IV,Limited,Extensive,ISS-I,ISS-II,ISS-III,R-ISS-I,R-ISS-II,R-ISS-III,N/A"</formula1>
+      <formula1>stage</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"t(8;21),inv(16),t(15;17),t(9;11),t(6;9),inv(3),t(v;11q23),del(5q),-5,del(7q),-7,complex,normal karyotype,t(9;22)/BCR-ABL,t(4;11),t(1;19),hyper(&gt;50),hypo(&lt;44),t(4;14),t(14;16),t(11;14),del(17p),gain(1q),del(20q),del(5q) isolated,その他,検査中,N/A"</formula1>
+      <formula1>cytogenetics</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"FLT3-ITD,FLT3-TKD,NPM1,CEBPA(bi),RUNX1,ASXL1,TP53,IDH1,IDH2,DNMT3A,KIT,IKZF1,PAX5,Ph-like,SF3B1,SRSF2,U2AF1,ZRSR2,EZH2,del(17p)/TP53,MYC rearr.,BCL2 rearr.,BCL6 rearr.,Double-hit,Triple-hit,その他,検査中,N/A"</formula1>
+      <formula1>gene</formula1>
     </dataValidation>
     <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"Favorable,Intermediate,Adverse,Very high,High,Standard,Low,N/A"</formula1>
+      <formula1>risk</formula1>
     </dataValidation>
     <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"0,1,2,3,4"</formula1>
+      <formula1>ps</formula1>
     </dataValidation>
     <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"化学療法,自家移植,同種移植,CAR-T,分子標的薬,免疫療法,放射線,BSC,経過観察"</formula1>
+      <formula1>label</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"AZA+VEN,7+3,FLAG-IDA,AZA,AZA+IVO,LDAC,HyperCVAD,Ino+mP,BLN+chemo,Ph+ALL(DAS),R-CHOP,Pola-R-CHP,R-ICE,R-DHAP,R-GDP,R-MPV,BR,R-CVP,R2,Ob-CHOP,ABVD,A-AVD,BV+AVD,VRd,DRd,Dara-VRd,KRd,IRd,Dara-Kd,VCd,Elo-Pd,IMA,DAS,NIL,BOS,PON,ASC,Auto-PBSCT,Allo-PBSCT,Allo-BMT,CBT,CAR-T(tisa),CAR-T(axi),CAR-T(liso),その他"</formula1>
+      <formula1>regimen</formula1>
     </dataValidation>
     <dataValidation sqref="P3:P102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
-      <formula1>"CR,CRi,PR,VGPR,sCR,SD,PD,再発,死亡,評価前,N/A"</formula1>
+      <formula1>outcome</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -7646,7 +8877,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A365D"/>

--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -28,11 +28,11 @@
     <definedName name="gene">'_Lists'!$L$2:$L$29</definedName>
     <definedName name="risk">'_Lists'!$M$2:$M$9</definedName>
     <definedName name="dept">'_Lists'!$N$2:$N$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$S$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入院患者'!$A$2:$R$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'入院患者'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'他科コンサルト'!$A$2:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'他科コンサルト'!$A$2:$L$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'他科コンサルト'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'初診外来'!$A$2:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'初診外来'!$A$2:$Q$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'初診外来'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -318,11 +318,11 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -946,28 +946,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,34 +977,33 @@
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>臨床情報</t>
         </is>
       </c>
+      <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
       <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
       <c r="I1" s="4" t="n"/>
       <c r="J1" s="4" t="n"/>
       <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>治療</t>
         </is>
       </c>
+      <c r="M1" s="6" t="n"/>
       <c r="N1" s="6" t="n"/>
       <c r="O1" s="6" t="n"/>
       <c r="P1" s="6" t="n"/>
-      <c r="Q1" s="6" t="n"/>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="S1" s="6" t="n"/>
+      <c r="R1" s="6" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -1015,90 +1013,85 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>イニシャル</t>
+          <t>年齢</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>年齢</t>
+          <t>性別</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>性別</t>
+          <t>疾患</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>疾患</t>
+          <t>病期/Stage</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>病期/Stage</t>
+          <t>染色体</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>染色体</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>遺伝子</t>
+          <t>リスク分類</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>リスク分類</t>
+          <t>入院日</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>入院日</t>
+          <t>退院日</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>退院日</t>
+          <t>在院日数</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>在院日数</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>治療区分</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>治療区分</t>
+          <t>治療レジメン</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>治療レジメン</t>
+          <t>サイクル数</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
-          <t>サイクル数</t>
+          <t>転帰</t>
         </is>
       </c>
       <c r="Q2" s="7" t="inlineStr">
         <is>
-          <t>転帰</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="R2" s="7" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -1113,20 +1106,19 @@
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
-      <c r="I3" s="10" t="n"/>
+      <c r="I3" s="11" t="n"/>
       <c r="J3" s="11" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="9">
-        <f>IF(AND(J3&lt;&gt;"",K3&lt;&gt;""),K3-J3,"")</f>
-        <v/>
-      </c>
+      <c r="K3" s="9">
+        <f>IF(AND(I3&lt;&gt;"",J3&lt;&gt;""),J3-I3,"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="10" t="n"/>
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
       <c r="P3" s="10" t="n"/>
       <c r="Q3" s="10" t="n"/>
       <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="12" t="n"/>
@@ -1137,20 +1129,19 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
       <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
+      <c r="I4" s="15" t="n"/>
       <c r="J4" s="15" t="n"/>
-      <c r="K4" s="15" t="n"/>
-      <c r="L4" s="13">
-        <f>IF(AND(J4&lt;&gt;"",K4&lt;&gt;""),K4-J4,"")</f>
-        <v/>
-      </c>
+      <c r="K4" s="13">
+        <f>IF(AND(I4&lt;&gt;"",J4&lt;&gt;""),J4-I4,"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="14" t="n"/>
       <c r="M4" s="14" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
       <c r="P4" s="14" t="n"/>
       <c r="Q4" s="14" t="n"/>
       <c r="R4" s="14" t="n"/>
-      <c r="S4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
@@ -1161,20 +1152,19 @@
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
+      <c r="I5" s="11" t="n"/>
       <c r="J5" s="11" t="n"/>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="9">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;""),K5-J5,"")</f>
-        <v/>
-      </c>
+      <c r="K5" s="9">
+        <f>IF(AND(I5&lt;&gt;"",J5&lt;&gt;""),J5-I5,"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="10" t="n"/>
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
       <c r="P5" s="10" t="n"/>
       <c r="Q5" s="10" t="n"/>
       <c r="R5" s="10" t="n"/>
-      <c r="S5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -1185,20 +1175,19 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
+      <c r="I6" s="15" t="n"/>
       <c r="J6" s="15" t="n"/>
-      <c r="K6" s="15" t="n"/>
-      <c r="L6" s="13">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;""),K6-J6,"")</f>
-        <v/>
-      </c>
+      <c r="K6" s="13">
+        <f>IF(AND(I6&lt;&gt;"",J6&lt;&gt;""),J6-I6,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
       <c r="P6" s="14" t="n"/>
       <c r="Q6" s="14" t="n"/>
       <c r="R6" s="14" t="n"/>
-      <c r="S6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
@@ -1209,20 +1198,19 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
-      <c r="I7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="9">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;""),K7-J7,"")</f>
-        <v/>
-      </c>
+      <c r="K7" s="9">
+        <f>IF(AND(I7&lt;&gt;"",J7&lt;&gt;""),J7-I7,"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="10" t="n"/>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
       <c r="P7" s="10" t="n"/>
       <c r="Q7" s="10" t="n"/>
       <c r="R7" s="10" t="n"/>
-      <c r="S7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -1233,20 +1221,19 @@
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="I8" s="15" t="n"/>
       <c r="J8" s="15" t="n"/>
-      <c r="K8" s="15" t="n"/>
-      <c r="L8" s="13">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;""),K8-J8,"")</f>
-        <v/>
-      </c>
+      <c r="K8" s="13">
+        <f>IF(AND(I8&lt;&gt;"",J8&lt;&gt;""),J8-I8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
       <c r="P8" s="14" t="n"/>
       <c r="Q8" s="14" t="n"/>
       <c r="R8" s="14" t="n"/>
-      <c r="S8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
@@ -1257,20 +1244,19 @@
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
       <c r="J9" s="11" t="n"/>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="9">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;""),K9-J9,"")</f>
-        <v/>
-      </c>
+      <c r="K9" s="9">
+        <f>IF(AND(I9&lt;&gt;"",J9&lt;&gt;""),J9-I9,"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="10" t="n"/>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
       <c r="P9" s="10" t="n"/>
       <c r="Q9" s="10" t="n"/>
       <c r="R9" s="10" t="n"/>
-      <c r="S9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -1281,20 +1267,19 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n"/>
-      <c r="I10" s="14" t="n"/>
+      <c r="I10" s="15" t="n"/>
       <c r="J10" s="15" t="n"/>
-      <c r="K10" s="15" t="n"/>
-      <c r="L10" s="13">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;""),K10-J10,"")</f>
-        <v/>
-      </c>
+      <c r="K10" s="13">
+        <f>IF(AND(I10&lt;&gt;"",J10&lt;&gt;""),J10-I10,"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
       <c r="P10" s="14" t="n"/>
       <c r="Q10" s="14" t="n"/>
       <c r="R10" s="14" t="n"/>
-      <c r="S10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
@@ -1305,20 +1290,19 @@
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
       <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="9">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;""),K11-J11,"")</f>
-        <v/>
-      </c>
+      <c r="K11" s="9">
+        <f>IF(AND(I11&lt;&gt;"",J11&lt;&gt;""),J11-I11,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="10" t="n"/>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
       <c r="P11" s="10" t="n"/>
       <c r="Q11" s="10" t="n"/>
       <c r="R11" s="10" t="n"/>
-      <c r="S11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -1329,20 +1313,19 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="14" t="n"/>
       <c r="H12" s="14" t="n"/>
-      <c r="I12" s="14" t="n"/>
+      <c r="I12" s="15" t="n"/>
       <c r="J12" s="15" t="n"/>
-      <c r="K12" s="15" t="n"/>
-      <c r="L12" s="13">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;""),K12-J12,"")</f>
-        <v/>
-      </c>
+      <c r="K12" s="13">
+        <f>IF(AND(I12&lt;&gt;"",J12&lt;&gt;""),J12-I12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="14" t="n"/>
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
       <c r="P12" s="14" t="n"/>
       <c r="Q12" s="14" t="n"/>
       <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
@@ -1353,20 +1336,19 @@
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="9">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;""),K13-J13,"")</f>
-        <v/>
-      </c>
+      <c r="K13" s="9">
+        <f>IF(AND(I13&lt;&gt;"",J13&lt;&gt;""),J13-I13,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="10" t="n"/>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
       <c r="P13" s="10" t="n"/>
       <c r="Q13" s="10" t="n"/>
       <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -1377,20 +1359,19 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="14" t="n"/>
       <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
+      <c r="I14" s="15" t="n"/>
       <c r="J14" s="15" t="n"/>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="13">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;""),K14-J14,"")</f>
-        <v/>
-      </c>
+      <c r="K14" s="13">
+        <f>IF(AND(I14&lt;&gt;"",J14&lt;&gt;""),J14-I14,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
       <c r="P14" s="14" t="n"/>
       <c r="Q14" s="14" t="n"/>
       <c r="R14" s="14" t="n"/>
-      <c r="S14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
@@ -1401,20 +1382,19 @@
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="10" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="9">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;""),K15-J15,"")</f>
-        <v/>
-      </c>
+      <c r="K15" s="9">
+        <f>IF(AND(I15&lt;&gt;"",J15&lt;&gt;""),J15-I15,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="10" t="n"/>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
       <c r="P15" s="10" t="n"/>
       <c r="Q15" s="10" t="n"/>
       <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1425,20 +1405,19 @@
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
       <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
+      <c r="I16" s="15" t="n"/>
       <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="13">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;""),K16-J16,"")</f>
-        <v/>
-      </c>
+      <c r="K16" s="13">
+        <f>IF(AND(I16&lt;&gt;"",J16&lt;&gt;""),J16-I16,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="14" t="n"/>
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
       <c r="P16" s="14" t="n"/>
       <c r="Q16" s="14" t="n"/>
       <c r="R16" s="14" t="n"/>
-      <c r="S16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
@@ -1449,20 +1428,19 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
+      <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
-      <c r="K17" s="11" t="n"/>
-      <c r="L17" s="9">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;""),K17-J17,"")</f>
-        <v/>
-      </c>
+      <c r="K17" s="9">
+        <f>IF(AND(I17&lt;&gt;"",J17&lt;&gt;""),J17-I17,"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="10" t="n"/>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
       <c r="P17" s="10" t="n"/>
       <c r="Q17" s="10" t="n"/>
       <c r="R17" s="10" t="n"/>
-      <c r="S17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -1473,20 +1451,19 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14" t="n"/>
       <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
+      <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="13">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;""),K18-J18,"")</f>
-        <v/>
-      </c>
+      <c r="K18" s="13">
+        <f>IF(AND(I18&lt;&gt;"",J18&lt;&gt;""),J18-I18,"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="14" t="n"/>
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
       <c r="P18" s="14" t="n"/>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14" t="n"/>
-      <c r="S18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
@@ -1497,20 +1474,19 @@
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
-      <c r="K19" s="11" t="n"/>
-      <c r="L19" s="9">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;""),K19-J19,"")</f>
-        <v/>
-      </c>
+      <c r="K19" s="9">
+        <f>IF(AND(I19&lt;&gt;"",J19&lt;&gt;""),J19-I19,"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
       <c r="P19" s="10" t="n"/>
       <c r="Q19" s="10" t="n"/>
       <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -1521,20 +1497,19 @@
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
       <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
+      <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="13">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;""),K20-J20,"")</f>
-        <v/>
-      </c>
+      <c r="K20" s="13">
+        <f>IF(AND(I20&lt;&gt;"",J20&lt;&gt;""),J20-I20,"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
       <c r="P20" s="14" t="n"/>
       <c r="Q20" s="14" t="n"/>
       <c r="R20" s="14" t="n"/>
-      <c r="S20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
@@ -1545,20 +1520,19 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
-      <c r="K21" s="11" t="n"/>
-      <c r="L21" s="9">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;""),K21-J21,"")</f>
-        <v/>
-      </c>
+      <c r="K21" s="9">
+        <f>IF(AND(I21&lt;&gt;"",J21&lt;&gt;""),J21-I21,"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
       <c r="P21" s="10" t="n"/>
       <c r="Q21" s="10" t="n"/>
       <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -1569,20 +1543,19 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="14" t="n"/>
       <c r="H22" s="14" t="n"/>
-      <c r="I22" s="14" t="n"/>
+      <c r="I22" s="15" t="n"/>
       <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="13">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;""),K22-J22,"")</f>
-        <v/>
-      </c>
+      <c r="K22" s="13">
+        <f>IF(AND(I22&lt;&gt;"",J22&lt;&gt;""),J22-I22,"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
       <c r="P22" s="14" t="n"/>
       <c r="Q22" s="14" t="n"/>
       <c r="R22" s="14" t="n"/>
-      <c r="S22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
@@ -1593,20 +1566,19 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
+      <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="9">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;""),K23-J23,"")</f>
-        <v/>
-      </c>
+      <c r="K23" s="9">
+        <f>IF(AND(I23&lt;&gt;"",J23&lt;&gt;""),J23-I23,"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
       <c r="P23" s="10" t="n"/>
       <c r="Q23" s="10" t="n"/>
       <c r="R23" s="10" t="n"/>
-      <c r="S23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -1617,20 +1589,19 @@
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
       <c r="H24" s="14" t="n"/>
-      <c r="I24" s="14" t="n"/>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="15" t="n"/>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="13">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;""),K24-J24,"")</f>
-        <v/>
-      </c>
+      <c r="K24" s="13">
+        <f>IF(AND(I24&lt;&gt;"",J24&lt;&gt;""),J24-I24,"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="14" t="n"/>
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
       <c r="P24" s="14" t="n"/>
       <c r="Q24" s="14" t="n"/>
       <c r="R24" s="14" t="n"/>
-      <c r="S24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
@@ -1641,20 +1612,19 @@
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
+      <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11" t="n"/>
-      <c r="L25" s="9">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;""),K25-J25,"")</f>
-        <v/>
-      </c>
+      <c r="K25" s="9">
+        <f>IF(AND(I25&lt;&gt;"",J25&lt;&gt;""),J25-I25,"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="10" t="n"/>
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="10" t="n"/>
       <c r="Q25" s="10" t="n"/>
       <c r="R25" s="10" t="n"/>
-      <c r="S25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -1665,20 +1635,19 @@
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="14" t="n"/>
-      <c r="I26" s="14" t="n"/>
+      <c r="I26" s="15" t="n"/>
       <c r="J26" s="15" t="n"/>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="13">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;""),K26-J26,"")</f>
-        <v/>
-      </c>
+      <c r="K26" s="13">
+        <f>IF(AND(I26&lt;&gt;"",J26&lt;&gt;""),J26-I26,"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
       <c r="O26" s="14" t="n"/>
       <c r="P26" s="14" t="n"/>
       <c r="Q26" s="14" t="n"/>
       <c r="R26" s="14" t="n"/>
-      <c r="S26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
@@ -1689,20 +1658,19 @@
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
-      <c r="K27" s="11" t="n"/>
-      <c r="L27" s="9">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;""),K27-J27,"")</f>
-        <v/>
-      </c>
+      <c r="K27" s="9">
+        <f>IF(AND(I27&lt;&gt;"",J27&lt;&gt;""),J27-I27,"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="10" t="n"/>
       <c r="Q27" s="10" t="n"/>
       <c r="R27" s="10" t="n"/>
-      <c r="S27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -1713,20 +1681,19 @@
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
+      <c r="I28" s="15" t="n"/>
       <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="13">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;""),K28-J28,"")</f>
-        <v/>
-      </c>
+      <c r="K28" s="13">
+        <f>IF(AND(I28&lt;&gt;"",J28&lt;&gt;""),J28-I28,"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
       <c r="P28" s="14" t="n"/>
       <c r="Q28" s="14" t="n"/>
       <c r="R28" s="14" t="n"/>
-      <c r="S28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
@@ -1737,20 +1704,19 @@
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
+      <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="9">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;""),K29-J29,"")</f>
-        <v/>
-      </c>
+      <c r="K29" s="9">
+        <f>IF(AND(I29&lt;&gt;"",J29&lt;&gt;""),J29-I29,"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="10" t="n"/>
       <c r="M29" s="10" t="n"/>
       <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
       <c r="P29" s="10" t="n"/>
       <c r="Q29" s="10" t="n"/>
       <c r="R29" s="10" t="n"/>
-      <c r="S29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -1761,20 +1727,19 @@
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="14" t="n"/>
       <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
+      <c r="I30" s="15" t="n"/>
       <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="13">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;""),K30-J30,"")</f>
-        <v/>
-      </c>
+      <c r="K30" s="13">
+        <f>IF(AND(I30&lt;&gt;"",J30&lt;&gt;""),J30-I30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
       <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
       <c r="P30" s="14" t="n"/>
       <c r="Q30" s="14" t="n"/>
       <c r="R30" s="14" t="n"/>
-      <c r="S30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
@@ -1785,20 +1750,19 @@
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
+      <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="9">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;""),K31-J31,"")</f>
-        <v/>
-      </c>
+      <c r="K31" s="9">
+        <f>IF(AND(I31&lt;&gt;"",J31&lt;&gt;""),J31-I31,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="10" t="n"/>
       <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
       <c r="P31" s="10" t="n"/>
       <c r="Q31" s="10" t="n"/>
       <c r="R31" s="10" t="n"/>
-      <c r="S31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -1809,20 +1773,19 @@
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
+      <c r="I32" s="15" t="n"/>
       <c r="J32" s="15" t="n"/>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="13">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;""),K32-J32,"")</f>
-        <v/>
-      </c>
+      <c r="K32" s="13">
+        <f>IF(AND(I32&lt;&gt;"",J32&lt;&gt;""),J32-I32,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
       <c r="P32" s="14" t="n"/>
       <c r="Q32" s="14" t="n"/>
       <c r="R32" s="14" t="n"/>
-      <c r="S32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
@@ -1833,20 +1796,19 @@
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
+      <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
-      <c r="K33" s="11" t="n"/>
-      <c r="L33" s="9">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;""),K33-J33,"")</f>
-        <v/>
-      </c>
+      <c r="K33" s="9">
+        <f>IF(AND(I33&lt;&gt;"",J33&lt;&gt;""),J33-I33,"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="10" t="n"/>
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
       <c r="P33" s="10" t="n"/>
       <c r="Q33" s="10" t="n"/>
       <c r="R33" s="10" t="n"/>
-      <c r="S33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -1857,20 +1819,19 @@
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
+      <c r="I34" s="15" t="n"/>
       <c r="J34" s="15" t="n"/>
-      <c r="K34" s="15" t="n"/>
-      <c r="L34" s="13">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;""),K34-J34,"")</f>
-        <v/>
-      </c>
+      <c r="K34" s="13">
+        <f>IF(AND(I34&lt;&gt;"",J34&lt;&gt;""),J34-I34,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="14" t="n"/>
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
       <c r="P34" s="14" t="n"/>
       <c r="Q34" s="14" t="n"/>
       <c r="R34" s="14" t="n"/>
-      <c r="S34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
@@ -1881,20 +1842,19 @@
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
+      <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="9">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;""),K35-J35,"")</f>
-        <v/>
-      </c>
+      <c r="K35" s="9">
+        <f>IF(AND(I35&lt;&gt;"",J35&lt;&gt;""),J35-I35,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="10" t="n"/>
       <c r="M35" s="10" t="n"/>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="10" t="n"/>
       <c r="Q35" s="10" t="n"/>
       <c r="R35" s="10" t="n"/>
-      <c r="S35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -1905,20 +1865,19 @@
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14" t="n"/>
       <c r="H36" s="14" t="n"/>
-      <c r="I36" s="14" t="n"/>
+      <c r="I36" s="15" t="n"/>
       <c r="J36" s="15" t="n"/>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="13">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;""),K36-J36,"")</f>
-        <v/>
-      </c>
+      <c r="K36" s="13">
+        <f>IF(AND(I36&lt;&gt;"",J36&lt;&gt;""),J36-I36,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="14" t="n"/>
       <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
       <c r="P36" s="14" t="n"/>
       <c r="Q36" s="14" t="n"/>
       <c r="R36" s="14" t="n"/>
-      <c r="S36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -1929,20 +1888,19 @@
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
+      <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
-      <c r="L37" s="9">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;""),K37-J37,"")</f>
-        <v/>
-      </c>
+      <c r="K37" s="9">
+        <f>IF(AND(I37&lt;&gt;"",J37&lt;&gt;""),J37-I37,"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
       <c r="P37" s="10" t="n"/>
       <c r="Q37" s="10" t="n"/>
       <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -1953,20 +1911,19 @@
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="14" t="n"/>
       <c r="H38" s="14" t="n"/>
-      <c r="I38" s="14" t="n"/>
+      <c r="I38" s="15" t="n"/>
       <c r="J38" s="15" t="n"/>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="13">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;""),K38-J38,"")</f>
-        <v/>
-      </c>
+      <c r="K38" s="13">
+        <f>IF(AND(I38&lt;&gt;"",J38&lt;&gt;""),J38-I38,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="14" t="n"/>
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
       <c r="P38" s="14" t="n"/>
       <c r="Q38" s="14" t="n"/>
       <c r="R38" s="14" t="n"/>
-      <c r="S38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -1977,20 +1934,19 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
+      <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
-      <c r="K39" s="11" t="n"/>
-      <c r="L39" s="9">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;""),K39-J39,"")</f>
-        <v/>
-      </c>
+      <c r="K39" s="9">
+        <f>IF(AND(I39&lt;&gt;"",J39&lt;&gt;""),J39-I39,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="10" t="n"/>
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
       <c r="P39" s="10" t="n"/>
       <c r="Q39" s="10" t="n"/>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -2001,20 +1957,19 @@
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="14" t="n"/>
       <c r="H40" s="14" t="n"/>
-      <c r="I40" s="14" t="n"/>
+      <c r="I40" s="15" t="n"/>
       <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="13">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;""),K40-J40,"")</f>
-        <v/>
-      </c>
+      <c r="K40" s="13">
+        <f>IF(AND(I40&lt;&gt;"",J40&lt;&gt;""),J40-I40,"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
       <c r="P40" s="14" t="n"/>
       <c r="Q40" s="14" t="n"/>
       <c r="R40" s="14" t="n"/>
-      <c r="S40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -2025,20 +1980,19 @@
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
+      <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
-      <c r="K41" s="11" t="n"/>
-      <c r="L41" s="9">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;""),K41-J41,"")</f>
-        <v/>
-      </c>
+      <c r="K41" s="9">
+        <f>IF(AND(I41&lt;&gt;"",J41&lt;&gt;""),J41-I41,"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="10" t="n"/>
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
       <c r="P41" s="10" t="n"/>
       <c r="Q41" s="10" t="n"/>
       <c r="R41" s="10" t="n"/>
-      <c r="S41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -2049,20 +2003,19 @@
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="14" t="n"/>
       <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n"/>
+      <c r="I42" s="15" t="n"/>
       <c r="J42" s="15" t="n"/>
-      <c r="K42" s="15" t="n"/>
-      <c r="L42" s="13">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;""),K42-J42,"")</f>
-        <v/>
-      </c>
+      <c r="K42" s="13">
+        <f>IF(AND(I42&lt;&gt;"",J42&lt;&gt;""),J42-I42,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="14" t="n"/>
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
       <c r="P42" s="14" t="n"/>
       <c r="Q42" s="14" t="n"/>
       <c r="R42" s="14" t="n"/>
-      <c r="S42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -2073,20 +2026,19 @@
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
+      <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
-      <c r="K43" s="11" t="n"/>
-      <c r="L43" s="9">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;""),K43-J43,"")</f>
-        <v/>
-      </c>
+      <c r="K43" s="9">
+        <f>IF(AND(I43&lt;&gt;"",J43&lt;&gt;""),J43-I43,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="10" t="n"/>
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
       <c r="P43" s="10" t="n"/>
       <c r="Q43" s="10" t="n"/>
       <c r="R43" s="10" t="n"/>
-      <c r="S43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -2097,20 +2049,19 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
       <c r="H44" s="14" t="n"/>
-      <c r="I44" s="14" t="n"/>
+      <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n"/>
-      <c r="K44" s="15" t="n"/>
-      <c r="L44" s="13">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;""),K44-J44,"")</f>
-        <v/>
-      </c>
+      <c r="K44" s="13">
+        <f>IF(AND(I44&lt;&gt;"",J44&lt;&gt;""),J44-I44,"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="14" t="n"/>
       <c r="O44" s="14" t="n"/>
       <c r="P44" s="14" t="n"/>
       <c r="Q44" s="14" t="n"/>
       <c r="R44" s="14" t="n"/>
-      <c r="S44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -2121,20 +2072,19 @@
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
+      <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="9">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;""),K45-J45,"")</f>
-        <v/>
-      </c>
+      <c r="K45" s="9">
+        <f>IF(AND(I45&lt;&gt;"",J45&lt;&gt;""),J45-I45,"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="10" t="n"/>
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
       <c r="P45" s="10" t="n"/>
       <c r="Q45" s="10" t="n"/>
       <c r="R45" s="10" t="n"/>
-      <c r="S45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -2145,20 +2095,19 @@
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="14" t="n"/>
       <c r="H46" s="14" t="n"/>
-      <c r="I46" s="14" t="n"/>
+      <c r="I46" s="15" t="n"/>
       <c r="J46" s="15" t="n"/>
-      <c r="K46" s="15" t="n"/>
-      <c r="L46" s="13">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;""),K46-J46,"")</f>
-        <v/>
-      </c>
+      <c r="K46" s="13">
+        <f>IF(AND(I46&lt;&gt;"",J46&lt;&gt;""),J46-I46,"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
       <c r="P46" s="14" t="n"/>
       <c r="Q46" s="14" t="n"/>
       <c r="R46" s="14" t="n"/>
-      <c r="S46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -2169,20 +2118,19 @@
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
+      <c r="I47" s="11" t="n"/>
       <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
-      <c r="L47" s="9">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;""),K47-J47,"")</f>
-        <v/>
-      </c>
+      <c r="K47" s="9">
+        <f>IF(AND(I47&lt;&gt;"",J47&lt;&gt;""),J47-I47,"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="10" t="n"/>
       <c r="M47" s="10" t="n"/>
       <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
       <c r="P47" s="10" t="n"/>
       <c r="Q47" s="10" t="n"/>
       <c r="R47" s="10" t="n"/>
-      <c r="S47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -2193,20 +2141,19 @@
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14" t="n"/>
       <c r="H48" s="14" t="n"/>
-      <c r="I48" s="14" t="n"/>
+      <c r="I48" s="15" t="n"/>
       <c r="J48" s="15" t="n"/>
-      <c r="K48" s="15" t="n"/>
-      <c r="L48" s="13">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;""),K48-J48,"")</f>
-        <v/>
-      </c>
+      <c r="K48" s="13">
+        <f>IF(AND(I48&lt;&gt;"",J48&lt;&gt;""),J48-I48,"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="14" t="n"/>
       <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
       <c r="P48" s="14" t="n"/>
       <c r="Q48" s="14" t="n"/>
       <c r="R48" s="14" t="n"/>
-      <c r="S48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -2217,20 +2164,19 @@
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
+      <c r="I49" s="11" t="n"/>
       <c r="J49" s="11" t="n"/>
-      <c r="K49" s="11" t="n"/>
-      <c r="L49" s="9">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;""),K49-J49,"")</f>
-        <v/>
-      </c>
+      <c r="K49" s="9">
+        <f>IF(AND(I49&lt;&gt;"",J49&lt;&gt;""),J49-I49,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="10" t="n"/>
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
       <c r="P49" s="10" t="n"/>
       <c r="Q49" s="10" t="n"/>
       <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -2241,20 +2187,19 @@
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14" t="n"/>
       <c r="H50" s="14" t="n"/>
-      <c r="I50" s="14" t="n"/>
+      <c r="I50" s="15" t="n"/>
       <c r="J50" s="15" t="n"/>
-      <c r="K50" s="15" t="n"/>
-      <c r="L50" s="13">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;""),K50-J50,"")</f>
-        <v/>
-      </c>
+      <c r="K50" s="13">
+        <f>IF(AND(I50&lt;&gt;"",J50&lt;&gt;""),J50-I50,"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="14" t="n"/>
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
       <c r="P50" s="14" t="n"/>
       <c r="Q50" s="14" t="n"/>
       <c r="R50" s="14" t="n"/>
-      <c r="S50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -2265,20 +2210,19 @@
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
+      <c r="I51" s="11" t="n"/>
       <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
-      <c r="L51" s="9">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;""),K51-J51,"")</f>
-        <v/>
-      </c>
+      <c r="K51" s="9">
+        <f>IF(AND(I51&lt;&gt;"",J51&lt;&gt;""),J51-I51,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="10" t="n"/>
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
       <c r="P51" s="10" t="n"/>
       <c r="Q51" s="10" t="n"/>
       <c r="R51" s="10" t="n"/>
-      <c r="S51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -2289,20 +2233,19 @@
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14" t="n"/>
       <c r="H52" s="14" t="n"/>
-      <c r="I52" s="14" t="n"/>
+      <c r="I52" s="15" t="n"/>
       <c r="J52" s="15" t="n"/>
-      <c r="K52" s="15" t="n"/>
-      <c r="L52" s="13">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;""),K52-J52,"")</f>
-        <v/>
-      </c>
+      <c r="K52" s="13">
+        <f>IF(AND(I52&lt;&gt;"",J52&lt;&gt;""),J52-I52,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="14" t="n"/>
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
       <c r="P52" s="14" t="n"/>
       <c r="Q52" s="14" t="n"/>
       <c r="R52" s="14" t="n"/>
-      <c r="S52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -2313,20 +2256,19 @@
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
+      <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
-      <c r="K53" s="11" t="n"/>
-      <c r="L53" s="9">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;""),K53-J53,"")</f>
-        <v/>
-      </c>
+      <c r="K53" s="9">
+        <f>IF(AND(I53&lt;&gt;"",J53&lt;&gt;""),J53-I53,"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="10" t="n"/>
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
       <c r="P53" s="10" t="n"/>
       <c r="Q53" s="10" t="n"/>
       <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -2337,20 +2279,19 @@
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="14" t="n"/>
       <c r="H54" s="14" t="n"/>
-      <c r="I54" s="14" t="n"/>
+      <c r="I54" s="15" t="n"/>
       <c r="J54" s="15" t="n"/>
-      <c r="K54" s="15" t="n"/>
-      <c r="L54" s="13">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;""),K54-J54,"")</f>
-        <v/>
-      </c>
+      <c r="K54" s="13">
+        <f>IF(AND(I54&lt;&gt;"",J54&lt;&gt;""),J54-I54,"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="14" t="n"/>
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="14" t="n"/>
       <c r="O54" s="14" t="n"/>
       <c r="P54" s="14" t="n"/>
       <c r="Q54" s="14" t="n"/>
       <c r="R54" s="14" t="n"/>
-      <c r="S54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -2361,20 +2302,19 @@
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
+      <c r="I55" s="11" t="n"/>
       <c r="J55" s="11" t="n"/>
-      <c r="K55" s="11" t="n"/>
-      <c r="L55" s="9">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;""),K55-J55,"")</f>
-        <v/>
-      </c>
+      <c r="K55" s="9">
+        <f>IF(AND(I55&lt;&gt;"",J55&lt;&gt;""),J55-I55,"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="10" t="n"/>
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
       <c r="P55" s="10" t="n"/>
       <c r="Q55" s="10" t="n"/>
       <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -2385,20 +2325,19 @@
       <c r="F56" s="14" t="n"/>
       <c r="G56" s="14" t="n"/>
       <c r="H56" s="14" t="n"/>
-      <c r="I56" s="14" t="n"/>
+      <c r="I56" s="15" t="n"/>
       <c r="J56" s="15" t="n"/>
-      <c r="K56" s="15" t="n"/>
-      <c r="L56" s="13">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;""),K56-J56,"")</f>
-        <v/>
-      </c>
+      <c r="K56" s="13">
+        <f>IF(AND(I56&lt;&gt;"",J56&lt;&gt;""),J56-I56,"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="14" t="n"/>
       <c r="M56" s="14" t="n"/>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
       <c r="P56" s="14" t="n"/>
       <c r="Q56" s="14" t="n"/>
       <c r="R56" s="14" t="n"/>
-      <c r="S56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -2409,20 +2348,19 @@
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
+      <c r="I57" s="11" t="n"/>
       <c r="J57" s="11" t="n"/>
-      <c r="K57" s="11" t="n"/>
-      <c r="L57" s="9">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;""),K57-J57,"")</f>
-        <v/>
-      </c>
+      <c r="K57" s="9">
+        <f>IF(AND(I57&lt;&gt;"",J57&lt;&gt;""),J57-I57,"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="10" t="n"/>
       <c r="M57" s="10" t="n"/>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
       <c r="P57" s="10" t="n"/>
       <c r="Q57" s="10" t="n"/>
       <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -2433,20 +2371,19 @@
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="14" t="n"/>
       <c r="H58" s="14" t="n"/>
-      <c r="I58" s="14" t="n"/>
+      <c r="I58" s="15" t="n"/>
       <c r="J58" s="15" t="n"/>
-      <c r="K58" s="15" t="n"/>
-      <c r="L58" s="13">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;""),K58-J58,"")</f>
-        <v/>
-      </c>
+      <c r="K58" s="13">
+        <f>IF(AND(I58&lt;&gt;"",J58&lt;&gt;""),J58-I58,"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="14" t="n"/>
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
       <c r="P58" s="14" t="n"/>
       <c r="Q58" s="14" t="n"/>
       <c r="R58" s="14" t="n"/>
-      <c r="S58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -2457,20 +2394,19 @@
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
-      <c r="K59" s="11" t="n"/>
-      <c r="L59" s="9">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;""),K59-J59,"")</f>
-        <v/>
-      </c>
+      <c r="K59" s="9">
+        <f>IF(AND(I59&lt;&gt;"",J59&lt;&gt;""),J59-I59,"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="10" t="n"/>
       <c r="M59" s="10" t="n"/>
       <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
       <c r="P59" s="10" t="n"/>
       <c r="Q59" s="10" t="n"/>
       <c r="R59" s="10" t="n"/>
-      <c r="S59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -2481,20 +2417,19 @@
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="14" t="n"/>
       <c r="H60" s="14" t="n"/>
-      <c r="I60" s="14" t="n"/>
+      <c r="I60" s="15" t="n"/>
       <c r="J60" s="15" t="n"/>
-      <c r="K60" s="15" t="n"/>
-      <c r="L60" s="13">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;""),K60-J60,"")</f>
-        <v/>
-      </c>
+      <c r="K60" s="13">
+        <f>IF(AND(I60&lt;&gt;"",J60&lt;&gt;""),J60-I60,"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="14" t="n"/>
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
       <c r="P60" s="14" t="n"/>
       <c r="Q60" s="14" t="n"/>
       <c r="R60" s="14" t="n"/>
-      <c r="S60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -2505,20 +2440,19 @@
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
       <c r="J61" s="11" t="n"/>
-      <c r="K61" s="11" t="n"/>
-      <c r="L61" s="9">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;""),K61-J61,"")</f>
-        <v/>
-      </c>
+      <c r="K61" s="9">
+        <f>IF(AND(I61&lt;&gt;"",J61&lt;&gt;""),J61-I61,"")</f>
+        <v/>
+      </c>
+      <c r="L61" s="10" t="n"/>
       <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
       <c r="P61" s="10" t="n"/>
       <c r="Q61" s="10" t="n"/>
       <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -2529,20 +2463,19 @@
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="14" t="n"/>
       <c r="H62" s="14" t="n"/>
-      <c r="I62" s="14" t="n"/>
+      <c r="I62" s="15" t="n"/>
       <c r="J62" s="15" t="n"/>
-      <c r="K62" s="15" t="n"/>
-      <c r="L62" s="13">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;""),K62-J62,"")</f>
-        <v/>
-      </c>
+      <c r="K62" s="13">
+        <f>IF(AND(I62&lt;&gt;"",J62&lt;&gt;""),J62-I62,"")</f>
+        <v/>
+      </c>
+      <c r="L62" s="14" t="n"/>
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
       <c r="P62" s="14" t="n"/>
       <c r="Q62" s="14" t="n"/>
       <c r="R62" s="14" t="n"/>
-      <c r="S62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -2553,20 +2486,19 @@
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
+      <c r="I63" s="11" t="n"/>
       <c r="J63" s="11" t="n"/>
-      <c r="K63" s="11" t="n"/>
-      <c r="L63" s="9">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;""),K63-J63,"")</f>
-        <v/>
-      </c>
+      <c r="K63" s="9">
+        <f>IF(AND(I63&lt;&gt;"",J63&lt;&gt;""),J63-I63,"")</f>
+        <v/>
+      </c>
+      <c r="L63" s="10" t="n"/>
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
       <c r="P63" s="10" t="n"/>
       <c r="Q63" s="10" t="n"/>
       <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -2577,20 +2509,19 @@
       <c r="F64" s="14" t="n"/>
       <c r="G64" s="14" t="n"/>
       <c r="H64" s="14" t="n"/>
-      <c r="I64" s="14" t="n"/>
+      <c r="I64" s="15" t="n"/>
       <c r="J64" s="15" t="n"/>
-      <c r="K64" s="15" t="n"/>
-      <c r="L64" s="13">
-        <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;""),K64-J64,"")</f>
-        <v/>
-      </c>
+      <c r="K64" s="13">
+        <f>IF(AND(I64&lt;&gt;"",J64&lt;&gt;""),J64-I64,"")</f>
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n"/>
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
       <c r="O64" s="14" t="n"/>
       <c r="P64" s="14" t="n"/>
       <c r="Q64" s="14" t="n"/>
       <c r="R64" s="14" t="n"/>
-      <c r="S64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -2601,20 +2532,19 @@
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
-      <c r="K65" s="11" t="n"/>
-      <c r="L65" s="9">
-        <f>IF(AND(J65&lt;&gt;"",K65&lt;&gt;""),K65-J65,"")</f>
-        <v/>
-      </c>
+      <c r="K65" s="9">
+        <f>IF(AND(I65&lt;&gt;"",J65&lt;&gt;""),J65-I65,"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="10" t="n"/>
       <c r="M65" s="10" t="n"/>
       <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
       <c r="P65" s="10" t="n"/>
       <c r="Q65" s="10" t="n"/>
       <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -2625,20 +2555,19 @@
       <c r="F66" s="14" t="n"/>
       <c r="G66" s="14" t="n"/>
       <c r="H66" s="14" t="n"/>
-      <c r="I66" s="14" t="n"/>
+      <c r="I66" s="15" t="n"/>
       <c r="J66" s="15" t="n"/>
-      <c r="K66" s="15" t="n"/>
-      <c r="L66" s="13">
-        <f>IF(AND(J66&lt;&gt;"",K66&lt;&gt;""),K66-J66,"")</f>
-        <v/>
-      </c>
+      <c r="K66" s="13">
+        <f>IF(AND(I66&lt;&gt;"",J66&lt;&gt;""),J66-I66,"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="14" t="n"/>
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
       <c r="P66" s="14" t="n"/>
       <c r="Q66" s="14" t="n"/>
       <c r="R66" s="14" t="n"/>
-      <c r="S66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -2649,20 +2578,19 @@
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
-      <c r="K67" s="11" t="n"/>
-      <c r="L67" s="9">
-        <f>IF(AND(J67&lt;&gt;"",K67&lt;&gt;""),K67-J67,"")</f>
-        <v/>
-      </c>
+      <c r="K67" s="9">
+        <f>IF(AND(I67&lt;&gt;"",J67&lt;&gt;""),J67-I67,"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="10" t="n"/>
       <c r="M67" s="10" t="n"/>
       <c r="N67" s="10" t="n"/>
       <c r="O67" s="10" t="n"/>
       <c r="P67" s="10" t="n"/>
       <c r="Q67" s="10" t="n"/>
       <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -2673,20 +2601,19 @@
       <c r="F68" s="14" t="n"/>
       <c r="G68" s="14" t="n"/>
       <c r="H68" s="14" t="n"/>
-      <c r="I68" s="14" t="n"/>
+      <c r="I68" s="15" t="n"/>
       <c r="J68" s="15" t="n"/>
-      <c r="K68" s="15" t="n"/>
-      <c r="L68" s="13">
-        <f>IF(AND(J68&lt;&gt;"",K68&lt;&gt;""),K68-J68,"")</f>
-        <v/>
-      </c>
+      <c r="K68" s="13">
+        <f>IF(AND(I68&lt;&gt;"",J68&lt;&gt;""),J68-I68,"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="14" t="n"/>
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
       <c r="P68" s="14" t="n"/>
       <c r="Q68" s="14" t="n"/>
       <c r="R68" s="14" t="n"/>
-      <c r="S68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -2697,20 +2624,19 @@
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
       <c r="J69" s="11" t="n"/>
-      <c r="K69" s="11" t="n"/>
-      <c r="L69" s="9">
-        <f>IF(AND(J69&lt;&gt;"",K69&lt;&gt;""),K69-J69,"")</f>
-        <v/>
-      </c>
+      <c r="K69" s="9">
+        <f>IF(AND(I69&lt;&gt;"",J69&lt;&gt;""),J69-I69,"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="10" t="n"/>
       <c r="M69" s="10" t="n"/>
       <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
       <c r="P69" s="10" t="n"/>
       <c r="Q69" s="10" t="n"/>
       <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -2721,20 +2647,19 @@
       <c r="F70" s="14" t="n"/>
       <c r="G70" s="14" t="n"/>
       <c r="H70" s="14" t="n"/>
-      <c r="I70" s="14" t="n"/>
+      <c r="I70" s="15" t="n"/>
       <c r="J70" s="15" t="n"/>
-      <c r="K70" s="15" t="n"/>
-      <c r="L70" s="13">
-        <f>IF(AND(J70&lt;&gt;"",K70&lt;&gt;""),K70-J70,"")</f>
-        <v/>
-      </c>
+      <c r="K70" s="13">
+        <f>IF(AND(I70&lt;&gt;"",J70&lt;&gt;""),J70-I70,"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="14" t="n"/>
       <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
       <c r="P70" s="14" t="n"/>
       <c r="Q70" s="14" t="n"/>
       <c r="R70" s="14" t="n"/>
-      <c r="S70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -2745,20 +2670,19 @@
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
+      <c r="I71" s="11" t="n"/>
       <c r="J71" s="11" t="n"/>
-      <c r="K71" s="11" t="n"/>
-      <c r="L71" s="9">
-        <f>IF(AND(J71&lt;&gt;"",K71&lt;&gt;""),K71-J71,"")</f>
-        <v/>
-      </c>
+      <c r="K71" s="9">
+        <f>IF(AND(I71&lt;&gt;"",J71&lt;&gt;""),J71-I71,"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="10" t="n"/>
       <c r="M71" s="10" t="n"/>
       <c r="N71" s="10" t="n"/>
       <c r="O71" s="10" t="n"/>
       <c r="P71" s="10" t="n"/>
       <c r="Q71" s="10" t="n"/>
       <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -2769,20 +2693,19 @@
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="14" t="n"/>
       <c r="H72" s="14" t="n"/>
-      <c r="I72" s="14" t="n"/>
+      <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n"/>
-      <c r="K72" s="15" t="n"/>
-      <c r="L72" s="13">
-        <f>IF(AND(J72&lt;&gt;"",K72&lt;&gt;""),K72-J72,"")</f>
-        <v/>
-      </c>
+      <c r="K72" s="13">
+        <f>IF(AND(I72&lt;&gt;"",J72&lt;&gt;""),J72-I72,"")</f>
+        <v/>
+      </c>
+      <c r="L72" s="14" t="n"/>
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
       <c r="O72" s="14" t="n"/>
       <c r="P72" s="14" t="n"/>
       <c r="Q72" s="14" t="n"/>
       <c r="R72" s="14" t="n"/>
-      <c r="S72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -2793,20 +2716,19 @@
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
+      <c r="I73" s="11" t="n"/>
       <c r="J73" s="11" t="n"/>
-      <c r="K73" s="11" t="n"/>
-      <c r="L73" s="9">
-        <f>IF(AND(J73&lt;&gt;"",K73&lt;&gt;""),K73-J73,"")</f>
-        <v/>
-      </c>
+      <c r="K73" s="9">
+        <f>IF(AND(I73&lt;&gt;"",J73&lt;&gt;""),J73-I73,"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="10" t="n"/>
       <c r="M73" s="10" t="n"/>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
       <c r="P73" s="10" t="n"/>
       <c r="Q73" s="10" t="n"/>
       <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -2817,20 +2739,19 @@
       <c r="F74" s="14" t="n"/>
       <c r="G74" s="14" t="n"/>
       <c r="H74" s="14" t="n"/>
-      <c r="I74" s="14" t="n"/>
+      <c r="I74" s="15" t="n"/>
       <c r="J74" s="15" t="n"/>
-      <c r="K74" s="15" t="n"/>
-      <c r="L74" s="13">
-        <f>IF(AND(J74&lt;&gt;"",K74&lt;&gt;""),K74-J74,"")</f>
-        <v/>
-      </c>
+      <c r="K74" s="13">
+        <f>IF(AND(I74&lt;&gt;"",J74&lt;&gt;""),J74-I74,"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="14" t="n"/>
       <c r="M74" s="14" t="n"/>
       <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
       <c r="P74" s="14" t="n"/>
       <c r="Q74" s="14" t="n"/>
       <c r="R74" s="14" t="n"/>
-      <c r="S74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -2841,20 +2762,19 @@
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
-      <c r="I75" s="10" t="n"/>
+      <c r="I75" s="11" t="n"/>
       <c r="J75" s="11" t="n"/>
-      <c r="K75" s="11" t="n"/>
-      <c r="L75" s="9">
-        <f>IF(AND(J75&lt;&gt;"",K75&lt;&gt;""),K75-J75,"")</f>
-        <v/>
-      </c>
+      <c r="K75" s="9">
+        <f>IF(AND(I75&lt;&gt;"",J75&lt;&gt;""),J75-I75,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="10" t="n"/>
       <c r="M75" s="10" t="n"/>
       <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
       <c r="P75" s="10" t="n"/>
       <c r="Q75" s="10" t="n"/>
       <c r="R75" s="10" t="n"/>
-      <c r="S75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -2865,20 +2785,19 @@
       <c r="F76" s="14" t="n"/>
       <c r="G76" s="14" t="n"/>
       <c r="H76" s="14" t="n"/>
-      <c r="I76" s="14" t="n"/>
+      <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n"/>
-      <c r="K76" s="15" t="n"/>
-      <c r="L76" s="13">
-        <f>IF(AND(J76&lt;&gt;"",K76&lt;&gt;""),K76-J76,"")</f>
-        <v/>
-      </c>
+      <c r="K76" s="13">
+        <f>IF(AND(I76&lt;&gt;"",J76&lt;&gt;""),J76-I76,"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="14" t="n"/>
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n"/>
       <c r="P76" s="14" t="n"/>
       <c r="Q76" s="14" t="n"/>
       <c r="R76" s="14" t="n"/>
-      <c r="S76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -2889,20 +2808,19 @@
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
+      <c r="I77" s="11" t="n"/>
       <c r="J77" s="11" t="n"/>
-      <c r="K77" s="11" t="n"/>
-      <c r="L77" s="9">
-        <f>IF(AND(J77&lt;&gt;"",K77&lt;&gt;""),K77-J77,"")</f>
-        <v/>
-      </c>
+      <c r="K77" s="9">
+        <f>IF(AND(I77&lt;&gt;"",J77&lt;&gt;""),J77-I77,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="10" t="n"/>
       <c r="M77" s="10" t="n"/>
       <c r="N77" s="10" t="n"/>
       <c r="O77" s="10" t="n"/>
       <c r="P77" s="10" t="n"/>
       <c r="Q77" s="10" t="n"/>
       <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -2913,20 +2831,19 @@
       <c r="F78" s="14" t="n"/>
       <c r="G78" s="14" t="n"/>
       <c r="H78" s="14" t="n"/>
-      <c r="I78" s="14" t="n"/>
+      <c r="I78" s="15" t="n"/>
       <c r="J78" s="15" t="n"/>
-      <c r="K78" s="15" t="n"/>
-      <c r="L78" s="13">
-        <f>IF(AND(J78&lt;&gt;"",K78&lt;&gt;""),K78-J78,"")</f>
-        <v/>
-      </c>
+      <c r="K78" s="13">
+        <f>IF(AND(I78&lt;&gt;"",J78&lt;&gt;""),J78-I78,"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="14" t="n"/>
       <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
       <c r="P78" s="14" t="n"/>
       <c r="Q78" s="14" t="n"/>
       <c r="R78" s="14" t="n"/>
-      <c r="S78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -2937,20 +2854,19 @@
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
+      <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
-      <c r="K79" s="11" t="n"/>
-      <c r="L79" s="9">
-        <f>IF(AND(J79&lt;&gt;"",K79&lt;&gt;""),K79-J79,"")</f>
-        <v/>
-      </c>
+      <c r="K79" s="9">
+        <f>IF(AND(I79&lt;&gt;"",J79&lt;&gt;""),J79-I79,"")</f>
+        <v/>
+      </c>
+      <c r="L79" s="10" t="n"/>
       <c r="M79" s="10" t="n"/>
       <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
       <c r="P79" s="10" t="n"/>
       <c r="Q79" s="10" t="n"/>
       <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -2961,20 +2877,19 @@
       <c r="F80" s="14" t="n"/>
       <c r="G80" s="14" t="n"/>
       <c r="H80" s="14" t="n"/>
-      <c r="I80" s="14" t="n"/>
+      <c r="I80" s="15" t="n"/>
       <c r="J80" s="15" t="n"/>
-      <c r="K80" s="15" t="n"/>
-      <c r="L80" s="13">
-        <f>IF(AND(J80&lt;&gt;"",K80&lt;&gt;""),K80-J80,"")</f>
-        <v/>
-      </c>
+      <c r="K80" s="13">
+        <f>IF(AND(I80&lt;&gt;"",J80&lt;&gt;""),J80-I80,"")</f>
+        <v/>
+      </c>
+      <c r="L80" s="14" t="n"/>
       <c r="M80" s="14" t="n"/>
       <c r="N80" s="14" t="n"/>
       <c r="O80" s="14" t="n"/>
       <c r="P80" s="14" t="n"/>
       <c r="Q80" s="14" t="n"/>
       <c r="R80" s="14" t="n"/>
-      <c r="S80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
@@ -2985,20 +2900,19 @@
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
+      <c r="I81" s="11" t="n"/>
       <c r="J81" s="11" t="n"/>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="9">
-        <f>IF(AND(J81&lt;&gt;"",K81&lt;&gt;""),K81-J81,"")</f>
-        <v/>
-      </c>
+      <c r="K81" s="9">
+        <f>IF(AND(I81&lt;&gt;"",J81&lt;&gt;""),J81-I81,"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="10" t="n"/>
       <c r="M81" s="10" t="n"/>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
       <c r="P81" s="10" t="n"/>
       <c r="Q81" s="10" t="n"/>
       <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -3009,20 +2923,19 @@
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="14" t="n"/>
       <c r="H82" s="14" t="n"/>
-      <c r="I82" s="14" t="n"/>
+      <c r="I82" s="15" t="n"/>
       <c r="J82" s="15" t="n"/>
-      <c r="K82" s="15" t="n"/>
-      <c r="L82" s="13">
-        <f>IF(AND(J82&lt;&gt;"",K82&lt;&gt;""),K82-J82,"")</f>
-        <v/>
-      </c>
+      <c r="K82" s="13">
+        <f>IF(AND(I82&lt;&gt;"",J82&lt;&gt;""),J82-I82,"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="14" t="n"/>
       <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="n"/>
       <c r="O82" s="14" t="n"/>
       <c r="P82" s="14" t="n"/>
       <c r="Q82" s="14" t="n"/>
       <c r="R82" s="14" t="n"/>
-      <c r="S82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
@@ -3033,20 +2946,19 @@
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
+      <c r="I83" s="11" t="n"/>
       <c r="J83" s="11" t="n"/>
-      <c r="K83" s="11" t="n"/>
-      <c r="L83" s="9">
-        <f>IF(AND(J83&lt;&gt;"",K83&lt;&gt;""),K83-J83,"")</f>
-        <v/>
-      </c>
+      <c r="K83" s="9">
+        <f>IF(AND(I83&lt;&gt;"",J83&lt;&gt;""),J83-I83,"")</f>
+        <v/>
+      </c>
+      <c r="L83" s="10" t="n"/>
       <c r="M83" s="10" t="n"/>
       <c r="N83" s="10" t="n"/>
       <c r="O83" s="10" t="n"/>
       <c r="P83" s="10" t="n"/>
       <c r="Q83" s="10" t="n"/>
       <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -3057,20 +2969,19 @@
       <c r="F84" s="14" t="n"/>
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
-      <c r="I84" s="14" t="n"/>
+      <c r="I84" s="15" t="n"/>
       <c r="J84" s="15" t="n"/>
-      <c r="K84" s="15" t="n"/>
-      <c r="L84" s="13">
-        <f>IF(AND(J84&lt;&gt;"",K84&lt;&gt;""),K84-J84,"")</f>
-        <v/>
-      </c>
+      <c r="K84" s="13">
+        <f>IF(AND(I84&lt;&gt;"",J84&lt;&gt;""),J84-I84,"")</f>
+        <v/>
+      </c>
+      <c r="L84" s="14" t="n"/>
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
       <c r="P84" s="14" t="n"/>
       <c r="Q84" s="14" t="n"/>
       <c r="R84" s="14" t="n"/>
-      <c r="S84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
@@ -3081,20 +2992,19 @@
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
+      <c r="I85" s="11" t="n"/>
       <c r="J85" s="11" t="n"/>
-      <c r="K85" s="11" t="n"/>
-      <c r="L85" s="9">
-        <f>IF(AND(J85&lt;&gt;"",K85&lt;&gt;""),K85-J85,"")</f>
-        <v/>
-      </c>
+      <c r="K85" s="9">
+        <f>IF(AND(I85&lt;&gt;"",J85&lt;&gt;""),J85-I85,"")</f>
+        <v/>
+      </c>
+      <c r="L85" s="10" t="n"/>
       <c r="M85" s="10" t="n"/>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
       <c r="P85" s="10" t="n"/>
       <c r="Q85" s="10" t="n"/>
       <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -3105,20 +3015,19 @@
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="14" t="n"/>
       <c r="H86" s="14" t="n"/>
-      <c r="I86" s="14" t="n"/>
+      <c r="I86" s="15" t="n"/>
       <c r="J86" s="15" t="n"/>
-      <c r="K86" s="15" t="n"/>
-      <c r="L86" s="13">
-        <f>IF(AND(J86&lt;&gt;"",K86&lt;&gt;""),K86-J86,"")</f>
-        <v/>
-      </c>
+      <c r="K86" s="13">
+        <f>IF(AND(I86&lt;&gt;"",J86&lt;&gt;""),J86-I86,"")</f>
+        <v/>
+      </c>
+      <c r="L86" s="14" t="n"/>
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
       <c r="O86" s="14" t="n"/>
       <c r="P86" s="14" t="n"/>
       <c r="Q86" s="14" t="n"/>
       <c r="R86" s="14" t="n"/>
-      <c r="S86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
@@ -3129,20 +3038,19 @@
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
+      <c r="I87" s="11" t="n"/>
       <c r="J87" s="11" t="n"/>
-      <c r="K87" s="11" t="n"/>
-      <c r="L87" s="9">
-        <f>IF(AND(J87&lt;&gt;"",K87&lt;&gt;""),K87-J87,"")</f>
-        <v/>
-      </c>
+      <c r="K87" s="9">
+        <f>IF(AND(I87&lt;&gt;"",J87&lt;&gt;""),J87-I87,"")</f>
+        <v/>
+      </c>
+      <c r="L87" s="10" t="n"/>
       <c r="M87" s="10" t="n"/>
       <c r="N87" s="10" t="n"/>
       <c r="O87" s="10" t="n"/>
       <c r="P87" s="10" t="n"/>
       <c r="Q87" s="10" t="n"/>
       <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -3153,20 +3061,19 @@
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="14" t="n"/>
       <c r="H88" s="14" t="n"/>
-      <c r="I88" s="14" t="n"/>
+      <c r="I88" s="15" t="n"/>
       <c r="J88" s="15" t="n"/>
-      <c r="K88" s="15" t="n"/>
-      <c r="L88" s="13">
-        <f>IF(AND(J88&lt;&gt;"",K88&lt;&gt;""),K88-J88,"")</f>
-        <v/>
-      </c>
+      <c r="K88" s="13">
+        <f>IF(AND(I88&lt;&gt;"",J88&lt;&gt;""),J88-I88,"")</f>
+        <v/>
+      </c>
+      <c r="L88" s="14" t="n"/>
       <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
       <c r="O88" s="14" t="n"/>
       <c r="P88" s="14" t="n"/>
       <c r="Q88" s="14" t="n"/>
       <c r="R88" s="14" t="n"/>
-      <c r="S88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
@@ -3177,20 +3084,19 @@
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
-      <c r="I89" s="10" t="n"/>
+      <c r="I89" s="11" t="n"/>
       <c r="J89" s="11" t="n"/>
-      <c r="K89" s="11" t="n"/>
-      <c r="L89" s="9">
-        <f>IF(AND(J89&lt;&gt;"",K89&lt;&gt;""),K89-J89,"")</f>
-        <v/>
-      </c>
+      <c r="K89" s="9">
+        <f>IF(AND(I89&lt;&gt;"",J89&lt;&gt;""),J89-I89,"")</f>
+        <v/>
+      </c>
+      <c r="L89" s="10" t="n"/>
       <c r="M89" s="10" t="n"/>
       <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
       <c r="P89" s="10" t="n"/>
       <c r="Q89" s="10" t="n"/>
       <c r="R89" s="10" t="n"/>
-      <c r="S89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -3201,20 +3107,19 @@
       <c r="F90" s="14" t="n"/>
       <c r="G90" s="14" t="n"/>
       <c r="H90" s="14" t="n"/>
-      <c r="I90" s="14" t="n"/>
+      <c r="I90" s="15" t="n"/>
       <c r="J90" s="15" t="n"/>
-      <c r="K90" s="15" t="n"/>
-      <c r="L90" s="13">
-        <f>IF(AND(J90&lt;&gt;"",K90&lt;&gt;""),K90-J90,"")</f>
-        <v/>
-      </c>
+      <c r="K90" s="13">
+        <f>IF(AND(I90&lt;&gt;"",J90&lt;&gt;""),J90-I90,"")</f>
+        <v/>
+      </c>
+      <c r="L90" s="14" t="n"/>
       <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n"/>
       <c r="P90" s="14" t="n"/>
       <c r="Q90" s="14" t="n"/>
       <c r="R90" s="14" t="n"/>
-      <c r="S90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
@@ -3225,20 +3130,19 @@
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
+      <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
-      <c r="K91" s="11" t="n"/>
-      <c r="L91" s="9">
-        <f>IF(AND(J91&lt;&gt;"",K91&lt;&gt;""),K91-J91,"")</f>
-        <v/>
-      </c>
+      <c r="K91" s="9">
+        <f>IF(AND(I91&lt;&gt;"",J91&lt;&gt;""),J91-I91,"")</f>
+        <v/>
+      </c>
+      <c r="L91" s="10" t="n"/>
       <c r="M91" s="10" t="n"/>
       <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
       <c r="P91" s="10" t="n"/>
       <c r="Q91" s="10" t="n"/>
       <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -3249,20 +3153,19 @@
       <c r="F92" s="14" t="n"/>
       <c r="G92" s="14" t="n"/>
       <c r="H92" s="14" t="n"/>
-      <c r="I92" s="14" t="n"/>
+      <c r="I92" s="15" t="n"/>
       <c r="J92" s="15" t="n"/>
-      <c r="K92" s="15" t="n"/>
-      <c r="L92" s="13">
-        <f>IF(AND(J92&lt;&gt;"",K92&lt;&gt;""),K92-J92,"")</f>
-        <v/>
-      </c>
+      <c r="K92" s="13">
+        <f>IF(AND(I92&lt;&gt;"",J92&lt;&gt;""),J92-I92,"")</f>
+        <v/>
+      </c>
+      <c r="L92" s="14" t="n"/>
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
       <c r="O92" s="14" t="n"/>
       <c r="P92" s="14" t="n"/>
       <c r="Q92" s="14" t="n"/>
       <c r="R92" s="14" t="n"/>
-      <c r="S92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
@@ -3273,20 +3176,19 @@
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
+      <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
-      <c r="K93" s="11" t="n"/>
-      <c r="L93" s="9">
-        <f>IF(AND(J93&lt;&gt;"",K93&lt;&gt;""),K93-J93,"")</f>
-        <v/>
-      </c>
+      <c r="K93" s="9">
+        <f>IF(AND(I93&lt;&gt;"",J93&lt;&gt;""),J93-I93,"")</f>
+        <v/>
+      </c>
+      <c r="L93" s="10" t="n"/>
       <c r="M93" s="10" t="n"/>
       <c r="N93" s="10" t="n"/>
       <c r="O93" s="10" t="n"/>
       <c r="P93" s="10" t="n"/>
       <c r="Q93" s="10" t="n"/>
       <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -3297,20 +3199,19 @@
       <c r="F94" s="14" t="n"/>
       <c r="G94" s="14" t="n"/>
       <c r="H94" s="14" t="n"/>
-      <c r="I94" s="14" t="n"/>
+      <c r="I94" s="15" t="n"/>
       <c r="J94" s="15" t="n"/>
-      <c r="K94" s="15" t="n"/>
-      <c r="L94" s="13">
-        <f>IF(AND(J94&lt;&gt;"",K94&lt;&gt;""),K94-J94,"")</f>
-        <v/>
-      </c>
+      <c r="K94" s="13">
+        <f>IF(AND(I94&lt;&gt;"",J94&lt;&gt;""),J94-I94,"")</f>
+        <v/>
+      </c>
+      <c r="L94" s="14" t="n"/>
       <c r="M94" s="14" t="n"/>
       <c r="N94" s="14" t="n"/>
       <c r="O94" s="14" t="n"/>
       <c r="P94" s="14" t="n"/>
       <c r="Q94" s="14" t="n"/>
       <c r="R94" s="14" t="n"/>
-      <c r="S94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
@@ -3321,20 +3222,19 @@
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
-      <c r="I95" s="10" t="n"/>
+      <c r="I95" s="11" t="n"/>
       <c r="J95" s="11" t="n"/>
-      <c r="K95" s="11" t="n"/>
-      <c r="L95" s="9">
-        <f>IF(AND(J95&lt;&gt;"",K95&lt;&gt;""),K95-J95,"")</f>
-        <v/>
-      </c>
+      <c r="K95" s="9">
+        <f>IF(AND(I95&lt;&gt;"",J95&lt;&gt;""),J95-I95,"")</f>
+        <v/>
+      </c>
+      <c r="L95" s="10" t="n"/>
       <c r="M95" s="10" t="n"/>
       <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
       <c r="P95" s="10" t="n"/>
       <c r="Q95" s="10" t="n"/>
       <c r="R95" s="10" t="n"/>
-      <c r="S95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -3345,20 +3245,19 @@
       <c r="F96" s="14" t="n"/>
       <c r="G96" s="14" t="n"/>
       <c r="H96" s="14" t="n"/>
-      <c r="I96" s="14" t="n"/>
+      <c r="I96" s="15" t="n"/>
       <c r="J96" s="15" t="n"/>
-      <c r="K96" s="15" t="n"/>
-      <c r="L96" s="13">
-        <f>IF(AND(J96&lt;&gt;"",K96&lt;&gt;""),K96-J96,"")</f>
-        <v/>
-      </c>
+      <c r="K96" s="13">
+        <f>IF(AND(I96&lt;&gt;"",J96&lt;&gt;""),J96-I96,"")</f>
+        <v/>
+      </c>
+      <c r="L96" s="14" t="n"/>
       <c r="M96" s="14" t="n"/>
       <c r="N96" s="14" t="n"/>
       <c r="O96" s="14" t="n"/>
       <c r="P96" s="14" t="n"/>
       <c r="Q96" s="14" t="n"/>
       <c r="R96" s="14" t="n"/>
-      <c r="S96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
@@ -3369,20 +3268,19 @@
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
+      <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
-      <c r="K97" s="11" t="n"/>
-      <c r="L97" s="9">
-        <f>IF(AND(J97&lt;&gt;"",K97&lt;&gt;""),K97-J97,"")</f>
-        <v/>
-      </c>
+      <c r="K97" s="9">
+        <f>IF(AND(I97&lt;&gt;"",J97&lt;&gt;""),J97-I97,"")</f>
+        <v/>
+      </c>
+      <c r="L97" s="10" t="n"/>
       <c r="M97" s="10" t="n"/>
       <c r="N97" s="10" t="n"/>
       <c r="O97" s="10" t="n"/>
       <c r="P97" s="10" t="n"/>
       <c r="Q97" s="10" t="n"/>
       <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -3393,20 +3291,19 @@
       <c r="F98" s="14" t="n"/>
       <c r="G98" s="14" t="n"/>
       <c r="H98" s="14" t="n"/>
-      <c r="I98" s="14" t="n"/>
+      <c r="I98" s="15" t="n"/>
       <c r="J98" s="15" t="n"/>
-      <c r="K98" s="15" t="n"/>
-      <c r="L98" s="13">
-        <f>IF(AND(J98&lt;&gt;"",K98&lt;&gt;""),K98-J98,"")</f>
-        <v/>
-      </c>
+      <c r="K98" s="13">
+        <f>IF(AND(I98&lt;&gt;"",J98&lt;&gt;""),J98-I98,"")</f>
+        <v/>
+      </c>
+      <c r="L98" s="14" t="n"/>
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
       <c r="O98" s="14" t="n"/>
       <c r="P98" s="14" t="n"/>
       <c r="Q98" s="14" t="n"/>
       <c r="R98" s="14" t="n"/>
-      <c r="S98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
@@ -3417,20 +3314,19 @@
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
+      <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
-      <c r="K99" s="11" t="n"/>
-      <c r="L99" s="9">
-        <f>IF(AND(J99&lt;&gt;"",K99&lt;&gt;""),K99-J99,"")</f>
-        <v/>
-      </c>
+      <c r="K99" s="9">
+        <f>IF(AND(I99&lt;&gt;"",J99&lt;&gt;""),J99-I99,"")</f>
+        <v/>
+      </c>
+      <c r="L99" s="10" t="n"/>
       <c r="M99" s="10" t="n"/>
       <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
       <c r="P99" s="10" t="n"/>
       <c r="Q99" s="10" t="n"/>
       <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -3441,20 +3337,19 @@
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="14" t="n"/>
       <c r="H100" s="14" t="n"/>
-      <c r="I100" s="14" t="n"/>
+      <c r="I100" s="15" t="n"/>
       <c r="J100" s="15" t="n"/>
-      <c r="K100" s="15" t="n"/>
-      <c r="L100" s="13">
-        <f>IF(AND(J100&lt;&gt;"",K100&lt;&gt;""),K100-J100,"")</f>
-        <v/>
-      </c>
+      <c r="K100" s="13">
+        <f>IF(AND(I100&lt;&gt;"",J100&lt;&gt;""),J100-I100,"")</f>
+        <v/>
+      </c>
+      <c r="L100" s="14" t="n"/>
       <c r="M100" s="14" t="n"/>
       <c r="N100" s="14" t="n"/>
       <c r="O100" s="14" t="n"/>
       <c r="P100" s="14" t="n"/>
       <c r="Q100" s="14" t="n"/>
       <c r="R100" s="14" t="n"/>
-      <c r="S100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
@@ -3465,20 +3360,19 @@
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
+      <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
-      <c r="K101" s="11" t="n"/>
-      <c r="L101" s="9">
-        <f>IF(AND(J101&lt;&gt;"",K101&lt;&gt;""),K101-J101,"")</f>
-        <v/>
-      </c>
+      <c r="K101" s="9">
+        <f>IF(AND(I101&lt;&gt;"",J101&lt;&gt;""),J101-I101,"")</f>
+        <v/>
+      </c>
+      <c r="L101" s="10" t="n"/>
       <c r="M101" s="10" t="n"/>
       <c r="N101" s="10" t="n"/>
       <c r="O101" s="10" t="n"/>
       <c r="P101" s="10" t="n"/>
       <c r="Q101" s="10" t="n"/>
       <c r="R101" s="10" t="n"/>
-      <c r="S101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -3489,30 +3383,29 @@
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="14" t="n"/>
       <c r="H102" s="14" t="n"/>
-      <c r="I102" s="14" t="n"/>
+      <c r="I102" s="15" t="n"/>
       <c r="J102" s="15" t="n"/>
-      <c r="K102" s="15" t="n"/>
-      <c r="L102" s="13">
-        <f>IF(AND(J102&lt;&gt;"",K102&lt;&gt;""),K102-J102,"")</f>
-        <v/>
-      </c>
+      <c r="K102" s="13">
+        <f>IF(AND(I102&lt;&gt;"",J102&lt;&gt;""),J102-I102,"")</f>
+        <v/>
+      </c>
+      <c r="L102" s="14" t="n"/>
       <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
       <c r="O102" s="14" t="n"/>
       <c r="P102" s="14" t="n"/>
       <c r="Q102" s="14" t="n"/>
       <c r="R102" s="14" t="n"/>
-      <c r="S102" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S2"/>
+  <autoFilter ref="A2:R2"/>
   <mergeCells count="4">
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="E1:L1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="N3:N102">
+  <conditionalFormatting sqref="M3:M102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"自家移植"</formula>
     </cfRule>
@@ -3541,7 +3434,7 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:R102">
+  <conditionalFormatting sqref="Q3:Q102">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="0">
       <formula>"入院中"</formula>
     </cfRule>
@@ -3552,7 +3445,7 @@
       <formula>"外来移行"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M102">
+  <conditionalFormatting sqref="L3:L102">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="9">
       <formula>"3"</formula>
     </cfRule>
@@ -3560,7 +3453,7 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q102">
+  <conditionalFormatting sqref="P3:P102">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="1">
       <formula>"CR"</formula>
     </cfRule>
@@ -3595,7 +3488,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I102">
+  <conditionalFormatting sqref="H3:H102">
     <cfRule type="cellIs" priority="26" operator="equal" dxfId="10">
       <formula>"Favorable"</formula>
     </cfRule>
@@ -3622,37 +3515,37 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
-    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="C3:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>sex</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>disease</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>stage</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>cytogenetics</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>gene</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>risk</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>ps</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>label</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>regimen</formula1>
     </dataValidation>
-    <dataValidation sqref="Q3:Q102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="P3:P102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>outcome</formula1>
     </dataValidation>
-    <dataValidation sqref="R3:R102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="Q3:Q102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>status</formula1>
     </dataValidation>
   </dataValidations>
@@ -4892,22 +4785,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4918,24 +4810,23 @@
       </c>
       <c r="B1" s="17" t="n"/>
       <c r="C1" s="17" t="n"/>
-      <c r="D1" s="17" t="n"/>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>コンサルト内容</t>
         </is>
       </c>
+      <c r="E1" s="19" t="n"/>
       <c r="F1" s="19" t="n"/>
       <c r="G1" s="19" t="n"/>
       <c r="H1" s="19" t="n"/>
       <c r="I1" s="19" t="n"/>
-      <c r="J1" s="19" t="n"/>
-      <c r="K1" s="20" t="inlineStr">
+      <c r="J1" s="20" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="L1" s="21" t="n"/>
-      <c r="M1" s="20" t="inlineStr">
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="20" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
@@ -4949,60 +4840,55 @@
       </c>
       <c r="B2" s="22" t="inlineStr">
         <is>
-          <t>イニシャル</t>
+          <t>年齢</t>
         </is>
       </c>
       <c r="C2" s="22" t="inlineStr">
         <is>
-          <t>年齢</t>
+          <t>性別</t>
         </is>
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>性別</t>
+          <t>緊急度</t>
         </is>
       </c>
       <c r="E2" s="22" t="inlineStr">
         <is>
-          <t>緊急度</t>
+          <t>コンサルト日</t>
         </is>
       </c>
       <c r="F2" s="22" t="inlineStr">
         <is>
-          <t>コンサルト日</t>
+          <t>依頼科</t>
         </is>
       </c>
       <c r="G2" s="22" t="inlineStr">
         <is>
-          <t>依頼科</t>
+          <t>依頼医</t>
         </is>
       </c>
       <c r="H2" s="22" t="inlineStr">
         <is>
-          <t>依頼医</t>
+          <t>コンサルト理由</t>
         </is>
       </c>
       <c r="I2" s="22" t="inlineStr">
         <is>
-          <t>コンサルト理由</t>
+          <t>疾患(疑い含む)</t>
         </is>
       </c>
       <c r="J2" s="22" t="inlineStr">
         <is>
-          <t>疾患(疑い含む)</t>
+          <t>対応内容</t>
         </is>
       </c>
       <c r="K2" s="22" t="inlineStr">
         <is>
-          <t>対応内容</t>
+          <t>フォロー要否</t>
         </is>
       </c>
       <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t>フォロー要否</t>
-        </is>
-      </c>
-      <c r="M2" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -5013,15 +4899,14 @@
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
       <c r="I3" s="10" t="n"/>
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
       <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="23" t="n"/>
@@ -5030,28 +4915,26 @@
       <c r="D4" s="24" t="n"/>
       <c r="E4" s="25" t="n"/>
       <c r="F4" s="26" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="26" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="26" t="n"/>
+      <c r="K4" s="26" t="n"/>
+      <c r="L4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
       <c r="L5" s="10" t="n"/>
-      <c r="M5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n"/>
@@ -5060,28 +4943,26 @@
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="25" t="n"/>
       <c r="F6" s="26" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="25" t="n"/>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="25" t="n"/>
-      <c r="L6" s="25" t="n"/>
-      <c r="M6" s="25" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="26" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="26" t="n"/>
+      <c r="L6" s="26" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
       <c r="L7" s="10" t="n"/>
-      <c r="M7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n"/>
@@ -5090,28 +4971,26 @@
       <c r="D8" s="24" t="n"/>
       <c r="E8" s="25" t="n"/>
       <c r="F8" s="26" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="25" t="n"/>
-      <c r="L8" s="25" t="n"/>
-      <c r="M8" s="25" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="26" t="n"/>
+      <c r="L8" s="26" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="n"/>
       <c r="L9" s="10" t="n"/>
-      <c r="M9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n"/>
@@ -5120,28 +4999,26 @@
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="25" t="n"/>
       <c r="F10" s="26" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="25" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="25" t="n"/>
-      <c r="L10" s="25" t="n"/>
-      <c r="M10" s="25" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="26" t="n"/>
+      <c r="K10" s="26" t="n"/>
+      <c r="L10" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="n"/>
       <c r="L11" s="10" t="n"/>
-      <c r="M11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="n"/>
@@ -5150,28 +5027,26 @@
       <c r="D12" s="24" t="n"/>
       <c r="E12" s="25" t="n"/>
       <c r="F12" s="26" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="25" t="n"/>
-      <c r="M12" s="25" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="26" t="n"/>
+      <c r="L12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="n"/>
       <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="n"/>
@@ -5180,28 +5055,26 @@
       <c r="D14" s="24" t="n"/>
       <c r="E14" s="25" t="n"/>
       <c r="F14" s="26" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="26" t="n"/>
+      <c r="I14" s="26" t="n"/>
+      <c r="J14" s="26" t="n"/>
+      <c r="K14" s="26" t="n"/>
+      <c r="L14" s="26" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
-      <c r="M15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n"/>
@@ -5210,28 +5083,26 @@
       <c r="D16" s="24" t="n"/>
       <c r="E16" s="25" t="n"/>
       <c r="F16" s="26" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="25" t="n"/>
+      <c r="G16" s="26" t="n"/>
+      <c r="H16" s="26" t="n"/>
+      <c r="I16" s="26" t="n"/>
+      <c r="J16" s="26" t="n"/>
+      <c r="K16" s="26" t="n"/>
+      <c r="L16" s="26" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="10" t="n"/>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="n"/>
@@ -5240,28 +5111,26 @@
       <c r="D18" s="24" t="n"/>
       <c r="E18" s="25" t="n"/>
       <c r="F18" s="26" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="25" t="n"/>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="25" t="n"/>
-      <c r="M18" s="25" t="n"/>
+      <c r="G18" s="26" t="n"/>
+      <c r="H18" s="26" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="26" t="n"/>
+      <c r="K18" s="26" t="n"/>
+      <c r="L18" s="26" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="10" t="n"/>
       <c r="K19" s="10" t="n"/>
       <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n"/>
@@ -5270,28 +5139,26 @@
       <c r="D20" s="24" t="n"/>
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="26" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="25" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="25" t="n"/>
-      <c r="L20" s="25" t="n"/>
-      <c r="M20" s="25" t="n"/>
+      <c r="G20" s="26" t="n"/>
+      <c r="H20" s="26" t="n"/>
+      <c r="I20" s="26" t="n"/>
+      <c r="J20" s="26" t="n"/>
+      <c r="K20" s="26" t="n"/>
+      <c r="L20" s="26" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n"/>
@@ -5300,28 +5167,26 @@
       <c r="D22" s="24" t="n"/>
       <c r="E22" s="25" t="n"/>
       <c r="F22" s="26" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="25" t="n"/>
-      <c r="M22" s="25" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="26" t="n"/>
+      <c r="I22" s="26" t="n"/>
+      <c r="J22" s="26" t="n"/>
+      <c r="K22" s="26" t="n"/>
+      <c r="L22" s="26" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="10" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
-      <c r="M23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="n"/>
@@ -5330,28 +5195,26 @@
       <c r="D24" s="24" t="n"/>
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="26" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
-      <c r="L24" s="25" t="n"/>
-      <c r="M24" s="25" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="26" t="n"/>
+      <c r="K24" s="26" t="n"/>
+      <c r="L24" s="26" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="10" t="n"/>
-      <c r="M25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="n"/>
@@ -5360,28 +5223,26 @@
       <c r="D26" s="24" t="n"/>
       <c r="E26" s="25" t="n"/>
       <c r="F26" s="26" t="n"/>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="25" t="n"/>
-      <c r="L26" s="25" t="n"/>
-      <c r="M26" s="25" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="26" t="n"/>
+      <c r="J26" s="26" t="n"/>
+      <c r="K26" s="26" t="n"/>
+      <c r="L26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23" t="n"/>
@@ -5390,28 +5251,26 @@
       <c r="D28" s="24" t="n"/>
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="26" t="n"/>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="25" t="n"/>
-      <c r="L28" s="25" t="n"/>
-      <c r="M28" s="25" t="n"/>
+      <c r="G28" s="26" t="n"/>
+      <c r="H28" s="26" t="n"/>
+      <c r="I28" s="26" t="n"/>
+      <c r="J28" s="26" t="n"/>
+      <c r="K28" s="26" t="n"/>
+      <c r="L28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
       <c r="D29" s="9" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="10" t="n"/>
       <c r="K29" s="10" t="n"/>
       <c r="L29" s="10" t="n"/>
-      <c r="M29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="23" t="n"/>
@@ -5420,28 +5279,26 @@
       <c r="D30" s="24" t="n"/>
       <c r="E30" s="25" t="n"/>
       <c r="F30" s="26" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="25" t="n"/>
-      <c r="M30" s="25" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="26" t="n"/>
+      <c r="J30" s="26" t="n"/>
+      <c r="K30" s="26" t="n"/>
+      <c r="L30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
       <c r="D31" s="9" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="10" t="n"/>
       <c r="K31" s="10" t="n"/>
       <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="23" t="n"/>
@@ -5450,28 +5307,26 @@
       <c r="D32" s="24" t="n"/>
       <c r="E32" s="25" t="n"/>
       <c r="F32" s="26" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="25" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="25" t="n"/>
-      <c r="L32" s="25" t="n"/>
-      <c r="M32" s="25" t="n"/>
+      <c r="G32" s="26" t="n"/>
+      <c r="H32" s="26" t="n"/>
+      <c r="I32" s="26" t="n"/>
+      <c r="J32" s="26" t="n"/>
+      <c r="K32" s="26" t="n"/>
+      <c r="L32" s="26" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
       <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="23" t="n"/>
@@ -5480,28 +5335,26 @@
       <c r="D34" s="24" t="n"/>
       <c r="E34" s="25" t="n"/>
       <c r="F34" s="26" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="25" t="n"/>
-      <c r="M34" s="25" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="26" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="26" t="n"/>
+      <c r="L34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
       <c r="D35" s="9" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="10" t="n"/>
-      <c r="M35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="23" t="n"/>
@@ -5510,28 +5363,26 @@
       <c r="D36" s="24" t="n"/>
       <c r="E36" s="25" t="n"/>
       <c r="F36" s="26" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="25" t="n"/>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="25" t="n"/>
-      <c r="L36" s="25" t="n"/>
-      <c r="M36" s="25" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="26" t="n"/>
+      <c r="K36" s="26" t="n"/>
+      <c r="L36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="23" t="n"/>
@@ -5540,28 +5391,26 @@
       <c r="D38" s="24" t="n"/>
       <c r="E38" s="25" t="n"/>
       <c r="F38" s="26" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="25" t="n"/>
-      <c r="I38" s="25" t="n"/>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="25" t="n"/>
-      <c r="M38" s="25" t="n"/>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="26" t="n"/>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="26" t="n"/>
+      <c r="K38" s="26" t="n"/>
+      <c r="L38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
       <c r="D39" s="9" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
       <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="23" t="n"/>
@@ -5570,28 +5419,26 @@
       <c r="D40" s="24" t="n"/>
       <c r="E40" s="25" t="n"/>
       <c r="F40" s="26" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="25" t="n"/>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="25" t="n"/>
-      <c r="L40" s="25" t="n"/>
-      <c r="M40" s="25" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="26" t="n"/>
+      <c r="L40" s="26" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
       <c r="D41" s="9" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
       <c r="J41" s="10" t="n"/>
       <c r="K41" s="10" t="n"/>
       <c r="L41" s="10" t="n"/>
-      <c r="M41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="23" t="n"/>
@@ -5600,28 +5447,26 @@
       <c r="D42" s="24" t="n"/>
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="26" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="25" t="n"/>
-      <c r="I42" s="25" t="n"/>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="25" t="n"/>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="25" t="n"/>
+      <c r="G42" s="26" t="n"/>
+      <c r="H42" s="26" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="26" t="n"/>
+      <c r="K42" s="26" t="n"/>
+      <c r="L42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="10" t="n"/>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="23" t="n"/>
@@ -5630,28 +5475,26 @@
       <c r="D44" s="24" t="n"/>
       <c r="E44" s="25" t="n"/>
       <c r="F44" s="26" t="n"/>
-      <c r="G44" s="25" t="n"/>
-      <c r="H44" s="25" t="n"/>
-      <c r="I44" s="25" t="n"/>
-      <c r="J44" s="25" t="n"/>
-      <c r="K44" s="25" t="n"/>
-      <c r="L44" s="25" t="n"/>
-      <c r="M44" s="25" t="n"/>
+      <c r="G44" s="26" t="n"/>
+      <c r="H44" s="26" t="n"/>
+      <c r="I44" s="26" t="n"/>
+      <c r="J44" s="26" t="n"/>
+      <c r="K44" s="26" t="n"/>
+      <c r="L44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="n"/>
       <c r="D45" s="9" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="23" t="n"/>
@@ -5660,28 +5503,26 @@
       <c r="D46" s="24" t="n"/>
       <c r="E46" s="25" t="n"/>
       <c r="F46" s="26" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
-      <c r="I46" s="25" t="n"/>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="25" t="n"/>
-      <c r="L46" s="25" t="n"/>
-      <c r="M46" s="25" t="n"/>
+      <c r="G46" s="26" t="n"/>
+      <c r="H46" s="26" t="n"/>
+      <c r="I46" s="26" t="n"/>
+      <c r="J46" s="26" t="n"/>
+      <c r="K46" s="26" t="n"/>
+      <c r="L46" s="26" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="10" t="n"/>
       <c r="K47" s="10" t="n"/>
       <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="23" t="n"/>
@@ -5690,28 +5531,26 @@
       <c r="D48" s="24" t="n"/>
       <c r="E48" s="25" t="n"/>
       <c r="F48" s="26" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="25" t="n"/>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="25" t="n"/>
-      <c r="L48" s="25" t="n"/>
-      <c r="M48" s="25" t="n"/>
+      <c r="G48" s="26" t="n"/>
+      <c r="H48" s="26" t="n"/>
+      <c r="I48" s="26" t="n"/>
+      <c r="J48" s="26" t="n"/>
+      <c r="K48" s="26" t="n"/>
+      <c r="L48" s="26" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
       <c r="D49" s="9" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
       <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="n"/>
       <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="23" t="n"/>
@@ -5720,28 +5559,26 @@
       <c r="D50" s="24" t="n"/>
       <c r="E50" s="25" t="n"/>
       <c r="F50" s="26" t="n"/>
-      <c r="G50" s="25" t="n"/>
-      <c r="H50" s="25" t="n"/>
-      <c r="I50" s="25" t="n"/>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="25" t="n"/>
-      <c r="L50" s="25" t="n"/>
-      <c r="M50" s="25" t="n"/>
+      <c r="G50" s="26" t="n"/>
+      <c r="H50" s="26" t="n"/>
+      <c r="I50" s="26" t="n"/>
+      <c r="J50" s="26" t="n"/>
+      <c r="K50" s="26" t="n"/>
+      <c r="L50" s="26" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="n"/>
       <c r="D51" s="9" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
       <c r="I51" s="10" t="n"/>
       <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="n"/>
       <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="23" t="n"/>
@@ -5750,28 +5587,26 @@
       <c r="D52" s="24" t="n"/>
       <c r="E52" s="25" t="n"/>
       <c r="F52" s="26" t="n"/>
-      <c r="G52" s="25" t="n"/>
-      <c r="H52" s="25" t="n"/>
-      <c r="I52" s="25" t="n"/>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="25" t="n"/>
-      <c r="L52" s="25" t="n"/>
-      <c r="M52" s="25" t="n"/>
+      <c r="G52" s="26" t="n"/>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="26" t="n"/>
+      <c r="J52" s="26" t="n"/>
+      <c r="K52" s="26" t="n"/>
+      <c r="L52" s="26" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
       <c r="D53" s="9" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="23" t="n"/>
@@ -5780,28 +5615,26 @@
       <c r="D54" s="24" t="n"/>
       <c r="E54" s="25" t="n"/>
       <c r="F54" s="26" t="n"/>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="25" t="n"/>
-      <c r="L54" s="25" t="n"/>
-      <c r="M54" s="25" t="n"/>
+      <c r="G54" s="26" t="n"/>
+      <c r="H54" s="26" t="n"/>
+      <c r="I54" s="26" t="n"/>
+      <c r="J54" s="26" t="n"/>
+      <c r="K54" s="26" t="n"/>
+      <c r="L54" s="26" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
       <c r="D55" s="9" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="11" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
       <c r="I55" s="10" t="n"/>
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="23" t="n"/>
@@ -5810,28 +5643,26 @@
       <c r="D56" s="24" t="n"/>
       <c r="E56" s="25" t="n"/>
       <c r="F56" s="26" t="n"/>
-      <c r="G56" s="25" t="n"/>
-      <c r="H56" s="25" t="n"/>
-      <c r="I56" s="25" t="n"/>
-      <c r="J56" s="25" t="n"/>
-      <c r="K56" s="25" t="n"/>
-      <c r="L56" s="25" t="n"/>
-      <c r="M56" s="25" t="n"/>
+      <c r="G56" s="26" t="n"/>
+      <c r="H56" s="26" t="n"/>
+      <c r="I56" s="26" t="n"/>
+      <c r="J56" s="26" t="n"/>
+      <c r="K56" s="26" t="n"/>
+      <c r="L56" s="26" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="9" t="n"/>
       <c r="D57" s="9" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
       <c r="I57" s="10" t="n"/>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
       <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="23" t="n"/>
@@ -5840,28 +5671,26 @@
       <c r="D58" s="24" t="n"/>
       <c r="E58" s="25" t="n"/>
       <c r="F58" s="26" t="n"/>
-      <c r="G58" s="25" t="n"/>
-      <c r="H58" s="25" t="n"/>
-      <c r="I58" s="25" t="n"/>
-      <c r="J58" s="25" t="n"/>
-      <c r="K58" s="25" t="n"/>
-      <c r="L58" s="25" t="n"/>
-      <c r="M58" s="25" t="n"/>
+      <c r="G58" s="26" t="n"/>
+      <c r="H58" s="26" t="n"/>
+      <c r="I58" s="26" t="n"/>
+      <c r="J58" s="26" t="n"/>
+      <c r="K58" s="26" t="n"/>
+      <c r="L58" s="26" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="9" t="n"/>
       <c r="D59" s="9" t="n"/>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
       <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
       <c r="L59" s="10" t="n"/>
-      <c r="M59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="23" t="n"/>
@@ -5870,28 +5699,26 @@
       <c r="D60" s="24" t="n"/>
       <c r="E60" s="25" t="n"/>
       <c r="F60" s="26" t="n"/>
-      <c r="G60" s="25" t="n"/>
-      <c r="H60" s="25" t="n"/>
-      <c r="I60" s="25" t="n"/>
-      <c r="J60" s="25" t="n"/>
-      <c r="K60" s="25" t="n"/>
-      <c r="L60" s="25" t="n"/>
-      <c r="M60" s="25" t="n"/>
+      <c r="G60" s="26" t="n"/>
+      <c r="H60" s="26" t="n"/>
+      <c r="I60" s="26" t="n"/>
+      <c r="J60" s="26" t="n"/>
+      <c r="K60" s="26" t="n"/>
+      <c r="L60" s="26" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
       <c r="D61" s="9" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
       <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="23" t="n"/>
@@ -5900,28 +5727,26 @@
       <c r="D62" s="24" t="n"/>
       <c r="E62" s="25" t="n"/>
       <c r="F62" s="26" t="n"/>
-      <c r="G62" s="25" t="n"/>
-      <c r="H62" s="25" t="n"/>
-      <c r="I62" s="25" t="n"/>
-      <c r="J62" s="25" t="n"/>
-      <c r="K62" s="25" t="n"/>
-      <c r="L62" s="25" t="n"/>
-      <c r="M62" s="25" t="n"/>
+      <c r="G62" s="26" t="n"/>
+      <c r="H62" s="26" t="n"/>
+      <c r="I62" s="26" t="n"/>
+      <c r="J62" s="26" t="n"/>
+      <c r="K62" s="26" t="n"/>
+      <c r="L62" s="26" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="9" t="n"/>
       <c r="D63" s="9" t="n"/>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
       <c r="L63" s="10" t="n"/>
-      <c r="M63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="23" t="n"/>
@@ -5930,28 +5755,26 @@
       <c r="D64" s="24" t="n"/>
       <c r="E64" s="25" t="n"/>
       <c r="F64" s="26" t="n"/>
-      <c r="G64" s="25" t="n"/>
-      <c r="H64" s="25" t="n"/>
-      <c r="I64" s="25" t="n"/>
-      <c r="J64" s="25" t="n"/>
-      <c r="K64" s="25" t="n"/>
-      <c r="L64" s="25" t="n"/>
-      <c r="M64" s="25" t="n"/>
+      <c r="G64" s="26" t="n"/>
+      <c r="H64" s="26" t="n"/>
+      <c r="I64" s="26" t="n"/>
+      <c r="J64" s="26" t="n"/>
+      <c r="K64" s="26" t="n"/>
+      <c r="L64" s="26" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
       <c r="I65" s="10" t="n"/>
       <c r="J65" s="10" t="n"/>
       <c r="K65" s="10" t="n"/>
       <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="23" t="n"/>
@@ -5960,28 +5783,26 @@
       <c r="D66" s="24" t="n"/>
       <c r="E66" s="25" t="n"/>
       <c r="F66" s="26" t="n"/>
-      <c r="G66" s="25" t="n"/>
-      <c r="H66" s="25" t="n"/>
-      <c r="I66" s="25" t="n"/>
-      <c r="J66" s="25" t="n"/>
-      <c r="K66" s="25" t="n"/>
-      <c r="L66" s="25" t="n"/>
-      <c r="M66" s="25" t="n"/>
+      <c r="G66" s="26" t="n"/>
+      <c r="H66" s="26" t="n"/>
+      <c r="I66" s="26" t="n"/>
+      <c r="J66" s="26" t="n"/>
+      <c r="K66" s="26" t="n"/>
+      <c r="L66" s="26" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="9" t="n"/>
       <c r="D67" s="9" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
       <c r="I67" s="10" t="n"/>
       <c r="J67" s="10" t="n"/>
       <c r="K67" s="10" t="n"/>
       <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="23" t="n"/>
@@ -5990,28 +5811,26 @@
       <c r="D68" s="24" t="n"/>
       <c r="E68" s="25" t="n"/>
       <c r="F68" s="26" t="n"/>
-      <c r="G68" s="25" t="n"/>
-      <c r="H68" s="25" t="n"/>
-      <c r="I68" s="25" t="n"/>
-      <c r="J68" s="25" t="n"/>
-      <c r="K68" s="25" t="n"/>
-      <c r="L68" s="25" t="n"/>
-      <c r="M68" s="25" t="n"/>
+      <c r="G68" s="26" t="n"/>
+      <c r="H68" s="26" t="n"/>
+      <c r="I68" s="26" t="n"/>
+      <c r="J68" s="26" t="n"/>
+      <c r="K68" s="26" t="n"/>
+      <c r="L68" s="26" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="9" t="n"/>
       <c r="D69" s="9" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
       <c r="I69" s="10" t="n"/>
       <c r="J69" s="10" t="n"/>
       <c r="K69" s="10" t="n"/>
       <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="23" t="n"/>
@@ -6020,28 +5839,26 @@
       <c r="D70" s="24" t="n"/>
       <c r="E70" s="25" t="n"/>
       <c r="F70" s="26" t="n"/>
-      <c r="G70" s="25" t="n"/>
-      <c r="H70" s="25" t="n"/>
-      <c r="I70" s="25" t="n"/>
-      <c r="J70" s="25" t="n"/>
-      <c r="K70" s="25" t="n"/>
-      <c r="L70" s="25" t="n"/>
-      <c r="M70" s="25" t="n"/>
+      <c r="G70" s="26" t="n"/>
+      <c r="H70" s="26" t="n"/>
+      <c r="I70" s="26" t="n"/>
+      <c r="J70" s="26" t="n"/>
+      <c r="K70" s="26" t="n"/>
+      <c r="L70" s="26" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="9" t="n"/>
       <c r="D71" s="9" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="11" t="n"/>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="10" t="n"/>
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="23" t="n"/>
@@ -6050,28 +5867,26 @@
       <c r="D72" s="24" t="n"/>
       <c r="E72" s="25" t="n"/>
       <c r="F72" s="26" t="n"/>
-      <c r="G72" s="25" t="n"/>
-      <c r="H72" s="25" t="n"/>
-      <c r="I72" s="25" t="n"/>
-      <c r="J72" s="25" t="n"/>
-      <c r="K72" s="25" t="n"/>
-      <c r="L72" s="25" t="n"/>
-      <c r="M72" s="25" t="n"/>
+      <c r="G72" s="26" t="n"/>
+      <c r="H72" s="26" t="n"/>
+      <c r="I72" s="26" t="n"/>
+      <c r="J72" s="26" t="n"/>
+      <c r="K72" s="26" t="n"/>
+      <c r="L72" s="26" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
       <c r="D73" s="9" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="11" t="n"/>
+      <c r="E73" s="11" t="n"/>
+      <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
       <c r="J73" s="10" t="n"/>
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="23" t="n"/>
@@ -6080,28 +5895,26 @@
       <c r="D74" s="24" t="n"/>
       <c r="E74" s="25" t="n"/>
       <c r="F74" s="26" t="n"/>
-      <c r="G74" s="25" t="n"/>
-      <c r="H74" s="25" t="n"/>
-      <c r="I74" s="25" t="n"/>
-      <c r="J74" s="25" t="n"/>
-      <c r="K74" s="25" t="n"/>
-      <c r="L74" s="25" t="n"/>
-      <c r="M74" s="25" t="n"/>
+      <c r="G74" s="26" t="n"/>
+      <c r="H74" s="26" t="n"/>
+      <c r="I74" s="26" t="n"/>
+      <c r="J74" s="26" t="n"/>
+      <c r="K74" s="26" t="n"/>
+      <c r="L74" s="26" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="9" t="n"/>
       <c r="D75" s="9" t="n"/>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="11" t="n"/>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
       <c r="J75" s="10" t="n"/>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
-      <c r="M75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="23" t="n"/>
@@ -6110,28 +5923,26 @@
       <c r="D76" s="24" t="n"/>
       <c r="E76" s="25" t="n"/>
       <c r="F76" s="26" t="n"/>
-      <c r="G76" s="25" t="n"/>
-      <c r="H76" s="25" t="n"/>
-      <c r="I76" s="25" t="n"/>
-      <c r="J76" s="25" t="n"/>
-      <c r="K76" s="25" t="n"/>
-      <c r="L76" s="25" t="n"/>
-      <c r="M76" s="25" t="n"/>
+      <c r="G76" s="26" t="n"/>
+      <c r="H76" s="26" t="n"/>
+      <c r="I76" s="26" t="n"/>
+      <c r="J76" s="26" t="n"/>
+      <c r="K76" s="26" t="n"/>
+      <c r="L76" s="26" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
       <c r="D77" s="9" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
       <c r="I77" s="10" t="n"/>
       <c r="J77" s="10" t="n"/>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="23" t="n"/>
@@ -6140,28 +5951,26 @@
       <c r="D78" s="24" t="n"/>
       <c r="E78" s="25" t="n"/>
       <c r="F78" s="26" t="n"/>
-      <c r="G78" s="25" t="n"/>
-      <c r="H78" s="25" t="n"/>
-      <c r="I78" s="25" t="n"/>
-      <c r="J78" s="25" t="n"/>
-      <c r="K78" s="25" t="n"/>
-      <c r="L78" s="25" t="n"/>
-      <c r="M78" s="25" t="n"/>
+      <c r="G78" s="26" t="n"/>
+      <c r="H78" s="26" t="n"/>
+      <c r="I78" s="26" t="n"/>
+      <c r="J78" s="26" t="n"/>
+      <c r="K78" s="26" t="n"/>
+      <c r="L78" s="26" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="9" t="n"/>
       <c r="D79" s="9" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="11" t="n"/>
+      <c r="E79" s="11" t="n"/>
+      <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
       <c r="J79" s="10" t="n"/>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="23" t="n"/>
@@ -6170,28 +5979,26 @@
       <c r="D80" s="24" t="n"/>
       <c r="E80" s="25" t="n"/>
       <c r="F80" s="26" t="n"/>
-      <c r="G80" s="25" t="n"/>
-      <c r="H80" s="25" t="n"/>
-      <c r="I80" s="25" t="n"/>
-      <c r="J80" s="25" t="n"/>
-      <c r="K80" s="25" t="n"/>
-      <c r="L80" s="25" t="n"/>
-      <c r="M80" s="25" t="n"/>
+      <c r="G80" s="26" t="n"/>
+      <c r="H80" s="26" t="n"/>
+      <c r="I80" s="26" t="n"/>
+      <c r="J80" s="26" t="n"/>
+      <c r="K80" s="26" t="n"/>
+      <c r="L80" s="26" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="9" t="n"/>
       <c r="D81" s="9" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="11" t="n"/>
+      <c r="E81" s="11" t="n"/>
+      <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
       <c r="I81" s="10" t="n"/>
       <c r="J81" s="10" t="n"/>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="23" t="n"/>
@@ -6200,28 +6007,26 @@
       <c r="D82" s="24" t="n"/>
       <c r="E82" s="25" t="n"/>
       <c r="F82" s="26" t="n"/>
-      <c r="G82" s="25" t="n"/>
-      <c r="H82" s="25" t="n"/>
-      <c r="I82" s="25" t="n"/>
-      <c r="J82" s="25" t="n"/>
-      <c r="K82" s="25" t="n"/>
-      <c r="L82" s="25" t="n"/>
-      <c r="M82" s="25" t="n"/>
+      <c r="G82" s="26" t="n"/>
+      <c r="H82" s="26" t="n"/>
+      <c r="I82" s="26" t="n"/>
+      <c r="J82" s="26" t="n"/>
+      <c r="K82" s="26" t="n"/>
+      <c r="L82" s="26" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="9" t="n"/>
       <c r="D83" s="9" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="11" t="n"/>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
       <c r="I83" s="10" t="n"/>
       <c r="J83" s="10" t="n"/>
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="23" t="n"/>
@@ -6230,28 +6035,26 @@
       <c r="D84" s="24" t="n"/>
       <c r="E84" s="25" t="n"/>
       <c r="F84" s="26" t="n"/>
-      <c r="G84" s="25" t="n"/>
-      <c r="H84" s="25" t="n"/>
-      <c r="I84" s="25" t="n"/>
-      <c r="J84" s="25" t="n"/>
-      <c r="K84" s="25" t="n"/>
-      <c r="L84" s="25" t="n"/>
-      <c r="M84" s="25" t="n"/>
+      <c r="G84" s="26" t="n"/>
+      <c r="H84" s="26" t="n"/>
+      <c r="I84" s="26" t="n"/>
+      <c r="J84" s="26" t="n"/>
+      <c r="K84" s="26" t="n"/>
+      <c r="L84" s="26" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="9" t="n"/>
       <c r="D85" s="9" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="11" t="n"/>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
       <c r="I85" s="10" t="n"/>
       <c r="J85" s="10" t="n"/>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="23" t="n"/>
@@ -6260,28 +6063,26 @@
       <c r="D86" s="24" t="n"/>
       <c r="E86" s="25" t="n"/>
       <c r="F86" s="26" t="n"/>
-      <c r="G86" s="25" t="n"/>
-      <c r="H86" s="25" t="n"/>
-      <c r="I86" s="25" t="n"/>
-      <c r="J86" s="25" t="n"/>
-      <c r="K86" s="25" t="n"/>
-      <c r="L86" s="25" t="n"/>
-      <c r="M86" s="25" t="n"/>
+      <c r="G86" s="26" t="n"/>
+      <c r="H86" s="26" t="n"/>
+      <c r="I86" s="26" t="n"/>
+      <c r="J86" s="26" t="n"/>
+      <c r="K86" s="26" t="n"/>
+      <c r="L86" s="26" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
       <c r="D87" s="9" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="11" t="n"/>
+      <c r="E87" s="11" t="n"/>
+      <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
       <c r="I87" s="10" t="n"/>
       <c r="J87" s="10" t="n"/>
       <c r="K87" s="10" t="n"/>
       <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="23" t="n"/>
@@ -6290,28 +6091,26 @@
       <c r="D88" s="24" t="n"/>
       <c r="E88" s="25" t="n"/>
       <c r="F88" s="26" t="n"/>
-      <c r="G88" s="25" t="n"/>
-      <c r="H88" s="25" t="n"/>
-      <c r="I88" s="25" t="n"/>
-      <c r="J88" s="25" t="n"/>
-      <c r="K88" s="25" t="n"/>
-      <c r="L88" s="25" t="n"/>
-      <c r="M88" s="25" t="n"/>
+      <c r="G88" s="26" t="n"/>
+      <c r="H88" s="26" t="n"/>
+      <c r="I88" s="26" t="n"/>
+      <c r="J88" s="26" t="n"/>
+      <c r="K88" s="26" t="n"/>
+      <c r="L88" s="26" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="9" t="n"/>
       <c r="D89" s="9" t="n"/>
-      <c r="E89" s="10" t="n"/>
-      <c r="F89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
       <c r="I89" s="10" t="n"/>
       <c r="J89" s="10" t="n"/>
       <c r="K89" s="10" t="n"/>
       <c r="L89" s="10" t="n"/>
-      <c r="M89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="23" t="n"/>
@@ -6320,28 +6119,26 @@
       <c r="D90" s="24" t="n"/>
       <c r="E90" s="25" t="n"/>
       <c r="F90" s="26" t="n"/>
-      <c r="G90" s="25" t="n"/>
-      <c r="H90" s="25" t="n"/>
-      <c r="I90" s="25" t="n"/>
-      <c r="J90" s="25" t="n"/>
-      <c r="K90" s="25" t="n"/>
-      <c r="L90" s="25" t="n"/>
-      <c r="M90" s="25" t="n"/>
+      <c r="G90" s="26" t="n"/>
+      <c r="H90" s="26" t="n"/>
+      <c r="I90" s="26" t="n"/>
+      <c r="J90" s="26" t="n"/>
+      <c r="K90" s="26" t="n"/>
+      <c r="L90" s="26" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="9" t="n"/>
       <c r="D91" s="9" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="11" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
       <c r="I91" s="10" t="n"/>
       <c r="J91" s="10" t="n"/>
       <c r="K91" s="10" t="n"/>
       <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="23" t="n"/>
@@ -6350,28 +6147,26 @@
       <c r="D92" s="24" t="n"/>
       <c r="E92" s="25" t="n"/>
       <c r="F92" s="26" t="n"/>
-      <c r="G92" s="25" t="n"/>
-      <c r="H92" s="25" t="n"/>
-      <c r="I92" s="25" t="n"/>
-      <c r="J92" s="25" t="n"/>
-      <c r="K92" s="25" t="n"/>
-      <c r="L92" s="25" t="n"/>
-      <c r="M92" s="25" t="n"/>
+      <c r="G92" s="26" t="n"/>
+      <c r="H92" s="26" t="n"/>
+      <c r="I92" s="26" t="n"/>
+      <c r="J92" s="26" t="n"/>
+      <c r="K92" s="26" t="n"/>
+      <c r="L92" s="26" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
       <c r="D93" s="9" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="11" t="n"/>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
       <c r="I93" s="10" t="n"/>
       <c r="J93" s="10" t="n"/>
       <c r="K93" s="10" t="n"/>
       <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="23" t="n"/>
@@ -6380,28 +6175,26 @@
       <c r="D94" s="24" t="n"/>
       <c r="E94" s="25" t="n"/>
       <c r="F94" s="26" t="n"/>
-      <c r="G94" s="25" t="n"/>
-      <c r="H94" s="25" t="n"/>
-      <c r="I94" s="25" t="n"/>
-      <c r="J94" s="25" t="n"/>
-      <c r="K94" s="25" t="n"/>
-      <c r="L94" s="25" t="n"/>
-      <c r="M94" s="25" t="n"/>
+      <c r="G94" s="26" t="n"/>
+      <c r="H94" s="26" t="n"/>
+      <c r="I94" s="26" t="n"/>
+      <c r="J94" s="26" t="n"/>
+      <c r="K94" s="26" t="n"/>
+      <c r="L94" s="26" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
       <c r="D95" s="9" t="n"/>
-      <c r="E95" s="10" t="n"/>
-      <c r="F95" s="11" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
       <c r="I95" s="10" t="n"/>
       <c r="J95" s="10" t="n"/>
       <c r="K95" s="10" t="n"/>
       <c r="L95" s="10" t="n"/>
-      <c r="M95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="23" t="n"/>
@@ -6410,28 +6203,26 @@
       <c r="D96" s="24" t="n"/>
       <c r="E96" s="25" t="n"/>
       <c r="F96" s="26" t="n"/>
-      <c r="G96" s="25" t="n"/>
-      <c r="H96" s="25" t="n"/>
-      <c r="I96" s="25" t="n"/>
-      <c r="J96" s="25" t="n"/>
-      <c r="K96" s="25" t="n"/>
-      <c r="L96" s="25" t="n"/>
-      <c r="M96" s="25" t="n"/>
+      <c r="G96" s="26" t="n"/>
+      <c r="H96" s="26" t="n"/>
+      <c r="I96" s="26" t="n"/>
+      <c r="J96" s="26" t="n"/>
+      <c r="K96" s="26" t="n"/>
+      <c r="L96" s="26" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
       <c r="D97" s="9" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="11" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
       <c r="J97" s="10" t="n"/>
       <c r="K97" s="10" t="n"/>
       <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="23" t="n"/>
@@ -6440,28 +6231,26 @@
       <c r="D98" s="24" t="n"/>
       <c r="E98" s="25" t="n"/>
       <c r="F98" s="26" t="n"/>
-      <c r="G98" s="25" t="n"/>
-      <c r="H98" s="25" t="n"/>
-      <c r="I98" s="25" t="n"/>
-      <c r="J98" s="25" t="n"/>
-      <c r="K98" s="25" t="n"/>
-      <c r="L98" s="25" t="n"/>
-      <c r="M98" s="25" t="n"/>
+      <c r="G98" s="26" t="n"/>
+      <c r="H98" s="26" t="n"/>
+      <c r="I98" s="26" t="n"/>
+      <c r="J98" s="26" t="n"/>
+      <c r="K98" s="26" t="n"/>
+      <c r="L98" s="26" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
       <c r="D99" s="9" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="11" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
       <c r="J99" s="10" t="n"/>
       <c r="K99" s="10" t="n"/>
       <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="23" t="n"/>
@@ -6470,28 +6259,26 @@
       <c r="D100" s="24" t="n"/>
       <c r="E100" s="25" t="n"/>
       <c r="F100" s="26" t="n"/>
-      <c r="G100" s="25" t="n"/>
-      <c r="H100" s="25" t="n"/>
-      <c r="I100" s="25" t="n"/>
-      <c r="J100" s="25" t="n"/>
-      <c r="K100" s="25" t="n"/>
-      <c r="L100" s="25" t="n"/>
-      <c r="M100" s="25" t="n"/>
+      <c r="G100" s="26" t="n"/>
+      <c r="H100" s="26" t="n"/>
+      <c r="I100" s="26" t="n"/>
+      <c r="J100" s="26" t="n"/>
+      <c r="K100" s="26" t="n"/>
+      <c r="L100" s="26" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
       <c r="D101" s="9" t="n"/>
-      <c r="E101" s="10" t="n"/>
-      <c r="F101" s="11" t="n"/>
+      <c r="E101" s="11" t="n"/>
+      <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
       <c r="I101" s="10" t="n"/>
       <c r="J101" s="10" t="n"/>
       <c r="K101" s="10" t="n"/>
       <c r="L101" s="10" t="n"/>
-      <c r="M101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="23" t="n"/>
@@ -6500,22 +6287,21 @@
       <c r="D102" s="24" t="n"/>
       <c r="E102" s="25" t="n"/>
       <c r="F102" s="26" t="n"/>
-      <c r="G102" s="25" t="n"/>
-      <c r="H102" s="25" t="n"/>
-      <c r="I102" s="25" t="n"/>
-      <c r="J102" s="25" t="n"/>
-      <c r="K102" s="25" t="n"/>
-      <c r="L102" s="25" t="n"/>
-      <c r="M102" s="25" t="n"/>
+      <c r="G102" s="26" t="n"/>
+      <c r="H102" s="26" t="n"/>
+      <c r="I102" s="26" t="n"/>
+      <c r="J102" s="26" t="n"/>
+      <c r="K102" s="26" t="n"/>
+      <c r="L102" s="26" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M2"/>
+  <autoFilter ref="A2:L2"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="D1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="L3:L102">
+  <conditionalFormatting sqref="K3:K102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="9">
       <formula>"要"</formula>
     </cfRule>
@@ -6526,7 +6312,7 @@
       <formula>"済"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E102">
+  <conditionalFormatting sqref="D3:D102">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="9">
       <formula>"緊急"</formula>
     </cfRule>
@@ -6535,19 +6321,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="C3:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>sex</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>urgency</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="F3:F102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>dept</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>disease</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>followup</formula1>
     </dataValidation>
   </dataValidations>
@@ -6571,27 +6357,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6602,33 +6387,32 @@
       </c>
       <c r="B1" s="28" t="n"/>
       <c r="C1" s="28" t="n"/>
-      <c r="D1" s="28" t="n"/>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>受診情報</t>
         </is>
       </c>
+      <c r="E1" s="30" t="n"/>
       <c r="F1" s="30" t="n"/>
-      <c r="G1" s="30" t="n"/>
-      <c r="H1" s="31" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>臨床情報</t>
         </is>
       </c>
+      <c r="H1" s="32" t="n"/>
       <c r="I1" s="32" t="n"/>
       <c r="J1" s="32" t="n"/>
       <c r="K1" s="32" t="n"/>
       <c r="L1" s="32" t="n"/>
-      <c r="M1" s="32" t="n"/>
-      <c r="N1" s="31" t="inlineStr">
+      <c r="M1" s="31" t="inlineStr">
         <is>
           <t>治療</t>
         </is>
       </c>
+      <c r="N1" s="32" t="n"/>
       <c r="O1" s="32" t="n"/>
       <c r="P1" s="32" t="n"/>
-      <c r="Q1" s="32" t="n"/>
-      <c r="R1" s="31" t="inlineStr">
+      <c r="Q1" s="31" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
@@ -6642,85 +6426,80 @@
       </c>
       <c r="B2" s="33" t="inlineStr">
         <is>
-          <t>イニシャル</t>
+          <t>年齢</t>
         </is>
       </c>
       <c r="C2" s="33" t="inlineStr">
         <is>
-          <t>年齢</t>
+          <t>性別</t>
         </is>
       </c>
       <c r="D2" s="33" t="inlineStr">
         <is>
-          <t>性別</t>
+          <t>初診日</t>
         </is>
       </c>
       <c r="E2" s="33" t="inlineStr">
         <is>
-          <t>初診日</t>
+          <t>紹介元</t>
         </is>
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>紹介元</t>
+          <t>主訴</t>
         </is>
       </c>
       <c r="G2" s="33" t="inlineStr">
         <is>
-          <t>主訴</t>
+          <t>疾患</t>
         </is>
       </c>
       <c r="H2" s="33" t="inlineStr">
         <is>
-          <t>疾患</t>
+          <t>病期/Stage</t>
         </is>
       </c>
       <c r="I2" s="33" t="inlineStr">
         <is>
-          <t>病期/Stage</t>
+          <t>染色体</t>
         </is>
       </c>
       <c r="J2" s="33" t="inlineStr">
         <is>
-          <t>染色体</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="K2" s="33" t="inlineStr">
         <is>
-          <t>遺伝子</t>
+          <t>リスク分類</t>
         </is>
       </c>
       <c r="L2" s="33" t="inlineStr">
         <is>
-          <t>リスク分類</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="M2" s="33" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>治療区分</t>
         </is>
       </c>
       <c r="N2" s="33" t="inlineStr">
         <is>
-          <t>治療区分</t>
+          <t>治療レジメン</t>
         </is>
       </c>
       <c r="O2" s="33" t="inlineStr">
         <is>
-          <t>治療レジメン</t>
+          <t>転帰</t>
         </is>
       </c>
       <c r="P2" s="33" t="inlineStr">
         <is>
-          <t>転帰</t>
+          <t>次回予約日</t>
         </is>
       </c>
       <c r="Q2" s="33" t="inlineStr">
-        <is>
-          <t>次回予約日</t>
-        </is>
-      </c>
-      <c r="R2" s="33" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -6730,8 +6509,8 @@
       <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
@@ -6742,16 +6521,15 @@
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="10" t="n"/>
       <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="10" t="n"/>
+      <c r="P3" s="11" t="n"/>
+      <c r="Q3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="34" t="n"/>
       <c r="B4" s="35" t="n"/>
       <c r="C4" s="35" t="n"/>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="37" t="n"/>
       <c r="F4" s="37" t="n"/>
       <c r="G4" s="37" t="n"/>
       <c r="H4" s="37" t="n"/>
@@ -6762,16 +6540,15 @@
       <c r="M4" s="37" t="n"/>
       <c r="N4" s="37" t="n"/>
       <c r="O4" s="37" t="n"/>
-      <c r="P4" s="37" t="n"/>
-      <c r="Q4" s="36" t="n"/>
-      <c r="R4" s="37" t="n"/>
+      <c r="P4" s="36" t="n"/>
+      <c r="Q4" s="37" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
@@ -6782,16 +6559,15 @@
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
       <c r="O5" s="10" t="n"/>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="10" t="n"/>
+      <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="34" t="n"/>
       <c r="B6" s="35" t="n"/>
       <c r="C6" s="35" t="n"/>
-      <c r="D6" s="35" t="n"/>
-      <c r="E6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="37" t="n"/>
       <c r="F6" s="37" t="n"/>
       <c r="G6" s="37" t="n"/>
       <c r="H6" s="37" t="n"/>
@@ -6802,16 +6578,15 @@
       <c r="M6" s="37" t="n"/>
       <c r="N6" s="37" t="n"/>
       <c r="O6" s="37" t="n"/>
-      <c r="P6" s="37" t="n"/>
-      <c r="Q6" s="36" t="n"/>
-      <c r="R6" s="37" t="n"/>
+      <c r="P6" s="36" t="n"/>
+      <c r="Q6" s="37" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
@@ -6822,16 +6597,15 @@
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="10" t="n"/>
       <c r="O7" s="10" t="n"/>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="10" t="n"/>
+      <c r="P7" s="11" t="n"/>
+      <c r="Q7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="34" t="n"/>
       <c r="B8" s="35" t="n"/>
       <c r="C8" s="35" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="37" t="n"/>
       <c r="F8" s="37" t="n"/>
       <c r="G8" s="37" t="n"/>
       <c r="H8" s="37" t="n"/>
@@ -6842,16 +6616,15 @@
       <c r="M8" s="37" t="n"/>
       <c r="N8" s="37" t="n"/>
       <c r="O8" s="37" t="n"/>
-      <c r="P8" s="37" t="n"/>
-      <c r="Q8" s="36" t="n"/>
-      <c r="R8" s="37" t="n"/>
+      <c r="P8" s="36" t="n"/>
+      <c r="Q8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
@@ -6862,16 +6635,15 @@
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="10" t="n"/>
       <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10" t="n"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="10" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="34" t="n"/>
       <c r="B10" s="35" t="n"/>
       <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="37" t="n"/>
       <c r="F10" s="37" t="n"/>
       <c r="G10" s="37" t="n"/>
       <c r="H10" s="37" t="n"/>
@@ -6882,16 +6654,15 @@
       <c r="M10" s="37" t="n"/>
       <c r="N10" s="37" t="n"/>
       <c r="O10" s="37" t="n"/>
-      <c r="P10" s="37" t="n"/>
-      <c r="Q10" s="36" t="n"/>
-      <c r="R10" s="37" t="n"/>
+      <c r="P10" s="36" t="n"/>
+      <c r="Q10" s="37" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
@@ -6902,16 +6673,15 @@
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="10" t="n"/>
       <c r="O11" s="10" t="n"/>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="10" t="n"/>
+      <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n"/>
       <c r="B12" s="35" t="n"/>
       <c r="C12" s="35" t="n"/>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="37" t="n"/>
       <c r="F12" s="37" t="n"/>
       <c r="G12" s="37" t="n"/>
       <c r="H12" s="37" t="n"/>
@@ -6922,16 +6692,15 @@
       <c r="M12" s="37" t="n"/>
       <c r="N12" s="37" t="n"/>
       <c r="O12" s="37" t="n"/>
-      <c r="P12" s="37" t="n"/>
-      <c r="Q12" s="36" t="n"/>
-      <c r="R12" s="37" t="n"/>
+      <c r="P12" s="36" t="n"/>
+      <c r="Q12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
@@ -6942,16 +6711,15 @@
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="10" t="n"/>
       <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="10" t="n"/>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="n"/>
       <c r="B14" s="35" t="n"/>
       <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="37" t="n"/>
       <c r="F14" s="37" t="n"/>
       <c r="G14" s="37" t="n"/>
       <c r="H14" s="37" t="n"/>
@@ -6962,16 +6730,15 @@
       <c r="M14" s="37" t="n"/>
       <c r="N14" s="37" t="n"/>
       <c r="O14" s="37" t="n"/>
-      <c r="P14" s="37" t="n"/>
-      <c r="Q14" s="36" t="n"/>
-      <c r="R14" s="37" t="n"/>
+      <c r="P14" s="36" t="n"/>
+      <c r="Q14" s="37" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
@@ -6982,16 +6749,15 @@
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="10" t="n"/>
+      <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="34" t="n"/>
       <c r="B16" s="35" t="n"/>
       <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="37" t="n"/>
       <c r="F16" s="37" t="n"/>
       <c r="G16" s="37" t="n"/>
       <c r="H16" s="37" t="n"/>
@@ -7002,16 +6768,15 @@
       <c r="M16" s="37" t="n"/>
       <c r="N16" s="37" t="n"/>
       <c r="O16" s="37" t="n"/>
-      <c r="P16" s="37" t="n"/>
-      <c r="Q16" s="36" t="n"/>
-      <c r="R16" s="37" t="n"/>
+      <c r="P16" s="36" t="n"/>
+      <c r="Q16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
@@ -7022,16 +6787,15 @@
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="10" t="n"/>
       <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="10" t="n"/>
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="34" t="n"/>
       <c r="B18" s="35" t="n"/>
       <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="37" t="n"/>
       <c r="F18" s="37" t="n"/>
       <c r="G18" s="37" t="n"/>
       <c r="H18" s="37" t="n"/>
@@ -7042,16 +6806,15 @@
       <c r="M18" s="37" t="n"/>
       <c r="N18" s="37" t="n"/>
       <c r="O18" s="37" t="n"/>
-      <c r="P18" s="37" t="n"/>
-      <c r="Q18" s="36" t="n"/>
-      <c r="R18" s="37" t="n"/>
+      <c r="P18" s="36" t="n"/>
+      <c r="Q18" s="37" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
@@ -7062,16 +6825,15 @@
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="10" t="n"/>
       <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="10" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="34" t="n"/>
       <c r="B20" s="35" t="n"/>
       <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="36" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="37" t="n"/>
       <c r="F20" s="37" t="n"/>
       <c r="G20" s="37" t="n"/>
       <c r="H20" s="37" t="n"/>
@@ -7082,16 +6844,15 @@
       <c r="M20" s="37" t="n"/>
       <c r="N20" s="37" t="n"/>
       <c r="O20" s="37" t="n"/>
-      <c r="P20" s="37" t="n"/>
-      <c r="Q20" s="36" t="n"/>
-      <c r="R20" s="37" t="n"/>
+      <c r="P20" s="36" t="n"/>
+      <c r="Q20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
@@ -7102,16 +6863,15 @@
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="10" t="n"/>
       <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="10" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="34" t="n"/>
       <c r="B22" s="35" t="n"/>
       <c r="C22" s="35" t="n"/>
-      <c r="D22" s="35" t="n"/>
-      <c r="E22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="37" t="n"/>
       <c r="F22" s="37" t="n"/>
       <c r="G22" s="37" t="n"/>
       <c r="H22" s="37" t="n"/>
@@ -7122,16 +6882,15 @@
       <c r="M22" s="37" t="n"/>
       <c r="N22" s="37" t="n"/>
       <c r="O22" s="37" t="n"/>
-      <c r="P22" s="37" t="n"/>
-      <c r="Q22" s="36" t="n"/>
-      <c r="R22" s="37" t="n"/>
+      <c r="P22" s="36" t="n"/>
+      <c r="Q22" s="37" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
@@ -7142,16 +6901,15 @@
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="10" t="n"/>
       <c r="O23" s="10" t="n"/>
-      <c r="P23" s="10" t="n"/>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="10" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="34" t="n"/>
       <c r="B24" s="35" t="n"/>
       <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="37" t="n"/>
       <c r="F24" s="37" t="n"/>
       <c r="G24" s="37" t="n"/>
       <c r="H24" s="37" t="n"/>
@@ -7162,16 +6920,15 @@
       <c r="M24" s="37" t="n"/>
       <c r="N24" s="37" t="n"/>
       <c r="O24" s="37" t="n"/>
-      <c r="P24" s="37" t="n"/>
-      <c r="Q24" s="36" t="n"/>
-      <c r="R24" s="37" t="n"/>
+      <c r="P24" s="36" t="n"/>
+      <c r="Q24" s="37" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n"/>
@@ -7182,16 +6939,15 @@
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
-      <c r="P25" s="10" t="n"/>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="34" t="n"/>
       <c r="B26" s="35" t="n"/>
       <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="37" t="n"/>
       <c r="F26" s="37" t="n"/>
       <c r="G26" s="37" t="n"/>
       <c r="H26" s="37" t="n"/>
@@ -7202,16 +6958,15 @@
       <c r="M26" s="37" t="n"/>
       <c r="N26" s="37" t="n"/>
       <c r="O26" s="37" t="n"/>
-      <c r="P26" s="37" t="n"/>
-      <c r="Q26" s="36" t="n"/>
-      <c r="R26" s="37" t="n"/>
+      <c r="P26" s="36" t="n"/>
+      <c r="Q26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
@@ -7222,16 +6977,15 @@
       <c r="M27" s="10" t="n"/>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
-      <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="10" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="34" t="n"/>
       <c r="B28" s="35" t="n"/>
       <c r="C28" s="35" t="n"/>
-      <c r="D28" s="35" t="n"/>
-      <c r="E28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="37" t="n"/>
       <c r="F28" s="37" t="n"/>
       <c r="G28" s="37" t="n"/>
       <c r="H28" s="37" t="n"/>
@@ -7242,16 +6996,15 @@
       <c r="M28" s="37" t="n"/>
       <c r="N28" s="37" t="n"/>
       <c r="O28" s="37" t="n"/>
-      <c r="P28" s="37" t="n"/>
-      <c r="Q28" s="36" t="n"/>
-      <c r="R28" s="37" t="n"/>
+      <c r="P28" s="36" t="n"/>
+      <c r="Q28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
@@ -7262,16 +7015,15 @@
       <c r="M29" s="10" t="n"/>
       <c r="N29" s="10" t="n"/>
       <c r="O29" s="10" t="n"/>
-      <c r="P29" s="10" t="n"/>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="34" t="n"/>
       <c r="B30" s="35" t="n"/>
       <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="37" t="n"/>
       <c r="F30" s="37" t="n"/>
       <c r="G30" s="37" t="n"/>
       <c r="H30" s="37" t="n"/>
@@ -7282,16 +7034,15 @@
       <c r="M30" s="37" t="n"/>
       <c r="N30" s="37" t="n"/>
       <c r="O30" s="37" t="n"/>
-      <c r="P30" s="37" t="n"/>
-      <c r="Q30" s="36" t="n"/>
-      <c r="R30" s="37" t="n"/>
+      <c r="P30" s="36" t="n"/>
+      <c r="Q30" s="37" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
@@ -7302,16 +7053,15 @@
       <c r="M31" s="10" t="n"/>
       <c r="N31" s="10" t="n"/>
       <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n"/>
-      <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="34" t="n"/>
       <c r="B32" s="35" t="n"/>
       <c r="C32" s="35" t="n"/>
-      <c r="D32" s="35" t="n"/>
-      <c r="E32" s="36" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="37" t="n"/>
       <c r="F32" s="37" t="n"/>
       <c r="G32" s="37" t="n"/>
       <c r="H32" s="37" t="n"/>
@@ -7322,16 +7072,15 @@
       <c r="M32" s="37" t="n"/>
       <c r="N32" s="37" t="n"/>
       <c r="O32" s="37" t="n"/>
-      <c r="P32" s="37" t="n"/>
-      <c r="Q32" s="36" t="n"/>
-      <c r="R32" s="37" t="n"/>
+      <c r="P32" s="36" t="n"/>
+      <c r="Q32" s="37" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
@@ -7342,16 +7091,15 @@
       <c r="M33" s="10" t="n"/>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="34" t="n"/>
       <c r="B34" s="35" t="n"/>
       <c r="C34" s="35" t="n"/>
-      <c r="D34" s="35" t="n"/>
-      <c r="E34" s="36" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="37" t="n"/>
       <c r="F34" s="37" t="n"/>
       <c r="G34" s="37" t="n"/>
       <c r="H34" s="37" t="n"/>
@@ -7362,16 +7110,15 @@
       <c r="M34" s="37" t="n"/>
       <c r="N34" s="37" t="n"/>
       <c r="O34" s="37" t="n"/>
-      <c r="P34" s="37" t="n"/>
-      <c r="Q34" s="36" t="n"/>
-      <c r="R34" s="37" t="n"/>
+      <c r="P34" s="36" t="n"/>
+      <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
@@ -7382,16 +7129,15 @@
       <c r="M35" s="10" t="n"/>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n"/>
-      <c r="Q35" s="11" t="n"/>
-      <c r="R35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="34" t="n"/>
       <c r="B36" s="35" t="n"/>
       <c r="C36" s="35" t="n"/>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="37" t="n"/>
       <c r="F36" s="37" t="n"/>
       <c r="G36" s="37" t="n"/>
       <c r="H36" s="37" t="n"/>
@@ -7402,16 +7148,15 @@
       <c r="M36" s="37" t="n"/>
       <c r="N36" s="37" t="n"/>
       <c r="O36" s="37" t="n"/>
-      <c r="P36" s="37" t="n"/>
-      <c r="Q36" s="36" t="n"/>
-      <c r="R36" s="37" t="n"/>
+      <c r="P36" s="36" t="n"/>
+      <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
@@ -7422,16 +7167,15 @@
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="11" t="n"/>
-      <c r="R37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="34" t="n"/>
       <c r="B38" s="35" t="n"/>
       <c r="C38" s="35" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="36" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="37" t="n"/>
       <c r="F38" s="37" t="n"/>
       <c r="G38" s="37" t="n"/>
       <c r="H38" s="37" t="n"/>
@@ -7442,16 +7186,15 @@
       <c r="M38" s="37" t="n"/>
       <c r="N38" s="37" t="n"/>
       <c r="O38" s="37" t="n"/>
-      <c r="P38" s="37" t="n"/>
-      <c r="Q38" s="36" t="n"/>
-      <c r="R38" s="37" t="n"/>
+      <c r="P38" s="36" t="n"/>
+      <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
@@ -7462,16 +7205,15 @@
       <c r="M39" s="10" t="n"/>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="11" t="n"/>
-      <c r="R39" s="10" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="34" t="n"/>
       <c r="B40" s="35" t="n"/>
       <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="36" t="n"/>
+      <c r="D40" s="36" t="n"/>
+      <c r="E40" s="37" t="n"/>
       <c r="F40" s="37" t="n"/>
       <c r="G40" s="37" t="n"/>
       <c r="H40" s="37" t="n"/>
@@ -7482,16 +7224,15 @@
       <c r="M40" s="37" t="n"/>
       <c r="N40" s="37" t="n"/>
       <c r="O40" s="37" t="n"/>
-      <c r="P40" s="37" t="n"/>
-      <c r="Q40" s="36" t="n"/>
-      <c r="R40" s="37" t="n"/>
+      <c r="P40" s="36" t="n"/>
+      <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
@@ -7502,16 +7243,15 @@
       <c r="M41" s="10" t="n"/>
       <c r="N41" s="10" t="n"/>
       <c r="O41" s="10" t="n"/>
-      <c r="P41" s="10" t="n"/>
-      <c r="Q41" s="11" t="n"/>
-      <c r="R41" s="10" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="34" t="n"/>
       <c r="B42" s="35" t="n"/>
       <c r="C42" s="35" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="37" t="n"/>
       <c r="F42" s="37" t="n"/>
       <c r="G42" s="37" t="n"/>
       <c r="H42" s="37" t="n"/>
@@ -7522,16 +7262,15 @@
       <c r="M42" s="37" t="n"/>
       <c r="N42" s="37" t="n"/>
       <c r="O42" s="37" t="n"/>
-      <c r="P42" s="37" t="n"/>
-      <c r="Q42" s="36" t="n"/>
-      <c r="R42" s="37" t="n"/>
+      <c r="P42" s="36" t="n"/>
+      <c r="Q42" s="37" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
@@ -7542,16 +7281,15 @@
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="11" t="n"/>
-      <c r="R43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="34" t="n"/>
       <c r="B44" s="35" t="n"/>
       <c r="C44" s="35" t="n"/>
-      <c r="D44" s="35" t="n"/>
-      <c r="E44" s="36" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="37" t="n"/>
       <c r="F44" s="37" t="n"/>
       <c r="G44" s="37" t="n"/>
       <c r="H44" s="37" t="n"/>
@@ -7562,16 +7300,15 @@
       <c r="M44" s="37" t="n"/>
       <c r="N44" s="37" t="n"/>
       <c r="O44" s="37" t="n"/>
-      <c r="P44" s="37" t="n"/>
-      <c r="Q44" s="36" t="n"/>
-      <c r="R44" s="37" t="n"/>
+      <c r="P44" s="36" t="n"/>
+      <c r="Q44" s="37" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="11" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
@@ -7582,16 +7319,15 @@
       <c r="M45" s="10" t="n"/>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="11" t="n"/>
-      <c r="R45" s="10" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="34" t="n"/>
       <c r="B46" s="35" t="n"/>
       <c r="C46" s="35" t="n"/>
-      <c r="D46" s="35" t="n"/>
-      <c r="E46" s="36" t="n"/>
+      <c r="D46" s="36" t="n"/>
+      <c r="E46" s="37" t="n"/>
       <c r="F46" s="37" t="n"/>
       <c r="G46" s="37" t="n"/>
       <c r="H46" s="37" t="n"/>
@@ -7602,16 +7338,15 @@
       <c r="M46" s="37" t="n"/>
       <c r="N46" s="37" t="n"/>
       <c r="O46" s="37" t="n"/>
-      <c r="P46" s="37" t="n"/>
-      <c r="Q46" s="36" t="n"/>
-      <c r="R46" s="37" t="n"/>
+      <c r="P46" s="36" t="n"/>
+      <c r="Q46" s="37" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="10" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
@@ -7622,16 +7357,15 @@
       <c r="M47" s="10" t="n"/>
       <c r="N47" s="10" t="n"/>
       <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="11" t="n"/>
-      <c r="R47" s="10" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="34" t="n"/>
       <c r="B48" s="35" t="n"/>
       <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="37" t="n"/>
       <c r="F48" s="37" t="n"/>
       <c r="G48" s="37" t="n"/>
       <c r="H48" s="37" t="n"/>
@@ -7642,16 +7376,15 @@
       <c r="M48" s="37" t="n"/>
       <c r="N48" s="37" t="n"/>
       <c r="O48" s="37" t="n"/>
-      <c r="P48" s="37" t="n"/>
-      <c r="Q48" s="36" t="n"/>
-      <c r="R48" s="37" t="n"/>
+      <c r="P48" s="36" t="n"/>
+      <c r="Q48" s="37" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="10" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
@@ -7662,16 +7395,15 @@
       <c r="M49" s="10" t="n"/>
       <c r="N49" s="10" t="n"/>
       <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="11" t="n"/>
-      <c r="R49" s="10" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="34" t="n"/>
       <c r="B50" s="35" t="n"/>
       <c r="C50" s="35" t="n"/>
-      <c r="D50" s="35" t="n"/>
-      <c r="E50" s="36" t="n"/>
+      <c r="D50" s="36" t="n"/>
+      <c r="E50" s="37" t="n"/>
       <c r="F50" s="37" t="n"/>
       <c r="G50" s="37" t="n"/>
       <c r="H50" s="37" t="n"/>
@@ -7682,16 +7414,15 @@
       <c r="M50" s="37" t="n"/>
       <c r="N50" s="37" t="n"/>
       <c r="O50" s="37" t="n"/>
-      <c r="P50" s="37" t="n"/>
-      <c r="Q50" s="36" t="n"/>
-      <c r="R50" s="37" t="n"/>
+      <c r="P50" s="36" t="n"/>
+      <c r="Q50" s="37" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="11" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
@@ -7702,16 +7433,15 @@
       <c r="M51" s="10" t="n"/>
       <c r="N51" s="10" t="n"/>
       <c r="O51" s="10" t="n"/>
-      <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="11" t="n"/>
-      <c r="R51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="34" t="n"/>
       <c r="B52" s="35" t="n"/>
       <c r="C52" s="35" t="n"/>
-      <c r="D52" s="35" t="n"/>
-      <c r="E52" s="36" t="n"/>
+      <c r="D52" s="36" t="n"/>
+      <c r="E52" s="37" t="n"/>
       <c r="F52" s="37" t="n"/>
       <c r="G52" s="37" t="n"/>
       <c r="H52" s="37" t="n"/>
@@ -7722,16 +7452,15 @@
       <c r="M52" s="37" t="n"/>
       <c r="N52" s="37" t="n"/>
       <c r="O52" s="37" t="n"/>
-      <c r="P52" s="37" t="n"/>
-      <c r="Q52" s="36" t="n"/>
-      <c r="R52" s="37" t="n"/>
+      <c r="P52" s="36" t="n"/>
+      <c r="Q52" s="37" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="11" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
@@ -7742,16 +7471,15 @@
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="11" t="n"/>
-      <c r="R53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="34" t="n"/>
       <c r="B54" s="35" t="n"/>
       <c r="C54" s="35" t="n"/>
-      <c r="D54" s="35" t="n"/>
-      <c r="E54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="37" t="n"/>
       <c r="F54" s="37" t="n"/>
       <c r="G54" s="37" t="n"/>
       <c r="H54" s="37" t="n"/>
@@ -7762,16 +7490,15 @@
       <c r="M54" s="37" t="n"/>
       <c r="N54" s="37" t="n"/>
       <c r="O54" s="37" t="n"/>
-      <c r="P54" s="37" t="n"/>
-      <c r="Q54" s="36" t="n"/>
-      <c r="R54" s="37" t="n"/>
+      <c r="P54" s="36" t="n"/>
+      <c r="Q54" s="37" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="11" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
@@ -7782,16 +7509,15 @@
       <c r="M55" s="10" t="n"/>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="11" t="n"/>
-      <c r="R55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="34" t="n"/>
       <c r="B56" s="35" t="n"/>
       <c r="C56" s="35" t="n"/>
-      <c r="D56" s="35" t="n"/>
-      <c r="E56" s="36" t="n"/>
+      <c r="D56" s="36" t="n"/>
+      <c r="E56" s="37" t="n"/>
       <c r="F56" s="37" t="n"/>
       <c r="G56" s="37" t="n"/>
       <c r="H56" s="37" t="n"/>
@@ -7802,16 +7528,15 @@
       <c r="M56" s="37" t="n"/>
       <c r="N56" s="37" t="n"/>
       <c r="O56" s="37" t="n"/>
-      <c r="P56" s="37" t="n"/>
-      <c r="Q56" s="36" t="n"/>
-      <c r="R56" s="37" t="n"/>
+      <c r="P56" s="36" t="n"/>
+      <c r="Q56" s="37" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="11" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
@@ -7822,16 +7547,15 @@
       <c r="M57" s="10" t="n"/>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="11" t="n"/>
-      <c r="R57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="34" t="n"/>
       <c r="B58" s="35" t="n"/>
       <c r="C58" s="35" t="n"/>
-      <c r="D58" s="35" t="n"/>
-      <c r="E58" s="36" t="n"/>
+      <c r="D58" s="36" t="n"/>
+      <c r="E58" s="37" t="n"/>
       <c r="F58" s="37" t="n"/>
       <c r="G58" s="37" t="n"/>
       <c r="H58" s="37" t="n"/>
@@ -7842,16 +7566,15 @@
       <c r="M58" s="37" t="n"/>
       <c r="N58" s="37" t="n"/>
       <c r="O58" s="37" t="n"/>
-      <c r="P58" s="37" t="n"/>
-      <c r="Q58" s="36" t="n"/>
-      <c r="R58" s="37" t="n"/>
+      <c r="P58" s="36" t="n"/>
+      <c r="Q58" s="37" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="10" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -7862,16 +7585,15 @@
       <c r="M59" s="10" t="n"/>
       <c r="N59" s="10" t="n"/>
       <c r="O59" s="10" t="n"/>
-      <c r="P59" s="10" t="n"/>
-      <c r="Q59" s="11" t="n"/>
-      <c r="R59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="34" t="n"/>
       <c r="B60" s="35" t="n"/>
       <c r="C60" s="35" t="n"/>
-      <c r="D60" s="35" t="n"/>
-      <c r="E60" s="36" t="n"/>
+      <c r="D60" s="36" t="n"/>
+      <c r="E60" s="37" t="n"/>
       <c r="F60" s="37" t="n"/>
       <c r="G60" s="37" t="n"/>
       <c r="H60" s="37" t="n"/>
@@ -7882,16 +7604,15 @@
       <c r="M60" s="37" t="n"/>
       <c r="N60" s="37" t="n"/>
       <c r="O60" s="37" t="n"/>
-      <c r="P60" s="37" t="n"/>
-      <c r="Q60" s="36" t="n"/>
-      <c r="R60" s="37" t="n"/>
+      <c r="P60" s="36" t="n"/>
+      <c r="Q60" s="37" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="10" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
@@ -7902,16 +7623,15 @@
       <c r="M61" s="10" t="n"/>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="11" t="n"/>
-      <c r="R61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="34" t="n"/>
       <c r="B62" s="35" t="n"/>
       <c r="C62" s="35" t="n"/>
-      <c r="D62" s="35" t="n"/>
-      <c r="E62" s="36" t="n"/>
+      <c r="D62" s="36" t="n"/>
+      <c r="E62" s="37" t="n"/>
       <c r="F62" s="37" t="n"/>
       <c r="G62" s="37" t="n"/>
       <c r="H62" s="37" t="n"/>
@@ -7922,16 +7642,15 @@
       <c r="M62" s="37" t="n"/>
       <c r="N62" s="37" t="n"/>
       <c r="O62" s="37" t="n"/>
-      <c r="P62" s="37" t="n"/>
-      <c r="Q62" s="36" t="n"/>
-      <c r="R62" s="37" t="n"/>
+      <c r="P62" s="36" t="n"/>
+      <c r="Q62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="10" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
@@ -7942,16 +7661,15 @@
       <c r="M63" s="10" t="n"/>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="11" t="n"/>
-      <c r="R63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="34" t="n"/>
       <c r="B64" s="35" t="n"/>
       <c r="C64" s="35" t="n"/>
-      <c r="D64" s="35" t="n"/>
-      <c r="E64" s="36" t="n"/>
+      <c r="D64" s="36" t="n"/>
+      <c r="E64" s="37" t="n"/>
       <c r="F64" s="37" t="n"/>
       <c r="G64" s="37" t="n"/>
       <c r="H64" s="37" t="n"/>
@@ -7962,16 +7680,15 @@
       <c r="M64" s="37" t="n"/>
       <c r="N64" s="37" t="n"/>
       <c r="O64" s="37" t="n"/>
-      <c r="P64" s="37" t="n"/>
-      <c r="Q64" s="36" t="n"/>
-      <c r="R64" s="37" t="n"/>
+      <c r="P64" s="36" t="n"/>
+      <c r="Q64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
-      <c r="E65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="10" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
@@ -7982,16 +7699,15 @@
       <c r="M65" s="10" t="n"/>
       <c r="N65" s="10" t="n"/>
       <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="11" t="n"/>
-      <c r="R65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="34" t="n"/>
       <c r="B66" s="35" t="n"/>
       <c r="C66" s="35" t="n"/>
-      <c r="D66" s="35" t="n"/>
-      <c r="E66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="37" t="n"/>
       <c r="F66" s="37" t="n"/>
       <c r="G66" s="37" t="n"/>
       <c r="H66" s="37" t="n"/>
@@ -8002,16 +7718,15 @@
       <c r="M66" s="37" t="n"/>
       <c r="N66" s="37" t="n"/>
       <c r="O66" s="37" t="n"/>
-      <c r="P66" s="37" t="n"/>
-      <c r="Q66" s="36" t="n"/>
-      <c r="R66" s="37" t="n"/>
+      <c r="P66" s="36" t="n"/>
+      <c r="Q66" s="37" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="11" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="10" t="n"/>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
@@ -8022,16 +7737,15 @@
       <c r="M67" s="10" t="n"/>
       <c r="N67" s="10" t="n"/>
       <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="11" t="n"/>
-      <c r="R67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="34" t="n"/>
       <c r="B68" s="35" t="n"/>
       <c r="C68" s="35" t="n"/>
-      <c r="D68" s="35" t="n"/>
-      <c r="E68" s="36" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="37" t="n"/>
       <c r="F68" s="37" t="n"/>
       <c r="G68" s="37" t="n"/>
       <c r="H68" s="37" t="n"/>
@@ -8042,16 +7756,15 @@
       <c r="M68" s="37" t="n"/>
       <c r="N68" s="37" t="n"/>
       <c r="O68" s="37" t="n"/>
-      <c r="P68" s="37" t="n"/>
-      <c r="Q68" s="36" t="n"/>
-      <c r="R68" s="37" t="n"/>
+      <c r="P68" s="36" t="n"/>
+      <c r="Q68" s="37" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
-      <c r="E69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="10" t="n"/>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
@@ -8062,16 +7775,15 @@
       <c r="M69" s="10" t="n"/>
       <c r="N69" s="10" t="n"/>
       <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="11" t="n"/>
-      <c r="R69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="34" t="n"/>
       <c r="B70" s="35" t="n"/>
       <c r="C70" s="35" t="n"/>
-      <c r="D70" s="35" t="n"/>
-      <c r="E70" s="36" t="n"/>
+      <c r="D70" s="36" t="n"/>
+      <c r="E70" s="37" t="n"/>
       <c r="F70" s="37" t="n"/>
       <c r="G70" s="37" t="n"/>
       <c r="H70" s="37" t="n"/>
@@ -8082,16 +7794,15 @@
       <c r="M70" s="37" t="n"/>
       <c r="N70" s="37" t="n"/>
       <c r="O70" s="37" t="n"/>
-      <c r="P70" s="37" t="n"/>
-      <c r="Q70" s="36" t="n"/>
-      <c r="R70" s="37" t="n"/>
+      <c r="P70" s="36" t="n"/>
+      <c r="Q70" s="37" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="11" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="10" t="n"/>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
@@ -8102,16 +7813,15 @@
       <c r="M71" s="10" t="n"/>
       <c r="N71" s="10" t="n"/>
       <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="11" t="n"/>
-      <c r="R71" s="10" t="n"/>
+      <c r="P71" s="11" t="n"/>
+      <c r="Q71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="34" t="n"/>
       <c r="B72" s="35" t="n"/>
       <c r="C72" s="35" t="n"/>
-      <c r="D72" s="35" t="n"/>
-      <c r="E72" s="36" t="n"/>
+      <c r="D72" s="36" t="n"/>
+      <c r="E72" s="37" t="n"/>
       <c r="F72" s="37" t="n"/>
       <c r="G72" s="37" t="n"/>
       <c r="H72" s="37" t="n"/>
@@ -8122,16 +7832,15 @@
       <c r="M72" s="37" t="n"/>
       <c r="N72" s="37" t="n"/>
       <c r="O72" s="37" t="n"/>
-      <c r="P72" s="37" t="n"/>
-      <c r="Q72" s="36" t="n"/>
-      <c r="R72" s="37" t="n"/>
+      <c r="P72" s="36" t="n"/>
+      <c r="Q72" s="37" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
-      <c r="E73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="10" t="n"/>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
@@ -8142,16 +7851,15 @@
       <c r="M73" s="10" t="n"/>
       <c r="N73" s="10" t="n"/>
       <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="11" t="n"/>
-      <c r="R73" s="10" t="n"/>
+      <c r="P73" s="11" t="n"/>
+      <c r="Q73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="34" t="n"/>
       <c r="B74" s="35" t="n"/>
       <c r="C74" s="35" t="n"/>
-      <c r="D74" s="35" t="n"/>
-      <c r="E74" s="36" t="n"/>
+      <c r="D74" s="36" t="n"/>
+      <c r="E74" s="37" t="n"/>
       <c r="F74" s="37" t="n"/>
       <c r="G74" s="37" t="n"/>
       <c r="H74" s="37" t="n"/>
@@ -8162,16 +7870,15 @@
       <c r="M74" s="37" t="n"/>
       <c r="N74" s="37" t="n"/>
       <c r="O74" s="37" t="n"/>
-      <c r="P74" s="37" t="n"/>
-      <c r="Q74" s="36" t="n"/>
-      <c r="R74" s="37" t="n"/>
+      <c r="P74" s="36" t="n"/>
+      <c r="Q74" s="37" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="11" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="10" t="n"/>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
@@ -8182,16 +7889,15 @@
       <c r="M75" s="10" t="n"/>
       <c r="N75" s="10" t="n"/>
       <c r="O75" s="10" t="n"/>
-      <c r="P75" s="10" t="n"/>
-      <c r="Q75" s="11" t="n"/>
-      <c r="R75" s="10" t="n"/>
+      <c r="P75" s="11" t="n"/>
+      <c r="Q75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="34" t="n"/>
       <c r="B76" s="35" t="n"/>
       <c r="C76" s="35" t="n"/>
-      <c r="D76" s="35" t="n"/>
-      <c r="E76" s="36" t="n"/>
+      <c r="D76" s="36" t="n"/>
+      <c r="E76" s="37" t="n"/>
       <c r="F76" s="37" t="n"/>
       <c r="G76" s="37" t="n"/>
       <c r="H76" s="37" t="n"/>
@@ -8202,16 +7908,15 @@
       <c r="M76" s="37" t="n"/>
       <c r="N76" s="37" t="n"/>
       <c r="O76" s="37" t="n"/>
-      <c r="P76" s="37" t="n"/>
-      <c r="Q76" s="36" t="n"/>
-      <c r="R76" s="37" t="n"/>
+      <c r="P76" s="36" t="n"/>
+      <c r="Q76" s="37" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
-      <c r="E77" s="11" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="10" t="n"/>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
@@ -8222,16 +7927,15 @@
       <c r="M77" s="10" t="n"/>
       <c r="N77" s="10" t="n"/>
       <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="11" t="n"/>
-      <c r="R77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="34" t="n"/>
       <c r="B78" s="35" t="n"/>
       <c r="C78" s="35" t="n"/>
-      <c r="D78" s="35" t="n"/>
-      <c r="E78" s="36" t="n"/>
+      <c r="D78" s="36" t="n"/>
+      <c r="E78" s="37" t="n"/>
       <c r="F78" s="37" t="n"/>
       <c r="G78" s="37" t="n"/>
       <c r="H78" s="37" t="n"/>
@@ -8242,16 +7946,15 @@
       <c r="M78" s="37" t="n"/>
       <c r="N78" s="37" t="n"/>
       <c r="O78" s="37" t="n"/>
-      <c r="P78" s="37" t="n"/>
-      <c r="Q78" s="36" t="n"/>
-      <c r="R78" s="37" t="n"/>
+      <c r="P78" s="36" t="n"/>
+      <c r="Q78" s="37" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="9" t="n"/>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="10" t="n"/>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
@@ -8262,16 +7965,15 @@
       <c r="M79" s="10" t="n"/>
       <c r="N79" s="10" t="n"/>
       <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="11" t="n"/>
-      <c r="R79" s="10" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="34" t="n"/>
       <c r="B80" s="35" t="n"/>
       <c r="C80" s="35" t="n"/>
-      <c r="D80" s="35" t="n"/>
-      <c r="E80" s="36" t="n"/>
+      <c r="D80" s="36" t="n"/>
+      <c r="E80" s="37" t="n"/>
       <c r="F80" s="37" t="n"/>
       <c r="G80" s="37" t="n"/>
       <c r="H80" s="37" t="n"/>
@@ -8282,16 +7984,15 @@
       <c r="M80" s="37" t="n"/>
       <c r="N80" s="37" t="n"/>
       <c r="O80" s="37" t="n"/>
-      <c r="P80" s="37" t="n"/>
-      <c r="Q80" s="36" t="n"/>
-      <c r="R80" s="37" t="n"/>
+      <c r="P80" s="36" t="n"/>
+      <c r="Q80" s="37" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
-      <c r="E81" s="11" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="10" t="n"/>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
@@ -8302,16 +8003,15 @@
       <c r="M81" s="10" t="n"/>
       <c r="N81" s="10" t="n"/>
       <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="11" t="n"/>
-      <c r="R81" s="10" t="n"/>
+      <c r="P81" s="11" t="n"/>
+      <c r="Q81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="34" t="n"/>
       <c r="B82" s="35" t="n"/>
       <c r="C82" s="35" t="n"/>
-      <c r="D82" s="35" t="n"/>
-      <c r="E82" s="36" t="n"/>
+      <c r="D82" s="36" t="n"/>
+      <c r="E82" s="37" t="n"/>
       <c r="F82" s="37" t="n"/>
       <c r="G82" s="37" t="n"/>
       <c r="H82" s="37" t="n"/>
@@ -8322,16 +8022,15 @@
       <c r="M82" s="37" t="n"/>
       <c r="N82" s="37" t="n"/>
       <c r="O82" s="37" t="n"/>
-      <c r="P82" s="37" t="n"/>
-      <c r="Q82" s="36" t="n"/>
-      <c r="R82" s="37" t="n"/>
+      <c r="P82" s="36" t="n"/>
+      <c r="Q82" s="37" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="11" t="n"/>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="10" t="n"/>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
@@ -8342,16 +8041,15 @@
       <c r="M83" s="10" t="n"/>
       <c r="N83" s="10" t="n"/>
       <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="11" t="n"/>
-      <c r="R83" s="10" t="n"/>
+      <c r="P83" s="11" t="n"/>
+      <c r="Q83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="34" t="n"/>
       <c r="B84" s="35" t="n"/>
       <c r="C84" s="35" t="n"/>
-      <c r="D84" s="35" t="n"/>
-      <c r="E84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="37" t="n"/>
       <c r="F84" s="37" t="n"/>
       <c r="G84" s="37" t="n"/>
       <c r="H84" s="37" t="n"/>
@@ -8362,16 +8060,15 @@
       <c r="M84" s="37" t="n"/>
       <c r="N84" s="37" t="n"/>
       <c r="O84" s="37" t="n"/>
-      <c r="P84" s="37" t="n"/>
-      <c r="Q84" s="36" t="n"/>
-      <c r="R84" s="37" t="n"/>
+      <c r="P84" s="36" t="n"/>
+      <c r="Q84" s="37" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
@@ -8382,16 +8079,15 @@
       <c r="M85" s="10" t="n"/>
       <c r="N85" s="10" t="n"/>
       <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="11" t="n"/>
-      <c r="R85" s="10" t="n"/>
+      <c r="P85" s="11" t="n"/>
+      <c r="Q85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="34" t="n"/>
       <c r="B86" s="35" t="n"/>
       <c r="C86" s="35" t="n"/>
-      <c r="D86" s="35" t="n"/>
-      <c r="E86" s="36" t="n"/>
+      <c r="D86" s="36" t="n"/>
+      <c r="E86" s="37" t="n"/>
       <c r="F86" s="37" t="n"/>
       <c r="G86" s="37" t="n"/>
       <c r="H86" s="37" t="n"/>
@@ -8402,16 +8098,15 @@
       <c r="M86" s="37" t="n"/>
       <c r="N86" s="37" t="n"/>
       <c r="O86" s="37" t="n"/>
-      <c r="P86" s="37" t="n"/>
-      <c r="Q86" s="36" t="n"/>
-      <c r="R86" s="37" t="n"/>
+      <c r="P86" s="36" t="n"/>
+      <c r="Q86" s="37" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
-      <c r="E87" s="11" t="n"/>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="10" t="n"/>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
@@ -8422,16 +8117,15 @@
       <c r="M87" s="10" t="n"/>
       <c r="N87" s="10" t="n"/>
       <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="11" t="n"/>
-      <c r="R87" s="10" t="n"/>
+      <c r="P87" s="11" t="n"/>
+      <c r="Q87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="34" t="n"/>
       <c r="B88" s="35" t="n"/>
       <c r="C88" s="35" t="n"/>
-      <c r="D88" s="35" t="n"/>
-      <c r="E88" s="36" t="n"/>
+      <c r="D88" s="36" t="n"/>
+      <c r="E88" s="37" t="n"/>
       <c r="F88" s="37" t="n"/>
       <c r="G88" s="37" t="n"/>
       <c r="H88" s="37" t="n"/>
@@ -8442,16 +8136,15 @@
       <c r="M88" s="37" t="n"/>
       <c r="N88" s="37" t="n"/>
       <c r="O88" s="37" t="n"/>
-      <c r="P88" s="37" t="n"/>
-      <c r="Q88" s="36" t="n"/>
-      <c r="R88" s="37" t="n"/>
+      <c r="P88" s="36" t="n"/>
+      <c r="Q88" s="37" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="11" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="10" t="n"/>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
@@ -8462,16 +8155,15 @@
       <c r="M89" s="10" t="n"/>
       <c r="N89" s="10" t="n"/>
       <c r="O89" s="10" t="n"/>
-      <c r="P89" s="10" t="n"/>
-      <c r="Q89" s="11" t="n"/>
-      <c r="R89" s="10" t="n"/>
+      <c r="P89" s="11" t="n"/>
+      <c r="Q89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="34" t="n"/>
       <c r="B90" s="35" t="n"/>
       <c r="C90" s="35" t="n"/>
-      <c r="D90" s="35" t="n"/>
-      <c r="E90" s="36" t="n"/>
+      <c r="D90" s="36" t="n"/>
+      <c r="E90" s="37" t="n"/>
       <c r="F90" s="37" t="n"/>
       <c r="G90" s="37" t="n"/>
       <c r="H90" s="37" t="n"/>
@@ -8482,16 +8174,15 @@
       <c r="M90" s="37" t="n"/>
       <c r="N90" s="37" t="n"/>
       <c r="O90" s="37" t="n"/>
-      <c r="P90" s="37" t="n"/>
-      <c r="Q90" s="36" t="n"/>
-      <c r="R90" s="37" t="n"/>
+      <c r="P90" s="36" t="n"/>
+      <c r="Q90" s="37" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="11" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="10" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
@@ -8502,16 +8193,15 @@
       <c r="M91" s="10" t="n"/>
       <c r="N91" s="10" t="n"/>
       <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="11" t="n"/>
-      <c r="R91" s="10" t="n"/>
+      <c r="P91" s="11" t="n"/>
+      <c r="Q91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="34" t="n"/>
       <c r="B92" s="35" t="n"/>
       <c r="C92" s="35" t="n"/>
-      <c r="D92" s="35" t="n"/>
-      <c r="E92" s="36" t="n"/>
+      <c r="D92" s="36" t="n"/>
+      <c r="E92" s="37" t="n"/>
       <c r="F92" s="37" t="n"/>
       <c r="G92" s="37" t="n"/>
       <c r="H92" s="37" t="n"/>
@@ -8522,16 +8212,15 @@
       <c r="M92" s="37" t="n"/>
       <c r="N92" s="37" t="n"/>
       <c r="O92" s="37" t="n"/>
-      <c r="P92" s="37" t="n"/>
-      <c r="Q92" s="36" t="n"/>
-      <c r="R92" s="37" t="n"/>
+      <c r="P92" s="36" t="n"/>
+      <c r="Q92" s="37" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
-      <c r="E93" s="11" t="n"/>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="10" t="n"/>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
@@ -8542,16 +8231,15 @@
       <c r="M93" s="10" t="n"/>
       <c r="N93" s="10" t="n"/>
       <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="11" t="n"/>
-      <c r="R93" s="10" t="n"/>
+      <c r="P93" s="11" t="n"/>
+      <c r="Q93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="34" t="n"/>
       <c r="B94" s="35" t="n"/>
       <c r="C94" s="35" t="n"/>
-      <c r="D94" s="35" t="n"/>
-      <c r="E94" s="36" t="n"/>
+      <c r="D94" s="36" t="n"/>
+      <c r="E94" s="37" t="n"/>
       <c r="F94" s="37" t="n"/>
       <c r="G94" s="37" t="n"/>
       <c r="H94" s="37" t="n"/>
@@ -8562,16 +8250,15 @@
       <c r="M94" s="37" t="n"/>
       <c r="N94" s="37" t="n"/>
       <c r="O94" s="37" t="n"/>
-      <c r="P94" s="37" t="n"/>
-      <c r="Q94" s="36" t="n"/>
-      <c r="R94" s="37" t="n"/>
+      <c r="P94" s="36" t="n"/>
+      <c r="Q94" s="37" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
-      <c r="E95" s="11" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="10" t="n"/>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
@@ -8582,16 +8269,15 @@
       <c r="M95" s="10" t="n"/>
       <c r="N95" s="10" t="n"/>
       <c r="O95" s="10" t="n"/>
-      <c r="P95" s="10" t="n"/>
-      <c r="Q95" s="11" t="n"/>
-      <c r="R95" s="10" t="n"/>
+      <c r="P95" s="11" t="n"/>
+      <c r="Q95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="34" t="n"/>
       <c r="B96" s="35" t="n"/>
       <c r="C96" s="35" t="n"/>
-      <c r="D96" s="35" t="n"/>
-      <c r="E96" s="36" t="n"/>
+      <c r="D96" s="36" t="n"/>
+      <c r="E96" s="37" t="n"/>
       <c r="F96" s="37" t="n"/>
       <c r="G96" s="37" t="n"/>
       <c r="H96" s="37" t="n"/>
@@ -8602,16 +8288,15 @@
       <c r="M96" s="37" t="n"/>
       <c r="N96" s="37" t="n"/>
       <c r="O96" s="37" t="n"/>
-      <c r="P96" s="37" t="n"/>
-      <c r="Q96" s="36" t="n"/>
-      <c r="R96" s="37" t="n"/>
+      <c r="P96" s="36" t="n"/>
+      <c r="Q96" s="37" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
-      <c r="D97" s="9" t="n"/>
-      <c r="E97" s="11" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="10" t="n"/>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
@@ -8622,16 +8307,15 @@
       <c r="M97" s="10" t="n"/>
       <c r="N97" s="10" t="n"/>
       <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="11" t="n"/>
-      <c r="R97" s="10" t="n"/>
+      <c r="P97" s="11" t="n"/>
+      <c r="Q97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="34" t="n"/>
       <c r="B98" s="35" t="n"/>
       <c r="C98" s="35" t="n"/>
-      <c r="D98" s="35" t="n"/>
-      <c r="E98" s="36" t="n"/>
+      <c r="D98" s="36" t="n"/>
+      <c r="E98" s="37" t="n"/>
       <c r="F98" s="37" t="n"/>
       <c r="G98" s="37" t="n"/>
       <c r="H98" s="37" t="n"/>
@@ -8642,16 +8326,15 @@
       <c r="M98" s="37" t="n"/>
       <c r="N98" s="37" t="n"/>
       <c r="O98" s="37" t="n"/>
-      <c r="P98" s="37" t="n"/>
-      <c r="Q98" s="36" t="n"/>
-      <c r="R98" s="37" t="n"/>
+      <c r="P98" s="36" t="n"/>
+      <c r="Q98" s="37" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="11" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="10" t="n"/>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
@@ -8662,16 +8345,15 @@
       <c r="M99" s="10" t="n"/>
       <c r="N99" s="10" t="n"/>
       <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="11" t="n"/>
-      <c r="R99" s="10" t="n"/>
+      <c r="P99" s="11" t="n"/>
+      <c r="Q99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="34" t="n"/>
       <c r="B100" s="35" t="n"/>
       <c r="C100" s="35" t="n"/>
-      <c r="D100" s="35" t="n"/>
-      <c r="E100" s="36" t="n"/>
+      <c r="D100" s="36" t="n"/>
+      <c r="E100" s="37" t="n"/>
       <c r="F100" s="37" t="n"/>
       <c r="G100" s="37" t="n"/>
       <c r="H100" s="37" t="n"/>
@@ -8682,16 +8364,15 @@
       <c r="M100" s="37" t="n"/>
       <c r="N100" s="37" t="n"/>
       <c r="O100" s="37" t="n"/>
-      <c r="P100" s="37" t="n"/>
-      <c r="Q100" s="36" t="n"/>
-      <c r="R100" s="37" t="n"/>
+      <c r="P100" s="36" t="n"/>
+      <c r="Q100" s="37" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
-      <c r="D101" s="9" t="n"/>
-      <c r="E101" s="11" t="n"/>
+      <c r="D101" s="11" t="n"/>
+      <c r="E101" s="10" t="n"/>
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
@@ -8702,16 +8383,15 @@
       <c r="M101" s="10" t="n"/>
       <c r="N101" s="10" t="n"/>
       <c r="O101" s="10" t="n"/>
-      <c r="P101" s="10" t="n"/>
-      <c r="Q101" s="11" t="n"/>
-      <c r="R101" s="10" t="n"/>
+      <c r="P101" s="11" t="n"/>
+      <c r="Q101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="34" t="n"/>
       <c r="B102" s="35" t="n"/>
       <c r="C102" s="35" t="n"/>
-      <c r="D102" s="35" t="n"/>
-      <c r="E102" s="36" t="n"/>
+      <c r="D102" s="36" t="n"/>
+      <c r="E102" s="37" t="n"/>
       <c r="F102" s="37" t="n"/>
       <c r="G102" s="37" t="n"/>
       <c r="H102" s="37" t="n"/>
@@ -8722,19 +8402,18 @@
       <c r="M102" s="37" t="n"/>
       <c r="N102" s="37" t="n"/>
       <c r="O102" s="37" t="n"/>
-      <c r="P102" s="37" t="n"/>
-      <c r="Q102" s="36" t="n"/>
-      <c r="R102" s="37" t="n"/>
+      <c r="P102" s="36" t="n"/>
+      <c r="Q102" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R2"/>
+  <autoFilter ref="A2:Q2"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="D1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="N3:N102">
+  <conditionalFormatting sqref="M3:M102">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"自家移植"</formula>
     </cfRule>
@@ -8763,7 +8442,7 @@
       <formula>"経過観察"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M102">
+  <conditionalFormatting sqref="L3:L102">
     <cfRule type="cellIs" priority="10" operator="equal" dxfId="9">
       <formula>"3"</formula>
     </cfRule>
@@ -8771,7 +8450,7 @@
       <formula>"4"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P102">
+  <conditionalFormatting sqref="O3:O102">
     <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
       <formula>"CR"</formula>
     </cfRule>
@@ -8806,7 +8485,7 @@
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L102">
+  <conditionalFormatting sqref="K3:K102">
     <cfRule type="cellIs" priority="23" operator="equal" dxfId="10">
       <formula>"Favorable"</formula>
     </cfRule>
@@ -8833,34 +8512,34 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation sqref="D3:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="C3:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>sex</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="G3:G102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>disease</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="H3:H102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>stage</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="I3:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>cytogenetics</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="J3:J102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>gene</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="K3:K102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>risk</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="L3:L102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>ps</formula1>
     </dataValidation>
-    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="M3:M102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>label</formula1>
     </dataValidation>
-    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="N3:N102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>regimen</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
+    <dataValidation sqref="O3:O102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" type="list">
       <formula1>outcome</formula1>
     </dataValidation>
   </dataValidations>
@@ -8964,7 +8643,7 @@
         </is>
       </c>
       <c r="C6" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"AML")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"AML")</f>
         <v/>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -8973,7 +8652,7 @@
         </is>
       </c>
       <c r="F6" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"化学療法")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"化学療法")</f>
         <v/>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -8982,7 +8661,7 @@
         </is>
       </c>
       <c r="I6" s="42">
-        <f>COUNTIF('入院患者'!R3:R102,"入院中")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"入院中")</f>
         <v/>
       </c>
     </row>
@@ -8993,7 +8672,7 @@
         </is>
       </c>
       <c r="C7" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"ALL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"ALL")</f>
         <v/>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -9002,7 +8681,7 @@
         </is>
       </c>
       <c r="F7" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"自家移植")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"自家移植")</f>
         <v/>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -9011,7 +8690,7 @@
         </is>
       </c>
       <c r="I7" s="43">
-        <f>COUNTIF('入院患者'!R3:R102,"退院済")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"退院済")</f>
         <v/>
       </c>
     </row>
@@ -9022,7 +8701,7 @@
         </is>
       </c>
       <c r="C8" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"CML")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"CML")</f>
         <v/>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -9031,7 +8710,7 @@
         </is>
       </c>
       <c r="F8" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"同種移植")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"同種移植")</f>
         <v/>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -9040,7 +8719,7 @@
         </is>
       </c>
       <c r="I8" s="42">
-        <f>COUNTIF('入院患者'!R3:R102,"外来移行")</f>
+        <f>COUNTIF('入院患者'!Q3:Q102,"外来移行")</f>
         <v/>
       </c>
     </row>
@@ -9051,7 +8730,7 @@
         </is>
       </c>
       <c r="C9" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"CLL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"CLL")</f>
         <v/>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -9060,7 +8739,7 @@
         </is>
       </c>
       <c r="F9" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"CAR-T")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"CAR-T")</f>
         <v/>
       </c>
       <c r="H9" s="44" t="inlineStr">
@@ -9080,7 +8759,7 @@
         </is>
       </c>
       <c r="C10" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"MDS")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"MDS")</f>
         <v/>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -9089,7 +8768,7 @@
         </is>
       </c>
       <c r="F10" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"分子標的薬")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"分子標的薬")</f>
         <v/>
       </c>
     </row>
@@ -9100,7 +8779,7 @@
         </is>
       </c>
       <c r="C11" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"MPN")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"MPN")</f>
         <v/>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -9109,7 +8788,7 @@
         </is>
       </c>
       <c r="F11" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"免疫療法")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"免疫療法")</f>
         <v/>
       </c>
     </row>
@@ -9120,7 +8799,7 @@
         </is>
       </c>
       <c r="C12" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"CMML")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"CMML")</f>
         <v/>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -9129,7 +8808,7 @@
         </is>
       </c>
       <c r="F12" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"放射線")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"放射線")</f>
         <v/>
       </c>
     </row>
@@ -9140,7 +8819,7 @@
         </is>
       </c>
       <c r="C13" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"DLBCL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"DLBCL")</f>
         <v/>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -9149,7 +8828,7 @@
         </is>
       </c>
       <c r="F13" s="43">
-        <f>COUNTIF('入院患者'!N3:N102,"BSC")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"BSC")</f>
         <v/>
       </c>
     </row>
@@ -9160,7 +8839,7 @@
         </is>
       </c>
       <c r="C14" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"FL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"FL")</f>
         <v/>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -9169,7 +8848,7 @@
         </is>
       </c>
       <c r="F14" s="42">
-        <f>COUNTIF('入院患者'!N3:N102,"経過観察")</f>
+        <f>COUNTIF('入院患者'!M3:M102,"経過観察")</f>
         <v/>
       </c>
     </row>
@@ -9180,7 +8859,7 @@
         </is>
       </c>
       <c r="C15" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"MCL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"MCL")</f>
         <v/>
       </c>
       <c r="E15" s="44" t="inlineStr">
@@ -9200,7 +8879,7 @@
         </is>
       </c>
       <c r="C16" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"BL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"BL")</f>
         <v/>
       </c>
     </row>
@@ -9211,7 +8890,7 @@
         </is>
       </c>
       <c r="C17" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"MALT")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"MALT")</f>
         <v/>
       </c>
     </row>
@@ -9222,7 +8901,7 @@
         </is>
       </c>
       <c r="C18" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"ATLL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"ATLL")</f>
         <v/>
       </c>
     </row>
@@ -9233,7 +8912,7 @@
         </is>
       </c>
       <c r="C19" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"PTCL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"PTCL")</f>
         <v/>
       </c>
     </row>
@@ -9244,7 +8923,7 @@
         </is>
       </c>
       <c r="C20" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"AITL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"AITL")</f>
         <v/>
       </c>
     </row>
@@ -9255,7 +8934,7 @@
         </is>
       </c>
       <c r="C21" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"NK/T")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"NK/T")</f>
         <v/>
       </c>
     </row>
@@ -9266,7 +8945,7 @@
         </is>
       </c>
       <c r="C22" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"HL")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"HL")</f>
         <v/>
       </c>
     </row>
@@ -9277,7 +8956,7 @@
         </is>
       </c>
       <c r="C23" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"MM")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"MM")</f>
         <v/>
       </c>
     </row>
@@ -9288,7 +8967,7 @@
         </is>
       </c>
       <c r="C24" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"WM")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"WM")</f>
         <v/>
       </c>
     </row>
@@ -9299,7 +8978,7 @@
         </is>
       </c>
       <c r="C25" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"AL amyloidosis")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
@@ -9310,7 +8989,7 @@
         </is>
       </c>
       <c r="C26" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"AA")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"AA")</f>
         <v/>
       </c>
     </row>
@@ -9321,7 +9000,7 @@
         </is>
       </c>
       <c r="C27" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"PNH")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"PNH")</f>
         <v/>
       </c>
     </row>
@@ -9332,7 +9011,7 @@
         </is>
       </c>
       <c r="C28" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"ITP")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"ITP")</f>
         <v/>
       </c>
     </row>
@@ -9343,7 +9022,7 @@
         </is>
       </c>
       <c r="C29" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"TTP")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"TTP")</f>
         <v/>
       </c>
     </row>
@@ -9354,7 +9033,7 @@
         </is>
       </c>
       <c r="C30" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"HUS")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"HUS")</f>
         <v/>
       </c>
     </row>
@@ -9365,7 +9044,7 @@
         </is>
       </c>
       <c r="C31" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"DIC")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"DIC")</f>
         <v/>
       </c>
     </row>
@@ -9376,7 +9055,7 @@
         </is>
       </c>
       <c r="C32" s="42">
-        <f>COUNTIF('入院患者'!E3:E102,"HLH")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"HLH")</f>
         <v/>
       </c>
     </row>
@@ -9387,7 +9066,7 @@
         </is>
       </c>
       <c r="C33" s="43">
-        <f>COUNTIF('入院患者'!E3:E102,"その他")</f>
+        <f>COUNTIF('入院患者'!D3:D102,"その他")</f>
         <v/>
       </c>
     </row>
@@ -9461,7 +9140,7 @@
         </is>
       </c>
       <c r="C38" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"CR")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"CR")</f>
         <v/>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -9470,7 +9149,7 @@
         </is>
       </c>
       <c r="F38" s="42">
-        <f>COUNTIF('入院患者'!I3:I102,"Favorable")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Favorable")</f>
         <v/>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -9479,7 +9158,7 @@
         </is>
       </c>
       <c r="I38" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AML")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"AML")</f>
         <v/>
       </c>
     </row>
@@ -9490,7 +9169,7 @@
         </is>
       </c>
       <c r="C39" s="43">
-        <f>COUNTIF('入院患者'!Q3:Q102,"CRi")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"CRi")</f>
         <v/>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -9499,7 +9178,7 @@
         </is>
       </c>
       <c r="F39" s="43">
-        <f>COUNTIF('入院患者'!I3:I102,"Intermediate")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Intermediate")</f>
         <v/>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -9508,7 +9187,7 @@
         </is>
       </c>
       <c r="I39" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"ALL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"ALL")</f>
         <v/>
       </c>
     </row>
@@ -9519,7 +9198,7 @@
         </is>
       </c>
       <c r="C40" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"PR")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"PR")</f>
         <v/>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -9528,7 +9207,7 @@
         </is>
       </c>
       <c r="F40" s="42">
-        <f>COUNTIF('入院患者'!I3:I102,"Adverse")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Adverse")</f>
         <v/>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -9537,7 +9216,7 @@
         </is>
       </c>
       <c r="I40" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"CML")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"CML")</f>
         <v/>
       </c>
     </row>
@@ -9548,7 +9227,7 @@
         </is>
       </c>
       <c r="C41" s="43">
-        <f>COUNTIF('入院患者'!Q3:Q102,"VGPR")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"VGPR")</f>
         <v/>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -9557,7 +9236,7 @@
         </is>
       </c>
       <c r="F41" s="43">
-        <f>COUNTIF('入院患者'!I3:I102,"Very high")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Very high")</f>
         <v/>
       </c>
       <c r="H41" s="14" t="inlineStr">
@@ -9566,7 +9245,7 @@
         </is>
       </c>
       <c r="I41" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"CLL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"CLL")</f>
         <v/>
       </c>
     </row>
@@ -9577,7 +9256,7 @@
         </is>
       </c>
       <c r="C42" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"sCR")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"sCR")</f>
         <v/>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -9586,7 +9265,7 @@
         </is>
       </c>
       <c r="F42" s="42">
-        <f>COUNTIF('入院患者'!I3:I102,"High")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"High")</f>
         <v/>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -9595,7 +9274,7 @@
         </is>
       </c>
       <c r="I42" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MDS")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"MDS")</f>
         <v/>
       </c>
     </row>
@@ -9606,7 +9285,7 @@
         </is>
       </c>
       <c r="C43" s="43">
-        <f>COUNTIF('入院患者'!Q3:Q102,"SD")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"SD")</f>
         <v/>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -9615,7 +9294,7 @@
         </is>
       </c>
       <c r="F43" s="43">
-        <f>COUNTIF('入院患者'!I3:I102,"Standard")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Standard")</f>
         <v/>
       </c>
       <c r="H43" s="14" t="inlineStr">
@@ -9624,7 +9303,7 @@
         </is>
       </c>
       <c r="I43" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MPN")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"MPN")</f>
         <v/>
       </c>
     </row>
@@ -9635,7 +9314,7 @@
         </is>
       </c>
       <c r="C44" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"PD")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"PD")</f>
         <v/>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -9644,7 +9323,7 @@
         </is>
       </c>
       <c r="F44" s="42">
-        <f>COUNTIF('入院患者'!I3:I102,"Low")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"Low")</f>
         <v/>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -9653,7 +9332,7 @@
         </is>
       </c>
       <c r="I44" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"CMML")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"CMML")</f>
         <v/>
       </c>
     </row>
@@ -9664,7 +9343,7 @@
         </is>
       </c>
       <c r="C45" s="43">
-        <f>COUNTIF('入院患者'!Q3:Q102,"再発")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"再発")</f>
         <v/>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -9673,7 +9352,7 @@
         </is>
       </c>
       <c r="F45" s="43">
-        <f>COUNTIF('入院患者'!I3:I102,"N/A")</f>
+        <f>COUNTIF('入院患者'!H3:H102,"N/A")</f>
         <v/>
       </c>
       <c r="H45" s="14" t="inlineStr">
@@ -9682,7 +9361,7 @@
         </is>
       </c>
       <c r="I45" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"DLBCL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"DLBCL")</f>
         <v/>
       </c>
     </row>
@@ -9693,7 +9372,7 @@
         </is>
       </c>
       <c r="C46" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"死亡")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"死亡")</f>
         <v/>
       </c>
       <c r="E46" s="44" t="inlineStr">
@@ -9711,7 +9390,7 @@
         </is>
       </c>
       <c r="I46" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"FL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"FL")</f>
         <v/>
       </c>
     </row>
@@ -9722,7 +9401,7 @@
         </is>
       </c>
       <c r="C47" s="43">
-        <f>COUNTIF('入院患者'!Q3:Q102,"評価前")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"評価前")</f>
         <v/>
       </c>
       <c r="H47" s="14" t="inlineStr">
@@ -9731,7 +9410,7 @@
         </is>
       </c>
       <c r="I47" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MCL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"MCL")</f>
         <v/>
       </c>
     </row>
@@ -9742,7 +9421,7 @@
         </is>
       </c>
       <c r="C48" s="42">
-        <f>COUNTIF('入院患者'!Q3:Q102,"N/A")</f>
+        <f>COUNTIF('入院患者'!P3:P102,"N/A")</f>
         <v/>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -9751,7 +9430,7 @@
         </is>
       </c>
       <c r="I48" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"BL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"BL")</f>
         <v/>
       </c>
     </row>
@@ -9771,7 +9450,7 @@
         </is>
       </c>
       <c r="I49" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MALT")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"MALT")</f>
         <v/>
       </c>
     </row>
@@ -9782,7 +9461,7 @@
         </is>
       </c>
       <c r="I50" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"ATLL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"ATLL")</f>
         <v/>
       </c>
     </row>
@@ -9793,7 +9472,7 @@
         </is>
       </c>
       <c r="I51" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"PTCL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"PTCL")</f>
         <v/>
       </c>
     </row>
@@ -9804,7 +9483,7 @@
         </is>
       </c>
       <c r="I52" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AITL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"AITL")</f>
         <v/>
       </c>
     </row>
@@ -9815,7 +9494,7 @@
         </is>
       </c>
       <c r="I53" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"NK/T")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"NK/T")</f>
         <v/>
       </c>
     </row>
@@ -9826,7 +9505,7 @@
         </is>
       </c>
       <c r="I54" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HL")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"HL")</f>
         <v/>
       </c>
     </row>
@@ -9837,7 +9516,7 @@
         </is>
       </c>
       <c r="I55" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"MM")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"MM")</f>
         <v/>
       </c>
     </row>
@@ -9848,7 +9527,7 @@
         </is>
       </c>
       <c r="I56" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"WM")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"WM")</f>
         <v/>
       </c>
     </row>
@@ -9859,7 +9538,7 @@
         </is>
       </c>
       <c r="I57" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AL amyloidosis")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
@@ -9870,7 +9549,7 @@
         </is>
       </c>
       <c r="I58" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"AA")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"AA")</f>
         <v/>
       </c>
     </row>
@@ -9881,7 +9560,7 @@
         </is>
       </c>
       <c r="I59" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"PNH")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"PNH")</f>
         <v/>
       </c>
     </row>
@@ -9892,7 +9571,7 @@
         </is>
       </c>
       <c r="I60" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"ITP")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"ITP")</f>
         <v/>
       </c>
     </row>
@@ -9903,7 +9582,7 @@
         </is>
       </c>
       <c r="I61" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"TTP")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"TTP")</f>
         <v/>
       </c>
     </row>
@@ -9914,7 +9593,7 @@
         </is>
       </c>
       <c r="I62" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HUS")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"HUS")</f>
         <v/>
       </c>
     </row>
@@ -9925,7 +9604,7 @@
         </is>
       </c>
       <c r="I63" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"DIC")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"DIC")</f>
         <v/>
       </c>
     </row>
@@ -9936,7 +9615,7 @@
         </is>
       </c>
       <c r="I64" s="42">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"HLH")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"HLH")</f>
         <v/>
       </c>
     </row>
@@ -9947,7 +9626,7 @@
         </is>
       </c>
       <c r="I65" s="43">
-        <f>COUNTIF('他科コンサルト'!J3:J102,"その他")</f>
+        <f>COUNTIF('他科コンサルト'!I3:I102,"その他")</f>
         <v/>
       </c>
     </row>
@@ -10021,7 +9700,7 @@
         </is>
       </c>
       <c r="C70" s="42">
-        <f>COUNTIF('他科コンサルト'!E3:E102,"緊急")</f>
+        <f>COUNTIF('他科コンサルト'!D3:D102,"緊急")</f>
         <v/>
       </c>
       <c r="E70" s="10" t="inlineStr">
@@ -10030,7 +9709,7 @@
         </is>
       </c>
       <c r="F70" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"AML")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"AML")</f>
         <v/>
       </c>
       <c r="H70" s="10" t="inlineStr">
@@ -10039,7 +9718,7 @@
         </is>
       </c>
       <c r="I70" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"CR")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"CR")</f>
         <v/>
       </c>
     </row>
@@ -10050,7 +9729,7 @@
         </is>
       </c>
       <c r="C71" s="43">
-        <f>COUNTIF('他科コンサルト'!E3:E102,"通常")</f>
+        <f>COUNTIF('他科コンサルト'!D3:D102,"通常")</f>
         <v/>
       </c>
       <c r="E71" s="14" t="inlineStr">
@@ -10059,7 +9738,7 @@
         </is>
       </c>
       <c r="F71" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"ALL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"ALL")</f>
         <v/>
       </c>
       <c r="H71" s="14" t="inlineStr">
@@ -10068,7 +9747,7 @@
         </is>
       </c>
       <c r="I71" s="43">
-        <f>COUNTIF('初診外来'!P3:P102,"CRi")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"CRi")</f>
         <v/>
       </c>
     </row>
@@ -10088,7 +9767,7 @@
         </is>
       </c>
       <c r="F72" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"CML")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"CML")</f>
         <v/>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -10097,7 +9776,7 @@
         </is>
       </c>
       <c r="I72" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"PR")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"PR")</f>
         <v/>
       </c>
     </row>
@@ -10108,7 +9787,7 @@
         </is>
       </c>
       <c r="F73" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"CLL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"CLL")</f>
         <v/>
       </c>
       <c r="H73" s="14" t="inlineStr">
@@ -10117,7 +9796,7 @@
         </is>
       </c>
       <c r="I73" s="43">
-        <f>COUNTIF('初診外来'!P3:P102,"VGPR")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"VGPR")</f>
         <v/>
       </c>
     </row>
@@ -10128,7 +9807,7 @@
         </is>
       </c>
       <c r="F74" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"MDS")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"MDS")</f>
         <v/>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -10137,7 +9816,7 @@
         </is>
       </c>
       <c r="I74" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"sCR")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"sCR")</f>
         <v/>
       </c>
     </row>
@@ -10148,7 +9827,7 @@
         </is>
       </c>
       <c r="F75" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MPN")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"MPN")</f>
         <v/>
       </c>
       <c r="H75" s="14" t="inlineStr">
@@ -10157,7 +9836,7 @@
         </is>
       </c>
       <c r="I75" s="43">
-        <f>COUNTIF('初診外来'!P3:P102,"SD")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"SD")</f>
         <v/>
       </c>
     </row>
@@ -10168,7 +9847,7 @@
         </is>
       </c>
       <c r="F76" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"CMML")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"CMML")</f>
         <v/>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -10177,7 +9856,7 @@
         </is>
       </c>
       <c r="I76" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"PD")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"PD")</f>
         <v/>
       </c>
     </row>
@@ -10188,7 +9867,7 @@
         </is>
       </c>
       <c r="F77" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"DLBCL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"DLBCL")</f>
         <v/>
       </c>
       <c r="H77" s="14" t="inlineStr">
@@ -10197,7 +9876,7 @@
         </is>
       </c>
       <c r="I77" s="43">
-        <f>COUNTIF('初診外来'!P3:P102,"再発")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"再発")</f>
         <v/>
       </c>
     </row>
@@ -10208,7 +9887,7 @@
         </is>
       </c>
       <c r="F78" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"FL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"FL")</f>
         <v/>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -10217,7 +9896,7 @@
         </is>
       </c>
       <c r="I78" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"死亡")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"死亡")</f>
         <v/>
       </c>
     </row>
@@ -10228,7 +9907,7 @@
         </is>
       </c>
       <c r="F79" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MCL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"MCL")</f>
         <v/>
       </c>
       <c r="H79" s="14" t="inlineStr">
@@ -10237,7 +9916,7 @@
         </is>
       </c>
       <c r="I79" s="43">
-        <f>COUNTIF('初診外来'!P3:P102,"評価前")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"評価前")</f>
         <v/>
       </c>
     </row>
@@ -10248,7 +9927,7 @@
         </is>
       </c>
       <c r="F80" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"BL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"BL")</f>
         <v/>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -10257,7 +9936,7 @@
         </is>
       </c>
       <c r="I80" s="42">
-        <f>COUNTIF('初診外来'!P3:P102,"N/A")</f>
+        <f>COUNTIF('初診外来'!O3:O102,"N/A")</f>
         <v/>
       </c>
     </row>
@@ -10268,7 +9947,7 @@
         </is>
       </c>
       <c r="F81" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MALT")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"MALT")</f>
         <v/>
       </c>
       <c r="H81" s="44" t="inlineStr">
@@ -10288,7 +9967,7 @@
         </is>
       </c>
       <c r="F82" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"ATLL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"ATLL")</f>
         <v/>
       </c>
     </row>
@@ -10299,7 +9978,7 @@
         </is>
       </c>
       <c r="F83" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"PTCL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"PTCL")</f>
         <v/>
       </c>
     </row>
@@ -10310,7 +9989,7 @@
         </is>
       </c>
       <c r="F84" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"AITL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"AITL")</f>
         <v/>
       </c>
     </row>
@@ -10321,7 +10000,7 @@
         </is>
       </c>
       <c r="F85" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"NK/T")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"NK/T")</f>
         <v/>
       </c>
     </row>
@@ -10332,7 +10011,7 @@
         </is>
       </c>
       <c r="F86" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"HL")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"HL")</f>
         <v/>
       </c>
     </row>
@@ -10343,7 +10022,7 @@
         </is>
       </c>
       <c r="F87" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"MM")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"MM")</f>
         <v/>
       </c>
     </row>
@@ -10354,7 +10033,7 @@
         </is>
       </c>
       <c r="F88" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"WM")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"WM")</f>
         <v/>
       </c>
     </row>
@@ -10365,7 +10044,7 @@
         </is>
       </c>
       <c r="F89" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"AL amyloidosis")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"AL amyloidosis")</f>
         <v/>
       </c>
     </row>
@@ -10376,7 +10055,7 @@
         </is>
       </c>
       <c r="F90" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"AA")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"AA")</f>
         <v/>
       </c>
     </row>
@@ -10387,7 +10066,7 @@
         </is>
       </c>
       <c r="F91" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"PNH")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"PNH")</f>
         <v/>
       </c>
     </row>
@@ -10398,7 +10077,7 @@
         </is>
       </c>
       <c r="F92" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"ITP")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"ITP")</f>
         <v/>
       </c>
     </row>
@@ -10409,7 +10088,7 @@
         </is>
       </c>
       <c r="F93" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"TTP")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"TTP")</f>
         <v/>
       </c>
     </row>
@@ -10420,7 +10099,7 @@
         </is>
       </c>
       <c r="F94" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"HUS")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"HUS")</f>
         <v/>
       </c>
     </row>
@@ -10431,7 +10110,7 @@
         </is>
       </c>
       <c r="F95" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"DIC")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"DIC")</f>
         <v/>
       </c>
     </row>
@@ -10442,7 +10121,7 @@
         </is>
       </c>
       <c r="F96" s="42">
-        <f>COUNTIF('初診外来'!H3:H102,"HLH")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"HLH")</f>
         <v/>
       </c>
     </row>
@@ -10453,7 +10132,7 @@
         </is>
       </c>
       <c r="F97" s="43">
-        <f>COUNTIF('初診外来'!H3:H102,"その他")</f>
+        <f>COUNTIF('初診外来'!G3:G102,"その他")</f>
         <v/>
       </c>
     </row>

--- a/hematology_case_tracker.xlsx
+++ b/hematology_case_tracker.xlsx
@@ -318,11 +318,11 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1101,7 +1101,7 @@
       <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
@@ -1124,7 +1124,7 @@
       <c r="A4" s="12" t="n"/>
       <c r="B4" s="13" t="n"/>
       <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
+      <c r="D4" s="14" t="n"/>
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
@@ -1147,7 +1147,7 @@
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
@@ -1170,7 +1170,7 @@
       <c r="A6" s="12" t="n"/>
       <c r="B6" s="13" t="n"/>
       <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
+      <c r="D6" s="14" t="n"/>
       <c r="E6" s="14" t="n"/>
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="14" t="n"/>
@@ -1193,7 +1193,7 @@
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
@@ -1216,7 +1216,7 @@
       <c r="A8" s="12" t="n"/>
       <c r="B8" s="13" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
+      <c r="D8" s="14" t="n"/>
       <c r="E8" s="14" t="n"/>
       <c r="F8" s="14" t="n"/>
       <c r="G8" s="14" t="n"/>
@@ -1239,7 +1239,7 @@
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
@@ -1262,7 +1262,7 @@
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="13" t="n"/>
       <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
+      <c r="D10" s="14" t="n"/>
       <c r="E10" s="14" t="n"/>
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
@@ -1285,7 +1285,7 @@
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
@@ -1308,7 +1308,7 @@
       <c r="A12" s="12" t="n"/>
       <c r="B12" s="13" t="n"/>
       <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
+      <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="14" t="n"/>
@@ -1331,7 +1331,7 @@
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
@@ -1354,7 +1354,7 @@
       <c r="A14" s="12" t="n"/>
       <c r="B14" s="13" t="n"/>
       <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
+      <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="14" t="n"/>
@@ -1377,7 +1377,7 @@
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
@@ -1400,7 +1400,7 @@
       <c r="A16" s="12" t="n"/>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
+      <c r="D16" s="14" t="n"/>
       <c r="E16" s="14" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14" t="n"/>
@@ -1423,7 +1423,7 @@
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
@@ -1446,7 +1446,7 @@
       <c r="A18" s="12" t="n"/>
       <c r="B18" s="13" t="n"/>
       <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14" t="n"/>
@@ -1469,7 +1469,7 @@
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
@@ -1492,7 +1492,7 @@
       <c r="A20" s="12" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
+      <c r="D20" s="14" t="n"/>
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14" t="n"/>
@@ -1515,7 +1515,7 @@
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
@@ -1538,7 +1538,7 @@
       <c r="A22" s="12" t="n"/>
       <c r="B22" s="13" t="n"/>
       <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
+      <c r="D22" s="14" t="n"/>
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="14" t="n"/>
@@ -1561,7 +1561,7 @@
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
@@ -1584,7 +1584,7 @@
       <c r="A24" s="12" t="n"/>
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
+      <c r="D24" s="14" t="n"/>
       <c r="E24" s="14" t="n"/>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14" t="n"/>
@@ -1607,7 +1607,7 @@
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
@@ -1630,7 +1630,7 @@
       <c r="A26" s="12" t="n"/>
       <c r="B26" s="13" t="n"/>
       <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
       <c r="E26" s="14" t="n"/>
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="14" t="n"/>
@@ -1653,7 +1653,7 @@
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
@@ -1676,7 +1676,7 @@
       <c r="A28" s="12" t="n"/>
       <c r="B28" s="13" t="n"/>
       <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
+      <c r="D28" s="14" t="n"/>
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14" t="n"/>
@@ -1699,7 +1699,7 @@
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
@@ -1722,7 +1722,7 @@
       <c r="A30" s="12" t="n"/>
       <c r="B30" s="13" t="n"/>
       <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
+      <c r="D30" s="14" t="n"/>
       <c r="E30" s="14" t="n"/>
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="14" t="n"/>
@@ -1745,7 +1745,7 @@
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
@@ -1768,7 +1768,7 @@
       <c r="A32" s="12" t="n"/>
       <c r="B32" s="13" t="n"/>
       <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
+      <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
@@ -1791,7 +1791,7 @@
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -1814,7 +1814,7 @@
       <c r="A34" s="12" t="n"/>
       <c r="B34" s="13" t="n"/>
       <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
+      <c r="D34" s="14" t="n"/>
       <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14" t="n"/>
@@ -1837,7 +1837,7 @@
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -1860,7 +1860,7 @@
       <c r="A36" s="12" t="n"/>
       <c r="B36" s="13" t="n"/>
       <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
+      <c r="D36" s="14" t="n"/>
       <c r="E36" s="14" t="n"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14" t="n"/>
@@ -1883,7 +1883,7 @@
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -1906,7 +1906,7 @@
       <c r="A38" s="12" t="n"/>
       <c r="B38" s="13" t="n"/>
       <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
+      <c r="D38" s="14" t="n"/>
       <c r="E38" s="14" t="n"/>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="14" t="n"/>
@@ -1929,7 +1929,7 @@
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="A40" s="12" t="n"/>
       <c r="B40" s="13" t="n"/>
       <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
+      <c r="D40" s="14" t="n"/>
       <c r="E40" s="14" t="n"/>
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="14" t="n"/>
@@ -1975,7 +1975,7 @@
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
       <c r="E41" s="10" t="n"/>
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
@@ -1998,7 +1998,7 @@
       <c r="A42" s="12" t="n"/>
       <c r="B42" s="13" t="n"/>
       <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
+      <c r="D42" s="14" t="n"/>
       <c r="E42" s="14" t="n"/>
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="14" t="n"/>
@@ -2021,7 +2021,7 @@
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
       <c r="E43" s="10" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
@@ -2044,7 +2044,7 @@
       <c r="A44" s="12" t="n"/>
       <c r="B44" s="13" t="n"/>
       <c r="C44" s="13" t="n"/>
-      <c r="D44" s="13" t="n"/>
+      <c r="D44" s="14" t="n"/>
       <c r="E44" s="14" t="n"/>
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
@@ -2067,7 +2067,7 @@
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="10" t="n"/>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
@@ -2090,7 +2090,7 @@
       <c r="A46" s="12" t="n"/>
       <c r="B46" s="13" t="n"/>
       <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
+      <c r="D46" s="14" t="n"/>
       <c r="E46" s="14" t="n"/>
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="14" t="n"/>
@@ -2113,7 +2113,7 @@
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="10" t="n"/>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
@@ -2136,7 +2136,7 @@
       <c r="A48" s="12" t="n"/>
       <c r="B48" s="13" t="n"/>
       <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
+      <c r="D48" s="14" t="n"/>
       <c r="E48" s="14" t="n"/>
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14" t="n"/>
@@ -2159,7 +2159,7 @@
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
+      <c r="D49" s="10" t="n"/>
       <c r="E49" s="10" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
@@ -2182,7 +2182,7 @@
       <c r="A50" s="12" t="n"/>
       <c r="B50" s="13" t="n"/>
       <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
+      <c r="D50" s="14" t="n"/>
       <c r="E50" s="14" t="n"/>
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14" t="n"/>
@@ -2205,7 +2205,7 @@
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -2228,7 +2228,7 @@
       <c r="A52" s="12" t="n"/>
       <c r="B52" s="13" t="n"/>
       <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="n"/>
+      <c r="D52" s="14" t="n"/>
       <c r="E52" s="14" t="n"/>
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14" t="n"/>
@@ -2251,7 +2251,7 @@
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
+      <c r="D53" s="10" t="n"/>
       <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
@@ -2274,7 +2274,7 @@
       <c r="A54" s="12" t="n"/>
       <c r="B54" s="13" t="n"/>
       <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="n"/>
+      <c r="D54" s="14" t="n"/>
       <c r="E54" s="14" t="n"/>
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="14" t="n"/>
@@ -2297,7 +2297,7 @@
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
+      <c r="D55" s="10" t="n"/>
       <c r="E55" s="10" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
@@ -2320,7 +2320,7 @@
       <c r="A56" s="12" t="n"/>
       <c r="B56" s="13" t="n"/>
       <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
+      <c r="D56" s="14" t="n"/>
       <c r="E56" s="14" t="n"/>
       <c r="F56" s="14" t="n"/>
       <c r="G56" s="14" t="n"/>
@@ -2343,7 +2343,7 @@
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
+      <c r="D57" s="10" t="n"/>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -2366,7 +2366,7 @@
       <c r="A58" s="12" t="n"/>
       <c r="B58" s="13" t="n"/>
       <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
+      <c r="D58" s="14" t="n"/>
       <c r="E58" s="14" t="n"/>
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="14" t="n"/>
@@ -2389,7 +2389,7 @@
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
+      <c r="D59" s="10" t="n"/>
       <c r="E59" s="10" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
@@ -2412,7 +2412,7 @@
       <c r="A60" s="12" t="n"/>
       <c r="B60" s="13" t="n"/>
       <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
+      <c r="D60" s="14" t="n"/>
       <c r="E60" s="14" t="n"/>
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="14" t="n"/>
@@ -2435,7 +2435,7 @@
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
+      <c r="D61" s="10" t="n"/>
       <c r="E61" s="10" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
@@ -2458,7 +2458,7 @@
       <c r="A62" s="12" t="n"/>
       <c r="B62" s="13" t="n"/>
       <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
+      <c r="D62" s="14" t="n"/>
       <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="14" t="n"/>
@@ -2481,7 +2481,7 @@
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
+      <c r="D63" s="10" t="n"/>
       <c r="E63" s="10" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
@@ -2504,7 +2504,7 @@
       <c r="A64" s="12" t="n"/>
       <c r="B64" s="13" t="n"/>
       <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
+      <c r="D64" s="14" t="n"/>
       <c r="E64" s="14" t="n"/>
       <c r="F64" s="14" t="n"/>
       <c r="G64" s="14" t="n"/>
@@ -2527,7 +2527,7 @@
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
+      <c r="D65" s="10" t="n"/>
       <c r="E65" s="10" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
@@ -2550,7 +2550,7 @@
       <c r="A66" s="12" t="n"/>
       <c r="B66" s="13" t="n"/>
       <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="n"/>
+      <c r="D66" s="14" t="n"/>
       <c r="E66" s="14" t="n"/>
       <c r="F66" s="14" t="n"/>
       <c r="G66" s="14" t="n"/>
@@ -2573,7 +2573,7 @@
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
+      <c r="D67" s="10" t="n"/>
       <c r="E67" s="10" t="n"/>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
@@ -2596,7 +2596,7 @@
       <c r="A68" s="12" t="n"/>
       <c r="B68" s="13" t="n"/>
       <c r="C68" s="13" t="n"/>
-      <c r="D68" s="13" t="n"/>
+      <c r="D68" s="14" t="n"/>
       <c r="E68" s="14" t="n"/>
       <c r="F68" s="14" t="n"/>
       <c r="G68" s="14" t="n"/>
@@ -2619,7 +2619,7 @@
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
+      <c r="D69" s="10" t="n"/>
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="A70" s="12" t="n"/>
       <c r="B70" s="13" t="n"/>
       <c r="C70" s="13" t="n"/>
-      <c r="D70" s="13" t="n"/>
+      <c r="D70" s="14" t="n"/>
       <c r="E70" s="14" t="n"/>
       <c r="F70" s="14" t="n"/>
       <c r="G70" s="14" t="n"/>
@@ -2665,7 +2665,7 @@
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
+      <c r="D71" s="10" t="n"/>
       <c r="E71" s="10" t="n"/>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
@@ -2688,7 +2688,7 @@
       <c r="A72" s="12" t="n"/>
       <c r="B72" s="13" t="n"/>
       <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="n"/>
+      <c r="D72" s="14" t="n"/>
       <c r="E72" s="14" t="n"/>
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="14" t="n"/>
@@ -2711,7 +2711,7 @@
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
+      <c r="D73" s="10" t="n"/>
       <c r="E73" s="10" t="n"/>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
@@ -2734,7 +2734,7 @@
       <c r="A74" s="12" t="n"/>
       <c r="B74" s="13" t="n"/>
       <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
+      <c r="D74" s="14" t="n"/>
       <c r="E74" s="14" t="n"/>
       <c r="F74" s="14" t="n"/>
       <c r="G74" s="14" t="n"/>
@@ -2757,7 +2757,7 @@
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
+      <c r="D75" s="10" t="n"/>
       <c r="E75" s="10" t="n"/>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
@@ -2780,7 +2780,7 @@
       <c r="A76" s="12" t="n"/>
       <c r="B76" s="13" t="n"/>
       <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
+      <c r="D76" s="14" t="n"/>
       <c r="E76" s="14" t="n"/>
       <c r="F76" s="14" t="n"/>
       <c r="G76" s="14" t="n"/>
@@ -2803,7 +2803,7 @@
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
+      <c r="D77" s="10" t="n"/>
       <c r="E77" s="10" t="n"/>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
@@ -2826,7 +2826,7 @@
       <c r="A78" s="12" t="n"/>
       <c r="B78" s="13" t="n"/>
       <c r="C78" s="13" t="n"/>
-      <c r="D78" s="13" t="n"/>
+      <c r="D78" s="14" t="n"/>
       <c r="E78" s="14" t="n"/>
       <c r="F78" s="14" t="n"/>
       <c r="G78" s="14" t="n"/>
@@ -2849,7 +2849,7 @@
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="9" t="n"/>
-      <c r="D79" s="9" t="n"/>
+      <c r="D79" s="10" t="n"/>
       <c r="E79" s="10" t="n"/>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
@@ -2872,7 +2872,7 @@
       <c r="A80" s="12" t="n"/>
       <c r="B80" s="13" t="n"/>
       <c r="C80" s="13" t="n"/>
-      <c r="D80" s="13" t="n"/>
+      <c r="D80" s="14" t="n"/>
       <c r="E80" s="14" t="n"/>
       <c r="F80" s="14" t="n"/>
       <c r="G80" s="14" t="n"/>
@@ -2895,7 +2895,7 @@
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
+      <c r="D81" s="10" t="n"/>
       <c r="E81" s="10" t="n"/>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
@@ -2918,7 +2918,7 @@
       <c r="A82" s="12" t="n"/>
       <c r="B82" s="13" t="n"/>
       <c r="C82" s="13" t="n"/>
-      <c r="D82" s="13" t="n"/>
+      <c r="D82" s="14" t="n"/>
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="14" t="n"/>
@@ -2941,7 +2941,7 @@
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n"/>
+      <c r="D83" s="10" t="n"/>
       <c r="E83" s="10" t="n"/>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
@@ -2964,7 +2964,7 @@
       <c r="A84" s="12" t="n"/>
       <c r="B84" s="13" t="n"/>
       <c r="C84" s="13" t="n"/>
-      <c r="D84" s="13" t="n"/>
+      <c r="D84" s="14" t="n"/>
       <c r="E84" s="14" t="n"/>
       <c r="F84" s="14" t="n"/>
       <c r="G84" s="14" t="n"/>
@@ -2987,7 +2987,7 @@
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
+      <c r="D85" s="10" t="n"/>
       <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
@@ -3010,7 +3010,7 @@
       <c r="A86" s="12" t="n"/>
       <c r="B86" s="13" t="n"/>
       <c r="C86" s="13" t="n"/>
-      <c r="D86" s="13" t="n"/>
+      <c r="D86" s="14" t="n"/>
       <c r="E86" s="14" t="n"/>
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="14" t="n"/>
@@ -3033,7 +3033,7 @@
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
+      <c r="D87" s="10" t="n"/>
       <c r="E87" s="10" t="n"/>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
@@ -3056,7 +3056,7 @@
       <c r="A88" s="12" t="n"/>
       <c r="B88" s="13" t="n"/>
       <c r="C88" s="13" t="n"/>
-      <c r="D88" s="13" t="n"/>
+      <c r="D88" s="14" t="n"/>
       <c r="E88" s="14" t="n"/>
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="14" t="n"/>
@@ -3079,7 +3079,7 @@
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
+      <c r="D89" s="10" t="n"/>
       <c r="E89" s="10" t="n"/>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
@@ -3102,7 +3102,7 @@
       <c r="A90" s="12" t="n"/>
       <c r="B90" s="13" t="n"/>
       <c r="C90" s="13" t="n"/>
-      <c r="D90" s="13" t="n"/>
+      <c r="D90" s="14" t="n"/>
       <c r="E90" s="14" t="n"/>
       <c r="F90" s="14" t="n"/>
       <c r="G90" s="14" t="n"/>
@@ -3125,7 +3125,7 @@
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
+      <c r="D91" s="10" t="n"/>
       <c r="E91" s="10" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -3148,7 +3148,7 @@
       <c r="A92" s="12" t="n"/>
       <c r="B92" s="13" t="n"/>
       <c r="C92" s="13" t="n"/>
-      <c r="D92" s="13" t="n"/>
+      <c r="D92" s="14" t="n"/>
       <c r="E92" s="14" t="n"/>
       <c r="F92" s="14" t="n"/>
       <c r="G92" s="14" t="n"/>
@@ -3171,7 +3171,7 @@
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
+      <c r="D93" s="10" t="n"/>
       <c r="E93" s="10" t="n"/>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
@@ -3194,7 +3194,7 @@
       <c r="A94" s="12" t="n"/>
       <c r="B94" s="13" t="n"/>
       <c r="C94" s="13" t="n"/>
-      <c r="D94" s="13" t="n"/>
+      <c r="D94" s="14" t="n"/>
       <c r="E94" s="14" t="n"/>
       <c r="F94" s="14" t="n"/>
       <c r="G94" s="14" t="n"/>
@@ -3217,7 +3217,7 @@
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
+      <c r="D95" s="10" t="n"/>
       <c r="E95" s="10" t="n"/>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
@@ -3240,7 +3240,7 @@
       <c r="A96" s="12" t="n"/>
       <c r="B96" s="13" t="n"/>
       <c r="C96" s="13" t="n"/>
-      <c r="D96" s="13" t="n"/>
+      <c r="D96" s="14" t="n"/>
       <c r="E96" s="14" t="n"/>
       <c r="F96" s="14" t="n"/>
       <c r="G96" s="14" t="n"/>
@@ -3263,7 +3263,7 @@
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
-      <c r="D97" s="9" t="n"/>
+      <c r="D97" s="10" t="n"/>
       <c r="E97" s="10" t="n"/>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
@@ -3286,7 +3286,7 @@
       <c r="A98" s="12" t="n"/>
       <c r="B98" s="13" t="n"/>
       <c r="C98" s="13" t="n"/>
-      <c r="D98" s="13" t="n"/>
+      <c r="D98" s="14" t="n"/>
       <c r="E98" s="14" t="n"/>
       <c r="F98" s="14" t="n"/>
       <c r="G98" s="14" t="n"/>
@@ -3309,7 +3309,7 @@
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
+      <c r="D99" s="10" t="n"/>
       <c r="E99" s="10" t="n"/>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
@@ -3332,7 +3332,7 @@
       <c r="A100" s="12" t="n"/>
       <c r="B100" s="13" t="n"/>
       <c r="C100" s="13" t="n"/>
-      <c r="D100" s="13" t="n"/>
+      <c r="D100" s="14" t="n"/>
       <c r="E100" s="14" t="n"/>
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="14" t="n"/>
@@ -3355,7 +3355,7 @@
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
-      <c r="D101" s="9" t="n"/>
+      <c r="D101" s="10" t="n"/>
       <c r="E101" s="10" t="n"/>
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
@@ -3378,7 +3378,7 @@
       <c r="A102" s="12" t="n"/>
       <c r="B102" s="13" t="n"/>
       <c r="C102" s="13" t="n"/>
-      <c r="D102" s="13" t="n"/>
+      <c r="D102" s="14" t="n"/>
       <c r="E102" s="14" t="n"/>
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="14" t="n"/>
@@ -4898,7 +4898,7 @@
       <c r="A3" s="8" t="n"/>
       <c r="B3" s="9" t="n"/>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="11" t="n"/>
       <c r="F3" s="10" t="n"/>
       <c r="G3" s="10" t="n"/>
@@ -4912,21 +4912,21 @@
       <c r="A4" s="23" t="n"/>
       <c r="B4" s="24" t="n"/>
       <c r="C4" s="24" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
-      <c r="H4" s="26" t="n"/>
-      <c r="I4" s="26" t="n"/>
-      <c r="J4" s="26" t="n"/>
-      <c r="K4" s="26" t="n"/>
-      <c r="L4" s="26" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
@@ -4940,21 +4940,21 @@
       <c r="A6" s="23" t="n"/>
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
-      <c r="H6" s="26" t="n"/>
-      <c r="I6" s="26" t="n"/>
-      <c r="J6" s="26" t="n"/>
-      <c r="K6" s="26" t="n"/>
-      <c r="L6" s="26" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+      <c r="H6" s="25" t="n"/>
+      <c r="I6" s="25" t="n"/>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="25" t="n"/>
+      <c r="L6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
@@ -4968,21 +4968,21 @@
       <c r="A8" s="23" t="n"/>
       <c r="B8" s="24" t="n"/>
       <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="26" t="n"/>
-      <c r="L8" s="26" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="25" t="n"/>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="25" t="n"/>
+      <c r="L8" s="25" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
@@ -4996,21 +4996,21 @@
       <c r="A10" s="23" t="n"/>
       <c r="B10" s="24" t="n"/>
       <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="26" t="n"/>
-      <c r="L10" s="26" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="25" t="n"/>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="25" t="n"/>
+      <c r="L10" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
@@ -5024,21 +5024,21 @@
       <c r="A12" s="23" t="n"/>
       <c r="B12" s="24" t="n"/>
       <c r="C12" s="24" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="26" t="n"/>
-      <c r="L12" s="26" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="26" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="25" t="n"/>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="25" t="n"/>
+      <c r="L12" s="25" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
@@ -5052,21 +5052,21 @@
       <c r="A14" s="23" t="n"/>
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="24" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="25" t="n"/>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="25" t="n"/>
+      <c r="L14" s="25" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n"/>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
@@ -5080,21 +5080,21 @@
       <c r="A16" s="23" t="n"/>
       <c r="B16" s="24" t="n"/>
       <c r="C16" s="24" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="26" t="n"/>
-      <c r="L16" s="26" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="25" t="n"/>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="25" t="n"/>
+      <c r="L16" s="25" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
@@ -5108,21 +5108,21 @@
       <c r="A18" s="23" t="n"/>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="24" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="26" t="n"/>
-      <c r="K18" s="26" t="n"/>
-      <c r="L18" s="26" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="25" t="n"/>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="25" t="n"/>
+      <c r="L18" s="25" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n"/>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
@@ -5136,21 +5136,21 @@
       <c r="A20" s="23" t="n"/>
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="24" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="26" t="n"/>
-      <c r="I20" s="26" t="n"/>
-      <c r="J20" s="26" t="n"/>
-      <c r="K20" s="26" t="n"/>
-      <c r="L20" s="26" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="25" t="n"/>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="25" t="n"/>
+      <c r="L20" s="25" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n"/>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
@@ -5164,21 +5164,21 @@
       <c r="A22" s="23" t="n"/>
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="24" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="26" t="n"/>
-      <c r="I22" s="26" t="n"/>
-      <c r="J22" s="26" t="n"/>
-      <c r="K22" s="26" t="n"/>
-      <c r="L22" s="26" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="25" t="n"/>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="25" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n"/>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
@@ -5192,21 +5192,21 @@
       <c r="A24" s="23" t="n"/>
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="24" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="26" t="n"/>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="26" t="n"/>
-      <c r="L24" s="26" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="25" t="n"/>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="25" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n"/>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
@@ -5220,21 +5220,21 @@
       <c r="A26" s="23" t="n"/>
       <c r="B26" s="24" t="n"/>
       <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="26" t="n"/>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="26" t="n"/>
-      <c r="L26" s="26" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="25" t="n"/>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="25" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n"/>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
@@ -5248,21 +5248,21 @@
       <c r="A28" s="23" t="n"/>
       <c r="B28" s="24" t="n"/>
       <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="26" t="n"/>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="26" t="n"/>
-      <c r="L28" s="26" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="25" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n"/>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
@@ -5276,21 +5276,21 @@
       <c r="A30" s="23" t="n"/>
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="26" t="n"/>
-      <c r="I30" s="26" t="n"/>
-      <c r="J30" s="26" t="n"/>
-      <c r="K30" s="26" t="n"/>
-      <c r="L30" s="26" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n"/>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
@@ -5304,21 +5304,21 @@
       <c r="A32" s="23" t="n"/>
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="26" t="n"/>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="26" t="n"/>
-      <c r="L32" s="26" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="25" t="n"/>
+      <c r="G32" s="25" t="n"/>
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="25" t="n"/>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="25" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n"/>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -5332,21 +5332,21 @@
       <c r="A34" s="23" t="n"/>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="24" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="26" t="n"/>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="26" t="n"/>
-      <c r="L34" s="26" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="25" t="n"/>
+      <c r="G34" s="25" t="n"/>
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="25" t="n"/>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="25" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n"/>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -5360,21 +5360,21 @@
       <c r="A36" s="23" t="n"/>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="26" t="n"/>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="26" t="n"/>
-      <c r="L36" s="26" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="26" t="n"/>
+      <c r="F36" s="25" t="n"/>
+      <c r="G36" s="25" t="n"/>
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="25" t="n"/>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="25" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -5388,21 +5388,21 @@
       <c r="A38" s="23" t="n"/>
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="24" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="n"/>
-      <c r="I38" s="26" t="n"/>
-      <c r="J38" s="26" t="n"/>
-      <c r="K38" s="26" t="n"/>
-      <c r="L38" s="26" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="26" t="n"/>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="n"/>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -5416,21 +5416,21 @@
       <c r="A40" s="23" t="n"/>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="K40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="25" t="n"/>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="25" t="n"/>
+      <c r="L40" s="25" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
@@ -5444,21 +5444,21 @@
       <c r="A42" s="23" t="n"/>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="24" t="n"/>
-      <c r="D42" s="24" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
-      <c r="I42" s="26" t="n"/>
-      <c r="J42" s="26" t="n"/>
-      <c r="K42" s="26" t="n"/>
-      <c r="L42" s="26" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="25" t="n"/>
+      <c r="G42" s="25" t="n"/>
+      <c r="H42" s="25" t="n"/>
+      <c r="I42" s="25" t="n"/>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="25" t="n"/>
+      <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
@@ -5472,21 +5472,21 @@
       <c r="A44" s="23" t="n"/>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="24" t="n"/>
-      <c r="D44" s="24" t="n"/>
-      <c r="E44" s="25" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="n"/>
-      <c r="H44" s="26" t="n"/>
-      <c r="I44" s="26" t="n"/>
-      <c r="J44" s="26" t="n"/>
-      <c r="K44" s="26" t="n"/>
-      <c r="L44" s="26" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="26" t="n"/>
+      <c r="F44" s="25" t="n"/>
+      <c r="G44" s="25" t="n"/>
+      <c r="H44" s="25" t="n"/>
+      <c r="I44" s="25" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="10" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
@@ -5500,21 +5500,21 @@
       <c r="A46" s="23" t="n"/>
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="24" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="n"/>
-      <c r="I46" s="26" t="n"/>
-      <c r="J46" s="26" t="n"/>
-      <c r="K46" s="26" t="n"/>
-      <c r="L46" s="26" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="25" t="n"/>
+      <c r="G46" s="25" t="n"/>
+      <c r="H46" s="25" t="n"/>
+      <c r="I46" s="25" t="n"/>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="25" t="n"/>
+      <c r="L46" s="25" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="10" t="n"/>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
@@ -5528,21 +5528,21 @@
       <c r="A48" s="23" t="n"/>
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="24" t="n"/>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="26" t="n"/>
-      <c r="G48" s="26" t="n"/>
-      <c r="H48" s="26" t="n"/>
-      <c r="I48" s="26" t="n"/>
-      <c r="J48" s="26" t="n"/>
-      <c r="K48" s="26" t="n"/>
-      <c r="L48" s="26" t="n"/>
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="26" t="n"/>
+      <c r="F48" s="25" t="n"/>
+      <c r="G48" s="25" t="n"/>
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="25" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
+      <c r="D49" s="10" t="n"/>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
@@ -5556,21 +5556,21 @@
       <c r="A50" s="23" t="n"/>
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="24" t="n"/>
-      <c r="D50" s="24" t="n"/>
-      <c r="E50" s="25" t="n"/>
-      <c r="F50" s="26" t="n"/>
-      <c r="G50" s="26" t="n"/>
-      <c r="H50" s="26" t="n"/>
-      <c r="I50" s="26" t="n"/>
-      <c r="J50" s="26" t="n"/>
-      <c r="K50" s="26" t="n"/>
-      <c r="L50" s="26" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="26" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -5584,21 +5584,21 @@
       <c r="A52" s="23" t="n"/>
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="24" t="n"/>
-      <c r="D52" s="24" t="n"/>
-      <c r="E52" s="25" t="n"/>
-      <c r="F52" s="26" t="n"/>
-      <c r="G52" s="26" t="n"/>
-      <c r="H52" s="26" t="n"/>
-      <c r="I52" s="26" t="n"/>
-      <c r="J52" s="26" t="n"/>
-      <c r="K52" s="26" t="n"/>
-      <c r="L52" s="26" t="n"/>
+      <c r="D52" s="25" t="n"/>
+      <c r="E52" s="26" t="n"/>
+      <c r="F52" s="25" t="n"/>
+      <c r="G52" s="25" t="n"/>
+      <c r="H52" s="25" t="n"/>
+      <c r="I52" s="25" t="n"/>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="25" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
+      <c r="D53" s="10" t="n"/>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
@@ -5612,21 +5612,21 @@
       <c r="A54" s="23" t="n"/>
       <c r="B54" s="24" t="n"/>
       <c r="C54" s="24" t="n"/>
-      <c r="D54" s="24" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="26" t="n"/>
-      <c r="G54" s="26" t="n"/>
-      <c r="H54" s="26" t="n"/>
-      <c r="I54" s="26" t="n"/>
-      <c r="J54" s="26" t="n"/>
-      <c r="K54" s="26" t="n"/>
-      <c r="L54" s="26" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="25" t="n"/>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
       <c r="B55" s="9" t="n"/>
       <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
+      <c r="D55" s="10" t="n"/>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
@@ -5640,21 +5640,21 @@
       <c r="A56" s="23" t="n"/>
       <c r="B56" s="24" t="n"/>
       <c r="C56" s="24" t="n"/>
-      <c r="D56" s="24" t="n"/>
-      <c r="E56" s="25" t="n"/>
-      <c r="F56" s="26" t="n"/>
-      <c r="G56" s="26" t="n"/>
-      <c r="H56" s="26" t="n"/>
-      <c r="I56" s="26" t="n"/>
-      <c r="J56" s="26" t="n"/>
-      <c r="K56" s="26" t="n"/>
-      <c r="L56" s="26" t="n"/>
+      <c r="D56" s="25" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="25" t="n"/>
+      <c r="G56" s="25" t="n"/>
+      <c r="H56" s="25" t="n"/>
+      <c r="I56" s="25" t="n"/>
+      <c r="J56" s="25" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="25" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
       <c r="B57" s="9" t="n"/>
       <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
+      <c r="D57" s="10" t="n"/>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -5668,21 +5668,21 @@
       <c r="A58" s="23" t="n"/>
       <c r="B58" s="24" t="n"/>
       <c r="C58" s="24" t="n"/>
-      <c r="D58" s="24" t="n"/>
-      <c r="E58" s="25" t="n"/>
-      <c r="F58" s="26" t="n"/>
-      <c r="G58" s="26" t="n"/>
-      <c r="H58" s="26" t="n"/>
-      <c r="I58" s="26" t="n"/>
-      <c r="J58" s="26" t="n"/>
-      <c r="K58" s="26" t="n"/>
-      <c r="L58" s="26" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="26" t="n"/>
+      <c r="F58" s="25" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="25" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="25" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
       <c r="B59" s="9" t="n"/>
       <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
+      <c r="D59" s="10" t="n"/>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
@@ -5696,21 +5696,21 @@
       <c r="A60" s="23" t="n"/>
       <c r="B60" s="24" t="n"/>
       <c r="C60" s="24" t="n"/>
-      <c r="D60" s="24" t="n"/>
-      <c r="E60" s="25" t="n"/>
-      <c r="F60" s="26" t="n"/>
-      <c r="G60" s="26" t="n"/>
-      <c r="H60" s="26" t="n"/>
-      <c r="I60" s="26" t="n"/>
-      <c r="J60" s="26" t="n"/>
-      <c r="K60" s="26" t="n"/>
-      <c r="L60" s="26" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="25" t="n"/>
+      <c r="G60" s="25" t="n"/>
+      <c r="H60" s="25" t="n"/>
+      <c r="I60" s="25" t="n"/>
+      <c r="J60" s="25" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="25" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
       <c r="B61" s="9" t="n"/>
       <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
+      <c r="D61" s="10" t="n"/>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
@@ -5724,21 +5724,21 @@
       <c r="A62" s="23" t="n"/>
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="24" t="n"/>
-      <c r="D62" s="24" t="n"/>
-      <c r="E62" s="25" t="n"/>
-      <c r="F62" s="26" t="n"/>
-      <c r="G62" s="26" t="n"/>
-      <c r="H62" s="26" t="n"/>
-      <c r="I62" s="26" t="n"/>
-      <c r="J62" s="26" t="n"/>
-      <c r="K62" s="26" t="n"/>
-      <c r="L62" s="26" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="25" t="n"/>
+      <c r="G62" s="25" t="n"/>
+      <c r="H62" s="25" t="n"/>
+      <c r="I62" s="25" t="n"/>
+      <c r="J62" s="25" t="n"/>
+      <c r="K62" s="25" t="n"/>
+      <c r="L62" s="25" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
       <c r="B63" s="9" t="n"/>
       <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
+      <c r="D63" s="10" t="n"/>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
@@ -5752,21 +5752,21 @@
       <c r="A64" s="23" t="n"/>
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="24" t="n"/>
-      <c r="D64" s="24" t="n"/>
-      <c r="E64" s="25" t="n"/>
-      <c r="F64" s="26" t="n"/>
-      <c r="G64" s="26" t="n"/>
-      <c r="H64" s="26" t="n"/>
-      <c r="I64" s="26" t="n"/>
-      <c r="J64" s="26" t="n"/>
-      <c r="K64" s="26" t="n"/>
-      <c r="L64" s="26" t="n"/>
+      <c r="D64" s="25" t="n"/>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="25" t="n"/>
+      <c r="G64" s="25" t="n"/>
+      <c r="H64" s="25" t="n"/>
+      <c r="I64" s="25" t="n"/>
+      <c r="J64" s="25" t="n"/>
+      <c r="K64" s="25" t="n"/>
+      <c r="L64" s="25" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
       <c r="B65" s="9" t="n"/>
       <c r="C65" s="9" t="n"/>
-      <c r="D65" s="9" t="n"/>
+      <c r="D65" s="10" t="n"/>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
@@ -5780,21 +5780,21 @@
       <c r="A66" s="23" t="n"/>
       <c r="B66" s="24" t="n"/>
       <c r="C66" s="24" t="n"/>
-      <c r="D66" s="24" t="n"/>
-      <c r="E66" s="25" t="n"/>
-      <c r="F66" s="26" t="n"/>
-      <c r="G66" s="26" t="n"/>
-      <c r="H66" s="26" t="n"/>
-      <c r="I66" s="26" t="n"/>
-      <c r="J66" s="26" t="n"/>
-      <c r="K66" s="26" t="n"/>
-      <c r="L66" s="26" t="n"/>
+      <c r="D66" s="25" t="n"/>
+      <c r="E66" s="26" t="n"/>
+      <c r="F66" s="25" t="n"/>
+      <c r="G66" s="25" t="n"/>
+      <c r="H66" s="25" t="n"/>
+      <c r="I66" s="25" t="n"/>
+      <c r="J66" s="25" t="n"/>
+      <c r="K66" s="25" t="n"/>
+      <c r="L66" s="25" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
       <c r="B67" s="9" t="n"/>
       <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
+      <c r="D67" s="10" t="n"/>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
@@ -5808,21 +5808,21 @@
       <c r="A68" s="23" t="n"/>
       <c r="B68" s="24" t="n"/>
       <c r="C68" s="24" t="n"/>
-      <c r="D68" s="24" t="n"/>
-      <c r="E68" s="25" t="n"/>
-      <c r="F68" s="26" t="n"/>
-      <c r="G68" s="26" t="n"/>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26" t="n"/>
-      <c r="J68" s="26" t="n"/>
-      <c r="K68" s="26" t="n"/>
-      <c r="L68" s="26" t="n"/>
+      <c r="D68" s="25" t="n"/>
+      <c r="E68" s="26" t="n"/>
+      <c r="F68" s="25" t="n"/>
+      <c r="G68" s="25" t="n"/>
+      <c r="H68" s="25" t="n"/>
+      <c r="I68" s="25" t="n"/>
+      <c r="J68" s="25" t="n"/>
+      <c r="K68" s="25" t="n"/>
+      <c r="L68" s="25" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
       <c r="B69" s="9" t="n"/>
       <c r="C69" s="9" t="n"/>
-      <c r="D69" s="9" t="n"/>
+      <c r="D69" s="10" t="n"/>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
@@ -5836,21 +5836,21 @@
       <c r="A70" s="23" t="n"/>
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="24" t="n"/>
-      <c r="D70" s="24" t="n"/>
-      <c r="E70" s="25" t="n"/>
-      <c r="F70" s="26" t="n"/>
-      <c r="G70" s="26" t="n"/>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26" t="n"/>
-      <c r="J70" s="26" t="n"/>
-      <c r="K70" s="26" t="n"/>
-      <c r="L70" s="26" t="n"/>
+      <c r="D70" s="25" t="n"/>
+      <c r="E70" s="26" t="n"/>
+      <c r="F70" s="25" t="n"/>
+      <c r="G70" s="25" t="n"/>
+      <c r="H70" s="25" t="n"/>
+      <c r="I70" s="25" t="n"/>
+      <c r="J70" s="25" t="n"/>
+      <c r="K70" s="25" t="n"/>
+      <c r="L70" s="25" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
       <c r="B71" s="9" t="n"/>
       <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
+      <c r="D71" s="10" t="n"/>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
@@ -5864,21 +5864,21 @@
       <c r="A72" s="23" t="n"/>
       <c r="B72" s="24" t="n"/>
       <c r="C72" s="24" t="n"/>
-      <c r="D72" s="24" t="n"/>
-      <c r="E72" s="25" t="n"/>
-      <c r="F72" s="26" t="n"/>
-      <c r="G72" s="26" t="n"/>
-      <c r="H72" s="26" t="n"/>
-      <c r="I72" s="26" t="n"/>
-      <c r="J72" s="26" t="n"/>
-      <c r="K72" s="26" t="n"/>
-      <c r="L72" s="26" t="n"/>
+      <c r="D72" s="25" t="n"/>
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="25" t="n"/>
+      <c r="G72" s="25" t="n"/>
+      <c r="H72" s="25" t="n"/>
+      <c r="I72" s="25" t="n"/>
+      <c r="J72" s="25" t="n"/>
+      <c r="K72" s="25" t="n"/>
+      <c r="L72" s="25" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
       <c r="B73" s="9" t="n"/>
       <c r="C73" s="9" t="n"/>
-      <c r="D73" s="9" t="n"/>
+      <c r="D73" s="10" t="n"/>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
@@ -5892,21 +5892,21 @@
       <c r="A74" s="23" t="n"/>
       <c r="B74" s="24" t="n"/>
       <c r="C74" s="24" t="n"/>
-      <c r="D74" s="24" t="n"/>
-      <c r="E74" s="25" t="n"/>
-      <c r="F74" s="26" t="n"/>
-      <c r="G74" s="26" t="n"/>
-      <c r="H74" s="26" t="n"/>
-      <c r="I74" s="26" t="n"/>
-      <c r="J74" s="26" t="n"/>
-      <c r="K74" s="26" t="n"/>
-      <c r="L74" s="26" t="n"/>
+      <c r="D74" s="25" t="n"/>
+      <c r="E74" s="26" t="n"/>
+      <c r="F74" s="25" t="n"/>
+      <c r="G74" s="25" t="n"/>
+      <c r="H74" s="25" t="n"/>
+      <c r="I74" s="25" t="n"/>
+      <c r="J74" s="25" t="n"/>
+      <c r="K74" s="25" t="n"/>
+      <c r="L74" s="25" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
       <c r="B75" s="9" t="n"/>
       <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
+      <c r="D75" s="10" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
@@ -5920,21 +5920,21 @@
       <c r="A76" s="23" t="n"/>
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="24" t="n"/>
-      <c r="D76" s="24" t="n"/>
-      <c r="E76" s="25" t="n"/>
-      <c r="F76" s="26" t="n"/>
-      <c r="G76" s="26" t="n"/>
-      <c r="H76" s="26" t="n"/>
-      <c r="I76" s="26" t="n"/>
-      <c r="J76" s="26" t="n"/>
-      <c r="K76" s="26" t="n"/>
-      <c r="L76" s="26" t="n"/>
+      <c r="D76" s="25" t="n"/>
+      <c r="E76" s="26" t="n"/>
+      <c r="F76" s="25" t="n"/>
+      <c r="G76" s="25" t="n"/>
+      <c r="H76" s="25" t="n"/>
+      <c r="I76" s="25" t="n"/>
+      <c r="J76" s="25" t="n"/>
+      <c r="K76" s="25" t="n"/>
+      <c r="L76" s="25" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
       <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
-      <c r="D77" s="9" t="n"/>
+      <c r="D77" s="10" t="n"/>
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
@@ -5948,21 +5948,21 @@
       <c r="A78" s="23" t="n"/>
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="24" t="n"/>
-      <c r="D78" s="24" t="n"/>
-      <c r="E78" s="25" t="n"/>
-      <c r="F78" s="26" t="n"/>
-      <c r="G78" s="26" t="n"/>
-      <c r="H78" s="26" t="n"/>
-      <c r="I78" s="26" t="n"/>
-      <c r="J78" s="26" t="n"/>
-      <c r="K78" s="26" t="n"/>
-      <c r="L78" s="26" t="n"/>
+      <c r="D78" s="25" t="n"/>
+      <c r="E78" s="26" t="n"/>
+      <c r="F78" s="25" t="n"/>
+      <c r="G78" s="25" t="n"/>
+      <c r="H78" s="25" t="n"/>
+      <c r="I78" s="25" t="n"/>
+      <c r="J78" s="25" t="n"/>
+      <c r="K78" s="25" t="n"/>
+      <c r="L78" s="25" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
       <c r="B79" s="9" t="n"/>
       <c r="C79" s="9" t="n"/>
-      <c r="D79" s="9" t="n"/>
+      <c r="D79" s="10" t="n"/>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
@@ -5976,21 +5976,21 @@
       <c r="A80" s="23" t="n"/>
       <c r="B80" s="24" t="n"/>
       <c r="C80" s="24" t="n"/>
-      <c r="D80" s="24" t="n"/>
-      <c r="E80" s="25" t="n"/>
-      <c r="F80" s="26" t="n"/>
-      <c r="G80" s="26" t="n"/>
-      <c r="H80" s="26" t="n"/>
-      <c r="I80" s="26" t="n"/>
-      <c r="J80" s="26" t="n"/>
-      <c r="K80" s="26" t="n"/>
-      <c r="L80" s="26" t="n"/>
+      <c r="D80" s="25" t="n"/>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="25" t="n"/>
+      <c r="G80" s="25" t="n"/>
+      <c r="H80" s="25" t="n"/>
+      <c r="I80" s="25" t="n"/>
+      <c r="J80" s="25" t="n"/>
+      <c r="K80" s="25" t="n"/>
+      <c r="L80" s="25" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="n"/>
       <c r="B81" s="9" t="n"/>
       <c r="C81" s="9" t="n"/>
-      <c r="D81" s="9" t="n"/>
+      <c r="D81" s="10" t="n"/>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
@@ -6004,21 +6004,21 @@
       <c r="A82" s="23" t="n"/>
       <c r="B82" s="24" t="n"/>
       <c r="C82" s="24" t="n"/>
-      <c r="D82" s="24" t="n"/>
-      <c r="E82" s="25" t="n"/>
-      <c r="F82" s="26" t="n"/>
-      <c r="G82" s="26" t="n"/>
-      <c r="H82" s="26" t="n"/>
-      <c r="I82" s="26" t="n"/>
-      <c r="J82" s="26" t="n"/>
-      <c r="K82" s="26" t="n"/>
-      <c r="L82" s="26" t="n"/>
+      <c r="D82" s="25" t="n"/>
+      <c r="E82" s="26" t="n"/>
+      <c r="F82" s="25" t="n"/>
+      <c r="G82" s="25" t="n"/>
+      <c r="H82" s="25" t="n"/>
+      <c r="I82" s="25" t="n"/>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="25" t="n"/>
+      <c r="L82" s="25" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="n"/>
       <c r="B83" s="9" t="n"/>
       <c r="C83" s="9" t="n"/>
-      <c r="D83" s="9" t="n"/>
+      <c r="D83" s="10" t="n"/>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
@@ -6032,21 +6032,21 @@
       <c r="A84" s="23" t="n"/>
       <c r="B84" s="24" t="n"/>
       <c r="C84" s="24" t="n"/>
-      <c r="D84" s="24" t="n"/>
-      <c r="E84" s="25" t="n"/>
-      <c r="F84" s="26" t="n"/>
-      <c r="G84" s="26" t="n"/>
-      <c r="H84" s="26" t="n"/>
-      <c r="I84" s="26" t="n"/>
-      <c r="J84" s="26" t="n"/>
-      <c r="K84" s="26" t="n"/>
-      <c r="L84" s="26" t="n"/>
+      <c r="D84" s="25" t="n"/>
+      <c r="E84" s="26" t="n"/>
+      <c r="F84" s="25" t="n"/>
+      <c r="G84" s="25" t="n"/>
+      <c r="H84" s="25" t="n"/>
+      <c r="I84" s="25" t="n"/>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="25" t="n"/>
+      <c r="L84" s="25" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="n"/>
       <c r="B85" s="9" t="n"/>
       <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
+      <c r="D85" s="10" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
@@ -6060,21 +6060,21 @@
       <c r="A86" s="23" t="n"/>
       <c r="B86" s="24" t="n"/>
       <c r="C86" s="24" t="n"/>
-      <c r="D86" s="24" t="n"/>
-      <c r="E86" s="25" t="n"/>
-      <c r="F86" s="26" t="n"/>
-      <c r="G86" s="26" t="n"/>
-      <c r="H86" s="26" t="n"/>
-      <c r="I86" s="26" t="n"/>
-      <c r="J86" s="26" t="n"/>
-      <c r="K86" s="26" t="n"/>
-      <c r="L86" s="26" t="n"/>
+      <c r="D86" s="25" t="n"/>
+      <c r="E86" s="26" t="n"/>
+      <c r="F86" s="25" t="n"/>
+      <c r="G86" s="25" t="n"/>
+      <c r="H86" s="25" t="n"/>
+      <c r="I86" s="25" t="n"/>
+      <c r="J86" s="25" t="n"/>
+      <c r="K86" s="25" t="n"/>
+      <c r="L86" s="25" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="8" t="n"/>
       <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
-      <c r="D87" s="9" t="n"/>
+      <c r="D87" s="10" t="n"/>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
@@ -6088,21 +6088,21 @@
       <c r="A88" s="23" t="n"/>
       <c r="B88" s="24" t="n"/>
       <c r="C88" s="24" t="n"/>
-      <c r="D88" s="24" t="n"/>
-      <c r="E88" s="25" t="n"/>
-      <c r="F88" s="26" t="n"/>
-      <c r="G88" s="26" t="n"/>
-      <c r="H88" s="26" t="n"/>
-      <c r="I88" s="26" t="n"/>
-      <c r="J88" s="26" t="n"/>
-      <c r="K88" s="26" t="n"/>
-      <c r="L88" s="26" t="n"/>
+      <c r="D88" s="25" t="n"/>
+      <c r="E88" s="26" t="n"/>
+      <c r="F88" s="25" t="n"/>
+      <c r="G88" s="25" t="n"/>
+      <c r="H88" s="25" t="n"/>
+      <c r="I88" s="25" t="n"/>
+      <c r="J88" s="25" t="n"/>
+      <c r="K88" s="25" t="n"/>
+      <c r="L88" s="25" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="n"/>
       <c r="B89" s="9" t="n"/>
       <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
+      <c r="D89" s="10" t="n"/>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
@@ -6116,21 +6116,21 @@
       <c r="A90" s="23" t="n"/>
       <c r="B90" s="24" t="n"/>
       <c r="C90" s="24" t="n"/>
-      <c r="D90" s="24" t="n"/>
-      <c r="E90" s="25" t="n"/>
-      <c r="F90" s="26" t="n"/>
-      <c r="G90" s="26" t="n"/>
-      <c r="H90" s="26" t="n"/>
-      <c r="I90" s="26" t="n"/>
-      <c r="J90" s="26" t="n"/>
-      <c r="K90" s="26" t="n"/>
-      <c r="L90" s="26" t="n"/>
+      <c r="D90" s="25" t="n"/>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="25" t="n"/>
+      <c r="G90" s="25" t="n"/>
+      <c r="H90" s="25" t="n"/>
+      <c r="I90" s="25" t="n"/>
+      <c r="J90" s="25" t="n"/>
+      <c r="K90" s="25" t="n"/>
+      <c r="L90" s="25" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="n"/>
       <c r="B91" s="9" t="n"/>
       <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
+      <c r="D91" s="10" t="n"/>
       <c r="E91" s="11" t="n"/>
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
@@ -6144,21 +6144,21 @@
       <c r="A92" s="23" t="n"/>
       <c r="B92" s="24" t="n"/>
       <c r="C92" s="24" t="n"/>
-      <c r="D92" s="24" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="26" t="n"/>
-      <c r="G92" s="26" t="n"/>
-      <c r="H92" s="26" t="n"/>
-      <c r="I92" s="26" t="n"/>
-      <c r="J92" s="26" t="n"/>
-      <c r="K92" s="26" t="n"/>
-      <c r="L92" s="26" t="n"/>
+      <c r="D92" s="25" t="n"/>
+      <c r="E92" s="26" t="n"/>
+      <c r="F92" s="25" t="n"/>
+      <c r="G92" s="25" t="n"/>
+      <c r="H92" s="25" t="n"/>
+      <c r="I92" s="25" t="n"/>
+      <c r="J92" s="25" t="n"/>
+      <c r="K92" s="25" t="n"/>
+      <c r="L92" s="25" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="n"/>
       <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
-      <c r="D93" s="9" t="n"/>
+      <c r="D93" s="10" t="n"/>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
@@ -6172,21 +6172,21 @@
       <c r="A94" s="23" t="n"/>
       <c r="B94" s="24" t="n"/>
       <c r="C94" s="24" t="n"/>
-      <c r="D94" s="24" t="n"/>
-      <c r="E94" s="25" t="n"/>
-      <c r="F94" s="26" t="n"/>
-      <c r="G94" s="26" t="n"/>
-      <c r="H94" s="26" t="n"/>
-      <c r="I94" s="26" t="n"/>
-      <c r="J94" s="26" t="n"/>
-      <c r="K94" s="26" t="n"/>
-      <c r="L94" s="26" t="n"/>
+      <c r="D94" s="25" t="n"/>
+      <c r="E94" s="26" t="n"/>
+      <c r="F94" s="25" t="n"/>
+      <c r="G94" s="25" t="n"/>
+      <c r="H94" s="25" t="n"/>
+      <c r="I94" s="25" t="n"/>
+      <c r="J94" s="25" t="n"/>
+      <c r="K94" s="25" t="n"/>
+      <c r="L94" s="25" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="n"/>
       <c r="B95" s="9" t="n"/>
       <c r="C95" s="9" t="n"/>
-      <c r="D95" s="9" t="n"/>
+      <c r="D95" s="10" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
@@ -6200,21 +6200,21 @@
       <c r="A96" s="23" t="n"/>
       <c r="B96" s="24" t="n"/>
       <c r="C96" s="24" t="n"/>
-      <c r="D96" s="24" t="n"/>
-      <c r="E96" s="25" t="n"/>
-      <c r="F96" s="26" t="n"/>
-      <c r="G96" s="26" t="n"/>
-      <c r="H96" s="26" t="n"/>
-      <c r="I96" s="26" t="n"/>
-      <c r="J96" s="26" t="n"/>
-      <c r="K96" s="26" t="n"/>
-      <c r="L96" s="26" t="n"/>
+      <c r="D96" s="25" t="n"/>
+      <c r="E96" s="26" t="n"/>
+      <c r="F96" s="25" t="n"/>
+      <c r="G96" s="25" t="n"/>
+      <c r="H96" s="25" t="n"/>
+      <c r="I96" s="25" t="n"/>
+      <c r="J96" s="25" t="n"/>
+      <c r="K96" s="25" t="n"/>
+      <c r="L96" s="25" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="8" t="n"/>
       <c r="B97" s="9" t="n"/>
       <c r="C97" s="9" t="n"/>
-      <c r="D97" s="9" t="n"/>
+      <c r="D97" s="10" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
@@ -6228,21 +6228,21 @@
       <c r="A98" s="23" t="n"/>
       <c r="B98" s="24" t="n"/>
       <c r="C98" s="24" t="n"/>
-      <c r="D98" s="24" t="n"/>
-      <c r="E98" s="25" t="n"/>
-      <c r="F98" s="26" t="n"/>
-      <c r="G98" s="26" t="n"/>
-      <c r="H98" s="26" t="n"/>
-      <c r="I98" s="26" t="n"/>
-      <c r="J98" s="26" t="n"/>
-      <c r="K98" s="26" t="n"/>
-      <c r="L98" s="26" t="n"/>
+      <c r="D98" s="25" t="n"/>
+      <c r="E98" s="26" t="n"/>
+      <c r="F98" s="25" t="n"/>
+      <c r="G98" s="25" t="n"/>
+      <c r="H98" s="25" t="n"/>
+      <c r="I98" s="25" t="n"/>
+      <c r="J98" s="25" t="n"/>
+      <c r="K98" s="25" t="n"/>
+      <c r="L98" s="25" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="n"/>
       <c r="B99" s="9" t="n"/>
       <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
+      <c r="D99" s="10" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
@@ -6256,21 +6256,21 @@
       <c r="A100" s="23" t="n"/>
       <c r="B100" s="24" t="n"/>
       <c r="C100" s="24" t="n"/>
-      <c r="D100" s="24" t="n"/>
-      <c r="E100" s="25" t="n"/>
-      <c r="F100" s="26" t="n"/>
-      <c r="G100" s="26" t="n"/>
-      <c r="H100" s="26" t="n"/>
-      <c r="I100" s="26" t="n"/>
-      <c r="J100" s="26" t="n"/>
-      <c r="K100" s="26" t="n"/>
-      <c r="L100" s="26" t="n"/>
+      <c r="D100" s="25" t="n"/>
+      <c r="E100" s="26" t="n"/>
+      <c r="F100" s="25" t="n"/>
+      <c r="G100" s="25" t="n"/>
+      <c r="H100" s="25" t="n"/>
+      <c r="I100" s="25" t="n"/>
+      <c r="J100" s="25" t="n"/>
+      <c r="K100" s="25" t="n"/>
+      <c r="L100" s="25" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="n"/>
       <c r="B101" s="9" t="n"/>
       <c r="C101" s="9" t="n"/>
-      <c r="D101" s="9" t="n"/>
+      <c r="D101" s="10" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
@@ -6284,15 +6284,15 @@
       <c r="A102" s="23" t="n"/>
       <c r="B102" s="24" t="n"/>
       <c r="C102" s="24" t="n"/>
-      <c r="D102" s="24" t="n"/>
-      <c r="E102" s="25" t="n"/>
-      <c r="F102" s="26" t="n"/>
-      <c r="G102" s="26" t="n"/>
-      <c r="H102" s="26" t="n"/>
-      <c r="I102" s="26" t="n"/>
-      <c r="J102" s="26" t="n"/>
-      <c r="K102" s="26" t="n"/>
-      <c r="L102" s="26" t="n"/>
+      <c r="D102" s="25" t="n"/>
+      <c r="E102" s="26" t="n"/>
+      <c r="F102" s="25" t="n"/>
+      <c r="G102" s="25" t="n"/>
+      <c r="H102" s="25" t="n"/>
+      <c r="I102" s="25" t="n"/>
+      <c r="J102" s="25" t="n"/>
+      <c r="K102" s="25" t="n"/>
+      <c r="L102" s="25" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L2"/>
